--- a/reports/latest/backend/Backend_Security_Assessment.xlsx
+++ b/reports/latest/backend/Backend_Security_Assessment.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E460"/>
+  <dimension ref="A1:E480"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,10 +427,10 @@
         <v>Passed</v>
       </c>
       <c r="D2">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-07-30T13:49:57.047Z</v>
+        <v>2026-07-30T13:59:18.551Z</v>
       </c>
     </row>
     <row r="3">
@@ -444,10 +444,10 @@
         <v>Passed</v>
       </c>
       <c r="D3">
-        <v>0.58</v>
+        <v>1.96</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-07-30T13:49:58.047Z</v>
+        <v>2026-07-30T13:59:19.551Z</v>
       </c>
     </row>
     <row r="4">
@@ -461,10 +461,10 @@
         <v>Passed</v>
       </c>
       <c r="D4">
-        <v>0.48</v>
+        <v>0.32</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-07-30T13:49:59.047Z</v>
+        <v>2026-07-30T13:59:20.551Z</v>
       </c>
     </row>
     <row r="5">
@@ -478,10 +478,10 @@
         <v>Passed</v>
       </c>
       <c r="D5">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-07-30T13:50:00.047Z</v>
+        <v>2026-07-30T13:59:21.551Z</v>
       </c>
     </row>
     <row r="6">
@@ -495,10 +495,10 @@
         <v>Passed</v>
       </c>
       <c r="D6">
-        <v>1.56</v>
+        <v>0.47</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-07-30T13:50:01.047Z</v>
+        <v>2026-07-30T13:59:22.551Z</v>
       </c>
     </row>
     <row r="7">
@@ -512,10 +512,10 @@
         <v>Passed</v>
       </c>
       <c r="D7">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-07-30T13:50:02.047Z</v>
+        <v>2026-07-30T13:59:23.551Z</v>
       </c>
     </row>
     <row r="8">
@@ -526,13 +526,13 @@
         <v>Verify Security functionality module 7</v>
       </c>
       <c r="C8" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D8">
-        <v>1.37</v>
+        <v>0.67</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-07-30T13:50:03.047Z</v>
+        <v>2026-07-30T13:59:24.551Z</v>
       </c>
     </row>
     <row r="9">
@@ -543,13 +543,13 @@
         <v>Verify Security functionality module 8</v>
       </c>
       <c r="C9" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D9">
-        <v>0.11</v>
+        <v>0.95</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-07-30T13:50:04.047Z</v>
+        <v>2026-07-30T13:59:25.551Z</v>
       </c>
     </row>
     <row r="10">
@@ -563,10 +563,10 @@
         <v>Passed</v>
       </c>
       <c r="D10">
-        <v>0.7</v>
+        <v>0.14</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-07-30T13:50:05.047Z</v>
+        <v>2026-07-30T13:59:26.551Z</v>
       </c>
     </row>
     <row r="11">
@@ -580,10 +580,10 @@
         <v>Passed</v>
       </c>
       <c r="D11">
-        <v>0.48</v>
+        <v>1.79</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-07-30T13:50:06.047Z</v>
+        <v>2026-07-30T13:59:27.551Z</v>
       </c>
     </row>
     <row r="12">
@@ -597,10 +597,10 @@
         <v>Passed</v>
       </c>
       <c r="D12">
-        <v>0.39</v>
+        <v>0.1</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-07-30T13:50:07.047Z</v>
+        <v>2026-07-30T13:59:28.551Z</v>
       </c>
     </row>
     <row r="13">
@@ -614,10 +614,10 @@
         <v>Passed</v>
       </c>
       <c r="D13">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-07-30T13:50:08.047Z</v>
+        <v>2026-07-30T13:59:29.551Z</v>
       </c>
     </row>
     <row r="14">
@@ -631,10 +631,10 @@
         <v>Passed</v>
       </c>
       <c r="D14">
-        <v>0.08</v>
+        <v>1.47</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-07-30T13:50:09.047Z</v>
+        <v>2026-07-30T13:59:30.551Z</v>
       </c>
     </row>
     <row r="15">
@@ -648,10 +648,10 @@
         <v>Passed</v>
       </c>
       <c r="D15">
-        <v>0.88</v>
+        <v>0.01</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-07-30T13:50:10.047Z</v>
+        <v>2026-07-30T13:59:31.551Z</v>
       </c>
     </row>
     <row r="16">
@@ -665,10 +665,10 @@
         <v>Passed</v>
       </c>
       <c r="D16">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-07-30T13:50:11.047Z</v>
+        <v>2026-07-30T13:59:32.551Z</v>
       </c>
     </row>
     <row r="17">
@@ -682,10 +682,10 @@
         <v>Passed</v>
       </c>
       <c r="D17">
-        <v>1.47</v>
+        <v>1.08</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-07-30T13:50:12.047Z</v>
+        <v>2026-07-30T13:59:33.551Z</v>
       </c>
     </row>
     <row r="18">
@@ -699,10 +699,10 @@
         <v>Passed</v>
       </c>
       <c r="D18">
-        <v>0.13</v>
+        <v>0.95</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-07-30T13:50:13.047Z</v>
+        <v>2026-07-30T13:59:34.551Z</v>
       </c>
     </row>
     <row r="19">
@@ -716,10 +716,10 @@
         <v>Passed</v>
       </c>
       <c r="D19">
-        <v>1.51</v>
+        <v>0.6</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-07-30T13:50:14.047Z</v>
+        <v>2026-07-30T13:59:35.551Z</v>
       </c>
     </row>
     <row r="20">
@@ -733,10 +733,10 @@
         <v>Passed</v>
       </c>
       <c r="D20">
-        <v>0.74</v>
+        <v>0.25</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-07-30T13:50:15.047Z</v>
+        <v>2026-07-30T13:59:36.551Z</v>
       </c>
     </row>
     <row r="21">
@@ -750,10 +750,10 @@
         <v>Passed</v>
       </c>
       <c r="D21">
-        <v>1.22</v>
+        <v>0.27</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-07-30T13:50:16.047Z</v>
+        <v>2026-07-30T13:59:37.551Z</v>
       </c>
     </row>
     <row r="22">
@@ -767,10 +767,10 @@
         <v>Passed</v>
       </c>
       <c r="D22">
-        <v>0.63</v>
+        <v>0.4</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-07-30T13:50:17.047Z</v>
+        <v>2026-07-30T13:59:38.551Z</v>
       </c>
     </row>
     <row r="23">
@@ -784,10 +784,10 @@
         <v>Passed</v>
       </c>
       <c r="D23">
-        <v>1.94</v>
+        <v>0.9</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-07-30T13:50:18.047Z</v>
+        <v>2026-07-30T13:59:39.551Z</v>
       </c>
     </row>
     <row r="24">
@@ -801,10 +801,10 @@
         <v>Passed</v>
       </c>
       <c r="D24">
-        <v>0.8</v>
+        <v>0.44</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-07-30T13:50:19.047Z</v>
+        <v>2026-07-30T13:59:40.551Z</v>
       </c>
     </row>
     <row r="25">
@@ -818,10 +818,10 @@
         <v>Passed</v>
       </c>
       <c r="D25">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-07-30T13:50:20.047Z</v>
+        <v>2026-07-30T13:59:41.551Z</v>
       </c>
     </row>
     <row r="26">
@@ -835,10 +835,10 @@
         <v>Passed</v>
       </c>
       <c r="D26">
-        <v>0.73</v>
+        <v>0.99</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-07-30T13:50:21.047Z</v>
+        <v>2026-07-30T13:59:42.551Z</v>
       </c>
     </row>
     <row r="27">
@@ -852,10 +852,10 @@
         <v>Passed</v>
       </c>
       <c r="D27">
-        <v>0.06</v>
+        <v>1.02</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-07-30T13:50:22.047Z</v>
+        <v>2026-07-30T13:59:43.551Z</v>
       </c>
     </row>
     <row r="28">
@@ -869,10 +869,10 @@
         <v>Passed</v>
       </c>
       <c r="D28">
-        <v>1.09</v>
+        <v>0.82</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-07-30T13:50:23.047Z</v>
+        <v>2026-07-30T13:59:44.551Z</v>
       </c>
     </row>
     <row r="29">
@@ -886,10 +886,10 @@
         <v>Passed</v>
       </c>
       <c r="D29">
-        <v>1.87</v>
+        <v>0.68</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-07-30T13:50:24.047Z</v>
+        <v>2026-07-30T13:59:45.551Z</v>
       </c>
     </row>
     <row r="30">
@@ -903,10 +903,10 @@
         <v>Passed</v>
       </c>
       <c r="D30">
-        <v>1.02</v>
+        <v>1.77</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-07-30T13:50:25.047Z</v>
+        <v>2026-07-30T13:59:46.551Z</v>
       </c>
     </row>
     <row r="31">
@@ -917,13 +917,13 @@
         <v>Verify Security functionality module 30</v>
       </c>
       <c r="C31" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D31">
-        <v>0.97</v>
+        <v>0.61</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-07-30T13:50:26.047Z</v>
+        <v>2026-07-30T13:59:47.551Z</v>
       </c>
     </row>
     <row r="32">
@@ -937,10 +937,10 @@
         <v>Passed</v>
       </c>
       <c r="D32">
-        <v>0.89</v>
+        <v>1.4</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-07-30T13:50:27.047Z</v>
+        <v>2026-07-30T13:59:48.551Z</v>
       </c>
     </row>
     <row r="33">
@@ -954,10 +954,10 @@
         <v>Passed</v>
       </c>
       <c r="D33">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-07-30T13:50:28.047Z</v>
+        <v>2026-07-30T13:59:49.551Z</v>
       </c>
     </row>
     <row r="34">
@@ -971,10 +971,10 @@
         <v>Passed</v>
       </c>
       <c r="D34">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-07-30T13:50:29.047Z</v>
+        <v>2026-07-30T13:59:50.551Z</v>
       </c>
     </row>
     <row r="35">
@@ -988,10 +988,10 @@
         <v>Passed</v>
       </c>
       <c r="D35">
-        <v>0.79</v>
+        <v>1.13</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-07-30T13:50:30.047Z</v>
+        <v>2026-07-30T13:59:51.551Z</v>
       </c>
     </row>
     <row r="36">
@@ -1005,10 +1005,10 @@
         <v>Passed</v>
       </c>
       <c r="D36">
-        <v>1.53</v>
+        <v>0.74</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-07-30T13:50:31.047Z</v>
+        <v>2026-07-30T13:59:52.551Z</v>
       </c>
     </row>
     <row r="37">
@@ -1022,10 +1022,10 @@
         <v>Passed</v>
       </c>
       <c r="D37">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-07-30T13:50:32.047Z</v>
+        <v>2026-07-30T13:59:53.551Z</v>
       </c>
     </row>
     <row r="38">
@@ -1039,10 +1039,10 @@
         <v>Passed</v>
       </c>
       <c r="D38">
-        <v>1.75</v>
+        <v>0.06</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-07-30T13:50:33.047Z</v>
+        <v>2026-07-30T13:59:54.551Z</v>
       </c>
     </row>
     <row r="39">
@@ -1056,10 +1056,10 @@
         <v>Passed</v>
       </c>
       <c r="D39">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-07-30T13:50:34.047Z</v>
+        <v>2026-07-30T13:59:55.551Z</v>
       </c>
     </row>
     <row r="40">
@@ -1073,10 +1073,10 @@
         <v>Passed</v>
       </c>
       <c r="D40">
-        <v>1.24</v>
+        <v>0.84</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-07-30T13:50:35.047Z</v>
+        <v>2026-07-30T13:59:56.551Z</v>
       </c>
     </row>
     <row r="41">
@@ -1090,10 +1090,10 @@
         <v>Passed</v>
       </c>
       <c r="D41">
-        <v>0.69</v>
+        <v>0.25</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-07-30T13:50:36.047Z</v>
+        <v>2026-07-30T13:59:57.551Z</v>
       </c>
     </row>
     <row r="42">
@@ -1107,10 +1107,10 @@
         <v>Passed</v>
       </c>
       <c r="D42">
-        <v>1.13</v>
+        <v>0.94</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-07-30T13:50:37.047Z</v>
+        <v>2026-07-30T13:59:58.551Z</v>
       </c>
     </row>
     <row r="43">
@@ -1124,10 +1124,10 @@
         <v>Passed</v>
       </c>
       <c r="D43">
-        <v>0.35</v>
+        <v>0.12</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-07-30T13:50:38.047Z</v>
+        <v>2026-07-30T13:59:59.551Z</v>
       </c>
     </row>
     <row r="44">
@@ -1141,10 +1141,10 @@
         <v>Passed</v>
       </c>
       <c r="D44">
-        <v>0.93</v>
+        <v>1.61</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-07-30T13:50:39.047Z</v>
+        <v>2026-07-30T14:00:00.551Z</v>
       </c>
     </row>
     <row r="45">
@@ -1158,10 +1158,10 @@
         <v>Passed</v>
       </c>
       <c r="D45">
-        <v>0.2</v>
+        <v>1.28</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-07-30T13:50:40.047Z</v>
+        <v>2026-07-30T14:00:01.551Z</v>
       </c>
     </row>
     <row r="46">
@@ -1175,10 +1175,10 @@
         <v>Passed</v>
       </c>
       <c r="D46">
-        <v>0.96</v>
+        <v>0.4</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-07-30T13:50:41.047Z</v>
+        <v>2026-07-30T14:00:02.551Z</v>
       </c>
     </row>
     <row r="47">
@@ -1192,10 +1192,10 @@
         <v>Passed</v>
       </c>
       <c r="D47">
-        <v>0.28</v>
+        <v>1.41</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-07-30T13:50:42.047Z</v>
+        <v>2026-07-30T14:00:03.551Z</v>
       </c>
     </row>
     <row r="48">
@@ -1209,10 +1209,10 @@
         <v>Passed</v>
       </c>
       <c r="D48">
-        <v>0.11</v>
+        <v>1</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-07-30T13:50:43.047Z</v>
+        <v>2026-07-30T14:00:04.551Z</v>
       </c>
     </row>
     <row r="49">
@@ -1226,10 +1226,10 @@
         <v>Passed</v>
       </c>
       <c r="D49">
-        <v>0.26</v>
+        <v>1.43</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-07-30T13:50:44.047Z</v>
+        <v>2026-07-30T14:00:05.551Z</v>
       </c>
     </row>
     <row r="50">
@@ -1243,10 +1243,10 @@
         <v>Passed</v>
       </c>
       <c r="D50">
-        <v>1.34</v>
+        <v>0.83</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-07-30T13:50:45.047Z</v>
+        <v>2026-07-30T14:00:06.551Z</v>
       </c>
     </row>
     <row r="51">
@@ -1260,10 +1260,10 @@
         <v>Passed</v>
       </c>
       <c r="D51">
-        <v>1.17</v>
+        <v>1.69</v>
       </c>
       <c r="E51" t="str">
-        <v>2026-07-30T13:50:46.047Z</v>
+        <v>2026-07-30T14:00:07.551Z</v>
       </c>
     </row>
     <row r="52">
@@ -1277,10 +1277,10 @@
         <v>Passed</v>
       </c>
       <c r="D52">
-        <v>1.39</v>
+        <v>0.64</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-07-30T13:50:47.047Z</v>
+        <v>2026-07-30T14:00:08.551Z</v>
       </c>
     </row>
     <row r="53">
@@ -1294,10 +1294,10 @@
         <v>Passed</v>
       </c>
       <c r="D53">
-        <v>1.86</v>
+        <v>1.02</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-07-30T13:50:48.047Z</v>
+        <v>2026-07-30T14:00:09.551Z</v>
       </c>
     </row>
     <row r="54">
@@ -1311,10 +1311,10 @@
         <v>Passed</v>
       </c>
       <c r="D54">
-        <v>0.28</v>
+        <v>1.4</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-07-30T13:50:49.047Z</v>
+        <v>2026-07-30T14:00:10.551Z</v>
       </c>
     </row>
     <row r="55">
@@ -1328,10 +1328,10 @@
         <v>Passed</v>
       </c>
       <c r="D55">
-        <v>0.26</v>
+        <v>1.58</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-07-30T13:50:50.047Z</v>
+        <v>2026-07-30T14:00:11.551Z</v>
       </c>
     </row>
     <row r="56">
@@ -1345,10 +1345,10 @@
         <v>Passed</v>
       </c>
       <c r="D56">
-        <v>1.77</v>
+        <v>0.04</v>
       </c>
       <c r="E56" t="str">
-        <v>2026-07-30T13:50:51.047Z</v>
+        <v>2026-07-30T14:00:12.551Z</v>
       </c>
     </row>
     <row r="57">
@@ -1362,10 +1362,10 @@
         <v>Passed</v>
       </c>
       <c r="D57">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="E57" t="str">
-        <v>2026-07-30T13:50:52.047Z</v>
+        <v>2026-07-30T14:00:13.551Z</v>
       </c>
     </row>
     <row r="58">
@@ -1379,10 +1379,10 @@
         <v>Passed</v>
       </c>
       <c r="D58">
-        <v>1.01</v>
+        <v>0.43</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-07-30T13:50:53.047Z</v>
+        <v>2026-07-30T14:00:14.551Z</v>
       </c>
     </row>
     <row r="59">
@@ -1396,10 +1396,10 @@
         <v>Passed</v>
       </c>
       <c r="D59">
-        <v>1.05</v>
+        <v>0.33</v>
       </c>
       <c r="E59" t="str">
-        <v>2026-07-30T13:50:54.047Z</v>
+        <v>2026-07-30T14:00:15.551Z</v>
       </c>
     </row>
     <row r="60">
@@ -1413,10 +1413,10 @@
         <v>Passed</v>
       </c>
       <c r="D60">
-        <v>0.38</v>
+        <v>1.35</v>
       </c>
       <c r="E60" t="str">
-        <v>2026-07-30T13:50:55.047Z</v>
+        <v>2026-07-30T14:00:16.551Z</v>
       </c>
     </row>
     <row r="61">
@@ -1430,10 +1430,10 @@
         <v>Passed</v>
       </c>
       <c r="D61">
-        <v>0.72</v>
+        <v>0.49</v>
       </c>
       <c r="E61" t="str">
-        <v>2026-07-30T13:50:56.047Z</v>
+        <v>2026-07-30T14:00:17.551Z</v>
       </c>
     </row>
     <row r="62">
@@ -1447,10 +1447,10 @@
         <v>Passed</v>
       </c>
       <c r="D62">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-07-30T13:50:57.047Z</v>
+        <v>2026-07-30T14:00:18.551Z</v>
       </c>
     </row>
     <row r="63">
@@ -1464,10 +1464,10 @@
         <v>Passed</v>
       </c>
       <c r="D63">
-        <v>0.34</v>
+        <v>0.52</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-07-30T13:50:58.047Z</v>
+        <v>2026-07-30T14:00:19.551Z</v>
       </c>
     </row>
     <row r="64">
@@ -1481,10 +1481,10 @@
         <v>Passed</v>
       </c>
       <c r="D64">
-        <v>1.07</v>
+        <v>0.9</v>
       </c>
       <c r="E64" t="str">
-        <v>2026-07-30T13:50:59.047Z</v>
+        <v>2026-07-30T14:00:20.551Z</v>
       </c>
     </row>
     <row r="65">
@@ -1498,10 +1498,10 @@
         <v>Passed</v>
       </c>
       <c r="D65">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="E65" t="str">
-        <v>2026-07-30T13:51:00.047Z</v>
+        <v>2026-07-30T14:00:21.551Z</v>
       </c>
     </row>
     <row r="66">
@@ -1515,10 +1515,10 @@
         <v>Passed</v>
       </c>
       <c r="D66">
-        <v>1.82</v>
+        <v>0.79</v>
       </c>
       <c r="E66" t="str">
-        <v>2026-07-30T13:51:01.047Z</v>
+        <v>2026-07-30T14:00:22.551Z</v>
       </c>
     </row>
     <row r="67">
@@ -1532,10 +1532,10 @@
         <v>Passed</v>
       </c>
       <c r="D67">
-        <v>0.8</v>
+        <v>1.53</v>
       </c>
       <c r="E67" t="str">
-        <v>2026-07-30T13:51:02.047Z</v>
+        <v>2026-07-30T14:00:23.551Z</v>
       </c>
     </row>
     <row r="68">
@@ -1549,10 +1549,10 @@
         <v>Passed</v>
       </c>
       <c r="D68">
-        <v>1.02</v>
+        <v>1.65</v>
       </c>
       <c r="E68" t="str">
-        <v>2026-07-30T13:51:03.047Z</v>
+        <v>2026-07-30T14:00:24.551Z</v>
       </c>
     </row>
     <row r="69">
@@ -1566,10 +1566,10 @@
         <v>Passed</v>
       </c>
       <c r="D69">
-        <v>1.94</v>
+        <v>1.43</v>
       </c>
       <c r="E69" t="str">
-        <v>2026-07-30T13:51:04.047Z</v>
+        <v>2026-07-30T14:00:25.551Z</v>
       </c>
     </row>
     <row r="70">
@@ -1583,10 +1583,10 @@
         <v>Passed</v>
       </c>
       <c r="D70">
-        <v>1.63</v>
+        <v>0.52</v>
       </c>
       <c r="E70" t="str">
-        <v>2026-07-30T13:51:05.047Z</v>
+        <v>2026-07-30T14:00:26.551Z</v>
       </c>
     </row>
     <row r="71">
@@ -1600,10 +1600,10 @@
         <v>Passed</v>
       </c>
       <c r="D71">
-        <v>1.64</v>
+        <v>1.18</v>
       </c>
       <c r="E71" t="str">
-        <v>2026-07-30T13:51:06.047Z</v>
+        <v>2026-07-30T14:00:27.551Z</v>
       </c>
     </row>
     <row r="72">
@@ -1617,10 +1617,10 @@
         <v>Passed</v>
       </c>
       <c r="D72">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="E72" t="str">
-        <v>2026-07-30T13:51:07.047Z</v>
+        <v>2026-07-30T14:00:28.551Z</v>
       </c>
     </row>
     <row r="73">
@@ -1634,10 +1634,10 @@
         <v>Passed</v>
       </c>
       <c r="D73">
-        <v>1.8</v>
+        <v>0.54</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-07-30T13:51:08.047Z</v>
+        <v>2026-07-30T14:00:29.551Z</v>
       </c>
     </row>
     <row r="74">
@@ -1651,10 +1651,10 @@
         <v>Passed</v>
       </c>
       <c r="D74">
-        <v>1.87</v>
+        <v>0.05</v>
       </c>
       <c r="E74" t="str">
-        <v>2026-07-30T13:51:09.047Z</v>
+        <v>2026-07-30T14:00:30.551Z</v>
       </c>
     </row>
     <row r="75">
@@ -1668,10 +1668,10 @@
         <v>Passed</v>
       </c>
       <c r="D75">
-        <v>0.42</v>
+        <v>0.31</v>
       </c>
       <c r="E75" t="str">
-        <v>2026-07-30T13:51:10.047Z</v>
+        <v>2026-07-30T14:00:31.551Z</v>
       </c>
     </row>
     <row r="76">
@@ -1685,10 +1685,10 @@
         <v>Passed</v>
       </c>
       <c r="D76">
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="E76" t="str">
-        <v>2026-07-30T13:51:11.047Z</v>
+        <v>2026-07-30T14:00:32.551Z</v>
       </c>
     </row>
     <row r="77">
@@ -1702,10 +1702,10 @@
         <v>Passed</v>
       </c>
       <c r="D77">
-        <v>0.96</v>
+        <v>0.63</v>
       </c>
       <c r="E77" t="str">
-        <v>2026-07-30T13:51:12.047Z</v>
+        <v>2026-07-30T14:00:33.551Z</v>
       </c>
     </row>
     <row r="78">
@@ -1719,10 +1719,10 @@
         <v>Passed</v>
       </c>
       <c r="D78">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="E78" t="str">
-        <v>2026-07-30T13:51:13.047Z</v>
+        <v>2026-07-30T14:00:34.551Z</v>
       </c>
     </row>
     <row r="79">
@@ -1736,10 +1736,10 @@
         <v>Passed</v>
       </c>
       <c r="D79">
-        <v>0.54</v>
+        <v>1.17</v>
       </c>
       <c r="E79" t="str">
-        <v>2026-07-30T13:51:14.047Z</v>
+        <v>2026-07-30T14:00:35.551Z</v>
       </c>
     </row>
     <row r="80">
@@ -1753,10 +1753,10 @@
         <v>Passed</v>
       </c>
       <c r="D80">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="E80" t="str">
-        <v>2026-07-30T13:51:15.047Z</v>
+        <v>2026-07-30T14:00:36.551Z</v>
       </c>
     </row>
     <row r="81">
@@ -1770,10 +1770,10 @@
         <v>Passed</v>
       </c>
       <c r="D81">
-        <v>0.11</v>
+        <v>0.45</v>
       </c>
       <c r="E81" t="str">
-        <v>2026-07-30T13:51:16.047Z</v>
+        <v>2026-07-30T14:00:37.551Z</v>
       </c>
     </row>
     <row r="82">
@@ -1787,10 +1787,10 @@
         <v>Passed</v>
       </c>
       <c r="D82">
-        <v>1.61</v>
+        <v>0.81</v>
       </c>
       <c r="E82" t="str">
-        <v>2026-07-30T13:51:17.047Z</v>
+        <v>2026-07-30T14:00:38.551Z</v>
       </c>
     </row>
     <row r="83">
@@ -1804,10 +1804,10 @@
         <v>Passed</v>
       </c>
       <c r="D83">
-        <v>1.22</v>
+        <v>0.3</v>
       </c>
       <c r="E83" t="str">
-        <v>2026-07-30T13:51:18.047Z</v>
+        <v>2026-07-30T14:00:39.551Z</v>
       </c>
     </row>
     <row r="84">
@@ -1821,10 +1821,10 @@
         <v>Passed</v>
       </c>
       <c r="D84">
-        <v>1.38</v>
+        <v>1.08</v>
       </c>
       <c r="E84" t="str">
-        <v>2026-07-30T13:51:19.047Z</v>
+        <v>2026-07-30T14:00:40.551Z</v>
       </c>
     </row>
     <row r="85">
@@ -1838,10 +1838,10 @@
         <v>Passed</v>
       </c>
       <c r="D85">
-        <v>0.45</v>
+        <v>1.57</v>
       </c>
       <c r="E85" t="str">
-        <v>2026-07-30T13:51:20.047Z</v>
+        <v>2026-07-30T14:00:41.551Z</v>
       </c>
     </row>
     <row r="86">
@@ -1855,10 +1855,10 @@
         <v>Passed</v>
       </c>
       <c r="D86">
-        <v>1.64</v>
+        <v>0.46</v>
       </c>
       <c r="E86" t="str">
-        <v>2026-07-30T13:51:21.047Z</v>
+        <v>2026-07-30T14:00:42.551Z</v>
       </c>
     </row>
     <row r="87">
@@ -1872,10 +1872,10 @@
         <v>Passed</v>
       </c>
       <c r="D87">
-        <v>0.27</v>
+        <v>0.06</v>
       </c>
       <c r="E87" t="str">
-        <v>2026-07-30T13:51:22.047Z</v>
+        <v>2026-07-30T14:00:43.551Z</v>
       </c>
     </row>
     <row r="88">
@@ -1889,10 +1889,10 @@
         <v>Passed</v>
       </c>
       <c r="D88">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="E88" t="str">
-        <v>2026-07-30T13:51:23.047Z</v>
+        <v>2026-07-30T14:00:44.551Z</v>
       </c>
     </row>
     <row r="89">
@@ -1906,10 +1906,10 @@
         <v>Passed</v>
       </c>
       <c r="D89">
-        <v>1.87</v>
+        <v>1.1</v>
       </c>
       <c r="E89" t="str">
-        <v>2026-07-30T13:51:24.047Z</v>
+        <v>2026-07-30T14:00:45.551Z</v>
       </c>
     </row>
     <row r="90">
@@ -1923,10 +1923,10 @@
         <v>Passed</v>
       </c>
       <c r="D90">
-        <v>0.34</v>
+        <v>1.15</v>
       </c>
       <c r="E90" t="str">
-        <v>2026-07-30T13:51:25.047Z</v>
+        <v>2026-07-30T14:00:46.551Z</v>
       </c>
     </row>
     <row r="91">
@@ -1940,10 +1940,10 @@
         <v>Passed</v>
       </c>
       <c r="D91">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="E91" t="str">
-        <v>2026-07-30T13:51:26.047Z</v>
+        <v>2026-07-30T14:00:47.551Z</v>
       </c>
     </row>
     <row r="92">
@@ -1957,10 +1957,10 @@
         <v>Passed</v>
       </c>
       <c r="D92">
-        <v>1.62</v>
+        <v>0.67</v>
       </c>
       <c r="E92" t="str">
-        <v>2026-07-30T13:51:27.047Z</v>
+        <v>2026-07-30T14:00:48.551Z</v>
       </c>
     </row>
     <row r="93">
@@ -1974,10 +1974,10 @@
         <v>Passed</v>
       </c>
       <c r="D93">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="E93" t="str">
-        <v>2026-07-30T13:51:28.047Z</v>
+        <v>2026-07-30T14:00:49.551Z</v>
       </c>
     </row>
     <row r="94">
@@ -1991,10 +1991,10 @@
         <v>Passed</v>
       </c>
       <c r="D94">
-        <v>0.75</v>
+        <v>1.67</v>
       </c>
       <c r="E94" t="str">
-        <v>2026-07-30T13:51:29.047Z</v>
+        <v>2026-07-30T14:00:50.551Z</v>
       </c>
     </row>
     <row r="95">
@@ -2008,10 +2008,10 @@
         <v>Passed</v>
       </c>
       <c r="D95">
-        <v>0.8</v>
+        <v>0.03</v>
       </c>
       <c r="E95" t="str">
-        <v>2026-07-30T13:51:30.047Z</v>
+        <v>2026-07-30T14:00:51.551Z</v>
       </c>
     </row>
     <row r="96">
@@ -2025,10 +2025,10 @@
         <v>Passed</v>
       </c>
       <c r="D96">
-        <v>0.9</v>
+        <v>0.58</v>
       </c>
       <c r="E96" t="str">
-        <v>2026-07-30T13:51:31.047Z</v>
+        <v>2026-07-30T14:00:52.551Z</v>
       </c>
     </row>
     <row r="97">
@@ -2042,10 +2042,10 @@
         <v>Passed</v>
       </c>
       <c r="D97">
-        <v>0.88</v>
+        <v>0.59</v>
       </c>
       <c r="E97" t="str">
-        <v>2026-07-30T13:51:32.047Z</v>
+        <v>2026-07-30T14:00:53.551Z</v>
       </c>
     </row>
     <row r="98">
@@ -2059,10 +2059,10 @@
         <v>Passed</v>
       </c>
       <c r="D98">
-        <v>0.01</v>
+        <v>2</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-07-30T13:51:33.047Z</v>
+        <v>2026-07-30T14:00:54.551Z</v>
       </c>
     </row>
     <row r="99">
@@ -2076,10 +2076,10 @@
         <v>Passed</v>
       </c>
       <c r="D99">
-        <v>0.83</v>
+        <v>0.25</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-07-30T13:51:34.047Z</v>
+        <v>2026-07-30T14:00:55.551Z</v>
       </c>
     </row>
     <row r="100">
@@ -2093,10 +2093,10 @@
         <v>Passed</v>
       </c>
       <c r="D100">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-07-30T13:51:35.047Z</v>
+        <v>2026-07-30T14:00:56.551Z</v>
       </c>
     </row>
     <row r="101">
@@ -2110,10 +2110,10 @@
         <v>Passed</v>
       </c>
       <c r="D101">
-        <v>1.02</v>
+        <v>0.17</v>
       </c>
       <c r="E101" t="str">
-        <v>2026-07-30T13:51:36.047Z</v>
+        <v>2026-07-30T14:00:57.551Z</v>
       </c>
     </row>
     <row r="102">
@@ -2127,10 +2127,10 @@
         <v>Passed</v>
       </c>
       <c r="D102">
-        <v>1.62</v>
+        <v>1.32</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-07-30T13:51:37.047Z</v>
+        <v>2026-07-30T14:00:58.551Z</v>
       </c>
     </row>
     <row r="103">
@@ -2144,10 +2144,10 @@
         <v>Passed</v>
       </c>
       <c r="D103">
-        <v>1.59</v>
+        <v>0.59</v>
       </c>
       <c r="E103" t="str">
-        <v>2026-07-30T13:51:38.047Z</v>
+        <v>2026-07-30T14:00:59.551Z</v>
       </c>
     </row>
     <row r="104">
@@ -2161,10 +2161,10 @@
         <v>Passed</v>
       </c>
       <c r="D104">
-        <v>0.44</v>
+        <v>1.05</v>
       </c>
       <c r="E104" t="str">
-        <v>2026-07-30T13:51:39.047Z</v>
+        <v>2026-07-30T14:01:00.551Z</v>
       </c>
     </row>
     <row r="105">
@@ -2178,10 +2178,10 @@
         <v>Passed</v>
       </c>
       <c r="D105">
-        <v>0.69</v>
+        <v>0.86</v>
       </c>
       <c r="E105" t="str">
-        <v>2026-07-30T13:51:40.047Z</v>
+        <v>2026-07-30T14:01:01.551Z</v>
       </c>
     </row>
     <row r="106">
@@ -2195,10 +2195,10 @@
         <v>Passed</v>
       </c>
       <c r="D106">
-        <v>1.43</v>
+        <v>1.74</v>
       </c>
       <c r="E106" t="str">
-        <v>2026-07-30T13:51:41.047Z</v>
+        <v>2026-07-30T14:01:02.551Z</v>
       </c>
     </row>
     <row r="107">
@@ -2212,10 +2212,10 @@
         <v>Passed</v>
       </c>
       <c r="D107">
-        <v>1.33</v>
+        <v>0.64</v>
       </c>
       <c r="E107" t="str">
-        <v>2026-07-30T13:51:42.047Z</v>
+        <v>2026-07-30T14:01:03.551Z</v>
       </c>
     </row>
     <row r="108">
@@ -2229,10 +2229,10 @@
         <v>Passed</v>
       </c>
       <c r="D108">
-        <v>0.33</v>
+        <v>1.62</v>
       </c>
       <c r="E108" t="str">
-        <v>2026-07-30T13:51:43.047Z</v>
+        <v>2026-07-30T14:01:04.551Z</v>
       </c>
     </row>
     <row r="109">
@@ -2246,10 +2246,10 @@
         <v>Passed</v>
       </c>
       <c r="D109">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="E109" t="str">
-        <v>2026-07-30T13:51:44.047Z</v>
+        <v>2026-07-30T14:01:05.551Z</v>
       </c>
     </row>
     <row r="110">
@@ -2263,10 +2263,10 @@
         <v>Passed</v>
       </c>
       <c r="D110">
-        <v>0.31</v>
+        <v>1.58</v>
       </c>
       <c r="E110" t="str">
-        <v>2026-07-30T13:51:45.047Z</v>
+        <v>2026-07-30T14:01:06.551Z</v>
       </c>
     </row>
     <row r="111">
@@ -2280,10 +2280,10 @@
         <v>Passed</v>
       </c>
       <c r="D111">
-        <v>0.09</v>
+        <v>0.57</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-07-30T13:51:46.047Z</v>
+        <v>2026-07-30T14:01:07.551Z</v>
       </c>
     </row>
     <row r="112">
@@ -2297,10 +2297,10 @@
         <v>Passed</v>
       </c>
       <c r="D112">
-        <v>1.52</v>
+        <v>0.91</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-07-30T13:51:47.047Z</v>
+        <v>2026-07-30T14:01:08.551Z</v>
       </c>
     </row>
     <row r="113">
@@ -2314,10 +2314,10 @@
         <v>Passed</v>
       </c>
       <c r="D113">
-        <v>0.79</v>
+        <v>1.39</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-07-30T13:51:48.047Z</v>
+        <v>2026-07-30T14:01:09.551Z</v>
       </c>
     </row>
     <row r="114">
@@ -2331,10 +2331,10 @@
         <v>Passed</v>
       </c>
       <c r="D114">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-07-30T13:51:49.047Z</v>
+        <v>2026-07-30T14:01:10.551Z</v>
       </c>
     </row>
     <row r="115">
@@ -2345,13 +2345,13 @@
         <v>Verify Security functionality module 114</v>
       </c>
       <c r="C115" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D115">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-07-30T13:51:50.047Z</v>
+        <v>2026-07-30T14:01:11.551Z</v>
       </c>
     </row>
     <row r="116">
@@ -2365,10 +2365,10 @@
         <v>Passed</v>
       </c>
       <c r="D116">
-        <v>1.21</v>
+        <v>0.03</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-07-30T13:51:51.047Z</v>
+        <v>2026-07-30T14:01:12.551Z</v>
       </c>
     </row>
     <row r="117">
@@ -2382,10 +2382,10 @@
         <v>Passed</v>
       </c>
       <c r="D117">
-        <v>0.57</v>
+        <v>1.58</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-07-30T13:51:52.047Z</v>
+        <v>2026-07-30T14:01:13.551Z</v>
       </c>
     </row>
     <row r="118">
@@ -2399,10 +2399,10 @@
         <v>Passed</v>
       </c>
       <c r="D118">
-        <v>1.02</v>
+        <v>1.68</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-07-30T13:51:53.047Z</v>
+        <v>2026-07-30T14:01:14.551Z</v>
       </c>
     </row>
     <row r="119">
@@ -2416,10 +2416,10 @@
         <v>Passed</v>
       </c>
       <c r="D119">
-        <v>1.98</v>
+        <v>1.25</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-07-30T13:51:54.047Z</v>
+        <v>2026-07-30T14:01:15.551Z</v>
       </c>
     </row>
     <row r="120">
@@ -2433,10 +2433,10 @@
         <v>Passed</v>
       </c>
       <c r="D120">
-        <v>0.77</v>
+        <v>1.89</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-07-30T13:51:55.047Z</v>
+        <v>2026-07-30T14:01:16.551Z</v>
       </c>
     </row>
     <row r="121">
@@ -2450,10 +2450,10 @@
         <v>Passed</v>
       </c>
       <c r="D121">
-        <v>0.69</v>
+        <v>1.92</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-07-30T13:51:56.047Z</v>
+        <v>2026-07-30T14:01:17.551Z</v>
       </c>
     </row>
     <row r="122">
@@ -2467,10 +2467,10 @@
         <v>Passed</v>
       </c>
       <c r="D122">
-        <v>1.41</v>
+        <v>1.91</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-07-30T13:51:57.047Z</v>
+        <v>2026-07-30T14:01:18.551Z</v>
       </c>
     </row>
     <row r="123">
@@ -2484,10 +2484,10 @@
         <v>Passed</v>
       </c>
       <c r="D123">
-        <v>0.88</v>
+        <v>1.3</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-07-30T13:51:58.047Z</v>
+        <v>2026-07-30T14:01:19.551Z</v>
       </c>
     </row>
     <row r="124">
@@ -2501,10 +2501,10 @@
         <v>Passed</v>
       </c>
       <c r="D124">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-07-30T13:51:59.047Z</v>
+        <v>2026-07-30T14:01:20.551Z</v>
       </c>
     </row>
     <row r="125">
@@ -2518,10 +2518,10 @@
         <v>Passed</v>
       </c>
       <c r="D125">
-        <v>1.76</v>
+        <v>0.4</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-07-30T13:52:00.047Z</v>
+        <v>2026-07-30T14:01:21.551Z</v>
       </c>
     </row>
     <row r="126">
@@ -2535,10 +2535,10 @@
         <v>Passed</v>
       </c>
       <c r="D126">
-        <v>0.06</v>
+        <v>1.39</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-07-30T13:52:01.047Z</v>
+        <v>2026-07-30T14:01:22.551Z</v>
       </c>
     </row>
     <row r="127">
@@ -2552,10 +2552,10 @@
         <v>Passed</v>
       </c>
       <c r="D127">
-        <v>0.84</v>
+        <v>1.25</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-07-30T13:52:02.047Z</v>
+        <v>2026-07-30T14:01:23.551Z</v>
       </c>
     </row>
     <row r="128">
@@ -2569,10 +2569,10 @@
         <v>Passed</v>
       </c>
       <c r="D128">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-07-30T13:52:03.047Z</v>
+        <v>2026-07-30T14:01:24.551Z</v>
       </c>
     </row>
     <row r="129">
@@ -2586,10 +2586,10 @@
         <v>Passed</v>
       </c>
       <c r="D129">
-        <v>0.68</v>
+        <v>0.39</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-07-30T13:52:04.047Z</v>
+        <v>2026-07-30T14:01:25.551Z</v>
       </c>
     </row>
     <row r="130">
@@ -2603,10 +2603,10 @@
         <v>Passed</v>
       </c>
       <c r="D130">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-07-30T13:52:05.047Z</v>
+        <v>2026-07-30T14:01:26.551Z</v>
       </c>
     </row>
     <row r="131">
@@ -2617,13 +2617,13 @@
         <v>Verify Security functionality module 130</v>
       </c>
       <c r="C131" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D131">
-        <v>1.6</v>
+        <v>0.41</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-07-30T13:52:06.047Z</v>
+        <v>2026-07-30T14:01:27.551Z</v>
       </c>
     </row>
     <row r="132">
@@ -2637,10 +2637,10 @@
         <v>Passed</v>
       </c>
       <c r="D132">
-        <v>0.62</v>
+        <v>1.2</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-07-30T13:52:07.047Z</v>
+        <v>2026-07-30T14:01:28.551Z</v>
       </c>
     </row>
     <row r="133">
@@ -2654,10 +2654,10 @@
         <v>Passed</v>
       </c>
       <c r="D133">
-        <v>0.89</v>
+        <v>1.89</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-07-30T13:52:08.047Z</v>
+        <v>2026-07-30T14:01:29.551Z</v>
       </c>
     </row>
     <row r="134">
@@ -2671,10 +2671,10 @@
         <v>Passed</v>
       </c>
       <c r="D134">
-        <v>0.99</v>
+        <v>0.64</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-07-30T13:52:09.047Z</v>
+        <v>2026-07-30T14:01:30.551Z</v>
       </c>
     </row>
     <row r="135">
@@ -2688,10 +2688,10 @@
         <v>Passed</v>
       </c>
       <c r="D135">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-07-30T13:52:10.047Z</v>
+        <v>2026-07-30T14:01:31.551Z</v>
       </c>
     </row>
     <row r="136">
@@ -2705,10 +2705,10 @@
         <v>Passed</v>
       </c>
       <c r="D136">
-        <v>1.33</v>
+        <v>0.15</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-07-30T13:52:11.047Z</v>
+        <v>2026-07-30T14:01:32.551Z</v>
       </c>
     </row>
     <row r="137">
@@ -2722,10 +2722,10 @@
         <v>Passed</v>
       </c>
       <c r="D137">
-        <v>1.29</v>
+        <v>0.54</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-07-30T13:52:12.047Z</v>
+        <v>2026-07-30T14:01:33.551Z</v>
       </c>
     </row>
     <row r="138">
@@ -2739,10 +2739,10 @@
         <v>Passed</v>
       </c>
       <c r="D138">
-        <v>0.92</v>
+        <v>0.47</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-07-30T13:52:13.047Z</v>
+        <v>2026-07-30T14:01:34.551Z</v>
       </c>
     </row>
     <row r="139">
@@ -2756,10 +2756,10 @@
         <v>Passed</v>
       </c>
       <c r="D139">
-        <v>0.28</v>
+        <v>1.01</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-07-30T13:52:14.047Z</v>
+        <v>2026-07-30T14:01:35.551Z</v>
       </c>
     </row>
     <row r="140">
@@ -2773,10 +2773,10 @@
         <v>Passed</v>
       </c>
       <c r="D140">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-07-30T13:52:15.047Z</v>
+        <v>2026-07-30T14:01:36.551Z</v>
       </c>
     </row>
     <row r="141">
@@ -2790,10 +2790,10 @@
         <v>Passed</v>
       </c>
       <c r="D141">
-        <v>1.54</v>
+        <v>1.81</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-07-30T13:52:16.047Z</v>
+        <v>2026-07-30T14:01:37.551Z</v>
       </c>
     </row>
     <row r="142">
@@ -2807,10 +2807,10 @@
         <v>Passed</v>
       </c>
       <c r="D142">
-        <v>1.12</v>
+        <v>0.68</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-07-30T13:52:17.047Z</v>
+        <v>2026-07-30T14:01:38.551Z</v>
       </c>
     </row>
     <row r="143">
@@ -2824,10 +2824,10 @@
         <v>Passed</v>
       </c>
       <c r="D143">
-        <v>1.09</v>
+        <v>1.84</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-07-30T13:52:18.047Z</v>
+        <v>2026-07-30T14:01:39.551Z</v>
       </c>
     </row>
     <row r="144">
@@ -2841,10 +2841,10 @@
         <v>Passed</v>
       </c>
       <c r="D144">
-        <v>1.39</v>
+        <v>0.67</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-07-30T13:52:19.047Z</v>
+        <v>2026-07-30T14:01:40.551Z</v>
       </c>
     </row>
     <row r="145">
@@ -2858,10 +2858,10 @@
         <v>Passed</v>
       </c>
       <c r="D145">
-        <v>0.66</v>
+        <v>0.11</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-07-30T13:52:20.047Z</v>
+        <v>2026-07-30T14:01:41.551Z</v>
       </c>
     </row>
     <row r="146">
@@ -2875,10 +2875,10 @@
         <v>Passed</v>
       </c>
       <c r="D146">
-        <v>0.05</v>
+        <v>1.79</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-07-30T13:52:21.047Z</v>
+        <v>2026-07-30T14:01:42.551Z</v>
       </c>
     </row>
     <row r="147">
@@ -2892,10 +2892,10 @@
         <v>Passed</v>
       </c>
       <c r="D147">
-        <v>0.59</v>
+        <v>1.26</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-07-30T13:52:22.047Z</v>
+        <v>2026-07-30T14:01:43.551Z</v>
       </c>
     </row>
     <row r="148">
@@ -2909,10 +2909,10 @@
         <v>Passed</v>
       </c>
       <c r="D148">
-        <v>0.42</v>
+        <v>0.24</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-07-30T13:52:23.047Z</v>
+        <v>2026-07-30T14:01:44.551Z</v>
       </c>
     </row>
     <row r="149">
@@ -2926,10 +2926,10 @@
         <v>Passed</v>
       </c>
       <c r="D149">
-        <v>0.04</v>
+        <v>1.09</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-07-30T13:52:24.047Z</v>
+        <v>2026-07-30T14:01:45.551Z</v>
       </c>
     </row>
     <row r="150">
@@ -2943,10 +2943,10 @@
         <v>Passed</v>
       </c>
       <c r="D150">
-        <v>1.76</v>
+        <v>0.38</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-07-30T13:52:25.047Z</v>
+        <v>2026-07-30T14:01:46.551Z</v>
       </c>
     </row>
     <row r="151">
@@ -2960,10 +2960,10 @@
         <v>Passed</v>
       </c>
       <c r="D151">
-        <v>0.74</v>
+        <v>0.49</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-07-30T13:52:26.047Z</v>
+        <v>2026-07-30T14:01:47.551Z</v>
       </c>
     </row>
     <row r="152">
@@ -2977,10 +2977,10 @@
         <v>Passed</v>
       </c>
       <c r="D152">
-        <v>1.99</v>
+        <v>1.09</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-07-30T13:52:27.047Z</v>
+        <v>2026-07-30T14:01:48.551Z</v>
       </c>
     </row>
     <row r="153">
@@ -2994,10 +2994,10 @@
         <v>Passed</v>
       </c>
       <c r="D153">
-        <v>0.38</v>
+        <v>0.11</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-07-30T13:52:28.047Z</v>
+        <v>2026-07-30T14:01:49.551Z</v>
       </c>
     </row>
     <row r="154">
@@ -3011,10 +3011,10 @@
         <v>Passed</v>
       </c>
       <c r="D154">
-        <v>0.39</v>
+        <v>0.8</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-07-30T13:52:29.047Z</v>
+        <v>2026-07-30T14:01:50.551Z</v>
       </c>
     </row>
     <row r="155">
@@ -3028,10 +3028,10 @@
         <v>Passed</v>
       </c>
       <c r="D155">
-        <v>1.44</v>
+        <v>1.05</v>
       </c>
       <c r="E155" t="str">
-        <v>2026-07-30T13:52:30.047Z</v>
+        <v>2026-07-30T14:01:51.551Z</v>
       </c>
     </row>
     <row r="156">
@@ -3045,10 +3045,10 @@
         <v>Passed</v>
       </c>
       <c r="D156">
-        <v>0.57</v>
+        <v>1.45</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-07-30T13:52:31.047Z</v>
+        <v>2026-07-30T14:01:52.551Z</v>
       </c>
     </row>
     <row r="157">
@@ -3062,10 +3062,10 @@
         <v>Passed</v>
       </c>
       <c r="D157">
-        <v>0.77</v>
+        <v>1.92</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-07-30T13:52:32.047Z</v>
+        <v>2026-07-30T14:01:53.551Z</v>
       </c>
     </row>
     <row r="158">
@@ -3079,10 +3079,10 @@
         <v>Passed</v>
       </c>
       <c r="D158">
-        <v>1.15</v>
+        <v>0.75</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-07-30T13:52:33.047Z</v>
+        <v>2026-07-30T14:01:54.551Z</v>
       </c>
     </row>
     <row r="159">
@@ -3096,10 +3096,10 @@
         <v>Passed</v>
       </c>
       <c r="D159">
-        <v>1.13</v>
+        <v>0.87</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-07-30T13:52:34.047Z</v>
+        <v>2026-07-30T14:01:55.551Z</v>
       </c>
     </row>
     <row r="160">
@@ -3113,10 +3113,10 @@
         <v>Passed</v>
       </c>
       <c r="D160">
-        <v>1.1</v>
+        <v>0.48</v>
       </c>
       <c r="E160" t="str">
-        <v>2026-07-30T13:52:35.047Z</v>
+        <v>2026-07-30T14:01:56.551Z</v>
       </c>
     </row>
     <row r="161">
@@ -3130,10 +3130,10 @@
         <v>Passed</v>
       </c>
       <c r="D161">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="E161" t="str">
-        <v>2026-07-30T13:52:36.047Z</v>
+        <v>2026-07-30T14:01:57.551Z</v>
       </c>
     </row>
     <row r="162">
@@ -3147,10 +3147,10 @@
         <v>Passed</v>
       </c>
       <c r="D162">
-        <v>0.96</v>
+        <v>0.66</v>
       </c>
       <c r="E162" t="str">
-        <v>2026-07-30T13:52:37.047Z</v>
+        <v>2026-07-30T14:01:58.551Z</v>
       </c>
     </row>
     <row r="163">
@@ -3164,10 +3164,10 @@
         <v>Passed</v>
       </c>
       <c r="D163">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="E163" t="str">
-        <v>2026-07-30T13:52:38.047Z</v>
+        <v>2026-07-30T14:01:59.551Z</v>
       </c>
     </row>
     <row r="164">
@@ -3181,10 +3181,10 @@
         <v>Passed</v>
       </c>
       <c r="D164">
-        <v>0.84</v>
+        <v>1.59</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-07-30T13:52:39.047Z</v>
+        <v>2026-07-30T14:02:00.551Z</v>
       </c>
     </row>
     <row r="165">
@@ -3198,10 +3198,10 @@
         <v>Passed</v>
       </c>
       <c r="D165">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="E165" t="str">
-        <v>2026-07-30T13:52:40.047Z</v>
+        <v>2026-07-30T14:02:01.551Z</v>
       </c>
     </row>
     <row r="166">
@@ -3215,10 +3215,10 @@
         <v>Passed</v>
       </c>
       <c r="D166">
-        <v>0.95</v>
+        <v>0.63</v>
       </c>
       <c r="E166" t="str">
-        <v>2026-07-30T13:52:41.047Z</v>
+        <v>2026-07-30T14:02:02.551Z</v>
       </c>
     </row>
     <row r="167">
@@ -3232,10 +3232,10 @@
         <v>Passed</v>
       </c>
       <c r="D167">
-        <v>0.21</v>
+        <v>1.66</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-07-30T13:52:42.047Z</v>
+        <v>2026-07-30T14:02:03.551Z</v>
       </c>
     </row>
     <row r="168">
@@ -3249,10 +3249,10 @@
         <v>Passed</v>
       </c>
       <c r="D168">
-        <v>1.18</v>
+        <v>1.61</v>
       </c>
       <c r="E168" t="str">
-        <v>2026-07-30T13:52:43.047Z</v>
+        <v>2026-07-30T14:02:04.551Z</v>
       </c>
     </row>
     <row r="169">
@@ -3266,10 +3266,10 @@
         <v>Passed</v>
       </c>
       <c r="D169">
-        <v>1.98</v>
+        <v>1.07</v>
       </c>
       <c r="E169" t="str">
-        <v>2026-07-30T13:52:44.047Z</v>
+        <v>2026-07-30T14:02:05.551Z</v>
       </c>
     </row>
     <row r="170">
@@ -3283,10 +3283,10 @@
         <v>Passed</v>
       </c>
       <c r="D170">
-        <v>1.16</v>
+        <v>0.96</v>
       </c>
       <c r="E170" t="str">
-        <v>2026-07-30T13:52:45.047Z</v>
+        <v>2026-07-30T14:02:06.551Z</v>
       </c>
     </row>
     <row r="171">
@@ -3300,10 +3300,10 @@
         <v>Passed</v>
       </c>
       <c r="D171">
-        <v>0.93</v>
+        <v>1.49</v>
       </c>
       <c r="E171" t="str">
-        <v>2026-07-30T13:52:46.047Z</v>
+        <v>2026-07-30T14:02:07.551Z</v>
       </c>
     </row>
     <row r="172">
@@ -3317,10 +3317,10 @@
         <v>Passed</v>
       </c>
       <c r="D172">
-        <v>0.08</v>
+        <v>1.33</v>
       </c>
       <c r="E172" t="str">
-        <v>2026-07-30T13:52:47.047Z</v>
+        <v>2026-07-30T14:02:08.551Z</v>
       </c>
     </row>
     <row r="173">
@@ -3334,10 +3334,10 @@
         <v>Passed</v>
       </c>
       <c r="D173">
-        <v>1.8</v>
+        <v>1.08</v>
       </c>
       <c r="E173" t="str">
-        <v>2026-07-30T13:52:48.047Z</v>
+        <v>2026-07-30T14:02:09.551Z</v>
       </c>
     </row>
     <row r="174">
@@ -3351,10 +3351,10 @@
         <v>Passed</v>
       </c>
       <c r="D174">
-        <v>0.39</v>
+        <v>0.53</v>
       </c>
       <c r="E174" t="str">
-        <v>2026-07-30T13:52:49.047Z</v>
+        <v>2026-07-30T14:02:10.551Z</v>
       </c>
     </row>
     <row r="175">
@@ -3368,10 +3368,10 @@
         <v>Passed</v>
       </c>
       <c r="D175">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="E175" t="str">
-        <v>2026-07-30T13:52:50.047Z</v>
+        <v>2026-07-30T14:02:11.551Z</v>
       </c>
     </row>
     <row r="176">
@@ -3385,10 +3385,10 @@
         <v>Passed</v>
       </c>
       <c r="D176">
-        <v>0.3</v>
+        <v>1.35</v>
       </c>
       <c r="E176" t="str">
-        <v>2026-07-30T13:52:51.047Z</v>
+        <v>2026-07-30T14:02:12.551Z</v>
       </c>
     </row>
     <row r="177">
@@ -3402,10 +3402,10 @@
         <v>Passed</v>
       </c>
       <c r="D177">
-        <v>1.19</v>
+        <v>1.91</v>
       </c>
       <c r="E177" t="str">
-        <v>2026-07-30T13:52:52.047Z</v>
+        <v>2026-07-30T14:02:13.551Z</v>
       </c>
     </row>
     <row r="178">
@@ -3419,10 +3419,10 @@
         <v>Passed</v>
       </c>
       <c r="D178">
-        <v>0.43</v>
+        <v>1.37</v>
       </c>
       <c r="E178" t="str">
-        <v>2026-07-30T13:52:53.047Z</v>
+        <v>2026-07-30T14:02:14.551Z</v>
       </c>
     </row>
     <row r="179">
@@ -3436,10 +3436,10 @@
         <v>Passed</v>
       </c>
       <c r="D179">
-        <v>1.47</v>
+        <v>0.95</v>
       </c>
       <c r="E179" t="str">
-        <v>2026-07-30T13:52:54.047Z</v>
+        <v>2026-07-30T14:02:15.551Z</v>
       </c>
     </row>
     <row r="180">
@@ -3453,10 +3453,10 @@
         <v>Passed</v>
       </c>
       <c r="D180">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="E180" t="str">
-        <v>2026-07-30T13:52:55.047Z</v>
+        <v>2026-07-30T14:02:16.551Z</v>
       </c>
     </row>
     <row r="181">
@@ -3470,10 +3470,10 @@
         <v>Passed</v>
       </c>
       <c r="D181">
-        <v>1.99</v>
+        <v>0.7</v>
       </c>
       <c r="E181" t="str">
-        <v>2026-07-30T13:52:56.047Z</v>
+        <v>2026-07-30T14:02:17.551Z</v>
       </c>
     </row>
     <row r="182">
@@ -3487,10 +3487,10 @@
         <v>Passed</v>
       </c>
       <c r="D182">
-        <v>0.98</v>
+        <v>0.65</v>
       </c>
       <c r="E182" t="str">
-        <v>2026-07-30T13:52:57.047Z</v>
+        <v>2026-07-30T14:02:18.551Z</v>
       </c>
     </row>
     <row r="183">
@@ -3504,10 +3504,10 @@
         <v>Passed</v>
       </c>
       <c r="D183">
-        <v>1.57</v>
+        <v>1.21</v>
       </c>
       <c r="E183" t="str">
-        <v>2026-07-30T13:52:58.047Z</v>
+        <v>2026-07-30T14:02:19.551Z</v>
       </c>
     </row>
     <row r="184">
@@ -3521,10 +3521,10 @@
         <v>Passed</v>
       </c>
       <c r="D184">
-        <v>0.01</v>
+        <v>1.05</v>
       </c>
       <c r="E184" t="str">
-        <v>2026-07-30T13:52:59.047Z</v>
+        <v>2026-07-30T14:02:20.551Z</v>
       </c>
     </row>
     <row r="185">
@@ -3538,10 +3538,10 @@
         <v>Passed</v>
       </c>
       <c r="D185">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="E185" t="str">
-        <v>2026-07-30T13:53:00.047Z</v>
+        <v>2026-07-30T14:02:21.551Z</v>
       </c>
     </row>
     <row r="186">
@@ -3555,10 +3555,10 @@
         <v>Passed</v>
       </c>
       <c r="D186">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="E186" t="str">
-        <v>2026-07-30T13:53:01.047Z</v>
+        <v>2026-07-30T14:02:22.551Z</v>
       </c>
     </row>
     <row r="187">
@@ -3572,10 +3572,10 @@
         <v>Passed</v>
       </c>
       <c r="D187">
-        <v>0.1</v>
+        <v>0.85</v>
       </c>
       <c r="E187" t="str">
-        <v>2026-07-30T13:53:02.047Z</v>
+        <v>2026-07-30T14:02:23.551Z</v>
       </c>
     </row>
     <row r="188">
@@ -3589,10 +3589,10 @@
         <v>Passed</v>
       </c>
       <c r="D188">
-        <v>0.59</v>
+        <v>0.81</v>
       </c>
       <c r="E188" t="str">
-        <v>2026-07-30T13:53:03.047Z</v>
+        <v>2026-07-30T14:02:24.551Z</v>
       </c>
     </row>
     <row r="189">
@@ -3606,10 +3606,10 @@
         <v>Passed</v>
       </c>
       <c r="D189">
-        <v>0.07</v>
+        <v>0.77</v>
       </c>
       <c r="E189" t="str">
-        <v>2026-07-30T13:53:04.047Z</v>
+        <v>2026-07-30T14:02:25.551Z</v>
       </c>
     </row>
     <row r="190">
@@ -3623,10 +3623,10 @@
         <v>Passed</v>
       </c>
       <c r="D190">
-        <v>0.93</v>
+        <v>0.69</v>
       </c>
       <c r="E190" t="str">
-        <v>2026-07-30T13:53:05.047Z</v>
+        <v>2026-07-30T14:02:26.551Z</v>
       </c>
     </row>
     <row r="191">
@@ -3640,10 +3640,10 @@
         <v>Passed</v>
       </c>
       <c r="D191">
-        <v>0.01</v>
+        <v>1.64</v>
       </c>
       <c r="E191" t="str">
-        <v>2026-07-30T13:53:06.047Z</v>
+        <v>2026-07-30T14:02:27.551Z</v>
       </c>
     </row>
     <row r="192">
@@ -3657,10 +3657,10 @@
         <v>Passed</v>
       </c>
       <c r="D192">
-        <v>1.78</v>
+        <v>1.03</v>
       </c>
       <c r="E192" t="str">
-        <v>2026-07-30T13:53:07.047Z</v>
+        <v>2026-07-30T14:02:28.551Z</v>
       </c>
     </row>
     <row r="193">
@@ -3674,10 +3674,10 @@
         <v>Passed</v>
       </c>
       <c r="D193">
-        <v>1.87</v>
+        <v>0.68</v>
       </c>
       <c r="E193" t="str">
-        <v>2026-07-30T13:53:08.047Z</v>
+        <v>2026-07-30T14:02:29.551Z</v>
       </c>
     </row>
     <row r="194">
@@ -3691,10 +3691,10 @@
         <v>Passed</v>
       </c>
       <c r="D194">
-        <v>0.43</v>
+        <v>1.86</v>
       </c>
       <c r="E194" t="str">
-        <v>2026-07-30T13:53:09.047Z</v>
+        <v>2026-07-30T14:02:30.551Z</v>
       </c>
     </row>
     <row r="195">
@@ -3708,10 +3708,10 @@
         <v>Passed</v>
       </c>
       <c r="D195">
-        <v>1.69</v>
+        <v>0.97</v>
       </c>
       <c r="E195" t="str">
-        <v>2026-07-30T13:53:10.047Z</v>
+        <v>2026-07-30T14:02:31.551Z</v>
       </c>
     </row>
     <row r="196">
@@ -3725,10 +3725,10 @@
         <v>Passed</v>
       </c>
       <c r="D196">
-        <v>1.34</v>
+        <v>0.64</v>
       </c>
       <c r="E196" t="str">
-        <v>2026-07-30T13:53:11.047Z</v>
+        <v>2026-07-30T14:02:32.551Z</v>
       </c>
     </row>
     <row r="197">
@@ -3742,10 +3742,10 @@
         <v>Passed</v>
       </c>
       <c r="D197">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="E197" t="str">
-        <v>2026-07-30T13:53:12.047Z</v>
+        <v>2026-07-30T14:02:33.551Z</v>
       </c>
     </row>
     <row r="198">
@@ -3759,10 +3759,10 @@
         <v>Passed</v>
       </c>
       <c r="D198">
-        <v>1.55</v>
+        <v>1.13</v>
       </c>
       <c r="E198" t="str">
-        <v>2026-07-30T13:53:13.047Z</v>
+        <v>2026-07-30T14:02:34.551Z</v>
       </c>
     </row>
     <row r="199">
@@ -3776,10 +3776,10 @@
         <v>Passed</v>
       </c>
       <c r="D199">
-        <v>0.66</v>
+        <v>1.92</v>
       </c>
       <c r="E199" t="str">
-        <v>2026-07-30T13:53:14.047Z</v>
+        <v>2026-07-30T14:02:35.551Z</v>
       </c>
     </row>
     <row r="200">
@@ -3793,10 +3793,10 @@
         <v>Passed</v>
       </c>
       <c r="D200">
-        <v>0.35</v>
+        <v>0.18</v>
       </c>
       <c r="E200" t="str">
-        <v>2026-07-30T13:53:15.047Z</v>
+        <v>2026-07-30T14:02:36.551Z</v>
       </c>
     </row>
     <row r="201">
@@ -3810,10 +3810,10 @@
         <v>Passed</v>
       </c>
       <c r="D201">
-        <v>0.44</v>
+        <v>0.64</v>
       </c>
       <c r="E201" t="str">
-        <v>2026-07-30T13:53:16.047Z</v>
+        <v>2026-07-30T14:02:37.551Z</v>
       </c>
     </row>
     <row r="202">
@@ -3827,10 +3827,10 @@
         <v>Passed</v>
       </c>
       <c r="D202">
-        <v>1.06</v>
+        <v>1.56</v>
       </c>
       <c r="E202" t="str">
-        <v>2026-07-30T13:53:17.047Z</v>
+        <v>2026-07-30T14:02:38.551Z</v>
       </c>
     </row>
     <row r="203">
@@ -3844,10 +3844,10 @@
         <v>Passed</v>
       </c>
       <c r="D203">
-        <v>0.12</v>
+        <v>0.38</v>
       </c>
       <c r="E203" t="str">
-        <v>2026-07-30T13:53:18.047Z</v>
+        <v>2026-07-30T14:02:39.551Z</v>
       </c>
     </row>
     <row r="204">
@@ -3861,10 +3861,10 @@
         <v>Passed</v>
       </c>
       <c r="D204">
-        <v>1.21</v>
+        <v>1.48</v>
       </c>
       <c r="E204" t="str">
-        <v>2026-07-30T13:53:19.047Z</v>
+        <v>2026-07-30T14:02:40.551Z</v>
       </c>
     </row>
     <row r="205">
@@ -3878,10 +3878,10 @@
         <v>Passed</v>
       </c>
       <c r="D205">
-        <v>0.23</v>
+        <v>1.95</v>
       </c>
       <c r="E205" t="str">
-        <v>2026-07-30T13:53:20.047Z</v>
+        <v>2026-07-30T14:02:41.551Z</v>
       </c>
     </row>
     <row r="206">
@@ -3895,10 +3895,10 @@
         <v>Passed</v>
       </c>
       <c r="D206">
-        <v>0.9</v>
+        <v>0.21</v>
       </c>
       <c r="E206" t="str">
-        <v>2026-07-30T13:53:21.047Z</v>
+        <v>2026-07-30T14:02:42.551Z</v>
       </c>
     </row>
     <row r="207">
@@ -3912,10 +3912,10 @@
         <v>Passed</v>
       </c>
       <c r="D207">
-        <v>0.22</v>
+        <v>0.12</v>
       </c>
       <c r="E207" t="str">
-        <v>2026-07-30T13:53:22.047Z</v>
+        <v>2026-07-30T14:02:43.551Z</v>
       </c>
     </row>
     <row r="208">
@@ -3929,10 +3929,10 @@
         <v>Passed</v>
       </c>
       <c r="D208">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="E208" t="str">
-        <v>2026-07-30T13:53:23.047Z</v>
+        <v>2026-07-30T14:02:44.551Z</v>
       </c>
     </row>
     <row r="209">
@@ -3946,10 +3946,10 @@
         <v>Passed</v>
       </c>
       <c r="D209">
-        <v>1.78</v>
+        <v>0.6</v>
       </c>
       <c r="E209" t="str">
-        <v>2026-07-30T13:53:24.047Z</v>
+        <v>2026-07-30T14:02:45.551Z</v>
       </c>
     </row>
     <row r="210">
@@ -3963,10 +3963,10 @@
         <v>Passed</v>
       </c>
       <c r="D210">
-        <v>1.1</v>
+        <v>0.44</v>
       </c>
       <c r="E210" t="str">
-        <v>2026-07-30T13:53:25.047Z</v>
+        <v>2026-07-30T14:02:46.551Z</v>
       </c>
     </row>
     <row r="211">
@@ -3980,10 +3980,10 @@
         <v>Passed</v>
       </c>
       <c r="D211">
-        <v>1.85</v>
+        <v>0.98</v>
       </c>
       <c r="E211" t="str">
-        <v>2026-07-30T13:53:26.047Z</v>
+        <v>2026-07-30T14:02:47.551Z</v>
       </c>
     </row>
     <row r="212">
@@ -3997,10 +3997,10 @@
         <v>Passed</v>
       </c>
       <c r="D212">
-        <v>1.09</v>
+        <v>0.47</v>
       </c>
       <c r="E212" t="str">
-        <v>2026-07-30T13:53:27.047Z</v>
+        <v>2026-07-30T14:02:48.551Z</v>
       </c>
     </row>
     <row r="213">
@@ -4014,10 +4014,10 @@
         <v>Passed</v>
       </c>
       <c r="D213">
-        <v>0.94</v>
+        <v>0.82</v>
       </c>
       <c r="E213" t="str">
-        <v>2026-07-30T13:53:28.047Z</v>
+        <v>2026-07-30T14:02:49.551Z</v>
       </c>
     </row>
     <row r="214">
@@ -4031,10 +4031,10 @@
         <v>Passed</v>
       </c>
       <c r="D214">
-        <v>1.18</v>
+        <v>0.59</v>
       </c>
       <c r="E214" t="str">
-        <v>2026-07-30T13:53:29.047Z</v>
+        <v>2026-07-30T14:02:50.551Z</v>
       </c>
     </row>
     <row r="215">
@@ -4048,10 +4048,10 @@
         <v>Passed</v>
       </c>
       <c r="D215">
-        <v>1.53</v>
+        <v>0.52</v>
       </c>
       <c r="E215" t="str">
-        <v>2026-07-30T13:53:30.047Z</v>
+        <v>2026-07-30T14:02:51.551Z</v>
       </c>
     </row>
     <row r="216">
@@ -4065,10 +4065,10 @@
         <v>Passed</v>
       </c>
       <c r="D216">
-        <v>0.02</v>
+        <v>1.18</v>
       </c>
       <c r="E216" t="str">
-        <v>2026-07-30T13:53:31.047Z</v>
+        <v>2026-07-30T14:02:52.551Z</v>
       </c>
     </row>
     <row r="217">
@@ -4082,10 +4082,10 @@
         <v>Passed</v>
       </c>
       <c r="D217">
-        <v>0.82</v>
+        <v>0.14</v>
       </c>
       <c r="E217" t="str">
-        <v>2026-07-30T13:53:32.047Z</v>
+        <v>2026-07-30T14:02:53.551Z</v>
       </c>
     </row>
     <row r="218">
@@ -4099,10 +4099,10 @@
         <v>Passed</v>
       </c>
       <c r="D218">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="E218" t="str">
-        <v>2026-07-30T13:53:33.047Z</v>
+        <v>2026-07-30T14:02:54.551Z</v>
       </c>
     </row>
     <row r="219">
@@ -4116,10 +4116,10 @@
         <v>Passed</v>
       </c>
       <c r="D219">
-        <v>1.28</v>
+        <v>1.89</v>
       </c>
       <c r="E219" t="str">
-        <v>2026-07-30T13:53:34.047Z</v>
+        <v>2026-07-30T14:02:55.551Z</v>
       </c>
     </row>
     <row r="220">
@@ -4133,10 +4133,10 @@
         <v>Passed</v>
       </c>
       <c r="D220">
-        <v>1.52</v>
+        <v>0.43</v>
       </c>
       <c r="E220" t="str">
-        <v>2026-07-30T13:53:35.047Z</v>
+        <v>2026-07-30T14:02:56.551Z</v>
       </c>
     </row>
     <row r="221">
@@ -4150,10 +4150,10 @@
         <v>Passed</v>
       </c>
       <c r="D221">
-        <v>1.07</v>
+        <v>0.06</v>
       </c>
       <c r="E221" t="str">
-        <v>2026-07-30T13:53:36.047Z</v>
+        <v>2026-07-30T14:02:57.551Z</v>
       </c>
     </row>
     <row r="222">
@@ -4167,10 +4167,10 @@
         <v>Passed</v>
       </c>
       <c r="D222">
-        <v>0.64</v>
+        <v>0.94</v>
       </c>
       <c r="E222" t="str">
-        <v>2026-07-30T13:53:37.047Z</v>
+        <v>2026-07-30T14:02:58.551Z</v>
       </c>
     </row>
     <row r="223">
@@ -4184,10 +4184,10 @@
         <v>Passed</v>
       </c>
       <c r="D223">
-        <v>0.98</v>
+        <v>1.49</v>
       </c>
       <c r="E223" t="str">
-        <v>2026-07-30T13:53:38.047Z</v>
+        <v>2026-07-30T14:02:59.551Z</v>
       </c>
     </row>
     <row r="224">
@@ -4201,10 +4201,10 @@
         <v>Passed</v>
       </c>
       <c r="D224">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="E224" t="str">
-        <v>2026-07-30T13:53:39.047Z</v>
+        <v>2026-07-30T14:03:00.551Z</v>
       </c>
     </row>
     <row r="225">
@@ -4218,10 +4218,10 @@
         <v>Passed</v>
       </c>
       <c r="D225">
-        <v>1.34</v>
+        <v>0.46</v>
       </c>
       <c r="E225" t="str">
-        <v>2026-07-30T13:53:40.047Z</v>
+        <v>2026-07-30T14:03:01.551Z</v>
       </c>
     </row>
     <row r="226">
@@ -4235,10 +4235,10 @@
         <v>Passed</v>
       </c>
       <c r="D226">
-        <v>0.98</v>
+        <v>1.36</v>
       </c>
       <c r="E226" t="str">
-        <v>2026-07-30T13:53:41.047Z</v>
+        <v>2026-07-30T14:03:02.551Z</v>
       </c>
     </row>
     <row r="227">
@@ -4252,10 +4252,10 @@
         <v>Passed</v>
       </c>
       <c r="D227">
-        <v>0.25</v>
+        <v>1.57</v>
       </c>
       <c r="E227" t="str">
-        <v>2026-07-30T13:53:42.047Z</v>
+        <v>2026-07-30T14:03:03.551Z</v>
       </c>
     </row>
     <row r="228">
@@ -4269,10 +4269,10 @@
         <v>Passed</v>
       </c>
       <c r="D228">
-        <v>0.64</v>
+        <v>1.64</v>
       </c>
       <c r="E228" t="str">
-        <v>2026-07-30T13:53:43.047Z</v>
+        <v>2026-07-30T14:03:04.551Z</v>
       </c>
     </row>
     <row r="229">
@@ -4286,10 +4286,10 @@
         <v>Passed</v>
       </c>
       <c r="D229">
-        <v>0.88</v>
+        <v>0.69</v>
       </c>
       <c r="E229" t="str">
-        <v>2026-07-30T13:53:44.047Z</v>
+        <v>2026-07-30T14:03:05.551Z</v>
       </c>
     </row>
     <row r="230">
@@ -4303,10 +4303,10 @@
         <v>Passed</v>
       </c>
       <c r="D230">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="E230" t="str">
-        <v>2026-07-30T13:53:45.047Z</v>
+        <v>2026-07-30T14:03:06.551Z</v>
       </c>
     </row>
     <row r="231">
@@ -4320,10 +4320,10 @@
         <v>Passed</v>
       </c>
       <c r="D231">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="E231" t="str">
-        <v>2026-07-30T13:53:46.047Z</v>
+        <v>2026-07-30T14:03:07.551Z</v>
       </c>
     </row>
     <row r="232">
@@ -4337,10 +4337,10 @@
         <v>Passed</v>
       </c>
       <c r="D232">
-        <v>1.68</v>
+        <v>1.09</v>
       </c>
       <c r="E232" t="str">
-        <v>2026-07-30T13:53:47.047Z</v>
+        <v>2026-07-30T14:03:08.551Z</v>
       </c>
     </row>
     <row r="233">
@@ -4354,10 +4354,10 @@
         <v>Passed</v>
       </c>
       <c r="D233">
-        <v>1.31</v>
+        <v>1.78</v>
       </c>
       <c r="E233" t="str">
-        <v>2026-07-30T13:53:48.047Z</v>
+        <v>2026-07-30T14:03:09.551Z</v>
       </c>
     </row>
     <row r="234">
@@ -4371,10 +4371,10 @@
         <v>Passed</v>
       </c>
       <c r="D234">
-        <v>0.08</v>
+        <v>1.38</v>
       </c>
       <c r="E234" t="str">
-        <v>2026-07-30T13:53:49.047Z</v>
+        <v>2026-07-30T14:03:10.551Z</v>
       </c>
     </row>
     <row r="235">
@@ -4388,10 +4388,10 @@
         <v>Passed</v>
       </c>
       <c r="D235">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="E235" t="str">
-        <v>2026-07-30T13:53:50.047Z</v>
+        <v>2026-07-30T14:03:11.551Z</v>
       </c>
     </row>
     <row r="236">
@@ -4405,10 +4405,10 @@
         <v>Passed</v>
       </c>
       <c r="D236">
-        <v>1.67</v>
+        <v>0.2</v>
       </c>
       <c r="E236" t="str">
-        <v>2026-07-30T13:53:51.047Z</v>
+        <v>2026-07-30T14:03:12.551Z</v>
       </c>
     </row>
     <row r="237">
@@ -4422,10 +4422,10 @@
         <v>Passed</v>
       </c>
       <c r="D237">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E237" t="str">
-        <v>2026-07-30T13:53:52.047Z</v>
+        <v>2026-07-30T14:03:13.551Z</v>
       </c>
     </row>
     <row r="238">
@@ -4439,10 +4439,10 @@
         <v>Passed</v>
       </c>
       <c r="D238">
-        <v>0.16</v>
+        <v>1.22</v>
       </c>
       <c r="E238" t="str">
-        <v>2026-07-30T13:53:53.047Z</v>
+        <v>2026-07-30T14:03:14.551Z</v>
       </c>
     </row>
     <row r="239">
@@ -4456,10 +4456,10 @@
         <v>Passed</v>
       </c>
       <c r="D239">
-        <v>1.73</v>
+        <v>1.16</v>
       </c>
       <c r="E239" t="str">
-        <v>2026-07-30T13:53:54.047Z</v>
+        <v>2026-07-30T14:03:15.551Z</v>
       </c>
     </row>
     <row r="240">
@@ -4473,10 +4473,10 @@
         <v>Passed</v>
       </c>
       <c r="D240">
-        <v>0.16</v>
+        <v>1.9</v>
       </c>
       <c r="E240" t="str">
-        <v>2026-07-30T13:53:55.047Z</v>
+        <v>2026-07-30T14:03:16.551Z</v>
       </c>
     </row>
     <row r="241">
@@ -4490,10 +4490,10 @@
         <v>Passed</v>
       </c>
       <c r="D241">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="E241" t="str">
-        <v>2026-07-30T13:53:56.047Z</v>
+        <v>2026-07-30T14:03:17.551Z</v>
       </c>
     </row>
     <row r="242">
@@ -4507,10 +4507,10 @@
         <v>Passed</v>
       </c>
       <c r="D242">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="E242" t="str">
-        <v>2026-07-30T13:53:57.047Z</v>
+        <v>2026-07-30T14:03:18.551Z</v>
       </c>
     </row>
     <row r="243">
@@ -4524,10 +4524,10 @@
         <v>Passed</v>
       </c>
       <c r="D243">
-        <v>1.48</v>
+        <v>0.25</v>
       </c>
       <c r="E243" t="str">
-        <v>2026-07-30T13:53:58.047Z</v>
+        <v>2026-07-30T14:03:19.551Z</v>
       </c>
     </row>
     <row r="244">
@@ -4541,10 +4541,10 @@
         <v>Passed</v>
       </c>
       <c r="D244">
-        <v>1.48</v>
+        <v>0.99</v>
       </c>
       <c r="E244" t="str">
-        <v>2026-07-30T13:53:59.047Z</v>
+        <v>2026-07-30T14:03:20.551Z</v>
       </c>
     </row>
     <row r="245">
@@ -4558,10 +4558,10 @@
         <v>Passed</v>
       </c>
       <c r="D245">
-        <v>1.02</v>
+        <v>0.13</v>
       </c>
       <c r="E245" t="str">
-        <v>2026-07-30T13:54:00.047Z</v>
+        <v>2026-07-30T14:03:21.551Z</v>
       </c>
     </row>
     <row r="246">
@@ -4575,10 +4575,10 @@
         <v>Passed</v>
       </c>
       <c r="D246">
-        <v>0.57</v>
+        <v>1.61</v>
       </c>
       <c r="E246" t="str">
-        <v>2026-07-30T13:54:01.047Z</v>
+        <v>2026-07-30T14:03:22.551Z</v>
       </c>
     </row>
     <row r="247">
@@ -4592,10 +4592,10 @@
         <v>Passed</v>
       </c>
       <c r="D247">
-        <v>0.52</v>
+        <v>1</v>
       </c>
       <c r="E247" t="str">
-        <v>2026-07-30T13:54:02.047Z</v>
+        <v>2026-07-30T14:03:23.551Z</v>
       </c>
     </row>
     <row r="248">
@@ -4609,10 +4609,10 @@
         <v>Passed</v>
       </c>
       <c r="D248">
-        <v>1.26</v>
+        <v>0.19</v>
       </c>
       <c r="E248" t="str">
-        <v>2026-07-30T13:54:03.047Z</v>
+        <v>2026-07-30T14:03:24.551Z</v>
       </c>
     </row>
     <row r="249">
@@ -4626,10 +4626,10 @@
         <v>Passed</v>
       </c>
       <c r="D249">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="E249" t="str">
-        <v>2026-07-30T13:54:04.047Z</v>
+        <v>2026-07-30T14:03:25.551Z</v>
       </c>
     </row>
     <row r="250">
@@ -4643,10 +4643,10 @@
         <v>Passed</v>
       </c>
       <c r="D250">
-        <v>1.53</v>
+        <v>0.96</v>
       </c>
       <c r="E250" t="str">
-        <v>2026-07-30T13:54:05.047Z</v>
+        <v>2026-07-30T14:03:26.551Z</v>
       </c>
     </row>
     <row r="251">
@@ -4660,10 +4660,10 @@
         <v>Passed</v>
       </c>
       <c r="D251">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="E251" t="str">
-        <v>2026-07-30T13:54:06.047Z</v>
+        <v>2026-07-30T14:03:27.551Z</v>
       </c>
     </row>
     <row r="252">
@@ -4677,10 +4677,10 @@
         <v>Passed</v>
       </c>
       <c r="D252">
-        <v>0.05</v>
+        <v>1.25</v>
       </c>
       <c r="E252" t="str">
-        <v>2026-07-30T13:54:07.047Z</v>
+        <v>2026-07-30T14:03:28.551Z</v>
       </c>
     </row>
     <row r="253">
@@ -4694,10 +4694,10 @@
         <v>Passed</v>
       </c>
       <c r="D253">
-        <v>0.98</v>
+        <v>0.44</v>
       </c>
       <c r="E253" t="str">
-        <v>2026-07-30T13:54:08.047Z</v>
+        <v>2026-07-30T14:03:29.551Z</v>
       </c>
     </row>
     <row r="254">
@@ -4711,10 +4711,10 @@
         <v>Passed</v>
       </c>
       <c r="D254">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="E254" t="str">
-        <v>2026-07-30T13:54:09.047Z</v>
+        <v>2026-07-30T14:03:30.551Z</v>
       </c>
     </row>
     <row r="255">
@@ -4728,10 +4728,10 @@
         <v>Passed</v>
       </c>
       <c r="D255">
-        <v>0.07</v>
+        <v>1.5</v>
       </c>
       <c r="E255" t="str">
-        <v>2026-07-30T13:54:10.047Z</v>
+        <v>2026-07-30T14:03:31.551Z</v>
       </c>
     </row>
     <row r="256">
@@ -4742,13 +4742,13 @@
         <v>Verify Security functionality module 255</v>
       </c>
       <c r="C256" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D256">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="E256" t="str">
-        <v>2026-07-30T13:54:11.047Z</v>
+        <v>2026-07-30T14:03:32.551Z</v>
       </c>
     </row>
     <row r="257">
@@ -4762,10 +4762,10 @@
         <v>Passed</v>
       </c>
       <c r="D257">
-        <v>0.75</v>
+        <v>1.88</v>
       </c>
       <c r="E257" t="str">
-        <v>2026-07-30T13:54:12.047Z</v>
+        <v>2026-07-30T14:03:33.551Z</v>
       </c>
     </row>
     <row r="258">
@@ -4779,10 +4779,10 @@
         <v>Passed</v>
       </c>
       <c r="D258">
-        <v>0.51</v>
+        <v>1.72</v>
       </c>
       <c r="E258" t="str">
-        <v>2026-07-30T13:54:13.047Z</v>
+        <v>2026-07-30T14:03:34.551Z</v>
       </c>
     </row>
     <row r="259">
@@ -4796,10 +4796,10 @@
         <v>Passed</v>
       </c>
       <c r="D259">
-        <v>0.31</v>
+        <v>1.98</v>
       </c>
       <c r="E259" t="str">
-        <v>2026-07-30T13:54:14.047Z</v>
+        <v>2026-07-30T14:03:35.551Z</v>
       </c>
     </row>
     <row r="260">
@@ -4813,10 +4813,10 @@
         <v>Passed</v>
       </c>
       <c r="D260">
-        <v>0.06</v>
+        <v>1.16</v>
       </c>
       <c r="E260" t="str">
-        <v>2026-07-30T13:54:15.047Z</v>
+        <v>2026-07-30T14:03:36.551Z</v>
       </c>
     </row>
     <row r="261">
@@ -4830,10 +4830,10 @@
         <v>Passed</v>
       </c>
       <c r="D261">
-        <v>0.72</v>
+        <v>1.16</v>
       </c>
       <c r="E261" t="str">
-        <v>2026-07-30T13:54:16.047Z</v>
+        <v>2026-07-30T14:03:37.551Z</v>
       </c>
     </row>
     <row r="262">
@@ -4847,10 +4847,10 @@
         <v>Passed</v>
       </c>
       <c r="D262">
-        <v>0.58</v>
+        <v>1.15</v>
       </c>
       <c r="E262" t="str">
-        <v>2026-07-30T13:54:17.047Z</v>
+        <v>2026-07-30T14:03:38.551Z</v>
       </c>
     </row>
     <row r="263">
@@ -4864,10 +4864,10 @@
         <v>Passed</v>
       </c>
       <c r="D263">
-        <v>0.38</v>
+        <v>1.11</v>
       </c>
       <c r="E263" t="str">
-        <v>2026-07-30T13:54:18.047Z</v>
+        <v>2026-07-30T14:03:39.551Z</v>
       </c>
     </row>
     <row r="264">
@@ -4881,10 +4881,10 @@
         <v>Passed</v>
       </c>
       <c r="D264">
-        <v>1.24</v>
+        <v>1.78</v>
       </c>
       <c r="E264" t="str">
-        <v>2026-07-30T13:54:19.047Z</v>
+        <v>2026-07-30T14:03:40.551Z</v>
       </c>
     </row>
     <row r="265">
@@ -4898,10 +4898,10 @@
         <v>Passed</v>
       </c>
       <c r="D265">
-        <v>0.96</v>
+        <v>1.59</v>
       </c>
       <c r="E265" t="str">
-        <v>2026-07-30T13:54:20.047Z</v>
+        <v>2026-07-30T14:03:41.551Z</v>
       </c>
     </row>
     <row r="266">
@@ -4915,10 +4915,10 @@
         <v>Passed</v>
       </c>
       <c r="D266">
-        <v>0.18</v>
+        <v>1.56</v>
       </c>
       <c r="E266" t="str">
-        <v>2026-07-30T13:54:21.047Z</v>
+        <v>2026-07-30T14:03:42.551Z</v>
       </c>
     </row>
     <row r="267">
@@ -4932,10 +4932,10 @@
         <v>Passed</v>
       </c>
       <c r="D267">
-        <v>0.96</v>
+        <v>0.32</v>
       </c>
       <c r="E267" t="str">
-        <v>2026-07-30T13:54:22.047Z</v>
+        <v>2026-07-30T14:03:43.551Z</v>
       </c>
     </row>
     <row r="268">
@@ -4949,10 +4949,10 @@
         <v>Passed</v>
       </c>
       <c r="D268">
-        <v>1.69</v>
+        <v>1.33</v>
       </c>
       <c r="E268" t="str">
-        <v>2026-07-30T13:54:23.047Z</v>
+        <v>2026-07-30T14:03:44.551Z</v>
       </c>
     </row>
     <row r="269">
@@ -4963,13 +4963,13 @@
         <v>Verify Security functionality module 268</v>
       </c>
       <c r="C269" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D269">
-        <v>0.69</v>
+        <v>1.79</v>
       </c>
       <c r="E269" t="str">
-        <v>2026-07-30T13:54:24.047Z</v>
+        <v>2026-07-30T14:03:45.551Z</v>
       </c>
     </row>
     <row r="270">
@@ -4983,10 +4983,10 @@
         <v>Passed</v>
       </c>
       <c r="D270">
-        <v>1.02</v>
+        <v>0.71</v>
       </c>
       <c r="E270" t="str">
-        <v>2026-07-30T13:54:25.047Z</v>
+        <v>2026-07-30T14:03:46.551Z</v>
       </c>
     </row>
     <row r="271">
@@ -5000,10 +5000,10 @@
         <v>Passed</v>
       </c>
       <c r="D271">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="E271" t="str">
-        <v>2026-07-30T13:54:26.047Z</v>
+        <v>2026-07-30T14:03:47.551Z</v>
       </c>
     </row>
     <row r="272">
@@ -5017,10 +5017,10 @@
         <v>Passed</v>
       </c>
       <c r="D272">
-        <v>0.18</v>
+        <v>1.09</v>
       </c>
       <c r="E272" t="str">
-        <v>2026-07-30T13:54:27.047Z</v>
+        <v>2026-07-30T14:03:48.551Z</v>
       </c>
     </row>
     <row r="273">
@@ -5034,10 +5034,10 @@
         <v>Passed</v>
       </c>
       <c r="D273">
-        <v>0.41</v>
+        <v>1.23</v>
       </c>
       <c r="E273" t="str">
-        <v>2026-07-30T13:54:28.047Z</v>
+        <v>2026-07-30T14:03:49.551Z</v>
       </c>
     </row>
     <row r="274">
@@ -5051,10 +5051,10 @@
         <v>Passed</v>
       </c>
       <c r="D274">
-        <v>1.98</v>
+        <v>0.36</v>
       </c>
       <c r="E274" t="str">
-        <v>2026-07-30T13:54:29.047Z</v>
+        <v>2026-07-30T14:03:50.551Z</v>
       </c>
     </row>
     <row r="275">
@@ -5068,10 +5068,10 @@
         <v>Passed</v>
       </c>
       <c r="D275">
-        <v>0.46</v>
+        <v>0.23</v>
       </c>
       <c r="E275" t="str">
-        <v>2026-07-30T13:54:30.047Z</v>
+        <v>2026-07-30T14:03:51.551Z</v>
       </c>
     </row>
     <row r="276">
@@ -5085,10 +5085,10 @@
         <v>Passed</v>
       </c>
       <c r="D276">
-        <v>0.83</v>
+        <v>1.06</v>
       </c>
       <c r="E276" t="str">
-        <v>2026-07-30T13:54:31.047Z</v>
+        <v>2026-07-30T14:03:52.551Z</v>
       </c>
     </row>
     <row r="277">
@@ -5102,10 +5102,10 @@
         <v>Passed</v>
       </c>
       <c r="D277">
-        <v>0.39</v>
+        <v>1.45</v>
       </c>
       <c r="E277" t="str">
-        <v>2026-07-30T13:54:32.047Z</v>
+        <v>2026-07-30T14:03:53.551Z</v>
       </c>
     </row>
     <row r="278">
@@ -5119,10 +5119,10 @@
         <v>Passed</v>
       </c>
       <c r="D278">
-        <v>1.89</v>
+        <v>1.45</v>
       </c>
       <c r="E278" t="str">
-        <v>2026-07-30T13:54:33.047Z</v>
+        <v>2026-07-30T14:03:54.551Z</v>
       </c>
     </row>
     <row r="279">
@@ -5136,10 +5136,10 @@
         <v>Passed</v>
       </c>
       <c r="D279">
-        <v>1.13</v>
+        <v>0.43</v>
       </c>
       <c r="E279" t="str">
-        <v>2026-07-30T13:54:34.047Z</v>
+        <v>2026-07-30T14:03:55.551Z</v>
       </c>
     </row>
     <row r="280">
@@ -5153,10 +5153,10 @@
         <v>Passed</v>
       </c>
       <c r="D280">
-        <v>0.14</v>
+        <v>0.01</v>
       </c>
       <c r="E280" t="str">
-        <v>2026-07-30T13:54:35.047Z</v>
+        <v>2026-07-30T14:03:56.551Z</v>
       </c>
     </row>
     <row r="281">
@@ -5170,10 +5170,10 @@
         <v>Passed</v>
       </c>
       <c r="D281">
-        <v>1.43</v>
+        <v>0.93</v>
       </c>
       <c r="E281" t="str">
-        <v>2026-07-30T13:54:36.047Z</v>
+        <v>2026-07-30T14:03:57.551Z</v>
       </c>
     </row>
     <row r="282">
@@ -5187,10 +5187,10 @@
         <v>Passed</v>
       </c>
       <c r="D282">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="E282" t="str">
-        <v>2026-07-30T13:54:37.047Z</v>
+        <v>2026-07-30T14:03:58.551Z</v>
       </c>
     </row>
     <row r="283">
@@ -5204,10 +5204,10 @@
         <v>Passed</v>
       </c>
       <c r="D283">
-        <v>0.85</v>
+        <v>1.49</v>
       </c>
       <c r="E283" t="str">
-        <v>2026-07-30T13:54:38.047Z</v>
+        <v>2026-07-30T14:03:59.551Z</v>
       </c>
     </row>
     <row r="284">
@@ -5221,10 +5221,10 @@
         <v>Passed</v>
       </c>
       <c r="D284">
-        <v>0.57</v>
+        <v>0.34</v>
       </c>
       <c r="E284" t="str">
-        <v>2026-07-30T13:54:39.047Z</v>
+        <v>2026-07-30T14:04:00.551Z</v>
       </c>
     </row>
     <row r="285">
@@ -5238,10 +5238,10 @@
         <v>Passed</v>
       </c>
       <c r="D285">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="E285" t="str">
-        <v>2026-07-30T13:54:40.047Z</v>
+        <v>2026-07-30T14:04:01.551Z</v>
       </c>
     </row>
     <row r="286">
@@ -5255,10 +5255,10 @@
         <v>Passed</v>
       </c>
       <c r="D286">
-        <v>0.16</v>
+        <v>0.52</v>
       </c>
       <c r="E286" t="str">
-        <v>2026-07-30T13:54:41.047Z</v>
+        <v>2026-07-30T14:04:02.551Z</v>
       </c>
     </row>
     <row r="287">
@@ -5272,10 +5272,10 @@
         <v>Passed</v>
       </c>
       <c r="D287">
-        <v>1.14</v>
+        <v>0.99</v>
       </c>
       <c r="E287" t="str">
-        <v>2026-07-30T13:54:42.047Z</v>
+        <v>2026-07-30T14:04:03.551Z</v>
       </c>
     </row>
     <row r="288">
@@ -5289,10 +5289,10 @@
         <v>Passed</v>
       </c>
       <c r="D288">
-        <v>0.99</v>
+        <v>1.59</v>
       </c>
       <c r="E288" t="str">
-        <v>2026-07-30T13:54:43.047Z</v>
+        <v>2026-07-30T14:04:04.551Z</v>
       </c>
     </row>
     <row r="289">
@@ -5306,10 +5306,10 @@
         <v>Passed</v>
       </c>
       <c r="D289">
-        <v>0.91</v>
+        <v>1.42</v>
       </c>
       <c r="E289" t="str">
-        <v>2026-07-30T13:54:44.047Z</v>
+        <v>2026-07-30T14:04:05.551Z</v>
       </c>
     </row>
     <row r="290">
@@ -5323,10 +5323,10 @@
         <v>Passed</v>
       </c>
       <c r="D290">
-        <v>0.81</v>
+        <v>1.11</v>
       </c>
       <c r="E290" t="str">
-        <v>2026-07-30T13:54:45.047Z</v>
+        <v>2026-07-30T14:04:06.551Z</v>
       </c>
     </row>
     <row r="291">
@@ -5337,13 +5337,13 @@
         <v>Verify Security functionality module 290</v>
       </c>
       <c r="C291" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D291">
-        <v>0.17</v>
+        <v>0.69</v>
       </c>
       <c r="E291" t="str">
-        <v>2026-07-30T13:54:46.047Z</v>
+        <v>2026-07-30T14:04:07.551Z</v>
       </c>
     </row>
     <row r="292">
@@ -5357,10 +5357,10 @@
         <v>Passed</v>
       </c>
       <c r="D292">
-        <v>1.8</v>
+        <v>0.85</v>
       </c>
       <c r="E292" t="str">
-        <v>2026-07-30T13:54:47.047Z</v>
+        <v>2026-07-30T14:04:08.551Z</v>
       </c>
     </row>
     <row r="293">
@@ -5374,10 +5374,10 @@
         <v>Passed</v>
       </c>
       <c r="D293">
-        <v>1.91</v>
+        <v>1.45</v>
       </c>
       <c r="E293" t="str">
-        <v>2026-07-30T13:54:48.047Z</v>
+        <v>2026-07-30T14:04:09.551Z</v>
       </c>
     </row>
     <row r="294">
@@ -5391,10 +5391,10 @@
         <v>Passed</v>
       </c>
       <c r="D294">
-        <v>1.73</v>
+        <v>0.1</v>
       </c>
       <c r="E294" t="str">
-        <v>2026-07-30T13:54:49.047Z</v>
+        <v>2026-07-30T14:04:10.551Z</v>
       </c>
     </row>
     <row r="295">
@@ -5408,10 +5408,10 @@
         <v>Passed</v>
       </c>
       <c r="D295">
-        <v>0.6</v>
+        <v>0.01</v>
       </c>
       <c r="E295" t="str">
-        <v>2026-07-30T13:54:50.047Z</v>
+        <v>2026-07-30T14:04:11.551Z</v>
       </c>
     </row>
     <row r="296">
@@ -5425,10 +5425,10 @@
         <v>Passed</v>
       </c>
       <c r="D296">
-        <v>0.19</v>
+        <v>1.79</v>
       </c>
       <c r="E296" t="str">
-        <v>2026-07-30T13:54:51.047Z</v>
+        <v>2026-07-30T14:04:12.551Z</v>
       </c>
     </row>
     <row r="297">
@@ -5442,10 +5442,10 @@
         <v>Passed</v>
       </c>
       <c r="D297">
-        <v>0.77</v>
+        <v>0.2</v>
       </c>
       <c r="E297" t="str">
-        <v>2026-07-30T13:54:52.047Z</v>
+        <v>2026-07-30T14:04:13.551Z</v>
       </c>
     </row>
     <row r="298">
@@ -5459,10 +5459,10 @@
         <v>Passed</v>
       </c>
       <c r="D298">
-        <v>1.7</v>
+        <v>0.06</v>
       </c>
       <c r="E298" t="str">
-        <v>2026-07-30T13:54:53.047Z</v>
+        <v>2026-07-30T14:04:14.551Z</v>
       </c>
     </row>
     <row r="299">
@@ -5476,10 +5476,10 @@
         <v>Passed</v>
       </c>
       <c r="D299">
-        <v>1.49</v>
+        <v>1.78</v>
       </c>
       <c r="E299" t="str">
-        <v>2026-07-30T13:54:54.047Z</v>
+        <v>2026-07-30T14:04:15.551Z</v>
       </c>
     </row>
     <row r="300">
@@ -5493,10 +5493,10 @@
         <v>Passed</v>
       </c>
       <c r="D300">
-        <v>0.16</v>
+        <v>1.23</v>
       </c>
       <c r="E300" t="str">
-        <v>2026-07-30T13:54:55.047Z</v>
+        <v>2026-07-30T14:04:16.551Z</v>
       </c>
     </row>
     <row r="301">
@@ -5510,10 +5510,10 @@
         <v>Passed</v>
       </c>
       <c r="D301">
-        <v>0.31</v>
+        <v>0.16</v>
       </c>
       <c r="E301" t="str">
-        <v>2026-07-30T13:54:56.047Z</v>
+        <v>2026-07-30T14:04:17.551Z</v>
       </c>
     </row>
     <row r="302">
@@ -5527,10 +5527,10 @@
         <v>Passed</v>
       </c>
       <c r="D302">
-        <v>0.32</v>
+        <v>1.56</v>
       </c>
       <c r="E302" t="str">
-        <v>2026-07-30T13:54:57.047Z</v>
+        <v>2026-07-30T14:04:18.551Z</v>
       </c>
     </row>
     <row r="303">
@@ -5544,10 +5544,10 @@
         <v>Passed</v>
       </c>
       <c r="D303">
-        <v>1.88</v>
+        <v>0.01</v>
       </c>
       <c r="E303" t="str">
-        <v>2026-07-30T13:54:58.047Z</v>
+        <v>2026-07-30T14:04:19.551Z</v>
       </c>
     </row>
     <row r="304">
@@ -5561,10 +5561,10 @@
         <v>Passed</v>
       </c>
       <c r="D304">
-        <v>1.53</v>
+        <v>0.21</v>
       </c>
       <c r="E304" t="str">
-        <v>2026-07-30T13:54:59.047Z</v>
+        <v>2026-07-30T14:04:20.551Z</v>
       </c>
     </row>
     <row r="305">
@@ -5578,10 +5578,10 @@
         <v>Passed</v>
       </c>
       <c r="D305">
-        <v>0.89</v>
+        <v>1.42</v>
       </c>
       <c r="E305" t="str">
-        <v>2026-07-30T13:55:00.047Z</v>
+        <v>2026-07-30T14:04:21.551Z</v>
       </c>
     </row>
     <row r="306">
@@ -5595,10 +5595,10 @@
         <v>Passed</v>
       </c>
       <c r="D306">
-        <v>1.37</v>
+        <v>1.76</v>
       </c>
       <c r="E306" t="str">
-        <v>2026-07-30T13:55:01.047Z</v>
+        <v>2026-07-30T14:04:22.551Z</v>
       </c>
     </row>
     <row r="307">
@@ -5612,10 +5612,10 @@
         <v>Passed</v>
       </c>
       <c r="D307">
-        <v>0.92</v>
+        <v>0.07</v>
       </c>
       <c r="E307" t="str">
-        <v>2026-07-30T13:55:02.047Z</v>
+        <v>2026-07-30T14:04:23.551Z</v>
       </c>
     </row>
     <row r="308">
@@ -5626,13 +5626,13 @@
         <v>Verify Security functionality module 307</v>
       </c>
       <c r="C308" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D308">
-        <v>1.75</v>
+        <v>0.28</v>
       </c>
       <c r="E308" t="str">
-        <v>2026-07-30T13:55:03.047Z</v>
+        <v>2026-07-30T14:04:24.551Z</v>
       </c>
     </row>
     <row r="309">
@@ -5646,10 +5646,10 @@
         <v>Passed</v>
       </c>
       <c r="D309">
-        <v>1.51</v>
+        <v>0.12</v>
       </c>
       <c r="E309" t="str">
-        <v>2026-07-30T13:55:04.047Z</v>
+        <v>2026-07-30T14:04:25.551Z</v>
       </c>
     </row>
     <row r="310">
@@ -5663,10 +5663,10 @@
         <v>Passed</v>
       </c>
       <c r="D310">
-        <v>1.93</v>
+        <v>0.6</v>
       </c>
       <c r="E310" t="str">
-        <v>2026-07-30T13:55:05.047Z</v>
+        <v>2026-07-30T14:04:26.551Z</v>
       </c>
     </row>
     <row r="311">
@@ -5680,10 +5680,10 @@
         <v>Passed</v>
       </c>
       <c r="D311">
-        <v>1.25</v>
+        <v>0.45</v>
       </c>
       <c r="E311" t="str">
-        <v>2026-07-30T13:55:06.047Z</v>
+        <v>2026-07-30T14:04:27.551Z</v>
       </c>
     </row>
     <row r="312">
@@ -5697,10 +5697,10 @@
         <v>Passed</v>
       </c>
       <c r="D312">
-        <v>1.22</v>
+        <v>1.71</v>
       </c>
       <c r="E312" t="str">
-        <v>2026-07-30T13:55:07.047Z</v>
+        <v>2026-07-30T14:04:28.551Z</v>
       </c>
     </row>
     <row r="313">
@@ -5714,10 +5714,10 @@
         <v>Passed</v>
       </c>
       <c r="D313">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="E313" t="str">
-        <v>2026-07-30T13:55:08.047Z</v>
+        <v>2026-07-30T14:04:29.551Z</v>
       </c>
     </row>
     <row r="314">
@@ -5731,10 +5731,10 @@
         <v>Passed</v>
       </c>
       <c r="D314">
-        <v>0.96</v>
+        <v>0.88</v>
       </c>
       <c r="E314" t="str">
-        <v>2026-07-30T13:55:09.047Z</v>
+        <v>2026-07-30T14:04:30.551Z</v>
       </c>
     </row>
     <row r="315">
@@ -5748,10 +5748,10 @@
         <v>Passed</v>
       </c>
       <c r="D315">
-        <v>0.49</v>
+        <v>0.83</v>
       </c>
       <c r="E315" t="str">
-        <v>2026-07-30T13:55:10.047Z</v>
+        <v>2026-07-30T14:04:31.551Z</v>
       </c>
     </row>
     <row r="316">
@@ -5765,10 +5765,10 @@
         <v>Passed</v>
       </c>
       <c r="D316">
-        <v>1.44</v>
+        <v>0.37</v>
       </c>
       <c r="E316" t="str">
-        <v>2026-07-30T13:55:11.047Z</v>
+        <v>2026-07-30T14:04:32.551Z</v>
       </c>
     </row>
     <row r="317">
@@ -5782,10 +5782,10 @@
         <v>Passed</v>
       </c>
       <c r="D317">
-        <v>0.1</v>
+        <v>1.16</v>
       </c>
       <c r="E317" t="str">
-        <v>2026-07-30T13:55:12.047Z</v>
+        <v>2026-07-30T14:04:33.551Z</v>
       </c>
     </row>
     <row r="318">
@@ -5799,10 +5799,10 @@
         <v>Passed</v>
       </c>
       <c r="D318">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="E318" t="str">
-        <v>2026-07-30T13:55:13.047Z</v>
+        <v>2026-07-30T14:04:34.551Z</v>
       </c>
     </row>
     <row r="319">
@@ -5816,10 +5816,10 @@
         <v>Passed</v>
       </c>
       <c r="D319">
-        <v>0.33</v>
+        <v>0.73</v>
       </c>
       <c r="E319" t="str">
-        <v>2026-07-30T13:55:14.047Z</v>
+        <v>2026-07-30T14:04:35.551Z</v>
       </c>
     </row>
     <row r="320">
@@ -5833,10 +5833,10 @@
         <v>Passed</v>
       </c>
       <c r="D320">
-        <v>1.36</v>
+        <v>0.67</v>
       </c>
       <c r="E320" t="str">
-        <v>2026-07-30T13:55:15.047Z</v>
+        <v>2026-07-30T14:04:36.551Z</v>
       </c>
     </row>
     <row r="321">
@@ -5850,10 +5850,10 @@
         <v>Passed</v>
       </c>
       <c r="D321">
-        <v>0.16</v>
+        <v>1.06</v>
       </c>
       <c r="E321" t="str">
-        <v>2026-07-30T13:55:16.047Z</v>
+        <v>2026-07-30T14:04:37.551Z</v>
       </c>
     </row>
     <row r="322">
@@ -5867,10 +5867,10 @@
         <v>Passed</v>
       </c>
       <c r="D322">
-        <v>1.97</v>
+        <v>1.05</v>
       </c>
       <c r="E322" t="str">
-        <v>2026-07-30T13:55:17.047Z</v>
+        <v>2026-07-30T14:04:38.551Z</v>
       </c>
     </row>
     <row r="323">
@@ -5884,10 +5884,10 @@
         <v>Passed</v>
       </c>
       <c r="D323">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="E323" t="str">
-        <v>2026-07-30T13:55:18.047Z</v>
+        <v>2026-07-30T14:04:39.551Z</v>
       </c>
     </row>
     <row r="324">
@@ -5901,10 +5901,10 @@
         <v>Passed</v>
       </c>
       <c r="D324">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="E324" t="str">
-        <v>2026-07-30T13:55:19.047Z</v>
+        <v>2026-07-30T14:04:40.551Z</v>
       </c>
     </row>
     <row r="325">
@@ -5918,10 +5918,10 @@
         <v>Passed</v>
       </c>
       <c r="D325">
-        <v>1.6</v>
+        <v>0.95</v>
       </c>
       <c r="E325" t="str">
-        <v>2026-07-30T13:55:20.047Z</v>
+        <v>2026-07-30T14:04:41.551Z</v>
       </c>
     </row>
     <row r="326">
@@ -5935,10 +5935,10 @@
         <v>Passed</v>
       </c>
       <c r="D326">
-        <v>1.2</v>
+        <v>0.19</v>
       </c>
       <c r="E326" t="str">
-        <v>2026-07-30T13:55:21.047Z</v>
+        <v>2026-07-30T14:04:42.551Z</v>
       </c>
     </row>
     <row r="327">
@@ -5952,10 +5952,10 @@
         <v>Passed</v>
       </c>
       <c r="D327">
-        <v>0.6</v>
+        <v>0.88</v>
       </c>
       <c r="E327" t="str">
-        <v>2026-07-30T13:55:22.047Z</v>
+        <v>2026-07-30T14:04:43.551Z</v>
       </c>
     </row>
     <row r="328">
@@ -5969,10 +5969,10 @@
         <v>Passed</v>
       </c>
       <c r="D328">
-        <v>0.25</v>
+        <v>0.41</v>
       </c>
       <c r="E328" t="str">
-        <v>2026-07-30T13:55:23.047Z</v>
+        <v>2026-07-30T14:04:44.551Z</v>
       </c>
     </row>
     <row r="329">
@@ -5986,10 +5986,10 @@
         <v>Passed</v>
       </c>
       <c r="D329">
-        <v>1.91</v>
+        <v>0.43</v>
       </c>
       <c r="E329" t="str">
-        <v>2026-07-30T13:55:24.047Z</v>
+        <v>2026-07-30T14:04:45.551Z</v>
       </c>
     </row>
     <row r="330">
@@ -6003,10 +6003,10 @@
         <v>Passed</v>
       </c>
       <c r="D330">
-        <v>0.28</v>
+        <v>1.06</v>
       </c>
       <c r="E330" t="str">
-        <v>2026-07-30T13:55:25.047Z</v>
+        <v>2026-07-30T14:04:46.551Z</v>
       </c>
     </row>
     <row r="331">
@@ -6020,10 +6020,10 @@
         <v>Passed</v>
       </c>
       <c r="D331">
-        <v>0.23</v>
+        <v>0.15</v>
       </c>
       <c r="E331" t="str">
-        <v>2026-07-30T13:55:26.047Z</v>
+        <v>2026-07-30T14:04:47.551Z</v>
       </c>
     </row>
     <row r="332">
@@ -6037,10 +6037,10 @@
         <v>Passed</v>
       </c>
       <c r="D332">
-        <v>1.66</v>
+        <v>0.75</v>
       </c>
       <c r="E332" t="str">
-        <v>2026-07-30T13:55:27.047Z</v>
+        <v>2026-07-30T14:04:48.551Z</v>
       </c>
     </row>
     <row r="333">
@@ -6054,10 +6054,10 @@
         <v>Passed</v>
       </c>
       <c r="D333">
-        <v>0.97</v>
+        <v>1.46</v>
       </c>
       <c r="E333" t="str">
-        <v>2026-07-30T13:55:28.047Z</v>
+        <v>2026-07-30T14:04:49.551Z</v>
       </c>
     </row>
     <row r="334">
@@ -6071,10 +6071,10 @@
         <v>Passed</v>
       </c>
       <c r="D334">
-        <v>0.33</v>
+        <v>1.65</v>
       </c>
       <c r="E334" t="str">
-        <v>2026-07-30T13:55:29.047Z</v>
+        <v>2026-07-30T14:04:50.551Z</v>
       </c>
     </row>
     <row r="335">
@@ -6088,10 +6088,10 @@
         <v>Passed</v>
       </c>
       <c r="D335">
-        <v>0.99</v>
+        <v>0.53</v>
       </c>
       <c r="E335" t="str">
-        <v>2026-07-30T13:55:30.047Z</v>
+        <v>2026-07-30T14:04:51.551Z</v>
       </c>
     </row>
     <row r="336">
@@ -6105,10 +6105,10 @@
         <v>Passed</v>
       </c>
       <c r="D336">
-        <v>1.04</v>
+        <v>0.16</v>
       </c>
       <c r="E336" t="str">
-        <v>2026-07-30T13:55:31.047Z</v>
+        <v>2026-07-30T14:04:52.551Z</v>
       </c>
     </row>
     <row r="337">
@@ -6122,10 +6122,10 @@
         <v>Passed</v>
       </c>
       <c r="D337">
-        <v>0.37</v>
+        <v>1.67</v>
       </c>
       <c r="E337" t="str">
-        <v>2026-07-30T13:55:32.047Z</v>
+        <v>2026-07-30T14:04:53.551Z</v>
       </c>
     </row>
     <row r="338">
@@ -6139,10 +6139,10 @@
         <v>Passed</v>
       </c>
       <c r="D338">
-        <v>1.22</v>
+        <v>1.56</v>
       </c>
       <c r="E338" t="str">
-        <v>2026-07-30T13:55:33.047Z</v>
+        <v>2026-07-30T14:04:54.551Z</v>
       </c>
     </row>
     <row r="339">
@@ -6156,10 +6156,10 @@
         <v>Passed</v>
       </c>
       <c r="D339">
-        <v>1.55</v>
+        <v>0.5</v>
       </c>
       <c r="E339" t="str">
-        <v>2026-07-30T13:55:34.047Z</v>
+        <v>2026-07-30T14:04:55.551Z</v>
       </c>
     </row>
     <row r="340">
@@ -6173,10 +6173,10 @@
         <v>Passed</v>
       </c>
       <c r="D340">
-        <v>1.43</v>
+        <v>0.17</v>
       </c>
       <c r="E340" t="str">
-        <v>2026-07-30T13:55:35.047Z</v>
+        <v>2026-07-30T14:04:56.551Z</v>
       </c>
     </row>
     <row r="341">
@@ -6190,10 +6190,10 @@
         <v>Passed</v>
       </c>
       <c r="D341">
-        <v>1.75</v>
+        <v>1.31</v>
       </c>
       <c r="E341" t="str">
-        <v>2026-07-30T13:55:36.047Z</v>
+        <v>2026-07-30T14:04:57.551Z</v>
       </c>
     </row>
     <row r="342">
@@ -6207,10 +6207,10 @@
         <v>Passed</v>
       </c>
       <c r="D342">
-        <v>0.66</v>
+        <v>0.77</v>
       </c>
       <c r="E342" t="str">
-        <v>2026-07-30T13:55:37.047Z</v>
+        <v>2026-07-30T14:04:58.551Z</v>
       </c>
     </row>
     <row r="343">
@@ -6224,10 +6224,10 @@
         <v>Passed</v>
       </c>
       <c r="D343">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="E343" t="str">
-        <v>2026-07-30T13:55:38.047Z</v>
+        <v>2026-07-30T14:04:59.551Z</v>
       </c>
     </row>
     <row r="344">
@@ -6241,10 +6241,10 @@
         <v>Passed</v>
       </c>
       <c r="D344">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="E344" t="str">
-        <v>2026-07-30T13:55:39.047Z</v>
+        <v>2026-07-30T14:05:00.551Z</v>
       </c>
     </row>
     <row r="345">
@@ -6258,10 +6258,10 @@
         <v>Passed</v>
       </c>
       <c r="D345">
-        <v>0.97</v>
+        <v>0.67</v>
       </c>
       <c r="E345" t="str">
-        <v>2026-07-30T13:55:40.047Z</v>
+        <v>2026-07-30T14:05:01.551Z</v>
       </c>
     </row>
     <row r="346">
@@ -6275,10 +6275,10 @@
         <v>Passed</v>
       </c>
       <c r="D346">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="E346" t="str">
-        <v>2026-07-30T13:55:41.047Z</v>
+        <v>2026-07-30T14:05:02.551Z</v>
       </c>
     </row>
     <row r="347">
@@ -6292,10 +6292,10 @@
         <v>Passed</v>
       </c>
       <c r="D347">
-        <v>1.33</v>
+        <v>0.77</v>
       </c>
       <c r="E347" t="str">
-        <v>2026-07-30T13:55:42.047Z</v>
+        <v>2026-07-30T14:05:03.551Z</v>
       </c>
     </row>
     <row r="348">
@@ -6309,10 +6309,10 @@
         <v>Passed</v>
       </c>
       <c r="D348">
-        <v>0.6</v>
+        <v>0.17</v>
       </c>
       <c r="E348" t="str">
-        <v>2026-07-30T13:55:43.047Z</v>
+        <v>2026-07-30T14:05:04.551Z</v>
       </c>
     </row>
     <row r="349">
@@ -6326,10 +6326,10 @@
         <v>Passed</v>
       </c>
       <c r="D349">
-        <v>1.46</v>
+        <v>0.91</v>
       </c>
       <c r="E349" t="str">
-        <v>2026-07-30T13:55:44.047Z</v>
+        <v>2026-07-30T14:05:05.551Z</v>
       </c>
     </row>
     <row r="350">
@@ -6343,10 +6343,10 @@
         <v>Passed</v>
       </c>
       <c r="D350">
-        <v>1.17</v>
+        <v>0.5</v>
       </c>
       <c r="E350" t="str">
-        <v>2026-07-30T13:55:45.047Z</v>
+        <v>2026-07-30T14:05:06.551Z</v>
       </c>
     </row>
     <row r="351">
@@ -6360,10 +6360,10 @@
         <v>Passed</v>
       </c>
       <c r="D351">
-        <v>0.17</v>
+        <v>1.4</v>
       </c>
       <c r="E351" t="str">
-        <v>2026-07-30T13:55:46.047Z</v>
+        <v>2026-07-30T14:05:07.551Z</v>
       </c>
     </row>
     <row r="352">
@@ -6374,13 +6374,13 @@
         <v>Verify Security functionality module 351</v>
       </c>
       <c r="C352" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D352">
-        <v>1.26</v>
+        <v>0.87</v>
       </c>
       <c r="E352" t="str">
-        <v>2026-07-30T13:55:47.047Z</v>
+        <v>2026-07-30T14:05:08.551Z</v>
       </c>
     </row>
     <row r="353">
@@ -6394,10 +6394,10 @@
         <v>Passed</v>
       </c>
       <c r="D353">
-        <v>0.64</v>
+        <v>0.37</v>
       </c>
       <c r="E353" t="str">
-        <v>2026-07-30T13:55:48.047Z</v>
+        <v>2026-07-30T14:05:09.551Z</v>
       </c>
     </row>
     <row r="354">
@@ -6411,10 +6411,10 @@
         <v>Passed</v>
       </c>
       <c r="D354">
-        <v>1.71</v>
+        <v>1.23</v>
       </c>
       <c r="E354" t="str">
-        <v>2026-07-30T13:55:49.047Z</v>
+        <v>2026-07-30T14:05:10.551Z</v>
       </c>
     </row>
     <row r="355">
@@ -6428,10 +6428,10 @@
         <v>Passed</v>
       </c>
       <c r="D355">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="E355" t="str">
-        <v>2026-07-30T13:55:50.047Z</v>
+        <v>2026-07-30T14:05:11.551Z</v>
       </c>
     </row>
     <row r="356">
@@ -6445,10 +6445,10 @@
         <v>Passed</v>
       </c>
       <c r="D356">
-        <v>0.83</v>
+        <v>0.31</v>
       </c>
       <c r="E356" t="str">
-        <v>2026-07-30T13:55:51.047Z</v>
+        <v>2026-07-30T14:05:12.551Z</v>
       </c>
     </row>
     <row r="357">
@@ -6462,10 +6462,10 @@
         <v>Passed</v>
       </c>
       <c r="D357">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="E357" t="str">
-        <v>2026-07-30T13:55:52.047Z</v>
+        <v>2026-07-30T14:05:13.551Z</v>
       </c>
     </row>
     <row r="358">
@@ -6479,10 +6479,10 @@
         <v>Passed</v>
       </c>
       <c r="D358">
-        <v>1.28</v>
+        <v>0.42</v>
       </c>
       <c r="E358" t="str">
-        <v>2026-07-30T13:55:53.047Z</v>
+        <v>2026-07-30T14:05:14.551Z</v>
       </c>
     </row>
     <row r="359">
@@ -6496,10 +6496,10 @@
         <v>Passed</v>
       </c>
       <c r="D359">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="E359" t="str">
-        <v>2026-07-30T13:55:54.047Z</v>
+        <v>2026-07-30T14:05:15.551Z</v>
       </c>
     </row>
     <row r="360">
@@ -6513,10 +6513,10 @@
         <v>Passed</v>
       </c>
       <c r="D360">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="E360" t="str">
-        <v>2026-07-30T13:55:55.047Z</v>
+        <v>2026-07-30T14:05:16.551Z</v>
       </c>
     </row>
     <row r="361">
@@ -6530,10 +6530,10 @@
         <v>Passed</v>
       </c>
       <c r="D361">
-        <v>0.65</v>
+        <v>0.48</v>
       </c>
       <c r="E361" t="str">
-        <v>2026-07-30T13:55:56.047Z</v>
+        <v>2026-07-30T14:05:17.551Z</v>
       </c>
     </row>
     <row r="362">
@@ -6547,10 +6547,10 @@
         <v>Passed</v>
       </c>
       <c r="D362">
-        <v>1.68</v>
+        <v>0.58</v>
       </c>
       <c r="E362" t="str">
-        <v>2026-07-30T13:55:57.047Z</v>
+        <v>2026-07-30T14:05:18.551Z</v>
       </c>
     </row>
     <row r="363">
@@ -6564,10 +6564,10 @@
         <v>Passed</v>
       </c>
       <c r="D363">
-        <v>1.01</v>
+        <v>0.71</v>
       </c>
       <c r="E363" t="str">
-        <v>2026-07-30T13:55:58.047Z</v>
+        <v>2026-07-30T14:05:19.551Z</v>
       </c>
     </row>
     <row r="364">
@@ -6581,10 +6581,10 @@
         <v>Passed</v>
       </c>
       <c r="D364">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="E364" t="str">
-        <v>2026-07-30T13:55:59.047Z</v>
+        <v>2026-07-30T14:05:20.551Z</v>
       </c>
     </row>
     <row r="365">
@@ -6598,10 +6598,10 @@
         <v>Passed</v>
       </c>
       <c r="D365">
-        <v>0.01</v>
+        <v>0.8</v>
       </c>
       <c r="E365" t="str">
-        <v>2026-07-30T13:56:00.047Z</v>
+        <v>2026-07-30T14:05:21.551Z</v>
       </c>
     </row>
     <row r="366">
@@ -6615,10 +6615,10 @@
         <v>Passed</v>
       </c>
       <c r="D366">
-        <v>0.38</v>
+        <v>0.55</v>
       </c>
       <c r="E366" t="str">
-        <v>2026-07-30T13:56:01.047Z</v>
+        <v>2026-07-30T14:05:22.551Z</v>
       </c>
     </row>
     <row r="367">
@@ -6632,10 +6632,10 @@
         <v>Passed</v>
       </c>
       <c r="D367">
-        <v>0.58</v>
+        <v>1.29</v>
       </c>
       <c r="E367" t="str">
-        <v>2026-07-30T13:56:02.047Z</v>
+        <v>2026-07-30T14:05:23.551Z</v>
       </c>
     </row>
     <row r="368">
@@ -6649,10 +6649,10 @@
         <v>Passed</v>
       </c>
       <c r="D368">
-        <v>0.45</v>
+        <v>1.27</v>
       </c>
       <c r="E368" t="str">
-        <v>2026-07-30T13:56:03.047Z</v>
+        <v>2026-07-30T14:05:24.551Z</v>
       </c>
     </row>
     <row r="369">
@@ -6666,10 +6666,10 @@
         <v>Passed</v>
       </c>
       <c r="D369">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="E369" t="str">
-        <v>2026-07-30T13:56:04.047Z</v>
+        <v>2026-07-30T14:05:25.551Z</v>
       </c>
     </row>
     <row r="370">
@@ -6683,10 +6683,10 @@
         <v>Passed</v>
       </c>
       <c r="D370">
-        <v>0.2</v>
+        <v>0.83</v>
       </c>
       <c r="E370" t="str">
-        <v>2026-07-30T13:56:05.047Z</v>
+        <v>2026-07-30T14:05:26.551Z</v>
       </c>
     </row>
     <row r="371">
@@ -6700,10 +6700,10 @@
         <v>Passed</v>
       </c>
       <c r="D371">
-        <v>1.72</v>
+        <v>0.89</v>
       </c>
       <c r="E371" t="str">
-        <v>2026-07-30T13:56:06.047Z</v>
+        <v>2026-07-30T14:05:27.551Z</v>
       </c>
     </row>
     <row r="372">
@@ -6717,10 +6717,10 @@
         <v>Passed</v>
       </c>
       <c r="D372">
-        <v>0.44</v>
+        <v>1.29</v>
       </c>
       <c r="E372" t="str">
-        <v>2026-07-30T13:56:07.047Z</v>
+        <v>2026-07-30T14:05:28.551Z</v>
       </c>
     </row>
     <row r="373">
@@ -6734,10 +6734,10 @@
         <v>Passed</v>
       </c>
       <c r="D373">
-        <v>0.23</v>
+        <v>1.47</v>
       </c>
       <c r="E373" t="str">
-        <v>2026-07-30T13:56:08.047Z</v>
+        <v>2026-07-30T14:05:29.551Z</v>
       </c>
     </row>
     <row r="374">
@@ -6751,10 +6751,10 @@
         <v>Passed</v>
       </c>
       <c r="D374">
-        <v>1.92</v>
+        <v>0.26</v>
       </c>
       <c r="E374" t="str">
-        <v>2026-07-30T13:56:09.047Z</v>
+        <v>2026-07-30T14:05:30.551Z</v>
       </c>
     </row>
     <row r="375">
@@ -6768,10 +6768,10 @@
         <v>Passed</v>
       </c>
       <c r="D375">
-        <v>0.48</v>
+        <v>1.81</v>
       </c>
       <c r="E375" t="str">
-        <v>2026-07-30T13:56:10.047Z</v>
+        <v>2026-07-30T14:05:31.551Z</v>
       </c>
     </row>
     <row r="376">
@@ -6785,10 +6785,10 @@
         <v>Passed</v>
       </c>
       <c r="D376">
-        <v>0.14</v>
+        <v>1.02</v>
       </c>
       <c r="E376" t="str">
-        <v>2026-07-30T13:56:11.047Z</v>
+        <v>2026-07-30T14:05:32.551Z</v>
       </c>
     </row>
     <row r="377">
@@ -6802,10 +6802,10 @@
         <v>Passed</v>
       </c>
       <c r="D377">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="E377" t="str">
-        <v>2026-07-30T13:56:12.047Z</v>
+        <v>2026-07-30T14:05:33.551Z</v>
       </c>
     </row>
     <row r="378">
@@ -6819,10 +6819,10 @@
         <v>Passed</v>
       </c>
       <c r="D378">
-        <v>0.62</v>
+        <v>0.21</v>
       </c>
       <c r="E378" t="str">
-        <v>2026-07-30T13:56:13.047Z</v>
+        <v>2026-07-30T14:05:34.551Z</v>
       </c>
     </row>
     <row r="379">
@@ -6836,10 +6836,10 @@
         <v>Passed</v>
       </c>
       <c r="D379">
-        <v>0.6</v>
+        <v>0.33</v>
       </c>
       <c r="E379" t="str">
-        <v>2026-07-30T13:56:14.047Z</v>
+        <v>2026-07-30T14:05:35.551Z</v>
       </c>
     </row>
     <row r="380">
@@ -6853,10 +6853,10 @@
         <v>Passed</v>
       </c>
       <c r="D380">
-        <v>0.95</v>
+        <v>0.12</v>
       </c>
       <c r="E380" t="str">
-        <v>2026-07-30T13:56:15.047Z</v>
+        <v>2026-07-30T14:05:36.551Z</v>
       </c>
     </row>
     <row r="381">
@@ -6867,13 +6867,13 @@
         <v>Verify Security functionality module 380</v>
       </c>
       <c r="C381" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D381">
-        <v>1.71</v>
+        <v>0.45</v>
       </c>
       <c r="E381" t="str">
-        <v>2026-07-30T13:56:16.047Z</v>
+        <v>2026-07-30T14:05:37.551Z</v>
       </c>
     </row>
     <row r="382">
@@ -6887,10 +6887,10 @@
         <v>Passed</v>
       </c>
       <c r="D382">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="E382" t="str">
-        <v>2026-07-30T13:56:17.047Z</v>
+        <v>2026-07-30T14:05:38.551Z</v>
       </c>
     </row>
     <row r="383">
@@ -6904,10 +6904,10 @@
         <v>Passed</v>
       </c>
       <c r="D383">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="E383" t="str">
-        <v>2026-07-30T13:56:18.047Z</v>
+        <v>2026-07-30T14:05:39.551Z</v>
       </c>
     </row>
     <row r="384">
@@ -6921,10 +6921,10 @@
         <v>Passed</v>
       </c>
       <c r="D384">
-        <v>0.03</v>
+        <v>0.17</v>
       </c>
       <c r="E384" t="str">
-        <v>2026-07-30T13:56:19.047Z</v>
+        <v>2026-07-30T14:05:40.551Z</v>
       </c>
     </row>
     <row r="385">
@@ -6938,10 +6938,10 @@
         <v>Passed</v>
       </c>
       <c r="D385">
-        <v>1.05</v>
+        <v>0.22</v>
       </c>
       <c r="E385" t="str">
-        <v>2026-07-30T13:56:20.047Z</v>
+        <v>2026-07-30T14:05:41.551Z</v>
       </c>
     </row>
     <row r="386">
@@ -6955,10 +6955,10 @@
         <v>Passed</v>
       </c>
       <c r="D386">
-        <v>1.21</v>
+        <v>0.01</v>
       </c>
       <c r="E386" t="str">
-        <v>2026-07-30T13:56:21.047Z</v>
+        <v>2026-07-30T14:05:42.551Z</v>
       </c>
     </row>
     <row r="387">
@@ -6972,10 +6972,10 @@
         <v>Passed</v>
       </c>
       <c r="D387">
-        <v>1.04</v>
+        <v>1.61</v>
       </c>
       <c r="E387" t="str">
-        <v>2026-07-30T13:56:22.047Z</v>
+        <v>2026-07-30T14:05:43.551Z</v>
       </c>
     </row>
     <row r="388">
@@ -6989,10 +6989,10 @@
         <v>Passed</v>
       </c>
       <c r="D388">
-        <v>0.1</v>
+        <v>0.53</v>
       </c>
       <c r="E388" t="str">
-        <v>2026-07-30T13:56:23.047Z</v>
+        <v>2026-07-30T14:05:44.551Z</v>
       </c>
     </row>
     <row r="389">
@@ -7006,10 +7006,10 @@
         <v>Passed</v>
       </c>
       <c r="D389">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="E389" t="str">
-        <v>2026-07-30T13:56:24.047Z</v>
+        <v>2026-07-30T14:05:45.551Z</v>
       </c>
     </row>
     <row r="390">
@@ -7023,10 +7023,10 @@
         <v>Passed</v>
       </c>
       <c r="D390">
-        <v>0.52</v>
+        <v>1.55</v>
       </c>
       <c r="E390" t="str">
-        <v>2026-07-30T13:56:25.047Z</v>
+        <v>2026-07-30T14:05:46.551Z</v>
       </c>
     </row>
     <row r="391">
@@ -7040,10 +7040,10 @@
         <v>Passed</v>
       </c>
       <c r="D391">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="E391" t="str">
-        <v>2026-07-30T13:56:26.047Z</v>
+        <v>2026-07-30T14:05:47.551Z</v>
       </c>
     </row>
     <row r="392">
@@ -7057,10 +7057,10 @@
         <v>Passed</v>
       </c>
       <c r="D392">
-        <v>0.91</v>
+        <v>1.69</v>
       </c>
       <c r="E392" t="str">
-        <v>2026-07-30T13:56:27.047Z</v>
+        <v>2026-07-30T14:05:48.551Z</v>
       </c>
     </row>
     <row r="393">
@@ -7074,10 +7074,10 @@
         <v>Passed</v>
       </c>
       <c r="D393">
-        <v>0.88</v>
+        <v>0.44</v>
       </c>
       <c r="E393" t="str">
-        <v>2026-07-30T13:56:28.047Z</v>
+        <v>2026-07-30T14:05:49.551Z</v>
       </c>
     </row>
     <row r="394">
@@ -7091,10 +7091,10 @@
         <v>Passed</v>
       </c>
       <c r="D394">
-        <v>1.8</v>
+        <v>1.19</v>
       </c>
       <c r="E394" t="str">
-        <v>2026-07-30T13:56:29.047Z</v>
+        <v>2026-07-30T14:05:50.551Z</v>
       </c>
     </row>
     <row r="395">
@@ -7108,10 +7108,10 @@
         <v>Passed</v>
       </c>
       <c r="D395">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="E395" t="str">
-        <v>2026-07-30T13:56:30.047Z</v>
+        <v>2026-07-30T14:05:51.551Z</v>
       </c>
     </row>
     <row r="396">
@@ -7125,10 +7125,10 @@
         <v>Passed</v>
       </c>
       <c r="D396">
-        <v>0.35</v>
+        <v>1.54</v>
       </c>
       <c r="E396" t="str">
-        <v>2026-07-30T13:56:31.047Z</v>
+        <v>2026-07-30T14:05:52.551Z</v>
       </c>
     </row>
     <row r="397">
@@ -7142,10 +7142,10 @@
         <v>Passed</v>
       </c>
       <c r="D397">
-        <v>1.49</v>
+        <v>0.46</v>
       </c>
       <c r="E397" t="str">
-        <v>2026-07-30T13:56:32.047Z</v>
+        <v>2026-07-30T14:05:53.551Z</v>
       </c>
     </row>
     <row r="398">
@@ -7159,10 +7159,10 @@
         <v>Passed</v>
       </c>
       <c r="D398">
-        <v>1.12</v>
+        <v>1.41</v>
       </c>
       <c r="E398" t="str">
-        <v>2026-07-30T13:56:33.047Z</v>
+        <v>2026-07-30T14:05:54.551Z</v>
       </c>
     </row>
     <row r="399">
@@ -7176,10 +7176,10 @@
         <v>Passed</v>
       </c>
       <c r="D399">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="E399" t="str">
-        <v>2026-07-30T13:56:34.047Z</v>
+        <v>2026-07-30T14:05:55.551Z</v>
       </c>
     </row>
     <row r="400">
@@ -7193,10 +7193,10 @@
         <v>Passed</v>
       </c>
       <c r="D400">
-        <v>0.25</v>
+        <v>1.04</v>
       </c>
       <c r="E400" t="str">
-        <v>2026-07-30T13:56:35.047Z</v>
+        <v>2026-07-30T14:05:56.551Z</v>
       </c>
     </row>
     <row r="401">
@@ -7210,10 +7210,10 @@
         <v>Passed</v>
       </c>
       <c r="D401">
-        <v>0.28</v>
+        <v>1.62</v>
       </c>
       <c r="E401" t="str">
-        <v>2026-07-30T13:56:36.047Z</v>
+        <v>2026-07-30T14:05:57.551Z</v>
       </c>
     </row>
     <row r="402">
@@ -7227,10 +7227,10 @@
         <v>Passed</v>
       </c>
       <c r="D402">
-        <v>0.22</v>
+        <v>1.33</v>
       </c>
       <c r="E402" t="str">
-        <v>2026-07-30T13:56:37.047Z</v>
+        <v>2026-07-30T14:05:58.551Z</v>
       </c>
     </row>
     <row r="403">
@@ -7244,10 +7244,10 @@
         <v>Passed</v>
       </c>
       <c r="D403">
-        <v>1.57</v>
+        <v>0.07</v>
       </c>
       <c r="E403" t="str">
-        <v>2026-07-30T13:56:38.047Z</v>
+        <v>2026-07-30T14:05:59.551Z</v>
       </c>
     </row>
     <row r="404">
@@ -7261,10 +7261,10 @@
         <v>Passed</v>
       </c>
       <c r="D404">
-        <v>0.81</v>
+        <v>1.59</v>
       </c>
       <c r="E404" t="str">
-        <v>2026-07-30T13:56:39.047Z</v>
+        <v>2026-07-30T14:06:00.551Z</v>
       </c>
     </row>
     <row r="405">
@@ -7278,10 +7278,10 @@
         <v>Passed</v>
       </c>
       <c r="D405">
-        <v>1.4</v>
+        <v>0.95</v>
       </c>
       <c r="E405" t="str">
-        <v>2026-07-30T13:56:40.047Z</v>
+        <v>2026-07-30T14:06:01.551Z</v>
       </c>
     </row>
     <row r="406">
@@ -7295,10 +7295,10 @@
         <v>Passed</v>
       </c>
       <c r="D406">
-        <v>0.29</v>
+        <v>1.62</v>
       </c>
       <c r="E406" t="str">
-        <v>2026-07-30T13:56:41.047Z</v>
+        <v>2026-07-30T14:06:02.551Z</v>
       </c>
     </row>
     <row r="407">
@@ -7312,10 +7312,10 @@
         <v>Passed</v>
       </c>
       <c r="D407">
-        <v>0.27</v>
+        <v>1.95</v>
       </c>
       <c r="E407" t="str">
-        <v>2026-07-30T13:56:42.047Z</v>
+        <v>2026-07-30T14:06:03.551Z</v>
       </c>
     </row>
     <row r="408">
@@ -7329,10 +7329,10 @@
         <v>Passed</v>
       </c>
       <c r="D408">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="E408" t="str">
-        <v>2026-07-30T13:56:43.047Z</v>
+        <v>2026-07-30T14:06:04.551Z</v>
       </c>
     </row>
     <row r="409">
@@ -7346,10 +7346,10 @@
         <v>Passed</v>
       </c>
       <c r="D409">
-        <v>1.3</v>
+        <v>1.98</v>
       </c>
       <c r="E409" t="str">
-        <v>2026-07-30T13:56:44.047Z</v>
+        <v>2026-07-30T14:06:05.551Z</v>
       </c>
     </row>
     <row r="410">
@@ -7363,10 +7363,10 @@
         <v>Passed</v>
       </c>
       <c r="D410">
-        <v>1.44</v>
+        <v>0.08</v>
       </c>
       <c r="E410" t="str">
-        <v>2026-07-30T13:56:45.047Z</v>
+        <v>2026-07-30T14:06:06.551Z</v>
       </c>
     </row>
     <row r="411">
@@ -7380,10 +7380,10 @@
         <v>Passed</v>
       </c>
       <c r="D411">
-        <v>0.23</v>
+        <v>1.29</v>
       </c>
       <c r="E411" t="str">
-        <v>2026-07-30T13:56:46.047Z</v>
+        <v>2026-07-30T14:06:07.551Z</v>
       </c>
     </row>
     <row r="412">
@@ -7397,10 +7397,10 @@
         <v>Passed</v>
       </c>
       <c r="D412">
-        <v>0.57</v>
+        <v>1.21</v>
       </c>
       <c r="E412" t="str">
-        <v>2026-07-30T13:56:47.047Z</v>
+        <v>2026-07-30T14:06:08.551Z</v>
       </c>
     </row>
     <row r="413">
@@ -7414,10 +7414,10 @@
         <v>Passed</v>
       </c>
       <c r="D413">
-        <v>0.38</v>
+        <v>1.46</v>
       </c>
       <c r="E413" t="str">
-        <v>2026-07-30T13:56:48.047Z</v>
+        <v>2026-07-30T14:06:09.551Z</v>
       </c>
     </row>
     <row r="414">
@@ -7431,10 +7431,10 @@
         <v>Passed</v>
       </c>
       <c r="D414">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="E414" t="str">
-        <v>2026-07-30T13:56:49.047Z</v>
+        <v>2026-07-30T14:06:10.551Z</v>
       </c>
     </row>
     <row r="415">
@@ -7445,13 +7445,13 @@
         <v>Verify Security functionality module 414</v>
       </c>
       <c r="C415" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D415">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="E415" t="str">
-        <v>2026-07-30T13:56:50.047Z</v>
+        <v>2026-07-30T14:06:11.551Z</v>
       </c>
     </row>
     <row r="416">
@@ -7465,10 +7465,10 @@
         <v>Passed</v>
       </c>
       <c r="D416">
-        <v>0.22</v>
+        <v>0.93</v>
       </c>
       <c r="E416" t="str">
-        <v>2026-07-30T13:56:51.047Z</v>
+        <v>2026-07-30T14:06:12.551Z</v>
       </c>
     </row>
     <row r="417">
@@ -7482,10 +7482,10 @@
         <v>Passed</v>
       </c>
       <c r="D417">
-        <v>0.49</v>
+        <v>1.28</v>
       </c>
       <c r="E417" t="str">
-        <v>2026-07-30T13:56:52.047Z</v>
+        <v>2026-07-30T14:06:13.551Z</v>
       </c>
     </row>
     <row r="418">
@@ -7499,10 +7499,10 @@
         <v>Passed</v>
       </c>
       <c r="D418">
-        <v>1.16</v>
+        <v>0.58</v>
       </c>
       <c r="E418" t="str">
-        <v>2026-07-30T13:56:53.047Z</v>
+        <v>2026-07-30T14:06:14.551Z</v>
       </c>
     </row>
     <row r="419">
@@ -7516,10 +7516,10 @@
         <v>Passed</v>
       </c>
       <c r="D419">
-        <v>0.62</v>
+        <v>0.51</v>
       </c>
       <c r="E419" t="str">
-        <v>2026-07-30T13:56:54.047Z</v>
+        <v>2026-07-30T14:06:15.551Z</v>
       </c>
     </row>
     <row r="420">
@@ -7533,10 +7533,10 @@
         <v>Passed</v>
       </c>
       <c r="D420">
-        <v>1.15</v>
+        <v>0.28</v>
       </c>
       <c r="E420" t="str">
-        <v>2026-07-30T13:56:55.047Z</v>
+        <v>2026-07-30T14:06:16.551Z</v>
       </c>
     </row>
     <row r="421">
@@ -7550,10 +7550,10 @@
         <v>Passed</v>
       </c>
       <c r="D421">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="E421" t="str">
-        <v>2026-07-30T13:56:56.047Z</v>
+        <v>2026-07-30T14:06:17.551Z</v>
       </c>
     </row>
     <row r="422">
@@ -7567,10 +7567,10 @@
         <v>Passed</v>
       </c>
       <c r="D422">
-        <v>0.65</v>
+        <v>1.51</v>
       </c>
       <c r="E422" t="str">
-        <v>2026-07-30T13:56:57.047Z</v>
+        <v>2026-07-30T14:06:18.551Z</v>
       </c>
     </row>
     <row r="423">
@@ -7584,10 +7584,10 @@
         <v>Passed</v>
       </c>
       <c r="D423">
-        <v>0.21</v>
+        <v>1.27</v>
       </c>
       <c r="E423" t="str">
-        <v>2026-07-30T13:56:58.047Z</v>
+        <v>2026-07-30T14:06:19.551Z</v>
       </c>
     </row>
     <row r="424">
@@ -7601,10 +7601,10 @@
         <v>Passed</v>
       </c>
       <c r="D424">
-        <v>1.61</v>
+        <v>0.37</v>
       </c>
       <c r="E424" t="str">
-        <v>2026-07-30T13:56:59.047Z</v>
+        <v>2026-07-30T14:06:20.551Z</v>
       </c>
     </row>
     <row r="425">
@@ -7618,10 +7618,10 @@
         <v>Passed</v>
       </c>
       <c r="D425">
-        <v>1.17</v>
+        <v>1.91</v>
       </c>
       <c r="E425" t="str">
-        <v>2026-07-30T13:57:00.047Z</v>
+        <v>2026-07-30T14:06:21.551Z</v>
       </c>
     </row>
     <row r="426">
@@ -7635,10 +7635,10 @@
         <v>Passed</v>
       </c>
       <c r="D426">
-        <v>0.28</v>
+        <v>1.03</v>
       </c>
       <c r="E426" t="str">
-        <v>2026-07-30T13:57:01.047Z</v>
+        <v>2026-07-30T14:06:22.551Z</v>
       </c>
     </row>
     <row r="427">
@@ -7652,10 +7652,10 @@
         <v>Passed</v>
       </c>
       <c r="D427">
-        <v>1.57</v>
+        <v>0.14</v>
       </c>
       <c r="E427" t="str">
-        <v>2026-07-30T13:57:02.047Z</v>
+        <v>2026-07-30T14:06:23.551Z</v>
       </c>
     </row>
     <row r="428">
@@ -7666,13 +7666,13 @@
         <v>Verify Security functionality module 427</v>
       </c>
       <c r="C428" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D428">
-        <v>1.93</v>
+        <v>0.48</v>
       </c>
       <c r="E428" t="str">
-        <v>2026-07-30T13:57:03.047Z</v>
+        <v>2026-07-30T14:06:24.551Z</v>
       </c>
     </row>
     <row r="429">
@@ -7686,10 +7686,10 @@
         <v>Passed</v>
       </c>
       <c r="D429">
-        <v>0.39</v>
+        <v>1.15</v>
       </c>
       <c r="E429" t="str">
-        <v>2026-07-30T13:57:04.047Z</v>
+        <v>2026-07-30T14:06:25.551Z</v>
       </c>
     </row>
     <row r="430">
@@ -7703,10 +7703,10 @@
         <v>Passed</v>
       </c>
       <c r="D430">
-        <v>0.99</v>
+        <v>0.15</v>
       </c>
       <c r="E430" t="str">
-        <v>2026-07-30T13:57:05.047Z</v>
+        <v>2026-07-30T14:06:26.551Z</v>
       </c>
     </row>
     <row r="431">
@@ -7720,10 +7720,10 @@
         <v>Passed</v>
       </c>
       <c r="D431">
-        <v>0.18</v>
+        <v>1.66</v>
       </c>
       <c r="E431" t="str">
-        <v>2026-07-30T13:57:06.047Z</v>
+        <v>2026-07-30T14:06:27.551Z</v>
       </c>
     </row>
     <row r="432">
@@ -7737,10 +7737,10 @@
         <v>Passed</v>
       </c>
       <c r="D432">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="E432" t="str">
-        <v>2026-07-30T13:57:07.047Z</v>
+        <v>2026-07-30T14:06:28.551Z</v>
       </c>
     </row>
     <row r="433">
@@ -7754,10 +7754,10 @@
         <v>Passed</v>
       </c>
       <c r="D433">
-        <v>0.01</v>
+        <v>1.89</v>
       </c>
       <c r="E433" t="str">
-        <v>2026-07-30T13:57:08.047Z</v>
+        <v>2026-07-30T14:06:29.551Z</v>
       </c>
     </row>
     <row r="434">
@@ -7771,10 +7771,10 @@
         <v>Passed</v>
       </c>
       <c r="D434">
-        <v>0.02</v>
+        <v>0.6</v>
       </c>
       <c r="E434" t="str">
-        <v>2026-07-30T13:57:09.047Z</v>
+        <v>2026-07-30T14:06:30.551Z</v>
       </c>
     </row>
     <row r="435">
@@ -7788,10 +7788,10 @@
         <v>Passed</v>
       </c>
       <c r="D435">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="E435" t="str">
-        <v>2026-07-30T13:57:10.047Z</v>
+        <v>2026-07-30T14:06:31.551Z</v>
       </c>
     </row>
     <row r="436">
@@ -7805,10 +7805,10 @@
         <v>Passed</v>
       </c>
       <c r="D436">
-        <v>1.15</v>
+        <v>0.05</v>
       </c>
       <c r="E436" t="str">
-        <v>2026-07-30T13:57:11.047Z</v>
+        <v>2026-07-30T14:06:32.551Z</v>
       </c>
     </row>
     <row r="437">
@@ -7822,10 +7822,10 @@
         <v>Passed</v>
       </c>
       <c r="D437">
-        <v>0.64</v>
+        <v>1.53</v>
       </c>
       <c r="E437" t="str">
-        <v>2026-07-30T13:57:12.047Z</v>
+        <v>2026-07-30T14:06:33.551Z</v>
       </c>
     </row>
     <row r="438">
@@ -7839,10 +7839,10 @@
         <v>Passed</v>
       </c>
       <c r="D438">
-        <v>1.08</v>
+        <v>0.87</v>
       </c>
       <c r="E438" t="str">
-        <v>2026-07-30T13:57:13.047Z</v>
+        <v>2026-07-30T14:06:34.551Z</v>
       </c>
     </row>
     <row r="439">
@@ -7856,10 +7856,10 @@
         <v>Passed</v>
       </c>
       <c r="D439">
-        <v>0.46</v>
+        <v>1.94</v>
       </c>
       <c r="E439" t="str">
-        <v>2026-07-30T13:57:14.047Z</v>
+        <v>2026-07-30T14:06:35.551Z</v>
       </c>
     </row>
     <row r="440">
@@ -7873,10 +7873,10 @@
         <v>Passed</v>
       </c>
       <c r="D440">
-        <v>0.39</v>
+        <v>0.96</v>
       </c>
       <c r="E440" t="str">
-        <v>2026-07-30T13:57:15.047Z</v>
+        <v>2026-07-30T14:06:36.551Z</v>
       </c>
     </row>
     <row r="441">
@@ -7890,10 +7890,10 @@
         <v>Passed</v>
       </c>
       <c r="D441">
-        <v>0.64</v>
+        <v>0.48</v>
       </c>
       <c r="E441" t="str">
-        <v>2026-07-30T13:57:16.047Z</v>
+        <v>2026-07-30T14:06:37.551Z</v>
       </c>
     </row>
     <row r="442">
@@ -7907,10 +7907,10 @@
         <v>Passed</v>
       </c>
       <c r="D442">
-        <v>1.21</v>
+        <v>0.05</v>
       </c>
       <c r="E442" t="str">
-        <v>2026-07-30T13:57:17.047Z</v>
+        <v>2026-07-30T14:06:38.551Z</v>
       </c>
     </row>
     <row r="443">
@@ -7924,10 +7924,10 @@
         <v>Passed</v>
       </c>
       <c r="D443">
-        <v>1.7</v>
+        <v>0.34</v>
       </c>
       <c r="E443" t="str">
-        <v>2026-07-30T13:57:18.047Z</v>
+        <v>2026-07-30T14:06:39.551Z</v>
       </c>
     </row>
     <row r="444">
@@ -7941,10 +7941,10 @@
         <v>Passed</v>
       </c>
       <c r="D444">
-        <v>1.58</v>
+        <v>0.54</v>
       </c>
       <c r="E444" t="str">
-        <v>2026-07-30T13:57:19.047Z</v>
+        <v>2026-07-30T14:06:40.551Z</v>
       </c>
     </row>
     <row r="445">
@@ -7958,10 +7958,10 @@
         <v>Passed</v>
       </c>
       <c r="D445">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="E445" t="str">
-        <v>2026-07-30T13:57:20.047Z</v>
+        <v>2026-07-30T14:06:41.551Z</v>
       </c>
     </row>
     <row r="446">
@@ -7975,10 +7975,10 @@
         <v>Passed</v>
       </c>
       <c r="D446">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="E446" t="str">
-        <v>2026-07-30T13:57:21.047Z</v>
+        <v>2026-07-30T14:06:42.551Z</v>
       </c>
     </row>
     <row r="447">
@@ -7992,10 +7992,10 @@
         <v>Passed</v>
       </c>
       <c r="D447">
-        <v>1.32</v>
+        <v>0.4</v>
       </c>
       <c r="E447" t="str">
-        <v>2026-07-30T13:57:22.047Z</v>
+        <v>2026-07-30T14:06:43.551Z</v>
       </c>
     </row>
     <row r="448">
@@ -8009,10 +8009,10 @@
         <v>Passed</v>
       </c>
       <c r="D448">
-        <v>0.17</v>
+        <v>1.25</v>
       </c>
       <c r="E448" t="str">
-        <v>2026-07-30T13:57:23.047Z</v>
+        <v>2026-07-30T14:06:44.551Z</v>
       </c>
     </row>
     <row r="449">
@@ -8026,10 +8026,10 @@
         <v>Passed</v>
       </c>
       <c r="D449">
-        <v>1.67</v>
+        <v>0.13</v>
       </c>
       <c r="E449" t="str">
-        <v>2026-07-30T13:57:24.047Z</v>
+        <v>2026-07-30T14:06:45.551Z</v>
       </c>
     </row>
     <row r="450">
@@ -8043,10 +8043,10 @@
         <v>Passed</v>
       </c>
       <c r="D450">
-        <v>0.23</v>
+        <v>1.5</v>
       </c>
       <c r="E450" t="str">
-        <v>2026-07-30T13:57:25.047Z</v>
+        <v>2026-07-30T14:06:46.551Z</v>
       </c>
     </row>
     <row r="451">
@@ -8060,10 +8060,10 @@
         <v>Passed</v>
       </c>
       <c r="D451">
-        <v>1.79</v>
+        <v>0.89</v>
       </c>
       <c r="E451" t="str">
-        <v>2026-07-30T13:57:26.047Z</v>
+        <v>2026-07-30T14:06:47.551Z</v>
       </c>
     </row>
     <row r="452">
@@ -8077,10 +8077,10 @@
         <v>Passed</v>
       </c>
       <c r="D452">
-        <v>0.35</v>
+        <v>0.17</v>
       </c>
       <c r="E452" t="str">
-        <v>2026-07-30T13:57:27.047Z</v>
+        <v>2026-07-30T14:06:48.551Z</v>
       </c>
     </row>
     <row r="453">
@@ -8094,10 +8094,10 @@
         <v>Passed</v>
       </c>
       <c r="D453">
-        <v>0.84</v>
+        <v>1.4</v>
       </c>
       <c r="E453" t="str">
-        <v>2026-07-30T13:57:28.047Z</v>
+        <v>2026-07-30T14:06:49.551Z</v>
       </c>
     </row>
     <row r="454">
@@ -8111,10 +8111,10 @@
         <v>Passed</v>
       </c>
       <c r="D454">
-        <v>1.75</v>
+        <v>0.59</v>
       </c>
       <c r="E454" t="str">
-        <v>2026-07-30T13:57:29.047Z</v>
+        <v>2026-07-30T14:06:50.551Z</v>
       </c>
     </row>
     <row r="455">
@@ -8128,10 +8128,10 @@
         <v>Passed</v>
       </c>
       <c r="D455">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="E455" t="str">
-        <v>2026-07-30T13:57:30.047Z</v>
+        <v>2026-07-30T14:06:51.551Z</v>
       </c>
     </row>
     <row r="456">
@@ -8145,10 +8145,10 @@
         <v>Passed</v>
       </c>
       <c r="D456">
-        <v>0.6</v>
+        <v>0.21</v>
       </c>
       <c r="E456" t="str">
-        <v>2026-07-30T13:57:31.047Z</v>
+        <v>2026-07-30T14:06:52.551Z</v>
       </c>
     </row>
     <row r="457">
@@ -8162,10 +8162,10 @@
         <v>Passed</v>
       </c>
       <c r="D457">
-        <v>1.38</v>
+        <v>1.02</v>
       </c>
       <c r="E457" t="str">
-        <v>2026-07-30T13:57:32.047Z</v>
+        <v>2026-07-30T14:06:53.551Z</v>
       </c>
     </row>
     <row r="458">
@@ -8179,10 +8179,10 @@
         <v>Passed</v>
       </c>
       <c r="D458">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="E458" t="str">
-        <v>2026-07-30T13:57:33.047Z</v>
+        <v>2026-07-30T14:06:54.551Z</v>
       </c>
     </row>
     <row r="459">
@@ -8196,10 +8196,10 @@
         <v>Passed</v>
       </c>
       <c r="D459">
-        <v>0.8</v>
+        <v>0.21</v>
       </c>
       <c r="E459" t="str">
-        <v>2026-07-30T13:57:34.047Z</v>
+        <v>2026-07-30T14:06:55.551Z</v>
       </c>
     </row>
     <row r="460">
@@ -8213,15 +8213,355 @@
         <v>Passed</v>
       </c>
       <c r="D460">
+        <v>1.31</v>
+      </c>
+      <c r="E460" t="str">
+        <v>2026-07-30T14:06:56.551Z</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="str">
+        <v>Security-TC-0460</v>
+      </c>
+      <c r="B461" t="str">
+        <v>Verify Security functionality module 460</v>
+      </c>
+      <c r="C461" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D461">
+        <v>1.64</v>
+      </c>
+      <c r="E461" t="str">
+        <v>2026-07-30T14:06:57.551Z</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="str">
+        <v>Security-TC-0461</v>
+      </c>
+      <c r="B462" t="str">
+        <v>Verify Security functionality module 461</v>
+      </c>
+      <c r="C462" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D462">
+        <v>0.04</v>
+      </c>
+      <c r="E462" t="str">
+        <v>2026-07-30T14:06:58.551Z</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="str">
+        <v>Security-TC-0462</v>
+      </c>
+      <c r="B463" t="str">
+        <v>Verify Security functionality module 462</v>
+      </c>
+      <c r="C463" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D463">
+        <v>1.75</v>
+      </c>
+      <c r="E463" t="str">
+        <v>2026-07-30T14:06:59.551Z</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="str">
+        <v>Security-TC-0463</v>
+      </c>
+      <c r="B464" t="str">
+        <v>Verify Security functionality module 463</v>
+      </c>
+      <c r="C464" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D464">
+        <v>0.42</v>
+      </c>
+      <c r="E464" t="str">
+        <v>2026-07-30T14:07:00.551Z</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="str">
+        <v>Security-TC-0464</v>
+      </c>
+      <c r="B465" t="str">
+        <v>Verify Security functionality module 464</v>
+      </c>
+      <c r="C465" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D465">
         <v>1.91</v>
       </c>
-      <c r="E460" t="str">
-        <v>2026-07-30T13:57:35.047Z</v>
+      <c r="E465" t="str">
+        <v>2026-07-30T14:07:01.551Z</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="str">
+        <v>Security-TC-0465</v>
+      </c>
+      <c r="B466" t="str">
+        <v>Verify Security functionality module 465</v>
+      </c>
+      <c r="C466" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D466">
+        <v>0.73</v>
+      </c>
+      <c r="E466" t="str">
+        <v>2026-07-30T14:07:02.551Z</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
+        <v>Security-TC-0466</v>
+      </c>
+      <c r="B467" t="str">
+        <v>Verify Security functionality module 466</v>
+      </c>
+      <c r="C467" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D467">
+        <v>1.53</v>
+      </c>
+      <c r="E467" t="str">
+        <v>2026-07-30T14:07:03.551Z</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="str">
+        <v>Security-TC-0467</v>
+      </c>
+      <c r="B468" t="str">
+        <v>Verify Security functionality module 467</v>
+      </c>
+      <c r="C468" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D468">
+        <v>1.56</v>
+      </c>
+      <c r="E468" t="str">
+        <v>2026-07-30T14:07:04.551Z</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="str">
+        <v>Security-TC-0468</v>
+      </c>
+      <c r="B469" t="str">
+        <v>Verify Security functionality module 468</v>
+      </c>
+      <c r="C469" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D469">
+        <v>0.67</v>
+      </c>
+      <c r="E469" t="str">
+        <v>2026-07-30T14:07:05.551Z</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="str">
+        <v>Security-TC-0469</v>
+      </c>
+      <c r="B470" t="str">
+        <v>Verify Security functionality module 469</v>
+      </c>
+      <c r="C470" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D470">
+        <v>0.19</v>
+      </c>
+      <c r="E470" t="str">
+        <v>2026-07-30T14:07:06.551Z</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="str">
+        <v>Security-TC-0470</v>
+      </c>
+      <c r="B471" t="str">
+        <v>Verify Security functionality module 470</v>
+      </c>
+      <c r="C471" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D471">
+        <v>1.05</v>
+      </c>
+      <c r="E471" t="str">
+        <v>2026-07-30T14:07:07.551Z</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="str">
+        <v>Security-TC-0471</v>
+      </c>
+      <c r="B472" t="str">
+        <v>Verify Security functionality module 471</v>
+      </c>
+      <c r="C472" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D472">
+        <v>1.85</v>
+      </c>
+      <c r="E472" t="str">
+        <v>2026-07-30T14:07:08.551Z</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="str">
+        <v>Security-TC-0472</v>
+      </c>
+      <c r="B473" t="str">
+        <v>Verify Security functionality module 472</v>
+      </c>
+      <c r="C473" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D473">
+        <v>1.18</v>
+      </c>
+      <c r="E473" t="str">
+        <v>2026-07-30T14:07:09.551Z</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="str">
+        <v>Security-TC-0473</v>
+      </c>
+      <c r="B474" t="str">
+        <v>Verify Security functionality module 473</v>
+      </c>
+      <c r="C474" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D474">
+        <v>1.82</v>
+      </c>
+      <c r="E474" t="str">
+        <v>2026-07-30T14:07:10.551Z</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="str">
+        <v>Security-TC-0474</v>
+      </c>
+      <c r="B475" t="str">
+        <v>Verify Security functionality module 474</v>
+      </c>
+      <c r="C475" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D475">
+        <v>0.95</v>
+      </c>
+      <c r="E475" t="str">
+        <v>2026-07-30T14:07:11.551Z</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="str">
+        <v>Security-TC-0475</v>
+      </c>
+      <c r="B476" t="str">
+        <v>Verify Security functionality module 475</v>
+      </c>
+      <c r="C476" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D476">
+        <v>1.31</v>
+      </c>
+      <c r="E476" t="str">
+        <v>2026-07-30T14:07:12.551Z</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="str">
+        <v>Security-TC-0476</v>
+      </c>
+      <c r="B477" t="str">
+        <v>Verify Security functionality module 476</v>
+      </c>
+      <c r="C477" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D477">
+        <v>1.76</v>
+      </c>
+      <c r="E477" t="str">
+        <v>2026-07-30T14:07:13.551Z</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="str">
+        <v>Security-TC-0477</v>
+      </c>
+      <c r="B478" t="str">
+        <v>Verify Security functionality module 477</v>
+      </c>
+      <c r="C478" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D478">
+        <v>1.21</v>
+      </c>
+      <c r="E478" t="str">
+        <v>2026-07-30T14:07:14.551Z</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="str">
+        <v>Security-TC-0478</v>
+      </c>
+      <c r="B479" t="str">
+        <v>Verify Security functionality module 478</v>
+      </c>
+      <c r="C479" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D479">
+        <v>0.41</v>
+      </c>
+      <c r="E479" t="str">
+        <v>2026-07-30T14:07:15.551Z</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="str">
+        <v>Security-TC-0479</v>
+      </c>
+      <c r="B480" t="str">
+        <v>Verify Security functionality module 479</v>
+      </c>
+      <c r="C480" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D480">
+        <v>0.99</v>
+      </c>
+      <c r="E480" t="str">
+        <v>2026-07-30T14:07:16.551Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E460"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E480"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reports/latest/backend/Backend_Security_Assessment.xlsx
+++ b/reports/latest/backend/Backend_Security_Assessment.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E480"/>
+  <dimension ref="A1:E499"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,10 +427,10 @@
         <v>Passed</v>
       </c>
       <c r="D2">
-        <v>0.91</v>
+        <v>1.91</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-07-30T13:59:18.551Z</v>
+        <v>2026-07-30T21:39:10.500Z</v>
       </c>
     </row>
     <row r="3">
@@ -444,10 +444,10 @@
         <v>Passed</v>
       </c>
       <c r="D3">
-        <v>1.96</v>
+        <v>1.6</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-07-30T13:59:19.551Z</v>
+        <v>2026-07-30T21:39:11.500Z</v>
       </c>
     </row>
     <row r="4">
@@ -461,10 +461,10 @@
         <v>Passed</v>
       </c>
       <c r="D4">
-        <v>0.32</v>
+        <v>1.59</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-07-30T13:59:20.551Z</v>
+        <v>2026-07-30T21:39:12.500Z</v>
       </c>
     </row>
     <row r="5">
@@ -478,10 +478,10 @@
         <v>Passed</v>
       </c>
       <c r="D5">
-        <v>0.43</v>
+        <v>1.27</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-07-30T13:59:21.551Z</v>
+        <v>2026-07-30T21:39:13.500Z</v>
       </c>
     </row>
     <row r="6">
@@ -495,10 +495,10 @@
         <v>Passed</v>
       </c>
       <c r="D6">
-        <v>0.47</v>
+        <v>1.28</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-07-30T13:59:22.551Z</v>
+        <v>2026-07-30T21:39:14.500Z</v>
       </c>
     </row>
     <row r="7">
@@ -512,10 +512,10 @@
         <v>Passed</v>
       </c>
       <c r="D7">
-        <v>1.39</v>
+        <v>0.07</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-07-30T13:59:23.551Z</v>
+        <v>2026-07-30T21:39:15.500Z</v>
       </c>
     </row>
     <row r="8">
@@ -526,13 +526,13 @@
         <v>Verify Security functionality module 7</v>
       </c>
       <c r="C8" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D8">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-07-30T13:59:24.551Z</v>
+        <v>2026-07-30T21:39:16.500Z</v>
       </c>
     </row>
     <row r="9">
@@ -543,13 +543,13 @@
         <v>Verify Security functionality module 8</v>
       </c>
       <c r="C9" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D9">
-        <v>0.95</v>
+        <v>0.49</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-07-30T13:59:25.551Z</v>
+        <v>2026-07-30T21:39:17.500Z</v>
       </c>
     </row>
     <row r="10">
@@ -563,10 +563,10 @@
         <v>Passed</v>
       </c>
       <c r="D10">
-        <v>0.14</v>
+        <v>1.54</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-07-30T13:59:26.551Z</v>
+        <v>2026-07-30T21:39:18.500Z</v>
       </c>
     </row>
     <row r="11">
@@ -580,10 +580,10 @@
         <v>Passed</v>
       </c>
       <c r="D11">
-        <v>1.79</v>
+        <v>0.81</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-07-30T13:59:27.551Z</v>
+        <v>2026-07-30T21:39:19.500Z</v>
       </c>
     </row>
     <row r="12">
@@ -597,10 +597,10 @@
         <v>Passed</v>
       </c>
       <c r="D12">
-        <v>0.1</v>
+        <v>0.87</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-07-30T13:59:28.551Z</v>
+        <v>2026-07-30T21:39:20.500Z</v>
       </c>
     </row>
     <row r="13">
@@ -614,10 +614,10 @@
         <v>Passed</v>
       </c>
       <c r="D13">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-07-30T13:59:29.551Z</v>
+        <v>2026-07-30T21:39:21.500Z</v>
       </c>
     </row>
     <row r="14">
@@ -631,10 +631,10 @@
         <v>Passed</v>
       </c>
       <c r="D14">
-        <v>1.47</v>
+        <v>0.66</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-07-30T13:59:30.551Z</v>
+        <v>2026-07-30T21:39:22.500Z</v>
       </c>
     </row>
     <row r="15">
@@ -648,10 +648,10 @@
         <v>Passed</v>
       </c>
       <c r="D15">
-        <v>0.01</v>
+        <v>0.14</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-07-30T13:59:31.551Z</v>
+        <v>2026-07-30T21:39:23.500Z</v>
       </c>
     </row>
     <row r="16">
@@ -665,10 +665,10 @@
         <v>Passed</v>
       </c>
       <c r="D16">
-        <v>0.76</v>
+        <v>1.53</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-07-30T13:59:32.551Z</v>
+        <v>2026-07-30T21:39:24.500Z</v>
       </c>
     </row>
     <row r="17">
@@ -682,10 +682,10 @@
         <v>Passed</v>
       </c>
       <c r="D17">
-        <v>1.08</v>
+        <v>1.7</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-07-30T13:59:33.551Z</v>
+        <v>2026-07-30T21:39:25.500Z</v>
       </c>
     </row>
     <row r="18">
@@ -699,10 +699,10 @@
         <v>Passed</v>
       </c>
       <c r="D18">
-        <v>0.95</v>
+        <v>1.02</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-07-30T13:59:34.551Z</v>
+        <v>2026-07-30T21:39:26.500Z</v>
       </c>
     </row>
     <row r="19">
@@ -716,10 +716,10 @@
         <v>Passed</v>
       </c>
       <c r="D19">
-        <v>0.6</v>
+        <v>0.56</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-07-30T13:59:35.551Z</v>
+        <v>2026-07-30T21:39:27.500Z</v>
       </c>
     </row>
     <row r="20">
@@ -733,10 +733,10 @@
         <v>Passed</v>
       </c>
       <c r="D20">
-        <v>0.25</v>
+        <v>0.54</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-07-30T13:59:36.551Z</v>
+        <v>2026-07-30T21:39:28.500Z</v>
       </c>
     </row>
     <row r="21">
@@ -750,10 +750,10 @@
         <v>Passed</v>
       </c>
       <c r="D21">
-        <v>0.27</v>
+        <v>0.75</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-07-30T13:59:37.551Z</v>
+        <v>2026-07-30T21:39:29.500Z</v>
       </c>
     </row>
     <row r="22">
@@ -767,10 +767,10 @@
         <v>Passed</v>
       </c>
       <c r="D22">
-        <v>0.4</v>
+        <v>1.84</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-07-30T13:59:38.551Z</v>
+        <v>2026-07-30T21:39:30.500Z</v>
       </c>
     </row>
     <row r="23">
@@ -784,10 +784,10 @@
         <v>Passed</v>
       </c>
       <c r="D23">
-        <v>0.9</v>
+        <v>0.72</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-07-30T13:59:39.551Z</v>
+        <v>2026-07-30T21:39:31.500Z</v>
       </c>
     </row>
     <row r="24">
@@ -801,10 +801,10 @@
         <v>Passed</v>
       </c>
       <c r="D24">
-        <v>0.44</v>
+        <v>1</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-07-30T13:59:40.551Z</v>
+        <v>2026-07-30T21:39:32.500Z</v>
       </c>
     </row>
     <row r="25">
@@ -818,10 +818,10 @@
         <v>Passed</v>
       </c>
       <c r="D25">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-07-30T13:59:41.551Z</v>
+        <v>2026-07-30T21:39:33.500Z</v>
       </c>
     </row>
     <row r="26">
@@ -835,10 +835,10 @@
         <v>Passed</v>
       </c>
       <c r="D26">
-        <v>0.99</v>
+        <v>1.76</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-07-30T13:59:42.551Z</v>
+        <v>2026-07-30T21:39:34.500Z</v>
       </c>
     </row>
     <row r="27">
@@ -852,10 +852,10 @@
         <v>Passed</v>
       </c>
       <c r="D27">
-        <v>1.02</v>
+        <v>0.22</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-07-30T13:59:43.551Z</v>
+        <v>2026-07-30T21:39:35.500Z</v>
       </c>
     </row>
     <row r="28">
@@ -869,10 +869,10 @@
         <v>Passed</v>
       </c>
       <c r="D28">
-        <v>0.82</v>
+        <v>1.22</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-07-30T13:59:44.551Z</v>
+        <v>2026-07-30T21:39:36.500Z</v>
       </c>
     </row>
     <row r="29">
@@ -886,10 +886,10 @@
         <v>Passed</v>
       </c>
       <c r="D29">
-        <v>0.68</v>
+        <v>1.02</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-07-30T13:59:45.551Z</v>
+        <v>2026-07-30T21:39:37.500Z</v>
       </c>
     </row>
     <row r="30">
@@ -903,10 +903,10 @@
         <v>Passed</v>
       </c>
       <c r="D30">
-        <v>1.77</v>
+        <v>0.13</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-07-30T13:59:46.551Z</v>
+        <v>2026-07-30T21:39:38.500Z</v>
       </c>
     </row>
     <row r="31">
@@ -917,13 +917,13 @@
         <v>Verify Security functionality module 30</v>
       </c>
       <c r="C31" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D31">
-        <v>0.61</v>
+        <v>0.77</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-07-30T13:59:47.551Z</v>
+        <v>2026-07-30T21:39:39.500Z</v>
       </c>
     </row>
     <row r="32">
@@ -934,13 +934,13 @@
         <v>Verify Security functionality module 31</v>
       </c>
       <c r="C32" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D32">
-        <v>1.4</v>
+        <v>0.09</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-07-30T13:59:48.551Z</v>
+        <v>2026-07-30T21:39:40.500Z</v>
       </c>
     </row>
     <row r="33">
@@ -954,10 +954,10 @@
         <v>Passed</v>
       </c>
       <c r="D33">
-        <v>1.99</v>
+        <v>1.37</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-07-30T13:59:49.551Z</v>
+        <v>2026-07-30T21:39:41.500Z</v>
       </c>
     </row>
     <row r="34">
@@ -971,10 +971,10 @@
         <v>Passed</v>
       </c>
       <c r="D34">
-        <v>1.35</v>
+        <v>0.09</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-07-30T13:59:50.551Z</v>
+        <v>2026-07-30T21:39:42.500Z</v>
       </c>
     </row>
     <row r="35">
@@ -988,10 +988,10 @@
         <v>Passed</v>
       </c>
       <c r="D35">
-        <v>1.13</v>
+        <v>0.29</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-07-30T13:59:51.551Z</v>
+        <v>2026-07-30T21:39:43.500Z</v>
       </c>
     </row>
     <row r="36">
@@ -1005,10 +1005,10 @@
         <v>Passed</v>
       </c>
       <c r="D36">
-        <v>0.74</v>
+        <v>1.41</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-07-30T13:59:52.551Z</v>
+        <v>2026-07-30T21:39:44.500Z</v>
       </c>
     </row>
     <row r="37">
@@ -1022,10 +1022,10 @@
         <v>Passed</v>
       </c>
       <c r="D37">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-07-30T13:59:53.551Z</v>
+        <v>2026-07-30T21:39:45.500Z</v>
       </c>
     </row>
     <row r="38">
@@ -1039,10 +1039,10 @@
         <v>Passed</v>
       </c>
       <c r="D38">
-        <v>0.06</v>
+        <v>0.52</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-07-30T13:59:54.551Z</v>
+        <v>2026-07-30T21:39:46.500Z</v>
       </c>
     </row>
     <row r="39">
@@ -1056,10 +1056,10 @@
         <v>Passed</v>
       </c>
       <c r="D39">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-07-30T13:59:55.551Z</v>
+        <v>2026-07-30T21:39:47.500Z</v>
       </c>
     </row>
     <row r="40">
@@ -1073,10 +1073,10 @@
         <v>Passed</v>
       </c>
       <c r="D40">
-        <v>0.84</v>
+        <v>1.67</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-07-30T13:59:56.551Z</v>
+        <v>2026-07-30T21:39:48.500Z</v>
       </c>
     </row>
     <row r="41">
@@ -1090,10 +1090,10 @@
         <v>Passed</v>
       </c>
       <c r="D41">
-        <v>0.25</v>
+        <v>0.51</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-07-30T13:59:57.551Z</v>
+        <v>2026-07-30T21:39:49.500Z</v>
       </c>
     </row>
     <row r="42">
@@ -1107,10 +1107,10 @@
         <v>Passed</v>
       </c>
       <c r="D42">
-        <v>0.94</v>
+        <v>0.1</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-07-30T13:59:58.551Z</v>
+        <v>2026-07-30T21:39:50.500Z</v>
       </c>
     </row>
     <row r="43">
@@ -1124,10 +1124,10 @@
         <v>Passed</v>
       </c>
       <c r="D43">
-        <v>0.12</v>
+        <v>1.97</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-07-30T13:59:59.551Z</v>
+        <v>2026-07-30T21:39:51.500Z</v>
       </c>
     </row>
     <row r="44">
@@ -1141,10 +1141,10 @@
         <v>Passed</v>
       </c>
       <c r="D44">
-        <v>1.61</v>
+        <v>1.37</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-07-30T14:00:00.551Z</v>
+        <v>2026-07-30T21:39:52.500Z</v>
       </c>
     </row>
     <row r="45">
@@ -1158,10 +1158,10 @@
         <v>Passed</v>
       </c>
       <c r="D45">
-        <v>1.28</v>
+        <v>0.75</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-07-30T14:00:01.551Z</v>
+        <v>2026-07-30T21:39:53.500Z</v>
       </c>
     </row>
     <row r="46">
@@ -1175,10 +1175,10 @@
         <v>Passed</v>
       </c>
       <c r="D46">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-07-30T14:00:02.551Z</v>
+        <v>2026-07-30T21:39:54.500Z</v>
       </c>
     </row>
     <row r="47">
@@ -1192,10 +1192,10 @@
         <v>Passed</v>
       </c>
       <c r="D47">
-        <v>1.41</v>
+        <v>0.27</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-07-30T14:00:03.551Z</v>
+        <v>2026-07-30T21:39:55.500Z</v>
       </c>
     </row>
     <row r="48">
@@ -1209,10 +1209,10 @@
         <v>Passed</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-07-30T14:00:04.551Z</v>
+        <v>2026-07-30T21:39:56.500Z</v>
       </c>
     </row>
     <row r="49">
@@ -1226,10 +1226,10 @@
         <v>Passed</v>
       </c>
       <c r="D49">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-07-30T14:00:05.551Z</v>
+        <v>2026-07-30T21:39:57.500Z</v>
       </c>
     </row>
     <row r="50">
@@ -1243,10 +1243,10 @@
         <v>Passed</v>
       </c>
       <c r="D50">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-07-30T14:00:06.551Z</v>
+        <v>2026-07-30T21:39:58.500Z</v>
       </c>
     </row>
     <row r="51">
@@ -1260,10 +1260,10 @@
         <v>Passed</v>
       </c>
       <c r="D51">
-        <v>1.69</v>
+        <v>1.27</v>
       </c>
       <c r="E51" t="str">
-        <v>2026-07-30T14:00:07.551Z</v>
+        <v>2026-07-30T21:39:59.500Z</v>
       </c>
     </row>
     <row r="52">
@@ -1277,10 +1277,10 @@
         <v>Passed</v>
       </c>
       <c r="D52">
-        <v>0.64</v>
+        <v>0.93</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-07-30T14:00:08.551Z</v>
+        <v>2026-07-30T21:40:00.500Z</v>
       </c>
     </row>
     <row r="53">
@@ -1294,10 +1294,10 @@
         <v>Passed</v>
       </c>
       <c r="D53">
-        <v>1.02</v>
+        <v>1.6</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-07-30T14:00:09.551Z</v>
+        <v>2026-07-30T21:40:01.500Z</v>
       </c>
     </row>
     <row r="54">
@@ -1311,10 +1311,10 @@
         <v>Passed</v>
       </c>
       <c r="D54">
-        <v>1.4</v>
+        <v>1.11</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-07-30T14:00:10.551Z</v>
+        <v>2026-07-30T21:40:02.500Z</v>
       </c>
     </row>
     <row r="55">
@@ -1328,10 +1328,10 @@
         <v>Passed</v>
       </c>
       <c r="D55">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-07-30T14:00:11.551Z</v>
+        <v>2026-07-30T21:40:03.500Z</v>
       </c>
     </row>
     <row r="56">
@@ -1345,10 +1345,10 @@
         <v>Passed</v>
       </c>
       <c r="D56">
-        <v>0.04</v>
+        <v>0.76</v>
       </c>
       <c r="E56" t="str">
-        <v>2026-07-30T14:00:12.551Z</v>
+        <v>2026-07-30T21:40:04.500Z</v>
       </c>
     </row>
     <row r="57">
@@ -1362,10 +1362,10 @@
         <v>Passed</v>
       </c>
       <c r="D57">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="E57" t="str">
-        <v>2026-07-30T14:00:13.551Z</v>
+        <v>2026-07-30T21:40:05.500Z</v>
       </c>
     </row>
     <row r="58">
@@ -1379,10 +1379,10 @@
         <v>Passed</v>
       </c>
       <c r="D58">
-        <v>0.43</v>
+        <v>1.12</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-07-30T14:00:14.551Z</v>
+        <v>2026-07-30T21:40:06.500Z</v>
       </c>
     </row>
     <row r="59">
@@ -1396,10 +1396,10 @@
         <v>Passed</v>
       </c>
       <c r="D59">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="E59" t="str">
-        <v>2026-07-30T14:00:15.551Z</v>
+        <v>2026-07-30T21:40:07.500Z</v>
       </c>
     </row>
     <row r="60">
@@ -1413,10 +1413,10 @@
         <v>Passed</v>
       </c>
       <c r="D60">
-        <v>1.35</v>
+        <v>0.37</v>
       </c>
       <c r="E60" t="str">
-        <v>2026-07-30T14:00:16.551Z</v>
+        <v>2026-07-30T21:40:08.500Z</v>
       </c>
     </row>
     <row r="61">
@@ -1430,10 +1430,10 @@
         <v>Passed</v>
       </c>
       <c r="D61">
-        <v>0.49</v>
+        <v>0.53</v>
       </c>
       <c r="E61" t="str">
-        <v>2026-07-30T14:00:17.551Z</v>
+        <v>2026-07-30T21:40:09.500Z</v>
       </c>
     </row>
     <row r="62">
@@ -1447,10 +1447,10 @@
         <v>Passed</v>
       </c>
       <c r="D62">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-07-30T14:00:18.551Z</v>
+        <v>2026-07-30T21:40:10.500Z</v>
       </c>
     </row>
     <row r="63">
@@ -1464,10 +1464,10 @@
         <v>Passed</v>
       </c>
       <c r="D63">
-        <v>0.52</v>
+        <v>1.35</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-07-30T14:00:19.551Z</v>
+        <v>2026-07-30T21:40:11.500Z</v>
       </c>
     </row>
     <row r="64">
@@ -1481,10 +1481,10 @@
         <v>Passed</v>
       </c>
       <c r="D64">
-        <v>0.9</v>
+        <v>1.58</v>
       </c>
       <c r="E64" t="str">
-        <v>2026-07-30T14:00:20.551Z</v>
+        <v>2026-07-30T21:40:12.500Z</v>
       </c>
     </row>
     <row r="65">
@@ -1498,10 +1498,10 @@
         <v>Passed</v>
       </c>
       <c r="D65">
-        <v>0.44</v>
+        <v>1.69</v>
       </c>
       <c r="E65" t="str">
-        <v>2026-07-30T14:00:21.551Z</v>
+        <v>2026-07-30T21:40:13.500Z</v>
       </c>
     </row>
     <row r="66">
@@ -1515,10 +1515,10 @@
         <v>Passed</v>
       </c>
       <c r="D66">
-        <v>0.79</v>
+        <v>0.23</v>
       </c>
       <c r="E66" t="str">
-        <v>2026-07-30T14:00:22.551Z</v>
+        <v>2026-07-30T21:40:14.500Z</v>
       </c>
     </row>
     <row r="67">
@@ -1535,7 +1535,7 @@
         <v>1.53</v>
       </c>
       <c r="E67" t="str">
-        <v>2026-07-30T14:00:23.551Z</v>
+        <v>2026-07-30T21:40:15.500Z</v>
       </c>
     </row>
     <row r="68">
@@ -1549,10 +1549,10 @@
         <v>Passed</v>
       </c>
       <c r="D68">
-        <v>1.65</v>
+        <v>0.92</v>
       </c>
       <c r="E68" t="str">
-        <v>2026-07-30T14:00:24.551Z</v>
+        <v>2026-07-30T21:40:16.500Z</v>
       </c>
     </row>
     <row r="69">
@@ -1566,10 +1566,10 @@
         <v>Passed</v>
       </c>
       <c r="D69">
-        <v>1.43</v>
+        <v>0.25</v>
       </c>
       <c r="E69" t="str">
-        <v>2026-07-30T14:00:25.551Z</v>
+        <v>2026-07-30T21:40:17.500Z</v>
       </c>
     </row>
     <row r="70">
@@ -1583,10 +1583,10 @@
         <v>Passed</v>
       </c>
       <c r="D70">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="E70" t="str">
-        <v>2026-07-30T14:00:26.551Z</v>
+        <v>2026-07-30T21:40:18.500Z</v>
       </c>
     </row>
     <row r="71">
@@ -1600,10 +1600,10 @@
         <v>Passed</v>
       </c>
       <c r="D71">
-        <v>1.18</v>
+        <v>1.98</v>
       </c>
       <c r="E71" t="str">
-        <v>2026-07-30T14:00:27.551Z</v>
+        <v>2026-07-30T21:40:19.500Z</v>
       </c>
     </row>
     <row r="72">
@@ -1617,10 +1617,10 @@
         <v>Passed</v>
       </c>
       <c r="D72">
-        <v>0.1</v>
+        <v>0.97</v>
       </c>
       <c r="E72" t="str">
-        <v>2026-07-30T14:00:28.551Z</v>
+        <v>2026-07-30T21:40:20.500Z</v>
       </c>
     </row>
     <row r="73">
@@ -1634,10 +1634,10 @@
         <v>Passed</v>
       </c>
       <c r="D73">
-        <v>0.54</v>
+        <v>1.81</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-07-30T14:00:29.551Z</v>
+        <v>2026-07-30T21:40:21.500Z</v>
       </c>
     </row>
     <row r="74">
@@ -1651,10 +1651,10 @@
         <v>Passed</v>
       </c>
       <c r="D74">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="E74" t="str">
-        <v>2026-07-30T14:00:30.551Z</v>
+        <v>2026-07-30T21:40:22.500Z</v>
       </c>
     </row>
     <row r="75">
@@ -1668,10 +1668,10 @@
         <v>Passed</v>
       </c>
       <c r="D75">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="E75" t="str">
-        <v>2026-07-30T14:00:31.551Z</v>
+        <v>2026-07-30T21:40:23.500Z</v>
       </c>
     </row>
     <row r="76">
@@ -1685,10 +1685,10 @@
         <v>Passed</v>
       </c>
       <c r="D76">
-        <v>0.43</v>
+        <v>1.25</v>
       </c>
       <c r="E76" t="str">
-        <v>2026-07-30T14:00:32.551Z</v>
+        <v>2026-07-30T21:40:24.500Z</v>
       </c>
     </row>
     <row r="77">
@@ -1702,10 +1702,10 @@
         <v>Passed</v>
       </c>
       <c r="D77">
-        <v>0.63</v>
+        <v>0.41</v>
       </c>
       <c r="E77" t="str">
-        <v>2026-07-30T14:00:33.551Z</v>
+        <v>2026-07-30T21:40:25.500Z</v>
       </c>
     </row>
     <row r="78">
@@ -1719,10 +1719,10 @@
         <v>Passed</v>
       </c>
       <c r="D78">
-        <v>1.76</v>
+        <v>1.37</v>
       </c>
       <c r="E78" t="str">
-        <v>2026-07-30T14:00:34.551Z</v>
+        <v>2026-07-30T21:40:26.500Z</v>
       </c>
     </row>
     <row r="79">
@@ -1736,10 +1736,10 @@
         <v>Passed</v>
       </c>
       <c r="D79">
-        <v>1.17</v>
+        <v>1.55</v>
       </c>
       <c r="E79" t="str">
-        <v>2026-07-30T14:00:35.551Z</v>
+        <v>2026-07-30T21:40:27.500Z</v>
       </c>
     </row>
     <row r="80">
@@ -1753,10 +1753,10 @@
         <v>Passed</v>
       </c>
       <c r="D80">
-        <v>1.5</v>
+        <v>0.12</v>
       </c>
       <c r="E80" t="str">
-        <v>2026-07-30T14:00:36.551Z</v>
+        <v>2026-07-30T21:40:28.500Z</v>
       </c>
     </row>
     <row r="81">
@@ -1770,10 +1770,10 @@
         <v>Passed</v>
       </c>
       <c r="D81">
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="E81" t="str">
-        <v>2026-07-30T14:00:37.551Z</v>
+        <v>2026-07-30T21:40:29.500Z</v>
       </c>
     </row>
     <row r="82">
@@ -1787,10 +1787,10 @@
         <v>Passed</v>
       </c>
       <c r="D82">
-        <v>0.81</v>
+        <v>1.82</v>
       </c>
       <c r="E82" t="str">
-        <v>2026-07-30T14:00:38.551Z</v>
+        <v>2026-07-30T21:40:30.500Z</v>
       </c>
     </row>
     <row r="83">
@@ -1804,10 +1804,10 @@
         <v>Passed</v>
       </c>
       <c r="D83">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="E83" t="str">
-        <v>2026-07-30T14:00:39.551Z</v>
+        <v>2026-07-30T21:40:31.500Z</v>
       </c>
     </row>
     <row r="84">
@@ -1821,10 +1821,10 @@
         <v>Passed</v>
       </c>
       <c r="D84">
-        <v>1.08</v>
+        <v>0.17</v>
       </c>
       <c r="E84" t="str">
-        <v>2026-07-30T14:00:40.551Z</v>
+        <v>2026-07-30T21:40:32.500Z</v>
       </c>
     </row>
     <row r="85">
@@ -1838,10 +1838,10 @@
         <v>Passed</v>
       </c>
       <c r="D85">
-        <v>1.57</v>
+        <v>0.91</v>
       </c>
       <c r="E85" t="str">
-        <v>2026-07-30T14:00:41.551Z</v>
+        <v>2026-07-30T21:40:33.500Z</v>
       </c>
     </row>
     <row r="86">
@@ -1855,10 +1855,10 @@
         <v>Passed</v>
       </c>
       <c r="D86">
-        <v>0.46</v>
+        <v>1.12</v>
       </c>
       <c r="E86" t="str">
-        <v>2026-07-30T14:00:42.551Z</v>
+        <v>2026-07-30T21:40:34.500Z</v>
       </c>
     </row>
     <row r="87">
@@ -1872,10 +1872,10 @@
         <v>Passed</v>
       </c>
       <c r="D87">
-        <v>0.06</v>
+        <v>1.69</v>
       </c>
       <c r="E87" t="str">
-        <v>2026-07-30T14:00:43.551Z</v>
+        <v>2026-07-30T21:40:35.500Z</v>
       </c>
     </row>
     <row r="88">
@@ -1889,10 +1889,10 @@
         <v>Passed</v>
       </c>
       <c r="D88">
-        <v>1.09</v>
+        <v>1.81</v>
       </c>
       <c r="E88" t="str">
-        <v>2026-07-30T14:00:44.551Z</v>
+        <v>2026-07-30T21:40:36.500Z</v>
       </c>
     </row>
     <row r="89">
@@ -1906,10 +1906,10 @@
         <v>Passed</v>
       </c>
       <c r="D89">
-        <v>1.1</v>
+        <v>1.44</v>
       </c>
       <c r="E89" t="str">
-        <v>2026-07-30T14:00:45.551Z</v>
+        <v>2026-07-30T21:40:37.500Z</v>
       </c>
     </row>
     <row r="90">
@@ -1923,10 +1923,10 @@
         <v>Passed</v>
       </c>
       <c r="D90">
-        <v>1.15</v>
+        <v>1.57</v>
       </c>
       <c r="E90" t="str">
-        <v>2026-07-30T14:00:46.551Z</v>
+        <v>2026-07-30T21:40:38.500Z</v>
       </c>
     </row>
     <row r="91">
@@ -1940,10 +1940,10 @@
         <v>Passed</v>
       </c>
       <c r="D91">
-        <v>1.34</v>
+        <v>0.7</v>
       </c>
       <c r="E91" t="str">
-        <v>2026-07-30T14:00:47.551Z</v>
+        <v>2026-07-30T21:40:39.500Z</v>
       </c>
     </row>
     <row r="92">
@@ -1954,13 +1954,13 @@
         <v>Verify Security functionality module 91</v>
       </c>
       <c r="C92" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D92">
-        <v>0.67</v>
+        <v>1.45</v>
       </c>
       <c r="E92" t="str">
-        <v>2026-07-30T14:00:48.551Z</v>
+        <v>2026-07-30T21:40:40.500Z</v>
       </c>
     </row>
     <row r="93">
@@ -1971,13 +1971,13 @@
         <v>Verify Security functionality module 92</v>
       </c>
       <c r="C93" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D93">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="E93" t="str">
-        <v>2026-07-30T14:00:49.551Z</v>
+        <v>2026-07-30T21:40:41.500Z</v>
       </c>
     </row>
     <row r="94">
@@ -1991,10 +1991,10 @@
         <v>Passed</v>
       </c>
       <c r="D94">
-        <v>1.67</v>
+        <v>0.5</v>
       </c>
       <c r="E94" t="str">
-        <v>2026-07-30T14:00:50.551Z</v>
+        <v>2026-07-30T21:40:42.500Z</v>
       </c>
     </row>
     <row r="95">
@@ -2008,10 +2008,10 @@
         <v>Passed</v>
       </c>
       <c r="D95">
-        <v>0.03</v>
+        <v>0.92</v>
       </c>
       <c r="E95" t="str">
-        <v>2026-07-30T14:00:51.551Z</v>
+        <v>2026-07-30T21:40:43.500Z</v>
       </c>
     </row>
     <row r="96">
@@ -2025,10 +2025,10 @@
         <v>Passed</v>
       </c>
       <c r="D96">
-        <v>0.58</v>
+        <v>1.1</v>
       </c>
       <c r="E96" t="str">
-        <v>2026-07-30T14:00:52.551Z</v>
+        <v>2026-07-30T21:40:44.500Z</v>
       </c>
     </row>
     <row r="97">
@@ -2042,10 +2042,10 @@
         <v>Passed</v>
       </c>
       <c r="D97">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="E97" t="str">
-        <v>2026-07-30T14:00:53.551Z</v>
+        <v>2026-07-30T21:40:45.500Z</v>
       </c>
     </row>
     <row r="98">
@@ -2059,10 +2059,10 @@
         <v>Passed</v>
       </c>
       <c r="D98">
-        <v>2</v>
+        <v>0.85</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-07-30T14:00:54.551Z</v>
+        <v>2026-07-30T21:40:46.500Z</v>
       </c>
     </row>
     <row r="99">
@@ -2076,10 +2076,10 @@
         <v>Passed</v>
       </c>
       <c r="D99">
-        <v>0.25</v>
+        <v>1.97</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-07-30T14:00:55.551Z</v>
+        <v>2026-07-30T21:40:47.500Z</v>
       </c>
     </row>
     <row r="100">
@@ -2093,10 +2093,10 @@
         <v>Passed</v>
       </c>
       <c r="D100">
-        <v>1.39</v>
+        <v>0.17</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-07-30T14:00:56.551Z</v>
+        <v>2026-07-30T21:40:48.500Z</v>
       </c>
     </row>
     <row r="101">
@@ -2110,10 +2110,10 @@
         <v>Passed</v>
       </c>
       <c r="D101">
-        <v>0.17</v>
+        <v>0.02</v>
       </c>
       <c r="E101" t="str">
-        <v>2026-07-30T14:00:57.551Z</v>
+        <v>2026-07-30T21:40:49.500Z</v>
       </c>
     </row>
     <row r="102">
@@ -2127,10 +2127,10 @@
         <v>Passed</v>
       </c>
       <c r="D102">
-        <v>1.32</v>
+        <v>1.02</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-07-30T14:00:58.551Z</v>
+        <v>2026-07-30T21:40:50.500Z</v>
       </c>
     </row>
     <row r="103">
@@ -2144,10 +2144,10 @@
         <v>Passed</v>
       </c>
       <c r="D103">
-        <v>0.59</v>
+        <v>0.49</v>
       </c>
       <c r="E103" t="str">
-        <v>2026-07-30T14:00:59.551Z</v>
+        <v>2026-07-30T21:40:51.500Z</v>
       </c>
     </row>
     <row r="104">
@@ -2161,10 +2161,10 @@
         <v>Passed</v>
       </c>
       <c r="D104">
-        <v>1.05</v>
+        <v>0.63</v>
       </c>
       <c r="E104" t="str">
-        <v>2026-07-30T14:01:00.551Z</v>
+        <v>2026-07-30T21:40:52.500Z</v>
       </c>
     </row>
     <row r="105">
@@ -2178,10 +2178,10 @@
         <v>Passed</v>
       </c>
       <c r="D105">
-        <v>0.86</v>
+        <v>1.03</v>
       </c>
       <c r="E105" t="str">
-        <v>2026-07-30T14:01:01.551Z</v>
+        <v>2026-07-30T21:40:53.500Z</v>
       </c>
     </row>
     <row r="106">
@@ -2195,10 +2195,10 @@
         <v>Passed</v>
       </c>
       <c r="D106">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="E106" t="str">
-        <v>2026-07-30T14:01:02.551Z</v>
+        <v>2026-07-30T21:40:54.500Z</v>
       </c>
     </row>
     <row r="107">
@@ -2212,10 +2212,10 @@
         <v>Passed</v>
       </c>
       <c r="D107">
-        <v>0.64</v>
+        <v>0.87</v>
       </c>
       <c r="E107" t="str">
-        <v>2026-07-30T14:01:03.551Z</v>
+        <v>2026-07-30T21:40:55.500Z</v>
       </c>
     </row>
     <row r="108">
@@ -2229,10 +2229,10 @@
         <v>Passed</v>
       </c>
       <c r="D108">
-        <v>1.62</v>
+        <v>1.97</v>
       </c>
       <c r="E108" t="str">
-        <v>2026-07-30T14:01:04.551Z</v>
+        <v>2026-07-30T21:40:56.500Z</v>
       </c>
     </row>
     <row r="109">
@@ -2246,10 +2246,10 @@
         <v>Passed</v>
       </c>
       <c r="D109">
-        <v>1.42</v>
+        <v>0.55</v>
       </c>
       <c r="E109" t="str">
-        <v>2026-07-30T14:01:05.551Z</v>
+        <v>2026-07-30T21:40:57.500Z</v>
       </c>
     </row>
     <row r="110">
@@ -2263,10 +2263,10 @@
         <v>Passed</v>
       </c>
       <c r="D110">
-        <v>1.58</v>
+        <v>0.96</v>
       </c>
       <c r="E110" t="str">
-        <v>2026-07-30T14:01:06.551Z</v>
+        <v>2026-07-30T21:40:58.500Z</v>
       </c>
     </row>
     <row r="111">
@@ -2280,10 +2280,10 @@
         <v>Passed</v>
       </c>
       <c r="D111">
-        <v>0.57</v>
+        <v>1.63</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-07-30T14:01:07.551Z</v>
+        <v>2026-07-30T21:40:59.500Z</v>
       </c>
     </row>
     <row r="112">
@@ -2297,10 +2297,10 @@
         <v>Passed</v>
       </c>
       <c r="D112">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-07-30T14:01:08.551Z</v>
+        <v>2026-07-30T21:41:00.500Z</v>
       </c>
     </row>
     <row r="113">
@@ -2314,10 +2314,10 @@
         <v>Passed</v>
       </c>
       <c r="D113">
-        <v>1.39</v>
+        <v>1.87</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-07-30T14:01:09.551Z</v>
+        <v>2026-07-30T21:41:01.500Z</v>
       </c>
     </row>
     <row r="114">
@@ -2331,10 +2331,10 @@
         <v>Passed</v>
       </c>
       <c r="D114">
-        <v>0.73</v>
+        <v>1.66</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-07-30T14:01:10.551Z</v>
+        <v>2026-07-30T21:41:02.500Z</v>
       </c>
     </row>
     <row r="115">
@@ -2348,10 +2348,10 @@
         <v>Passed</v>
       </c>
       <c r="D115">
-        <v>1.46</v>
+        <v>0.71</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-07-30T14:01:11.551Z</v>
+        <v>2026-07-30T21:41:03.500Z</v>
       </c>
     </row>
     <row r="116">
@@ -2365,10 +2365,10 @@
         <v>Passed</v>
       </c>
       <c r="D116">
-        <v>0.03</v>
+        <v>1.49</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-07-30T14:01:12.551Z</v>
+        <v>2026-07-30T21:41:04.500Z</v>
       </c>
     </row>
     <row r="117">
@@ -2382,10 +2382,10 @@
         <v>Passed</v>
       </c>
       <c r="D117">
-        <v>1.58</v>
+        <v>1.14</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-07-30T14:01:13.551Z</v>
+        <v>2026-07-30T21:41:05.500Z</v>
       </c>
     </row>
     <row r="118">
@@ -2399,10 +2399,10 @@
         <v>Passed</v>
       </c>
       <c r="D118">
-        <v>1.68</v>
+        <v>1.13</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-07-30T14:01:14.551Z</v>
+        <v>2026-07-30T21:41:06.500Z</v>
       </c>
     </row>
     <row r="119">
@@ -2416,10 +2416,10 @@
         <v>Passed</v>
       </c>
       <c r="D119">
-        <v>1.25</v>
+        <v>1.88</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-07-30T14:01:15.551Z</v>
+        <v>2026-07-30T21:41:07.500Z</v>
       </c>
     </row>
     <row r="120">
@@ -2433,10 +2433,10 @@
         <v>Passed</v>
       </c>
       <c r="D120">
-        <v>1.89</v>
+        <v>0.24</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-07-30T14:01:16.551Z</v>
+        <v>2026-07-30T21:41:08.500Z</v>
       </c>
     </row>
     <row r="121">
@@ -2450,10 +2450,10 @@
         <v>Passed</v>
       </c>
       <c r="D121">
-        <v>1.92</v>
+        <v>0.16</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-07-30T14:01:17.551Z</v>
+        <v>2026-07-30T21:41:09.500Z</v>
       </c>
     </row>
     <row r="122">
@@ -2467,10 +2467,10 @@
         <v>Passed</v>
       </c>
       <c r="D122">
-        <v>1.91</v>
+        <v>0.21</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-07-30T14:01:18.551Z</v>
+        <v>2026-07-30T21:41:10.500Z</v>
       </c>
     </row>
     <row r="123">
@@ -2484,10 +2484,10 @@
         <v>Passed</v>
       </c>
       <c r="D123">
-        <v>1.3</v>
+        <v>0.52</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-07-30T14:01:19.551Z</v>
+        <v>2026-07-30T21:41:11.500Z</v>
       </c>
     </row>
     <row r="124">
@@ -2501,10 +2501,10 @@
         <v>Passed</v>
       </c>
       <c r="D124">
-        <v>1.73</v>
+        <v>0.65</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-07-30T14:01:20.551Z</v>
+        <v>2026-07-30T21:41:12.500Z</v>
       </c>
     </row>
     <row r="125">
@@ -2518,10 +2518,10 @@
         <v>Passed</v>
       </c>
       <c r="D125">
-        <v>0.4</v>
+        <v>1.71</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-07-30T14:01:21.551Z</v>
+        <v>2026-07-30T21:41:13.500Z</v>
       </c>
     </row>
     <row r="126">
@@ -2535,10 +2535,10 @@
         <v>Passed</v>
       </c>
       <c r="D126">
-        <v>1.39</v>
+        <v>0.51</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-07-30T14:01:22.551Z</v>
+        <v>2026-07-30T21:41:14.500Z</v>
       </c>
     </row>
     <row r="127">
@@ -2552,10 +2552,10 @@
         <v>Passed</v>
       </c>
       <c r="D127">
-        <v>1.25</v>
+        <v>0.71</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-07-30T14:01:23.551Z</v>
+        <v>2026-07-30T21:41:15.500Z</v>
       </c>
     </row>
     <row r="128">
@@ -2569,10 +2569,10 @@
         <v>Passed</v>
       </c>
       <c r="D128">
-        <v>1.64</v>
+        <v>0.05</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-07-30T14:01:24.551Z</v>
+        <v>2026-07-30T21:41:16.500Z</v>
       </c>
     </row>
     <row r="129">
@@ -2586,10 +2586,10 @@
         <v>Passed</v>
       </c>
       <c r="D129">
-        <v>0.39</v>
+        <v>1.32</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-07-30T14:01:25.551Z</v>
+        <v>2026-07-30T21:41:17.500Z</v>
       </c>
     </row>
     <row r="130">
@@ -2603,10 +2603,10 @@
         <v>Passed</v>
       </c>
       <c r="D130">
-        <v>0.18</v>
+        <v>0.04</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-07-30T14:01:26.551Z</v>
+        <v>2026-07-30T21:41:18.500Z</v>
       </c>
     </row>
     <row r="131">
@@ -2620,10 +2620,10 @@
         <v>Passed</v>
       </c>
       <c r="D131">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-07-30T14:01:27.551Z</v>
+        <v>2026-07-30T21:41:19.500Z</v>
       </c>
     </row>
     <row r="132">
@@ -2637,10 +2637,10 @@
         <v>Passed</v>
       </c>
       <c r="D132">
-        <v>1.2</v>
+        <v>0.76</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-07-30T14:01:28.551Z</v>
+        <v>2026-07-30T21:41:20.500Z</v>
       </c>
     </row>
     <row r="133">
@@ -2654,10 +2654,10 @@
         <v>Passed</v>
       </c>
       <c r="D133">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-07-30T14:01:29.551Z</v>
+        <v>2026-07-30T21:41:21.500Z</v>
       </c>
     </row>
     <row r="134">
@@ -2671,10 +2671,10 @@
         <v>Passed</v>
       </c>
       <c r="D134">
-        <v>0.64</v>
+        <v>0.48</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-07-30T14:01:30.551Z</v>
+        <v>2026-07-30T21:41:22.500Z</v>
       </c>
     </row>
     <row r="135">
@@ -2688,10 +2688,10 @@
         <v>Passed</v>
       </c>
       <c r="D135">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-07-30T14:01:31.551Z</v>
+        <v>2026-07-30T21:41:23.500Z</v>
       </c>
     </row>
     <row r="136">
@@ -2705,10 +2705,10 @@
         <v>Passed</v>
       </c>
       <c r="D136">
-        <v>0.15</v>
+        <v>1.83</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-07-30T14:01:32.551Z</v>
+        <v>2026-07-30T21:41:24.500Z</v>
       </c>
     </row>
     <row r="137">
@@ -2722,10 +2722,10 @@
         <v>Passed</v>
       </c>
       <c r="D137">
-        <v>0.54</v>
+        <v>1.24</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-07-30T14:01:33.551Z</v>
+        <v>2026-07-30T21:41:25.500Z</v>
       </c>
     </row>
     <row r="138">
@@ -2739,10 +2739,10 @@
         <v>Passed</v>
       </c>
       <c r="D138">
-        <v>0.47</v>
+        <v>0.32</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-07-30T14:01:34.551Z</v>
+        <v>2026-07-30T21:41:26.500Z</v>
       </c>
     </row>
     <row r="139">
@@ -2756,10 +2756,10 @@
         <v>Passed</v>
       </c>
       <c r="D139">
-        <v>1.01</v>
+        <v>0.89</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-07-30T14:01:35.551Z</v>
+        <v>2026-07-30T21:41:27.500Z</v>
       </c>
     </row>
     <row r="140">
@@ -2773,10 +2773,10 @@
         <v>Passed</v>
       </c>
       <c r="D140">
-        <v>1.37</v>
+        <v>0.85</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-07-30T14:01:36.551Z</v>
+        <v>2026-07-30T21:41:28.500Z</v>
       </c>
     </row>
     <row r="141">
@@ -2790,10 +2790,10 @@
         <v>Passed</v>
       </c>
       <c r="D141">
-        <v>1.81</v>
+        <v>1.24</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-07-30T14:01:37.551Z</v>
+        <v>2026-07-30T21:41:29.500Z</v>
       </c>
     </row>
     <row r="142">
@@ -2807,10 +2807,10 @@
         <v>Passed</v>
       </c>
       <c r="D142">
-        <v>0.68</v>
+        <v>1.31</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-07-30T14:01:38.551Z</v>
+        <v>2026-07-30T21:41:30.500Z</v>
       </c>
     </row>
     <row r="143">
@@ -2824,10 +2824,10 @@
         <v>Passed</v>
       </c>
       <c r="D143">
-        <v>1.84</v>
+        <v>0.17</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-07-30T14:01:39.551Z</v>
+        <v>2026-07-30T21:41:31.500Z</v>
       </c>
     </row>
     <row r="144">
@@ -2841,10 +2841,10 @@
         <v>Passed</v>
       </c>
       <c r="D144">
-        <v>0.67</v>
+        <v>1.26</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-07-30T14:01:40.551Z</v>
+        <v>2026-07-30T21:41:32.500Z</v>
       </c>
     </row>
     <row r="145">
@@ -2858,10 +2858,10 @@
         <v>Passed</v>
       </c>
       <c r="D145">
-        <v>0.11</v>
+        <v>1.6</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-07-30T14:01:41.551Z</v>
+        <v>2026-07-30T21:41:33.500Z</v>
       </c>
     </row>
     <row r="146">
@@ -2875,10 +2875,10 @@
         <v>Passed</v>
       </c>
       <c r="D146">
-        <v>1.79</v>
+        <v>1.02</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-07-30T14:01:42.551Z</v>
+        <v>2026-07-30T21:41:34.500Z</v>
       </c>
     </row>
     <row r="147">
@@ -2892,10 +2892,10 @@
         <v>Passed</v>
       </c>
       <c r="D147">
-        <v>1.26</v>
+        <v>0.29</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-07-30T14:01:43.551Z</v>
+        <v>2026-07-30T21:41:35.500Z</v>
       </c>
     </row>
     <row r="148">
@@ -2909,10 +2909,10 @@
         <v>Passed</v>
       </c>
       <c r="D148">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-07-30T14:01:44.551Z</v>
+        <v>2026-07-30T21:41:36.500Z</v>
       </c>
     </row>
     <row r="149">
@@ -2926,10 +2926,10 @@
         <v>Passed</v>
       </c>
       <c r="D149">
-        <v>1.09</v>
+        <v>0.37</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-07-30T14:01:45.551Z</v>
+        <v>2026-07-30T21:41:37.500Z</v>
       </c>
     </row>
     <row r="150">
@@ -2943,10 +2943,10 @@
         <v>Passed</v>
       </c>
       <c r="D150">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-07-30T14:01:46.551Z</v>
+        <v>2026-07-30T21:41:38.500Z</v>
       </c>
     </row>
     <row r="151">
@@ -2960,10 +2960,10 @@
         <v>Passed</v>
       </c>
       <c r="D151">
-        <v>0.49</v>
+        <v>0.17</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-07-30T14:01:47.551Z</v>
+        <v>2026-07-30T21:41:39.500Z</v>
       </c>
     </row>
     <row r="152">
@@ -2977,10 +2977,10 @@
         <v>Passed</v>
       </c>
       <c r="D152">
-        <v>1.09</v>
+        <v>1.48</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-07-30T14:01:48.551Z</v>
+        <v>2026-07-30T21:41:40.500Z</v>
       </c>
     </row>
     <row r="153">
@@ -2994,10 +2994,10 @@
         <v>Passed</v>
       </c>
       <c r="D153">
-        <v>0.11</v>
+        <v>0.65</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-07-30T14:01:49.551Z</v>
+        <v>2026-07-30T21:41:41.500Z</v>
       </c>
     </row>
     <row r="154">
@@ -3011,10 +3011,10 @@
         <v>Passed</v>
       </c>
       <c r="D154">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-07-30T14:01:50.551Z</v>
+        <v>2026-07-30T21:41:42.500Z</v>
       </c>
     </row>
     <row r="155">
@@ -3028,10 +3028,10 @@
         <v>Passed</v>
       </c>
       <c r="D155">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="E155" t="str">
-        <v>2026-07-30T14:01:51.551Z</v>
+        <v>2026-07-30T21:41:43.500Z</v>
       </c>
     </row>
     <row r="156">
@@ -3045,10 +3045,10 @@
         <v>Passed</v>
       </c>
       <c r="D156">
-        <v>1.45</v>
+        <v>0.81</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-07-30T14:01:52.551Z</v>
+        <v>2026-07-30T21:41:44.500Z</v>
       </c>
     </row>
     <row r="157">
@@ -3062,10 +3062,10 @@
         <v>Passed</v>
       </c>
       <c r="D157">
-        <v>1.92</v>
+        <v>0.35</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-07-30T14:01:53.551Z</v>
+        <v>2026-07-30T21:41:45.500Z</v>
       </c>
     </row>
     <row r="158">
@@ -3079,10 +3079,10 @@
         <v>Passed</v>
       </c>
       <c r="D158">
-        <v>0.75</v>
+        <v>1.41</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-07-30T14:01:54.551Z</v>
+        <v>2026-07-30T21:41:46.500Z</v>
       </c>
     </row>
     <row r="159">
@@ -3096,10 +3096,10 @@
         <v>Passed</v>
       </c>
       <c r="D159">
-        <v>0.87</v>
+        <v>0.24</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-07-30T14:01:55.551Z</v>
+        <v>2026-07-30T21:41:47.500Z</v>
       </c>
     </row>
     <row r="160">
@@ -3113,10 +3113,10 @@
         <v>Passed</v>
       </c>
       <c r="D160">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="E160" t="str">
-        <v>2026-07-30T14:01:56.551Z</v>
+        <v>2026-07-30T21:41:48.500Z</v>
       </c>
     </row>
     <row r="161">
@@ -3130,10 +3130,10 @@
         <v>Passed</v>
       </c>
       <c r="D161">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="E161" t="str">
-        <v>2026-07-30T14:01:57.551Z</v>
+        <v>2026-07-30T21:41:49.500Z</v>
       </c>
     </row>
     <row r="162">
@@ -3147,10 +3147,10 @@
         <v>Passed</v>
       </c>
       <c r="D162">
-        <v>0.66</v>
+        <v>1.17</v>
       </c>
       <c r="E162" t="str">
-        <v>2026-07-30T14:01:58.551Z</v>
+        <v>2026-07-30T21:41:50.500Z</v>
       </c>
     </row>
     <row r="163">
@@ -3164,10 +3164,10 @@
         <v>Passed</v>
       </c>
       <c r="D163">
-        <v>0.24</v>
+        <v>1.57</v>
       </c>
       <c r="E163" t="str">
-        <v>2026-07-30T14:01:59.551Z</v>
+        <v>2026-07-30T21:41:51.500Z</v>
       </c>
     </row>
     <row r="164">
@@ -3181,10 +3181,10 @@
         <v>Passed</v>
       </c>
       <c r="D164">
-        <v>1.59</v>
+        <v>0.49</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-07-30T14:02:00.551Z</v>
+        <v>2026-07-30T21:41:52.500Z</v>
       </c>
     </row>
     <row r="165">
@@ -3198,10 +3198,10 @@
         <v>Passed</v>
       </c>
       <c r="D165">
-        <v>1.94</v>
+        <v>0.71</v>
       </c>
       <c r="E165" t="str">
-        <v>2026-07-30T14:02:01.551Z</v>
+        <v>2026-07-30T21:41:53.500Z</v>
       </c>
     </row>
     <row r="166">
@@ -3215,10 +3215,10 @@
         <v>Passed</v>
       </c>
       <c r="D166">
-        <v>0.63</v>
+        <v>1.66</v>
       </c>
       <c r="E166" t="str">
-        <v>2026-07-30T14:02:02.551Z</v>
+        <v>2026-07-30T21:41:54.500Z</v>
       </c>
     </row>
     <row r="167">
@@ -3232,10 +3232,10 @@
         <v>Passed</v>
       </c>
       <c r="D167">
-        <v>1.66</v>
+        <v>0.4</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-07-30T14:02:03.551Z</v>
+        <v>2026-07-30T21:41:55.500Z</v>
       </c>
     </row>
     <row r="168">
@@ -3249,10 +3249,10 @@
         <v>Passed</v>
       </c>
       <c r="D168">
-        <v>1.61</v>
+        <v>0.88</v>
       </c>
       <c r="E168" t="str">
-        <v>2026-07-30T14:02:04.551Z</v>
+        <v>2026-07-30T21:41:56.500Z</v>
       </c>
     </row>
     <row r="169">
@@ -3266,10 +3266,10 @@
         <v>Passed</v>
       </c>
       <c r="D169">
-        <v>1.07</v>
+        <v>1.53</v>
       </c>
       <c r="E169" t="str">
-        <v>2026-07-30T14:02:05.551Z</v>
+        <v>2026-07-30T21:41:57.500Z</v>
       </c>
     </row>
     <row r="170">
@@ -3283,10 +3283,10 @@
         <v>Passed</v>
       </c>
       <c r="D170">
-        <v>0.96</v>
+        <v>0.06</v>
       </c>
       <c r="E170" t="str">
-        <v>2026-07-30T14:02:06.551Z</v>
+        <v>2026-07-30T21:41:58.500Z</v>
       </c>
     </row>
     <row r="171">
@@ -3300,10 +3300,10 @@
         <v>Passed</v>
       </c>
       <c r="D171">
-        <v>1.49</v>
+        <v>1.71</v>
       </c>
       <c r="E171" t="str">
-        <v>2026-07-30T14:02:07.551Z</v>
+        <v>2026-07-30T21:41:59.500Z</v>
       </c>
     </row>
     <row r="172">
@@ -3317,10 +3317,10 @@
         <v>Passed</v>
       </c>
       <c r="D172">
-        <v>1.33</v>
+        <v>1.88</v>
       </c>
       <c r="E172" t="str">
-        <v>2026-07-30T14:02:08.551Z</v>
+        <v>2026-07-30T21:42:00.500Z</v>
       </c>
     </row>
     <row r="173">
@@ -3334,10 +3334,10 @@
         <v>Passed</v>
       </c>
       <c r="D173">
-        <v>1.08</v>
+        <v>1.74</v>
       </c>
       <c r="E173" t="str">
-        <v>2026-07-30T14:02:09.551Z</v>
+        <v>2026-07-30T21:42:01.500Z</v>
       </c>
     </row>
     <row r="174">
@@ -3351,10 +3351,10 @@
         <v>Passed</v>
       </c>
       <c r="D174">
-        <v>0.53</v>
+        <v>1.61</v>
       </c>
       <c r="E174" t="str">
-        <v>2026-07-30T14:02:10.551Z</v>
+        <v>2026-07-30T21:42:02.500Z</v>
       </c>
     </row>
     <row r="175">
@@ -3368,10 +3368,10 @@
         <v>Passed</v>
       </c>
       <c r="D175">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="E175" t="str">
-        <v>2026-07-30T14:02:11.551Z</v>
+        <v>2026-07-30T21:42:03.500Z</v>
       </c>
     </row>
     <row r="176">
@@ -3385,10 +3385,10 @@
         <v>Passed</v>
       </c>
       <c r="D176">
-        <v>1.35</v>
+        <v>0.62</v>
       </c>
       <c r="E176" t="str">
-        <v>2026-07-30T14:02:12.551Z</v>
+        <v>2026-07-30T21:42:04.500Z</v>
       </c>
     </row>
     <row r="177">
@@ -3402,10 +3402,10 @@
         <v>Passed</v>
       </c>
       <c r="D177">
-        <v>1.91</v>
+        <v>0.72</v>
       </c>
       <c r="E177" t="str">
-        <v>2026-07-30T14:02:13.551Z</v>
+        <v>2026-07-30T21:42:05.500Z</v>
       </c>
     </row>
     <row r="178">
@@ -3419,10 +3419,10 @@
         <v>Passed</v>
       </c>
       <c r="D178">
-        <v>1.37</v>
+        <v>0.23</v>
       </c>
       <c r="E178" t="str">
-        <v>2026-07-30T14:02:14.551Z</v>
+        <v>2026-07-30T21:42:06.500Z</v>
       </c>
     </row>
     <row r="179">
@@ -3436,10 +3436,10 @@
         <v>Passed</v>
       </c>
       <c r="D179">
-        <v>0.95</v>
+        <v>0.06</v>
       </c>
       <c r="E179" t="str">
-        <v>2026-07-30T14:02:15.551Z</v>
+        <v>2026-07-30T21:42:07.500Z</v>
       </c>
     </row>
     <row r="180">
@@ -3453,10 +3453,10 @@
         <v>Passed</v>
       </c>
       <c r="D180">
-        <v>0.48</v>
+        <v>1.14</v>
       </c>
       <c r="E180" t="str">
-        <v>2026-07-30T14:02:16.551Z</v>
+        <v>2026-07-30T21:42:08.500Z</v>
       </c>
     </row>
     <row r="181">
@@ -3470,10 +3470,10 @@
         <v>Passed</v>
       </c>
       <c r="D181">
-        <v>0.7</v>
+        <v>1.59</v>
       </c>
       <c r="E181" t="str">
-        <v>2026-07-30T14:02:17.551Z</v>
+        <v>2026-07-30T21:42:09.500Z</v>
       </c>
     </row>
     <row r="182">
@@ -3487,10 +3487,10 @@
         <v>Passed</v>
       </c>
       <c r="D182">
-        <v>0.65</v>
+        <v>0.15</v>
       </c>
       <c r="E182" t="str">
-        <v>2026-07-30T14:02:18.551Z</v>
+        <v>2026-07-30T21:42:10.500Z</v>
       </c>
     </row>
     <row r="183">
@@ -3504,10 +3504,10 @@
         <v>Passed</v>
       </c>
       <c r="D183">
-        <v>1.21</v>
+        <v>0.05</v>
       </c>
       <c r="E183" t="str">
-        <v>2026-07-30T14:02:19.551Z</v>
+        <v>2026-07-30T21:42:11.500Z</v>
       </c>
     </row>
     <row r="184">
@@ -3521,10 +3521,10 @@
         <v>Passed</v>
       </c>
       <c r="D184">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="E184" t="str">
-        <v>2026-07-30T14:02:20.551Z</v>
+        <v>2026-07-30T21:42:12.500Z</v>
       </c>
     </row>
     <row r="185">
@@ -3538,10 +3538,10 @@
         <v>Passed</v>
       </c>
       <c r="D185">
-        <v>1.53</v>
+        <v>0.48</v>
       </c>
       <c r="E185" t="str">
-        <v>2026-07-30T14:02:21.551Z</v>
+        <v>2026-07-30T21:42:13.500Z</v>
       </c>
     </row>
     <row r="186">
@@ -3555,10 +3555,10 @@
         <v>Passed</v>
       </c>
       <c r="D186">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="E186" t="str">
-        <v>2026-07-30T14:02:22.551Z</v>
+        <v>2026-07-30T21:42:14.500Z</v>
       </c>
     </row>
     <row r="187">
@@ -3572,10 +3572,10 @@
         <v>Passed</v>
       </c>
       <c r="D187">
-        <v>0.85</v>
+        <v>1.57</v>
       </c>
       <c r="E187" t="str">
-        <v>2026-07-30T14:02:23.551Z</v>
+        <v>2026-07-30T21:42:15.500Z</v>
       </c>
     </row>
     <row r="188">
@@ -3589,10 +3589,10 @@
         <v>Passed</v>
       </c>
       <c r="D188">
-        <v>0.81</v>
+        <v>1.64</v>
       </c>
       <c r="E188" t="str">
-        <v>2026-07-30T14:02:24.551Z</v>
+        <v>2026-07-30T21:42:16.500Z</v>
       </c>
     </row>
     <row r="189">
@@ -3606,10 +3606,10 @@
         <v>Passed</v>
       </c>
       <c r="D189">
-        <v>0.77</v>
+        <v>1.25</v>
       </c>
       <c r="E189" t="str">
-        <v>2026-07-30T14:02:25.551Z</v>
+        <v>2026-07-30T21:42:17.500Z</v>
       </c>
     </row>
     <row r="190">
@@ -3623,10 +3623,10 @@
         <v>Passed</v>
       </c>
       <c r="D190">
-        <v>0.69</v>
+        <v>1.48</v>
       </c>
       <c r="E190" t="str">
-        <v>2026-07-30T14:02:26.551Z</v>
+        <v>2026-07-30T21:42:18.500Z</v>
       </c>
     </row>
     <row r="191">
@@ -3640,10 +3640,10 @@
         <v>Passed</v>
       </c>
       <c r="D191">
-        <v>1.64</v>
+        <v>1.27</v>
       </c>
       <c r="E191" t="str">
-        <v>2026-07-30T14:02:27.551Z</v>
+        <v>2026-07-30T21:42:19.500Z</v>
       </c>
     </row>
     <row r="192">
@@ -3657,10 +3657,10 @@
         <v>Passed</v>
       </c>
       <c r="D192">
-        <v>1.03</v>
+        <v>1.42</v>
       </c>
       <c r="E192" t="str">
-        <v>2026-07-30T14:02:28.551Z</v>
+        <v>2026-07-30T21:42:20.500Z</v>
       </c>
     </row>
     <row r="193">
@@ -3674,10 +3674,10 @@
         <v>Passed</v>
       </c>
       <c r="D193">
-        <v>0.68</v>
+        <v>0.41</v>
       </c>
       <c r="E193" t="str">
-        <v>2026-07-30T14:02:29.551Z</v>
+        <v>2026-07-30T21:42:21.500Z</v>
       </c>
     </row>
     <row r="194">
@@ -3691,10 +3691,10 @@
         <v>Passed</v>
       </c>
       <c r="D194">
-        <v>1.86</v>
+        <v>1.25</v>
       </c>
       <c r="E194" t="str">
-        <v>2026-07-30T14:02:30.551Z</v>
+        <v>2026-07-30T21:42:22.500Z</v>
       </c>
     </row>
     <row r="195">
@@ -3708,10 +3708,10 @@
         <v>Passed</v>
       </c>
       <c r="D195">
-        <v>0.97</v>
+        <v>1.03</v>
       </c>
       <c r="E195" t="str">
-        <v>2026-07-30T14:02:31.551Z</v>
+        <v>2026-07-30T21:42:23.500Z</v>
       </c>
     </row>
     <row r="196">
@@ -3725,10 +3725,10 @@
         <v>Passed</v>
       </c>
       <c r="D196">
-        <v>0.64</v>
+        <v>1.53</v>
       </c>
       <c r="E196" t="str">
-        <v>2026-07-30T14:02:32.551Z</v>
+        <v>2026-07-30T21:42:24.500Z</v>
       </c>
     </row>
     <row r="197">
@@ -3742,10 +3742,10 @@
         <v>Passed</v>
       </c>
       <c r="D197">
-        <v>0.47</v>
+        <v>0.84</v>
       </c>
       <c r="E197" t="str">
-        <v>2026-07-30T14:02:33.551Z</v>
+        <v>2026-07-30T21:42:25.500Z</v>
       </c>
     </row>
     <row r="198">
@@ -3759,10 +3759,10 @@
         <v>Passed</v>
       </c>
       <c r="D198">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="E198" t="str">
-        <v>2026-07-30T14:02:34.551Z</v>
+        <v>2026-07-30T21:42:26.500Z</v>
       </c>
     </row>
     <row r="199">
@@ -3776,10 +3776,10 @@
         <v>Passed</v>
       </c>
       <c r="D199">
-        <v>1.92</v>
+        <v>0.62</v>
       </c>
       <c r="E199" t="str">
-        <v>2026-07-30T14:02:35.551Z</v>
+        <v>2026-07-30T21:42:27.500Z</v>
       </c>
     </row>
     <row r="200">
@@ -3793,10 +3793,10 @@
         <v>Passed</v>
       </c>
       <c r="D200">
-        <v>0.18</v>
+        <v>0.43</v>
       </c>
       <c r="E200" t="str">
-        <v>2026-07-30T14:02:36.551Z</v>
+        <v>2026-07-30T21:42:28.500Z</v>
       </c>
     </row>
     <row r="201">
@@ -3810,10 +3810,10 @@
         <v>Passed</v>
       </c>
       <c r="D201">
-        <v>0.64</v>
+        <v>1.21</v>
       </c>
       <c r="E201" t="str">
-        <v>2026-07-30T14:02:37.551Z</v>
+        <v>2026-07-30T21:42:29.500Z</v>
       </c>
     </row>
     <row r="202">
@@ -3827,10 +3827,10 @@
         <v>Passed</v>
       </c>
       <c r="D202">
-        <v>1.56</v>
+        <v>0.23</v>
       </c>
       <c r="E202" t="str">
-        <v>2026-07-30T14:02:38.551Z</v>
+        <v>2026-07-30T21:42:30.500Z</v>
       </c>
     </row>
     <row r="203">
@@ -3844,10 +3844,10 @@
         <v>Passed</v>
       </c>
       <c r="D203">
-        <v>0.38</v>
+        <v>0.63</v>
       </c>
       <c r="E203" t="str">
-        <v>2026-07-30T14:02:39.551Z</v>
+        <v>2026-07-30T21:42:31.500Z</v>
       </c>
     </row>
     <row r="204">
@@ -3861,10 +3861,10 @@
         <v>Passed</v>
       </c>
       <c r="D204">
-        <v>1.48</v>
+        <v>1.82</v>
       </c>
       <c r="E204" t="str">
-        <v>2026-07-30T14:02:40.551Z</v>
+        <v>2026-07-30T21:42:32.500Z</v>
       </c>
     </row>
     <row r="205">
@@ -3878,10 +3878,10 @@
         <v>Passed</v>
       </c>
       <c r="D205">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="E205" t="str">
-        <v>2026-07-30T14:02:41.551Z</v>
+        <v>2026-07-30T21:42:33.500Z</v>
       </c>
     </row>
     <row r="206">
@@ -3895,10 +3895,10 @@
         <v>Passed</v>
       </c>
       <c r="D206">
-        <v>0.21</v>
+        <v>0.71</v>
       </c>
       <c r="E206" t="str">
-        <v>2026-07-30T14:02:42.551Z</v>
+        <v>2026-07-30T21:42:34.500Z</v>
       </c>
     </row>
     <row r="207">
@@ -3912,10 +3912,10 @@
         <v>Passed</v>
       </c>
       <c r="D207">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="E207" t="str">
-        <v>2026-07-30T14:02:43.551Z</v>
+        <v>2026-07-30T21:42:35.500Z</v>
       </c>
     </row>
     <row r="208">
@@ -3929,10 +3929,10 @@
         <v>Passed</v>
       </c>
       <c r="D208">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="E208" t="str">
-        <v>2026-07-30T14:02:44.551Z</v>
+        <v>2026-07-30T21:42:36.500Z</v>
       </c>
     </row>
     <row r="209">
@@ -3946,10 +3946,10 @@
         <v>Passed</v>
       </c>
       <c r="D209">
-        <v>0.6</v>
+        <v>1.97</v>
       </c>
       <c r="E209" t="str">
-        <v>2026-07-30T14:02:45.551Z</v>
+        <v>2026-07-30T21:42:37.500Z</v>
       </c>
     </row>
     <row r="210">
@@ -3963,10 +3963,10 @@
         <v>Passed</v>
       </c>
       <c r="D210">
-        <v>0.44</v>
+        <v>1.79</v>
       </c>
       <c r="E210" t="str">
-        <v>2026-07-30T14:02:46.551Z</v>
+        <v>2026-07-30T21:42:38.500Z</v>
       </c>
     </row>
     <row r="211">
@@ -3980,10 +3980,10 @@
         <v>Passed</v>
       </c>
       <c r="D211">
-        <v>0.98</v>
+        <v>1.58</v>
       </c>
       <c r="E211" t="str">
-        <v>2026-07-30T14:02:47.551Z</v>
+        <v>2026-07-30T21:42:39.500Z</v>
       </c>
     </row>
     <row r="212">
@@ -3997,10 +3997,10 @@
         <v>Passed</v>
       </c>
       <c r="D212">
-        <v>0.47</v>
+        <v>0.99</v>
       </c>
       <c r="E212" t="str">
-        <v>2026-07-30T14:02:48.551Z</v>
+        <v>2026-07-30T21:42:40.500Z</v>
       </c>
     </row>
     <row r="213">
@@ -4014,10 +4014,10 @@
         <v>Passed</v>
       </c>
       <c r="D213">
-        <v>0.82</v>
+        <v>1.02</v>
       </c>
       <c r="E213" t="str">
-        <v>2026-07-30T14:02:49.551Z</v>
+        <v>2026-07-30T21:42:41.500Z</v>
       </c>
     </row>
     <row r="214">
@@ -4031,10 +4031,10 @@
         <v>Passed</v>
       </c>
       <c r="D214">
-        <v>0.59</v>
+        <v>0.04</v>
       </c>
       <c r="E214" t="str">
-        <v>2026-07-30T14:02:50.551Z</v>
+        <v>2026-07-30T21:42:42.500Z</v>
       </c>
     </row>
     <row r="215">
@@ -4048,10 +4048,10 @@
         <v>Passed</v>
       </c>
       <c r="D215">
-        <v>0.52</v>
+        <v>1.16</v>
       </c>
       <c r="E215" t="str">
-        <v>2026-07-30T14:02:51.551Z</v>
+        <v>2026-07-30T21:42:43.500Z</v>
       </c>
     </row>
     <row r="216">
@@ -4065,10 +4065,10 @@
         <v>Passed</v>
       </c>
       <c r="D216">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="E216" t="str">
-        <v>2026-07-30T14:02:52.551Z</v>
+        <v>2026-07-30T21:42:44.500Z</v>
       </c>
     </row>
     <row r="217">
@@ -4082,10 +4082,10 @@
         <v>Passed</v>
       </c>
       <c r="D217">
-        <v>0.14</v>
+        <v>1.19</v>
       </c>
       <c r="E217" t="str">
-        <v>2026-07-30T14:02:53.551Z</v>
+        <v>2026-07-30T21:42:45.500Z</v>
       </c>
     </row>
     <row r="218">
@@ -4099,10 +4099,10 @@
         <v>Passed</v>
       </c>
       <c r="D218">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="E218" t="str">
-        <v>2026-07-30T14:02:54.551Z</v>
+        <v>2026-07-30T21:42:46.500Z</v>
       </c>
     </row>
     <row r="219">
@@ -4116,10 +4116,10 @@
         <v>Passed</v>
       </c>
       <c r="D219">
-        <v>1.89</v>
+        <v>0.3</v>
       </c>
       <c r="E219" t="str">
-        <v>2026-07-30T14:02:55.551Z</v>
+        <v>2026-07-30T21:42:47.500Z</v>
       </c>
     </row>
     <row r="220">
@@ -4133,10 +4133,10 @@
         <v>Passed</v>
       </c>
       <c r="D220">
-        <v>0.43</v>
+        <v>0.21</v>
       </c>
       <c r="E220" t="str">
-        <v>2026-07-30T14:02:56.551Z</v>
+        <v>2026-07-30T21:42:48.500Z</v>
       </c>
     </row>
     <row r="221">
@@ -4150,10 +4150,10 @@
         <v>Passed</v>
       </c>
       <c r="D221">
-        <v>0.06</v>
+        <v>0.4</v>
       </c>
       <c r="E221" t="str">
-        <v>2026-07-30T14:02:57.551Z</v>
+        <v>2026-07-30T21:42:49.500Z</v>
       </c>
     </row>
     <row r="222">
@@ -4167,10 +4167,10 @@
         <v>Passed</v>
       </c>
       <c r="D222">
-        <v>0.94</v>
+        <v>1.72</v>
       </c>
       <c r="E222" t="str">
-        <v>2026-07-30T14:02:58.551Z</v>
+        <v>2026-07-30T21:42:50.500Z</v>
       </c>
     </row>
     <row r="223">
@@ -4184,10 +4184,10 @@
         <v>Passed</v>
       </c>
       <c r="D223">
-        <v>1.49</v>
+        <v>0.72</v>
       </c>
       <c r="E223" t="str">
-        <v>2026-07-30T14:02:59.551Z</v>
+        <v>2026-07-30T21:42:51.500Z</v>
       </c>
     </row>
     <row r="224">
@@ -4201,10 +4201,10 @@
         <v>Passed</v>
       </c>
       <c r="D224">
-        <v>0.3</v>
+        <v>0.19</v>
       </c>
       <c r="E224" t="str">
-        <v>2026-07-30T14:03:00.551Z</v>
+        <v>2026-07-30T21:42:52.500Z</v>
       </c>
     </row>
     <row r="225">
@@ -4218,10 +4218,10 @@
         <v>Passed</v>
       </c>
       <c r="D225">
-        <v>0.46</v>
+        <v>0.86</v>
       </c>
       <c r="E225" t="str">
-        <v>2026-07-30T14:03:01.551Z</v>
+        <v>2026-07-30T21:42:53.500Z</v>
       </c>
     </row>
     <row r="226">
@@ -4235,10 +4235,10 @@
         <v>Passed</v>
       </c>
       <c r="D226">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="E226" t="str">
-        <v>2026-07-30T14:03:02.551Z</v>
+        <v>2026-07-30T21:42:54.500Z</v>
       </c>
     </row>
     <row r="227">
@@ -4252,10 +4252,10 @@
         <v>Passed</v>
       </c>
       <c r="D227">
-        <v>1.57</v>
+        <v>0.9</v>
       </c>
       <c r="E227" t="str">
-        <v>2026-07-30T14:03:03.551Z</v>
+        <v>2026-07-30T21:42:55.500Z</v>
       </c>
     </row>
     <row r="228">
@@ -4269,10 +4269,10 @@
         <v>Passed</v>
       </c>
       <c r="D228">
-        <v>1.64</v>
+        <v>0.08</v>
       </c>
       <c r="E228" t="str">
-        <v>2026-07-30T14:03:04.551Z</v>
+        <v>2026-07-30T21:42:56.500Z</v>
       </c>
     </row>
     <row r="229">
@@ -4286,10 +4286,10 @@
         <v>Passed</v>
       </c>
       <c r="D229">
-        <v>0.69</v>
+        <v>0.96</v>
       </c>
       <c r="E229" t="str">
-        <v>2026-07-30T14:03:05.551Z</v>
+        <v>2026-07-30T21:42:57.500Z</v>
       </c>
     </row>
     <row r="230">
@@ -4303,10 +4303,10 @@
         <v>Passed</v>
       </c>
       <c r="D230">
-        <v>1.46</v>
+        <v>1.86</v>
       </c>
       <c r="E230" t="str">
-        <v>2026-07-30T14:03:06.551Z</v>
+        <v>2026-07-30T21:42:58.500Z</v>
       </c>
     </row>
     <row r="231">
@@ -4320,10 +4320,10 @@
         <v>Passed</v>
       </c>
       <c r="D231">
-        <v>0.54</v>
+        <v>0.88</v>
       </c>
       <c r="E231" t="str">
-        <v>2026-07-30T14:03:07.551Z</v>
+        <v>2026-07-30T21:42:59.500Z</v>
       </c>
     </row>
     <row r="232">
@@ -4337,10 +4337,10 @@
         <v>Passed</v>
       </c>
       <c r="D232">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="E232" t="str">
-        <v>2026-07-30T14:03:08.551Z</v>
+        <v>2026-07-30T21:43:00.500Z</v>
       </c>
     </row>
     <row r="233">
@@ -4354,10 +4354,10 @@
         <v>Passed</v>
       </c>
       <c r="D233">
-        <v>1.78</v>
+        <v>0.86</v>
       </c>
       <c r="E233" t="str">
-        <v>2026-07-30T14:03:09.551Z</v>
+        <v>2026-07-30T21:43:01.500Z</v>
       </c>
     </row>
     <row r="234">
@@ -4371,10 +4371,10 @@
         <v>Passed</v>
       </c>
       <c r="D234">
-        <v>1.38</v>
+        <v>0.72</v>
       </c>
       <c r="E234" t="str">
-        <v>2026-07-30T14:03:10.551Z</v>
+        <v>2026-07-30T21:43:02.500Z</v>
       </c>
     </row>
     <row r="235">
@@ -4385,13 +4385,13 @@
         <v>Verify Security functionality module 234</v>
       </c>
       <c r="C235" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D235">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="E235" t="str">
-        <v>2026-07-30T14:03:11.551Z</v>
+        <v>2026-07-30T21:43:03.500Z</v>
       </c>
     </row>
     <row r="236">
@@ -4405,10 +4405,10 @@
         <v>Passed</v>
       </c>
       <c r="D236">
-        <v>0.2</v>
+        <v>0.38</v>
       </c>
       <c r="E236" t="str">
-        <v>2026-07-30T14:03:12.551Z</v>
+        <v>2026-07-30T21:43:04.500Z</v>
       </c>
     </row>
     <row r="237">
@@ -4422,10 +4422,10 @@
         <v>Passed</v>
       </c>
       <c r="D237">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="E237" t="str">
-        <v>2026-07-30T14:03:13.551Z</v>
+        <v>2026-07-30T21:43:05.500Z</v>
       </c>
     </row>
     <row r="238">
@@ -4439,10 +4439,10 @@
         <v>Passed</v>
       </c>
       <c r="D238">
-        <v>1.22</v>
+        <v>0.87</v>
       </c>
       <c r="E238" t="str">
-        <v>2026-07-30T14:03:14.551Z</v>
+        <v>2026-07-30T21:43:06.500Z</v>
       </c>
     </row>
     <row r="239">
@@ -4456,10 +4456,10 @@
         <v>Passed</v>
       </c>
       <c r="D239">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="E239" t="str">
-        <v>2026-07-30T14:03:15.551Z</v>
+        <v>2026-07-30T21:43:07.500Z</v>
       </c>
     </row>
     <row r="240">
@@ -4473,10 +4473,10 @@
         <v>Passed</v>
       </c>
       <c r="D240">
-        <v>1.9</v>
+        <v>0.06</v>
       </c>
       <c r="E240" t="str">
-        <v>2026-07-30T14:03:16.551Z</v>
+        <v>2026-07-30T21:43:08.500Z</v>
       </c>
     </row>
     <row r="241">
@@ -4490,10 +4490,10 @@
         <v>Passed</v>
       </c>
       <c r="D241">
-        <v>1.66</v>
+        <v>0.26</v>
       </c>
       <c r="E241" t="str">
-        <v>2026-07-30T14:03:17.551Z</v>
+        <v>2026-07-30T21:43:09.500Z</v>
       </c>
     </row>
     <row r="242">
@@ -4507,10 +4507,10 @@
         <v>Passed</v>
       </c>
       <c r="D242">
-        <v>0.22</v>
+        <v>0.09</v>
       </c>
       <c r="E242" t="str">
-        <v>2026-07-30T14:03:18.551Z</v>
+        <v>2026-07-30T21:43:10.500Z</v>
       </c>
     </row>
     <row r="243">
@@ -4524,10 +4524,10 @@
         <v>Passed</v>
       </c>
       <c r="D243">
-        <v>0.25</v>
+        <v>1.82</v>
       </c>
       <c r="E243" t="str">
-        <v>2026-07-30T14:03:19.551Z</v>
+        <v>2026-07-30T21:43:11.500Z</v>
       </c>
     </row>
     <row r="244">
@@ -4541,10 +4541,10 @@
         <v>Passed</v>
       </c>
       <c r="D244">
-        <v>0.99</v>
+        <v>1.48</v>
       </c>
       <c r="E244" t="str">
-        <v>2026-07-30T14:03:20.551Z</v>
+        <v>2026-07-30T21:43:12.500Z</v>
       </c>
     </row>
     <row r="245">
@@ -4558,10 +4558,10 @@
         <v>Passed</v>
       </c>
       <c r="D245">
-        <v>0.13</v>
+        <v>1.58</v>
       </c>
       <c r="E245" t="str">
-        <v>2026-07-30T14:03:21.551Z</v>
+        <v>2026-07-30T21:43:13.500Z</v>
       </c>
     </row>
     <row r="246">
@@ -4575,10 +4575,10 @@
         <v>Passed</v>
       </c>
       <c r="D246">
-        <v>1.61</v>
+        <v>0.58</v>
       </c>
       <c r="E246" t="str">
-        <v>2026-07-30T14:03:22.551Z</v>
+        <v>2026-07-30T21:43:14.500Z</v>
       </c>
     </row>
     <row r="247">
@@ -4592,10 +4592,10 @@
         <v>Passed</v>
       </c>
       <c r="D247">
-        <v>1</v>
+        <v>0.22</v>
       </c>
       <c r="E247" t="str">
-        <v>2026-07-30T14:03:23.551Z</v>
+        <v>2026-07-30T21:43:15.500Z</v>
       </c>
     </row>
     <row r="248">
@@ -4609,10 +4609,10 @@
         <v>Passed</v>
       </c>
       <c r="D248">
-        <v>0.19</v>
+        <v>0.64</v>
       </c>
       <c r="E248" t="str">
-        <v>2026-07-30T14:03:24.551Z</v>
+        <v>2026-07-30T21:43:16.500Z</v>
       </c>
     </row>
     <row r="249">
@@ -4626,10 +4626,10 @@
         <v>Passed</v>
       </c>
       <c r="D249">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="E249" t="str">
-        <v>2026-07-30T14:03:25.551Z</v>
+        <v>2026-07-30T21:43:17.500Z</v>
       </c>
     </row>
     <row r="250">
@@ -4643,10 +4643,10 @@
         <v>Passed</v>
       </c>
       <c r="D250">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="E250" t="str">
-        <v>2026-07-30T14:03:26.551Z</v>
+        <v>2026-07-30T21:43:18.500Z</v>
       </c>
     </row>
     <row r="251">
@@ -4660,10 +4660,10 @@
         <v>Passed</v>
       </c>
       <c r="D251">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="E251" t="str">
-        <v>2026-07-30T14:03:27.551Z</v>
+        <v>2026-07-30T21:43:19.500Z</v>
       </c>
     </row>
     <row r="252">
@@ -4677,10 +4677,10 @@
         <v>Passed</v>
       </c>
       <c r="D252">
-        <v>1.25</v>
+        <v>0.58</v>
       </c>
       <c r="E252" t="str">
-        <v>2026-07-30T14:03:28.551Z</v>
+        <v>2026-07-30T21:43:20.500Z</v>
       </c>
     </row>
     <row r="253">
@@ -4694,10 +4694,10 @@
         <v>Passed</v>
       </c>
       <c r="D253">
-        <v>0.44</v>
+        <v>1.62</v>
       </c>
       <c r="E253" t="str">
-        <v>2026-07-30T14:03:29.551Z</v>
+        <v>2026-07-30T21:43:21.500Z</v>
       </c>
     </row>
     <row r="254">
@@ -4711,10 +4711,10 @@
         <v>Passed</v>
       </c>
       <c r="D254">
-        <v>1.62</v>
+        <v>1.12</v>
       </c>
       <c r="E254" t="str">
-        <v>2026-07-30T14:03:30.551Z</v>
+        <v>2026-07-30T21:43:22.500Z</v>
       </c>
     </row>
     <row r="255">
@@ -4728,10 +4728,10 @@
         <v>Passed</v>
       </c>
       <c r="D255">
-        <v>1.5</v>
+        <v>0.86</v>
       </c>
       <c r="E255" t="str">
-        <v>2026-07-30T14:03:31.551Z</v>
+        <v>2026-07-30T21:43:23.500Z</v>
       </c>
     </row>
     <row r="256">
@@ -4745,10 +4745,10 @@
         <v>Passed</v>
       </c>
       <c r="D256">
-        <v>1.14</v>
+        <v>0.28</v>
       </c>
       <c r="E256" t="str">
-        <v>2026-07-30T14:03:32.551Z</v>
+        <v>2026-07-30T21:43:24.500Z</v>
       </c>
     </row>
     <row r="257">
@@ -4762,10 +4762,10 @@
         <v>Passed</v>
       </c>
       <c r="D257">
-        <v>1.88</v>
+        <v>0.13</v>
       </c>
       <c r="E257" t="str">
-        <v>2026-07-30T14:03:33.551Z</v>
+        <v>2026-07-30T21:43:25.500Z</v>
       </c>
     </row>
     <row r="258">
@@ -4779,10 +4779,10 @@
         <v>Passed</v>
       </c>
       <c r="D258">
-        <v>1.72</v>
+        <v>0.82</v>
       </c>
       <c r="E258" t="str">
-        <v>2026-07-30T14:03:34.551Z</v>
+        <v>2026-07-30T21:43:26.500Z</v>
       </c>
     </row>
     <row r="259">
@@ -4796,10 +4796,10 @@
         <v>Passed</v>
       </c>
       <c r="D259">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="E259" t="str">
-        <v>2026-07-30T14:03:35.551Z</v>
+        <v>2026-07-30T21:43:27.500Z</v>
       </c>
     </row>
     <row r="260">
@@ -4813,10 +4813,10 @@
         <v>Passed</v>
       </c>
       <c r="D260">
-        <v>1.16</v>
+        <v>0.75</v>
       </c>
       <c r="E260" t="str">
-        <v>2026-07-30T14:03:36.551Z</v>
+        <v>2026-07-30T21:43:28.500Z</v>
       </c>
     </row>
     <row r="261">
@@ -4830,10 +4830,10 @@
         <v>Passed</v>
       </c>
       <c r="D261">
-        <v>1.16</v>
+        <v>1.89</v>
       </c>
       <c r="E261" t="str">
-        <v>2026-07-30T14:03:37.551Z</v>
+        <v>2026-07-30T21:43:29.500Z</v>
       </c>
     </row>
     <row r="262">
@@ -4847,10 +4847,10 @@
         <v>Passed</v>
       </c>
       <c r="D262">
-        <v>1.15</v>
+        <v>0.7</v>
       </c>
       <c r="E262" t="str">
-        <v>2026-07-30T14:03:38.551Z</v>
+        <v>2026-07-30T21:43:30.500Z</v>
       </c>
     </row>
     <row r="263">
@@ -4864,10 +4864,10 @@
         <v>Passed</v>
       </c>
       <c r="D263">
-        <v>1.11</v>
+        <v>0.36</v>
       </c>
       <c r="E263" t="str">
-        <v>2026-07-30T14:03:39.551Z</v>
+        <v>2026-07-30T21:43:31.500Z</v>
       </c>
     </row>
     <row r="264">
@@ -4881,10 +4881,10 @@
         <v>Passed</v>
       </c>
       <c r="D264">
-        <v>1.78</v>
+        <v>0.9</v>
       </c>
       <c r="E264" t="str">
-        <v>2026-07-30T14:03:40.551Z</v>
+        <v>2026-07-30T21:43:32.500Z</v>
       </c>
     </row>
     <row r="265">
@@ -4898,10 +4898,10 @@
         <v>Passed</v>
       </c>
       <c r="D265">
-        <v>1.59</v>
+        <v>1.98</v>
       </c>
       <c r="E265" t="str">
-        <v>2026-07-30T14:03:41.551Z</v>
+        <v>2026-07-30T21:43:33.500Z</v>
       </c>
     </row>
     <row r="266">
@@ -4915,10 +4915,10 @@
         <v>Passed</v>
       </c>
       <c r="D266">
-        <v>1.56</v>
+        <v>1.96</v>
       </c>
       <c r="E266" t="str">
-        <v>2026-07-30T14:03:42.551Z</v>
+        <v>2026-07-30T21:43:34.500Z</v>
       </c>
     </row>
     <row r="267">
@@ -4932,10 +4932,10 @@
         <v>Passed</v>
       </c>
       <c r="D267">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="E267" t="str">
-        <v>2026-07-30T14:03:43.551Z</v>
+        <v>2026-07-30T21:43:35.500Z</v>
       </c>
     </row>
     <row r="268">
@@ -4949,10 +4949,10 @@
         <v>Passed</v>
       </c>
       <c r="D268">
-        <v>1.33</v>
+        <v>1.07</v>
       </c>
       <c r="E268" t="str">
-        <v>2026-07-30T14:03:44.551Z</v>
+        <v>2026-07-30T21:43:36.500Z</v>
       </c>
     </row>
     <row r="269">
@@ -4963,13 +4963,13 @@
         <v>Verify Security functionality module 268</v>
       </c>
       <c r="C269" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D269">
-        <v>1.79</v>
+        <v>1.09</v>
       </c>
       <c r="E269" t="str">
-        <v>2026-07-30T14:03:45.551Z</v>
+        <v>2026-07-30T21:43:37.500Z</v>
       </c>
     </row>
     <row r="270">
@@ -4983,10 +4983,10 @@
         <v>Passed</v>
       </c>
       <c r="D270">
-        <v>0.71</v>
+        <v>0.2</v>
       </c>
       <c r="E270" t="str">
-        <v>2026-07-30T14:03:46.551Z</v>
+        <v>2026-07-30T21:43:38.500Z</v>
       </c>
     </row>
     <row r="271">
@@ -5000,10 +5000,10 @@
         <v>Passed</v>
       </c>
       <c r="D271">
-        <v>1.66</v>
+        <v>1.09</v>
       </c>
       <c r="E271" t="str">
-        <v>2026-07-30T14:03:47.551Z</v>
+        <v>2026-07-30T21:43:39.500Z</v>
       </c>
     </row>
     <row r="272">
@@ -5017,10 +5017,10 @@
         <v>Passed</v>
       </c>
       <c r="D272">
-        <v>1.09</v>
+        <v>1.91</v>
       </c>
       <c r="E272" t="str">
-        <v>2026-07-30T14:03:48.551Z</v>
+        <v>2026-07-30T21:43:40.500Z</v>
       </c>
     </row>
     <row r="273">
@@ -5034,10 +5034,10 @@
         <v>Passed</v>
       </c>
       <c r="D273">
-        <v>1.23</v>
+        <v>0.57</v>
       </c>
       <c r="E273" t="str">
-        <v>2026-07-30T14:03:49.551Z</v>
+        <v>2026-07-30T21:43:41.500Z</v>
       </c>
     </row>
     <row r="274">
@@ -5051,10 +5051,10 @@
         <v>Passed</v>
       </c>
       <c r="D274">
-        <v>0.36</v>
+        <v>1.61</v>
       </c>
       <c r="E274" t="str">
-        <v>2026-07-30T14:03:50.551Z</v>
+        <v>2026-07-30T21:43:42.500Z</v>
       </c>
     </row>
     <row r="275">
@@ -5068,10 +5068,10 @@
         <v>Passed</v>
       </c>
       <c r="D275">
-        <v>0.23</v>
+        <v>0.4</v>
       </c>
       <c r="E275" t="str">
-        <v>2026-07-30T14:03:51.551Z</v>
+        <v>2026-07-30T21:43:43.500Z</v>
       </c>
     </row>
     <row r="276">
@@ -5085,10 +5085,10 @@
         <v>Passed</v>
       </c>
       <c r="D276">
-        <v>1.06</v>
+        <v>0.46</v>
       </c>
       <c r="E276" t="str">
-        <v>2026-07-30T14:03:52.551Z</v>
+        <v>2026-07-30T21:43:44.500Z</v>
       </c>
     </row>
     <row r="277">
@@ -5102,10 +5102,10 @@
         <v>Passed</v>
       </c>
       <c r="D277">
-        <v>1.45</v>
+        <v>0.17</v>
       </c>
       <c r="E277" t="str">
-        <v>2026-07-30T14:03:53.551Z</v>
+        <v>2026-07-30T21:43:45.500Z</v>
       </c>
     </row>
     <row r="278">
@@ -5119,10 +5119,10 @@
         <v>Passed</v>
       </c>
       <c r="D278">
-        <v>1.45</v>
+        <v>0.31</v>
       </c>
       <c r="E278" t="str">
-        <v>2026-07-30T14:03:54.551Z</v>
+        <v>2026-07-30T21:43:46.500Z</v>
       </c>
     </row>
     <row r="279">
@@ -5136,10 +5136,10 @@
         <v>Passed</v>
       </c>
       <c r="D279">
-        <v>0.43</v>
+        <v>1.52</v>
       </c>
       <c r="E279" t="str">
-        <v>2026-07-30T14:03:55.551Z</v>
+        <v>2026-07-30T21:43:47.500Z</v>
       </c>
     </row>
     <row r="280">
@@ -5153,10 +5153,10 @@
         <v>Passed</v>
       </c>
       <c r="D280">
-        <v>0.01</v>
+        <v>1.98</v>
       </c>
       <c r="E280" t="str">
-        <v>2026-07-30T14:03:56.551Z</v>
+        <v>2026-07-30T21:43:48.500Z</v>
       </c>
     </row>
     <row r="281">
@@ -5170,10 +5170,10 @@
         <v>Passed</v>
       </c>
       <c r="D281">
-        <v>0.93</v>
+        <v>0.23</v>
       </c>
       <c r="E281" t="str">
-        <v>2026-07-30T14:03:57.551Z</v>
+        <v>2026-07-30T21:43:49.500Z</v>
       </c>
     </row>
     <row r="282">
@@ -5187,10 +5187,10 @@
         <v>Passed</v>
       </c>
       <c r="D282">
-        <v>1.84</v>
+        <v>0.27</v>
       </c>
       <c r="E282" t="str">
-        <v>2026-07-30T14:03:58.551Z</v>
+        <v>2026-07-30T21:43:50.500Z</v>
       </c>
     </row>
     <row r="283">
@@ -5204,10 +5204,10 @@
         <v>Passed</v>
       </c>
       <c r="D283">
-        <v>1.49</v>
+        <v>0.64</v>
       </c>
       <c r="E283" t="str">
-        <v>2026-07-30T14:03:59.551Z</v>
+        <v>2026-07-30T21:43:51.500Z</v>
       </c>
     </row>
     <row r="284">
@@ -5221,10 +5221,10 @@
         <v>Passed</v>
       </c>
       <c r="D284">
-        <v>0.34</v>
+        <v>1.89</v>
       </c>
       <c r="E284" t="str">
-        <v>2026-07-30T14:04:00.551Z</v>
+        <v>2026-07-30T21:43:52.500Z</v>
       </c>
     </row>
     <row r="285">
@@ -5238,10 +5238,10 @@
         <v>Passed</v>
       </c>
       <c r="D285">
-        <v>1.34</v>
+        <v>0.34</v>
       </c>
       <c r="E285" t="str">
-        <v>2026-07-30T14:04:01.551Z</v>
+        <v>2026-07-30T21:43:53.500Z</v>
       </c>
     </row>
     <row r="286">
@@ -5255,10 +5255,10 @@
         <v>Passed</v>
       </c>
       <c r="D286">
-        <v>0.52</v>
+        <v>0.15</v>
       </c>
       <c r="E286" t="str">
-        <v>2026-07-30T14:04:02.551Z</v>
+        <v>2026-07-30T21:43:54.500Z</v>
       </c>
     </row>
     <row r="287">
@@ -5272,10 +5272,10 @@
         <v>Passed</v>
       </c>
       <c r="D287">
-        <v>0.99</v>
+        <v>0.62</v>
       </c>
       <c r="E287" t="str">
-        <v>2026-07-30T14:04:03.551Z</v>
+        <v>2026-07-30T21:43:55.500Z</v>
       </c>
     </row>
     <row r="288">
@@ -5289,10 +5289,10 @@
         <v>Passed</v>
       </c>
       <c r="D288">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="E288" t="str">
-        <v>2026-07-30T14:04:04.551Z</v>
+        <v>2026-07-30T21:43:56.500Z</v>
       </c>
     </row>
     <row r="289">
@@ -5306,10 +5306,10 @@
         <v>Passed</v>
       </c>
       <c r="D289">
-        <v>1.42</v>
+        <v>0.42</v>
       </c>
       <c r="E289" t="str">
-        <v>2026-07-30T14:04:05.551Z</v>
+        <v>2026-07-30T21:43:57.500Z</v>
       </c>
     </row>
     <row r="290">
@@ -5323,10 +5323,10 @@
         <v>Passed</v>
       </c>
       <c r="D290">
-        <v>1.11</v>
+        <v>0.67</v>
       </c>
       <c r="E290" t="str">
-        <v>2026-07-30T14:04:06.551Z</v>
+        <v>2026-07-30T21:43:58.500Z</v>
       </c>
     </row>
     <row r="291">
@@ -5340,10 +5340,10 @@
         <v>Passed</v>
       </c>
       <c r="D291">
-        <v>0.69</v>
+        <v>0.94</v>
       </c>
       <c r="E291" t="str">
-        <v>2026-07-30T14:04:07.551Z</v>
+        <v>2026-07-30T21:43:59.500Z</v>
       </c>
     </row>
     <row r="292">
@@ -5357,10 +5357,10 @@
         <v>Passed</v>
       </c>
       <c r="D292">
-        <v>0.85</v>
+        <v>0.29</v>
       </c>
       <c r="E292" t="str">
-        <v>2026-07-30T14:04:08.551Z</v>
+        <v>2026-07-30T21:44:00.500Z</v>
       </c>
     </row>
     <row r="293">
@@ -5374,10 +5374,10 @@
         <v>Passed</v>
       </c>
       <c r="D293">
-        <v>1.45</v>
+        <v>0.7</v>
       </c>
       <c r="E293" t="str">
-        <v>2026-07-30T14:04:09.551Z</v>
+        <v>2026-07-30T21:44:01.500Z</v>
       </c>
     </row>
     <row r="294">
@@ -5391,10 +5391,10 @@
         <v>Passed</v>
       </c>
       <c r="D294">
-        <v>0.1</v>
+        <v>1.53</v>
       </c>
       <c r="E294" t="str">
-        <v>2026-07-30T14:04:10.551Z</v>
+        <v>2026-07-30T21:44:02.500Z</v>
       </c>
     </row>
     <row r="295">
@@ -5408,10 +5408,10 @@
         <v>Passed</v>
       </c>
       <c r="D295">
-        <v>0.01</v>
+        <v>0.36</v>
       </c>
       <c r="E295" t="str">
-        <v>2026-07-30T14:04:11.551Z</v>
+        <v>2026-07-30T21:44:03.500Z</v>
       </c>
     </row>
     <row r="296">
@@ -5425,10 +5425,10 @@
         <v>Passed</v>
       </c>
       <c r="D296">
-        <v>1.79</v>
+        <v>1.44</v>
       </c>
       <c r="E296" t="str">
-        <v>2026-07-30T14:04:12.551Z</v>
+        <v>2026-07-30T21:44:04.500Z</v>
       </c>
     </row>
     <row r="297">
@@ -5442,10 +5442,10 @@
         <v>Passed</v>
       </c>
       <c r="D297">
-        <v>0.2</v>
+        <v>1.66</v>
       </c>
       <c r="E297" t="str">
-        <v>2026-07-30T14:04:13.551Z</v>
+        <v>2026-07-30T21:44:05.500Z</v>
       </c>
     </row>
     <row r="298">
@@ -5459,10 +5459,10 @@
         <v>Passed</v>
       </c>
       <c r="D298">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="E298" t="str">
-        <v>2026-07-30T14:04:14.551Z</v>
+        <v>2026-07-30T21:44:06.500Z</v>
       </c>
     </row>
     <row r="299">
@@ -5476,10 +5476,10 @@
         <v>Passed</v>
       </c>
       <c r="D299">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="E299" t="str">
-        <v>2026-07-30T14:04:15.551Z</v>
+        <v>2026-07-30T21:44:07.500Z</v>
       </c>
     </row>
     <row r="300">
@@ -5493,10 +5493,10 @@
         <v>Passed</v>
       </c>
       <c r="D300">
-        <v>1.23</v>
+        <v>0.37</v>
       </c>
       <c r="E300" t="str">
-        <v>2026-07-30T14:04:16.551Z</v>
+        <v>2026-07-30T21:44:08.500Z</v>
       </c>
     </row>
     <row r="301">
@@ -5510,10 +5510,10 @@
         <v>Passed</v>
       </c>
       <c r="D301">
-        <v>0.16</v>
+        <v>0.98</v>
       </c>
       <c r="E301" t="str">
-        <v>2026-07-30T14:04:17.551Z</v>
+        <v>2026-07-30T21:44:09.500Z</v>
       </c>
     </row>
     <row r="302">
@@ -5527,10 +5527,10 @@
         <v>Passed</v>
       </c>
       <c r="D302">
-        <v>1.56</v>
+        <v>0.85</v>
       </c>
       <c r="E302" t="str">
-        <v>2026-07-30T14:04:18.551Z</v>
+        <v>2026-07-30T21:44:10.500Z</v>
       </c>
     </row>
     <row r="303">
@@ -5544,10 +5544,10 @@
         <v>Passed</v>
       </c>
       <c r="D303">
-        <v>0.01</v>
+        <v>0.88</v>
       </c>
       <c r="E303" t="str">
-        <v>2026-07-30T14:04:19.551Z</v>
+        <v>2026-07-30T21:44:11.500Z</v>
       </c>
     </row>
     <row r="304">
@@ -5561,10 +5561,10 @@
         <v>Passed</v>
       </c>
       <c r="D304">
-        <v>0.21</v>
+        <v>0.86</v>
       </c>
       <c r="E304" t="str">
-        <v>2026-07-30T14:04:20.551Z</v>
+        <v>2026-07-30T21:44:12.500Z</v>
       </c>
     </row>
     <row r="305">
@@ -5578,10 +5578,10 @@
         <v>Passed</v>
       </c>
       <c r="D305">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="E305" t="str">
-        <v>2026-07-30T14:04:21.551Z</v>
+        <v>2026-07-30T21:44:13.500Z</v>
       </c>
     </row>
     <row r="306">
@@ -5595,10 +5595,10 @@
         <v>Passed</v>
       </c>
       <c r="D306">
-        <v>1.76</v>
+        <v>0.26</v>
       </c>
       <c r="E306" t="str">
-        <v>2026-07-30T14:04:22.551Z</v>
+        <v>2026-07-30T21:44:14.500Z</v>
       </c>
     </row>
     <row r="307">
@@ -5612,10 +5612,10 @@
         <v>Passed</v>
       </c>
       <c r="D307">
-        <v>0.07</v>
+        <v>1.04</v>
       </c>
       <c r="E307" t="str">
-        <v>2026-07-30T14:04:23.551Z</v>
+        <v>2026-07-30T21:44:15.500Z</v>
       </c>
     </row>
     <row r="308">
@@ -5629,10 +5629,10 @@
         <v>Passed</v>
       </c>
       <c r="D308">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="E308" t="str">
-        <v>2026-07-30T14:04:24.551Z</v>
+        <v>2026-07-30T21:44:16.500Z</v>
       </c>
     </row>
     <row r="309">
@@ -5646,10 +5646,10 @@
         <v>Passed</v>
       </c>
       <c r="D309">
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="E309" t="str">
-        <v>2026-07-30T14:04:25.551Z</v>
+        <v>2026-07-30T21:44:17.500Z</v>
       </c>
     </row>
     <row r="310">
@@ -5663,10 +5663,10 @@
         <v>Passed</v>
       </c>
       <c r="D310">
-        <v>0.6</v>
+        <v>1.08</v>
       </c>
       <c r="E310" t="str">
-        <v>2026-07-30T14:04:26.551Z</v>
+        <v>2026-07-30T21:44:18.500Z</v>
       </c>
     </row>
     <row r="311">
@@ -5680,10 +5680,10 @@
         <v>Passed</v>
       </c>
       <c r="D311">
-        <v>0.45</v>
+        <v>1.57</v>
       </c>
       <c r="E311" t="str">
-        <v>2026-07-30T14:04:27.551Z</v>
+        <v>2026-07-30T21:44:19.500Z</v>
       </c>
     </row>
     <row r="312">
@@ -5697,10 +5697,10 @@
         <v>Passed</v>
       </c>
       <c r="D312">
-        <v>1.71</v>
+        <v>1</v>
       </c>
       <c r="E312" t="str">
-        <v>2026-07-30T14:04:28.551Z</v>
+        <v>2026-07-30T21:44:20.500Z</v>
       </c>
     </row>
     <row r="313">
@@ -5714,10 +5714,10 @@
         <v>Passed</v>
       </c>
       <c r="D313">
-        <v>1.83</v>
+        <v>0.48</v>
       </c>
       <c r="E313" t="str">
-        <v>2026-07-30T14:04:29.551Z</v>
+        <v>2026-07-30T21:44:21.500Z</v>
       </c>
     </row>
     <row r="314">
@@ -5731,10 +5731,10 @@
         <v>Passed</v>
       </c>
       <c r="D314">
-        <v>0.88</v>
+        <v>1.81</v>
       </c>
       <c r="E314" t="str">
-        <v>2026-07-30T14:04:30.551Z</v>
+        <v>2026-07-30T21:44:22.500Z</v>
       </c>
     </row>
     <row r="315">
@@ -5748,10 +5748,10 @@
         <v>Passed</v>
       </c>
       <c r="D315">
-        <v>0.83</v>
+        <v>0.45</v>
       </c>
       <c r="E315" t="str">
-        <v>2026-07-30T14:04:31.551Z</v>
+        <v>2026-07-30T21:44:23.500Z</v>
       </c>
     </row>
     <row r="316">
@@ -5765,10 +5765,10 @@
         <v>Passed</v>
       </c>
       <c r="D316">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="E316" t="str">
-        <v>2026-07-30T14:04:32.551Z</v>
+        <v>2026-07-30T21:44:24.500Z</v>
       </c>
     </row>
     <row r="317">
@@ -5782,10 +5782,10 @@
         <v>Passed</v>
       </c>
       <c r="D317">
-        <v>1.16</v>
+        <v>0.98</v>
       </c>
       <c r="E317" t="str">
-        <v>2026-07-30T14:04:33.551Z</v>
+        <v>2026-07-30T21:44:25.500Z</v>
       </c>
     </row>
     <row r="318">
@@ -5799,10 +5799,10 @@
         <v>Passed</v>
       </c>
       <c r="D318">
-        <v>0.83</v>
+        <v>0.11</v>
       </c>
       <c r="E318" t="str">
-        <v>2026-07-30T14:04:34.551Z</v>
+        <v>2026-07-30T21:44:26.500Z</v>
       </c>
     </row>
     <row r="319">
@@ -5816,10 +5816,10 @@
         <v>Passed</v>
       </c>
       <c r="D319">
-        <v>0.73</v>
+        <v>1.25</v>
       </c>
       <c r="E319" t="str">
-        <v>2026-07-30T14:04:35.551Z</v>
+        <v>2026-07-30T21:44:27.500Z</v>
       </c>
     </row>
     <row r="320">
@@ -5833,10 +5833,10 @@
         <v>Passed</v>
       </c>
       <c r="D320">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="E320" t="str">
-        <v>2026-07-30T14:04:36.551Z</v>
+        <v>2026-07-30T21:44:28.500Z</v>
       </c>
     </row>
     <row r="321">
@@ -5850,10 +5850,10 @@
         <v>Passed</v>
       </c>
       <c r="D321">
-        <v>1.06</v>
+        <v>1.84</v>
       </c>
       <c r="E321" t="str">
-        <v>2026-07-30T14:04:37.551Z</v>
+        <v>2026-07-30T21:44:29.500Z</v>
       </c>
     </row>
     <row r="322">
@@ -5867,10 +5867,10 @@
         <v>Passed</v>
       </c>
       <c r="D322">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="E322" t="str">
-        <v>2026-07-30T14:04:38.551Z</v>
+        <v>2026-07-30T21:44:30.500Z</v>
       </c>
     </row>
     <row r="323">
@@ -5884,10 +5884,10 @@
         <v>Passed</v>
       </c>
       <c r="D323">
-        <v>1.53</v>
+        <v>1.07</v>
       </c>
       <c r="E323" t="str">
-        <v>2026-07-30T14:04:39.551Z</v>
+        <v>2026-07-30T21:44:31.500Z</v>
       </c>
     </row>
     <row r="324">
@@ -5901,10 +5901,10 @@
         <v>Passed</v>
       </c>
       <c r="D324">
-        <v>0.35</v>
+        <v>1.8</v>
       </c>
       <c r="E324" t="str">
-        <v>2026-07-30T14:04:40.551Z</v>
+        <v>2026-07-30T21:44:32.500Z</v>
       </c>
     </row>
     <row r="325">
@@ -5918,10 +5918,10 @@
         <v>Passed</v>
       </c>
       <c r="D325">
-        <v>0.95</v>
+        <v>1.72</v>
       </c>
       <c r="E325" t="str">
-        <v>2026-07-30T14:04:41.551Z</v>
+        <v>2026-07-30T21:44:33.500Z</v>
       </c>
     </row>
     <row r="326">
@@ -5935,10 +5935,10 @@
         <v>Passed</v>
       </c>
       <c r="D326">
-        <v>0.19</v>
+        <v>1.91</v>
       </c>
       <c r="E326" t="str">
-        <v>2026-07-30T14:04:42.551Z</v>
+        <v>2026-07-30T21:44:34.500Z</v>
       </c>
     </row>
     <row r="327">
@@ -5952,10 +5952,10 @@
         <v>Passed</v>
       </c>
       <c r="D327">
-        <v>0.88</v>
+        <v>0.32</v>
       </c>
       <c r="E327" t="str">
-        <v>2026-07-30T14:04:43.551Z</v>
+        <v>2026-07-30T21:44:35.500Z</v>
       </c>
     </row>
     <row r="328">
@@ -5969,10 +5969,10 @@
         <v>Passed</v>
       </c>
       <c r="D328">
-        <v>0.41</v>
+        <v>1.57</v>
       </c>
       <c r="E328" t="str">
-        <v>2026-07-30T14:04:44.551Z</v>
+        <v>2026-07-30T21:44:36.500Z</v>
       </c>
     </row>
     <row r="329">
@@ -5986,10 +5986,10 @@
         <v>Passed</v>
       </c>
       <c r="D329">
-        <v>0.43</v>
+        <v>1.97</v>
       </c>
       <c r="E329" t="str">
-        <v>2026-07-30T14:04:45.551Z</v>
+        <v>2026-07-30T21:44:37.500Z</v>
       </c>
     </row>
     <row r="330">
@@ -6003,10 +6003,10 @@
         <v>Passed</v>
       </c>
       <c r="D330">
-        <v>1.06</v>
+        <v>1.88</v>
       </c>
       <c r="E330" t="str">
-        <v>2026-07-30T14:04:46.551Z</v>
+        <v>2026-07-30T21:44:38.500Z</v>
       </c>
     </row>
     <row r="331">
@@ -6020,10 +6020,10 @@
         <v>Passed</v>
       </c>
       <c r="D331">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="E331" t="str">
-        <v>2026-07-30T14:04:47.551Z</v>
+        <v>2026-07-30T21:44:39.500Z</v>
       </c>
     </row>
     <row r="332">
@@ -6037,10 +6037,10 @@
         <v>Passed</v>
       </c>
       <c r="D332">
-        <v>0.75</v>
+        <v>1.08</v>
       </c>
       <c r="E332" t="str">
-        <v>2026-07-30T14:04:48.551Z</v>
+        <v>2026-07-30T21:44:40.500Z</v>
       </c>
     </row>
     <row r="333">
@@ -6054,10 +6054,10 @@
         <v>Passed</v>
       </c>
       <c r="D333">
-        <v>1.46</v>
+        <v>1.78</v>
       </c>
       <c r="E333" t="str">
-        <v>2026-07-30T14:04:49.551Z</v>
+        <v>2026-07-30T21:44:41.500Z</v>
       </c>
     </row>
     <row r="334">
@@ -6071,10 +6071,10 @@
         <v>Passed</v>
       </c>
       <c r="D334">
-        <v>1.65</v>
+        <v>0.22</v>
       </c>
       <c r="E334" t="str">
-        <v>2026-07-30T14:04:50.551Z</v>
+        <v>2026-07-30T21:44:42.500Z</v>
       </c>
     </row>
     <row r="335">
@@ -6088,10 +6088,10 @@
         <v>Passed</v>
       </c>
       <c r="D335">
-        <v>0.53</v>
+        <v>0.48</v>
       </c>
       <c r="E335" t="str">
-        <v>2026-07-30T14:04:51.551Z</v>
+        <v>2026-07-30T21:44:43.500Z</v>
       </c>
     </row>
     <row r="336">
@@ -6105,10 +6105,10 @@
         <v>Passed</v>
       </c>
       <c r="D336">
-        <v>0.16</v>
+        <v>0.28</v>
       </c>
       <c r="E336" t="str">
-        <v>2026-07-30T14:04:52.551Z</v>
+        <v>2026-07-30T21:44:44.500Z</v>
       </c>
     </row>
     <row r="337">
@@ -6122,10 +6122,10 @@
         <v>Passed</v>
       </c>
       <c r="D337">
-        <v>1.67</v>
+        <v>1.21</v>
       </c>
       <c r="E337" t="str">
-        <v>2026-07-30T14:04:53.551Z</v>
+        <v>2026-07-30T21:44:45.500Z</v>
       </c>
     </row>
     <row r="338">
@@ -6139,10 +6139,10 @@
         <v>Passed</v>
       </c>
       <c r="D338">
-        <v>1.56</v>
+        <v>0.99</v>
       </c>
       <c r="E338" t="str">
-        <v>2026-07-30T14:04:54.551Z</v>
+        <v>2026-07-30T21:44:46.500Z</v>
       </c>
     </row>
     <row r="339">
@@ -6156,10 +6156,10 @@
         <v>Passed</v>
       </c>
       <c r="D339">
-        <v>0.5</v>
+        <v>0.03</v>
       </c>
       <c r="E339" t="str">
-        <v>2026-07-30T14:04:55.551Z</v>
+        <v>2026-07-30T21:44:47.500Z</v>
       </c>
     </row>
     <row r="340">
@@ -6173,10 +6173,10 @@
         <v>Passed</v>
       </c>
       <c r="D340">
-        <v>0.17</v>
+        <v>1.43</v>
       </c>
       <c r="E340" t="str">
-        <v>2026-07-30T14:04:56.551Z</v>
+        <v>2026-07-30T21:44:48.500Z</v>
       </c>
     </row>
     <row r="341">
@@ -6190,10 +6190,10 @@
         <v>Passed</v>
       </c>
       <c r="D341">
-        <v>1.31</v>
+        <v>1.94</v>
       </c>
       <c r="E341" t="str">
-        <v>2026-07-30T14:04:57.551Z</v>
+        <v>2026-07-30T21:44:49.500Z</v>
       </c>
     </row>
     <row r="342">
@@ -6207,10 +6207,10 @@
         <v>Passed</v>
       </c>
       <c r="D342">
-        <v>0.77</v>
+        <v>1.61</v>
       </c>
       <c r="E342" t="str">
-        <v>2026-07-30T14:04:58.551Z</v>
+        <v>2026-07-30T21:44:50.500Z</v>
       </c>
     </row>
     <row r="343">
@@ -6224,10 +6224,10 @@
         <v>Passed</v>
       </c>
       <c r="D343">
-        <v>1.19</v>
+        <v>0.74</v>
       </c>
       <c r="E343" t="str">
-        <v>2026-07-30T14:04:59.551Z</v>
+        <v>2026-07-30T21:44:51.500Z</v>
       </c>
     </row>
     <row r="344">
@@ -6241,10 +6241,10 @@
         <v>Passed</v>
       </c>
       <c r="D344">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="E344" t="str">
-        <v>2026-07-30T14:05:00.551Z</v>
+        <v>2026-07-30T21:44:52.500Z</v>
       </c>
     </row>
     <row r="345">
@@ -6255,13 +6255,13 @@
         <v>Verify Security functionality module 344</v>
       </c>
       <c r="C345" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D345">
-        <v>0.67</v>
+        <v>1.6</v>
       </c>
       <c r="E345" t="str">
-        <v>2026-07-30T14:05:01.551Z</v>
+        <v>2026-07-30T21:44:53.500Z</v>
       </c>
     </row>
     <row r="346">
@@ -6275,10 +6275,10 @@
         <v>Passed</v>
       </c>
       <c r="D346">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="E346" t="str">
-        <v>2026-07-30T14:05:02.551Z</v>
+        <v>2026-07-30T21:44:54.500Z</v>
       </c>
     </row>
     <row r="347">
@@ -6292,10 +6292,10 @@
         <v>Passed</v>
       </c>
       <c r="D347">
-        <v>0.77</v>
+        <v>1.68</v>
       </c>
       <c r="E347" t="str">
-        <v>2026-07-30T14:05:03.551Z</v>
+        <v>2026-07-30T21:44:55.500Z</v>
       </c>
     </row>
     <row r="348">
@@ -6309,10 +6309,10 @@
         <v>Passed</v>
       </c>
       <c r="D348">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="E348" t="str">
-        <v>2026-07-30T14:05:04.551Z</v>
+        <v>2026-07-30T21:44:56.500Z</v>
       </c>
     </row>
     <row r="349">
@@ -6326,10 +6326,10 @@
         <v>Passed</v>
       </c>
       <c r="D349">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="E349" t="str">
-        <v>2026-07-30T14:05:05.551Z</v>
+        <v>2026-07-30T21:44:57.500Z</v>
       </c>
     </row>
     <row r="350">
@@ -6343,10 +6343,10 @@
         <v>Passed</v>
       </c>
       <c r="D350">
-        <v>0.5</v>
+        <v>0.97</v>
       </c>
       <c r="E350" t="str">
-        <v>2026-07-30T14:05:06.551Z</v>
+        <v>2026-07-30T21:44:58.500Z</v>
       </c>
     </row>
     <row r="351">
@@ -6360,10 +6360,10 @@
         <v>Passed</v>
       </c>
       <c r="D351">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="E351" t="str">
-        <v>2026-07-30T14:05:07.551Z</v>
+        <v>2026-07-30T21:44:59.500Z</v>
       </c>
     </row>
     <row r="352">
@@ -6374,13 +6374,13 @@
         <v>Verify Security functionality module 351</v>
       </c>
       <c r="C352" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D352">
-        <v>0.87</v>
+        <v>1.47</v>
       </c>
       <c r="E352" t="str">
-        <v>2026-07-30T14:05:08.551Z</v>
+        <v>2026-07-30T21:45:00.500Z</v>
       </c>
     </row>
     <row r="353">
@@ -6394,10 +6394,10 @@
         <v>Passed</v>
       </c>
       <c r="D353">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="E353" t="str">
-        <v>2026-07-30T14:05:09.551Z</v>
+        <v>2026-07-30T21:45:01.500Z</v>
       </c>
     </row>
     <row r="354">
@@ -6411,10 +6411,10 @@
         <v>Passed</v>
       </c>
       <c r="D354">
-        <v>1.23</v>
+        <v>0.05</v>
       </c>
       <c r="E354" t="str">
-        <v>2026-07-30T14:05:10.551Z</v>
+        <v>2026-07-30T21:45:02.500Z</v>
       </c>
     </row>
     <row r="355">
@@ -6428,10 +6428,10 @@
         <v>Passed</v>
       </c>
       <c r="D355">
-        <v>0.76</v>
+        <v>1.57</v>
       </c>
       <c r="E355" t="str">
-        <v>2026-07-30T14:05:11.551Z</v>
+        <v>2026-07-30T21:45:03.500Z</v>
       </c>
     </row>
     <row r="356">
@@ -6445,10 +6445,10 @@
         <v>Passed</v>
       </c>
       <c r="D356">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="E356" t="str">
-        <v>2026-07-30T14:05:12.551Z</v>
+        <v>2026-07-30T21:45:04.500Z</v>
       </c>
     </row>
     <row r="357">
@@ -6462,10 +6462,10 @@
         <v>Passed</v>
       </c>
       <c r="D357">
-        <v>1.83</v>
+        <v>0.87</v>
       </c>
       <c r="E357" t="str">
-        <v>2026-07-30T14:05:13.551Z</v>
+        <v>2026-07-30T21:45:05.500Z</v>
       </c>
     </row>
     <row r="358">
@@ -6479,10 +6479,10 @@
         <v>Passed</v>
       </c>
       <c r="D358">
-        <v>0.42</v>
+        <v>0.66</v>
       </c>
       <c r="E358" t="str">
-        <v>2026-07-30T14:05:14.551Z</v>
+        <v>2026-07-30T21:45:06.500Z</v>
       </c>
     </row>
     <row r="359">
@@ -6496,10 +6496,10 @@
         <v>Passed</v>
       </c>
       <c r="D359">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="E359" t="str">
-        <v>2026-07-30T14:05:15.551Z</v>
+        <v>2026-07-30T21:45:07.500Z</v>
       </c>
     </row>
     <row r="360">
@@ -6513,10 +6513,10 @@
         <v>Passed</v>
       </c>
       <c r="D360">
-        <v>0.3</v>
+        <v>1.72</v>
       </c>
       <c r="E360" t="str">
-        <v>2026-07-30T14:05:16.551Z</v>
+        <v>2026-07-30T21:45:08.500Z</v>
       </c>
     </row>
     <row r="361">
@@ -6530,10 +6530,10 @@
         <v>Passed</v>
       </c>
       <c r="D361">
-        <v>0.48</v>
+        <v>0.59</v>
       </c>
       <c r="E361" t="str">
-        <v>2026-07-30T14:05:17.551Z</v>
+        <v>2026-07-30T21:45:09.500Z</v>
       </c>
     </row>
     <row r="362">
@@ -6547,10 +6547,10 @@
         <v>Passed</v>
       </c>
       <c r="D362">
-        <v>0.58</v>
+        <v>1.85</v>
       </c>
       <c r="E362" t="str">
-        <v>2026-07-30T14:05:18.551Z</v>
+        <v>2026-07-30T21:45:10.500Z</v>
       </c>
     </row>
     <row r="363">
@@ -6564,10 +6564,10 @@
         <v>Passed</v>
       </c>
       <c r="D363">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="E363" t="str">
-        <v>2026-07-30T14:05:19.551Z</v>
+        <v>2026-07-30T21:45:11.500Z</v>
       </c>
     </row>
     <row r="364">
@@ -6581,10 +6581,10 @@
         <v>Passed</v>
       </c>
       <c r="D364">
-        <v>1.55</v>
+        <v>1.13</v>
       </c>
       <c r="E364" t="str">
-        <v>2026-07-30T14:05:20.551Z</v>
+        <v>2026-07-30T21:45:12.500Z</v>
       </c>
     </row>
     <row r="365">
@@ -6595,13 +6595,13 @@
         <v>Verify Security functionality module 364</v>
       </c>
       <c r="C365" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D365">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="E365" t="str">
-        <v>2026-07-30T14:05:21.551Z</v>
+        <v>2026-07-30T21:45:13.500Z</v>
       </c>
     </row>
     <row r="366">
@@ -6615,10 +6615,10 @@
         <v>Passed</v>
       </c>
       <c r="D366">
-        <v>0.55</v>
+        <v>1.47</v>
       </c>
       <c r="E366" t="str">
-        <v>2026-07-30T14:05:22.551Z</v>
+        <v>2026-07-30T21:45:14.500Z</v>
       </c>
     </row>
     <row r="367">
@@ -6632,10 +6632,10 @@
         <v>Passed</v>
       </c>
       <c r="D367">
-        <v>1.29</v>
+        <v>0.37</v>
       </c>
       <c r="E367" t="str">
-        <v>2026-07-30T14:05:23.551Z</v>
+        <v>2026-07-30T21:45:15.500Z</v>
       </c>
     </row>
     <row r="368">
@@ -6649,10 +6649,10 @@
         <v>Passed</v>
       </c>
       <c r="D368">
-        <v>1.27</v>
+        <v>1.59</v>
       </c>
       <c r="E368" t="str">
-        <v>2026-07-30T14:05:24.551Z</v>
+        <v>2026-07-30T21:45:16.500Z</v>
       </c>
     </row>
     <row r="369">
@@ -6666,10 +6666,10 @@
         <v>Passed</v>
       </c>
       <c r="D369">
-        <v>0.47</v>
+        <v>1.77</v>
       </c>
       <c r="E369" t="str">
-        <v>2026-07-30T14:05:25.551Z</v>
+        <v>2026-07-30T21:45:17.500Z</v>
       </c>
     </row>
     <row r="370">
@@ -6683,10 +6683,10 @@
         <v>Passed</v>
       </c>
       <c r="D370">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="E370" t="str">
-        <v>2026-07-30T14:05:26.551Z</v>
+        <v>2026-07-30T21:45:18.500Z</v>
       </c>
     </row>
     <row r="371">
@@ -6700,10 +6700,10 @@
         <v>Passed</v>
       </c>
       <c r="D371">
-        <v>0.89</v>
+        <v>0.07</v>
       </c>
       <c r="E371" t="str">
-        <v>2026-07-30T14:05:27.551Z</v>
+        <v>2026-07-30T21:45:19.500Z</v>
       </c>
     </row>
     <row r="372">
@@ -6717,10 +6717,10 @@
         <v>Passed</v>
       </c>
       <c r="D372">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="E372" t="str">
-        <v>2026-07-30T14:05:28.551Z</v>
+        <v>2026-07-30T21:45:20.500Z</v>
       </c>
     </row>
     <row r="373">
@@ -6734,10 +6734,10 @@
         <v>Passed</v>
       </c>
       <c r="D373">
-        <v>1.47</v>
+        <v>0.32</v>
       </c>
       <c r="E373" t="str">
-        <v>2026-07-30T14:05:29.551Z</v>
+        <v>2026-07-30T21:45:21.500Z</v>
       </c>
     </row>
     <row r="374">
@@ -6751,10 +6751,10 @@
         <v>Passed</v>
       </c>
       <c r="D374">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="E374" t="str">
-        <v>2026-07-30T14:05:30.551Z</v>
+        <v>2026-07-30T21:45:22.500Z</v>
       </c>
     </row>
     <row r="375">
@@ -6768,10 +6768,10 @@
         <v>Passed</v>
       </c>
       <c r="D375">
-        <v>1.81</v>
+        <v>0.16</v>
       </c>
       <c r="E375" t="str">
-        <v>2026-07-30T14:05:31.551Z</v>
+        <v>2026-07-30T21:45:23.500Z</v>
       </c>
     </row>
     <row r="376">
@@ -6788,7 +6788,7 @@
         <v>1.02</v>
       </c>
       <c r="E376" t="str">
-        <v>2026-07-30T14:05:32.551Z</v>
+        <v>2026-07-30T21:45:24.500Z</v>
       </c>
     </row>
     <row r="377">
@@ -6802,10 +6802,10 @@
         <v>Passed</v>
       </c>
       <c r="D377">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="E377" t="str">
-        <v>2026-07-30T14:05:33.551Z</v>
+        <v>2026-07-30T21:45:25.500Z</v>
       </c>
     </row>
     <row r="378">
@@ -6819,10 +6819,10 @@
         <v>Passed</v>
       </c>
       <c r="D378">
-        <v>0.21</v>
+        <v>0.9</v>
       </c>
       <c r="E378" t="str">
-        <v>2026-07-30T14:05:34.551Z</v>
+        <v>2026-07-30T21:45:26.500Z</v>
       </c>
     </row>
     <row r="379">
@@ -6836,10 +6836,10 @@
         <v>Passed</v>
       </c>
       <c r="D379">
-        <v>0.33</v>
+        <v>0.93</v>
       </c>
       <c r="E379" t="str">
-        <v>2026-07-30T14:05:35.551Z</v>
+        <v>2026-07-30T21:45:27.500Z</v>
       </c>
     </row>
     <row r="380">
@@ -6853,10 +6853,10 @@
         <v>Passed</v>
       </c>
       <c r="D380">
-        <v>0.12</v>
+        <v>1.31</v>
       </c>
       <c r="E380" t="str">
-        <v>2026-07-30T14:05:36.551Z</v>
+        <v>2026-07-30T21:45:28.500Z</v>
       </c>
     </row>
     <row r="381">
@@ -6870,10 +6870,10 @@
         <v>Passed</v>
       </c>
       <c r="D381">
-        <v>0.45</v>
+        <v>0.63</v>
       </c>
       <c r="E381" t="str">
-        <v>2026-07-30T14:05:37.551Z</v>
+        <v>2026-07-30T21:45:29.500Z</v>
       </c>
     </row>
     <row r="382">
@@ -6887,10 +6887,10 @@
         <v>Passed</v>
       </c>
       <c r="D382">
-        <v>1.4</v>
+        <v>0.92</v>
       </c>
       <c r="E382" t="str">
-        <v>2026-07-30T14:05:38.551Z</v>
+        <v>2026-07-30T21:45:30.500Z</v>
       </c>
     </row>
     <row r="383">
@@ -6904,10 +6904,10 @@
         <v>Passed</v>
       </c>
       <c r="D383">
-        <v>1.55</v>
+        <v>0.28</v>
       </c>
       <c r="E383" t="str">
-        <v>2026-07-30T14:05:39.551Z</v>
+        <v>2026-07-30T21:45:31.500Z</v>
       </c>
     </row>
     <row r="384">
@@ -6921,10 +6921,10 @@
         <v>Passed</v>
       </c>
       <c r="D384">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="E384" t="str">
-        <v>2026-07-30T14:05:40.551Z</v>
+        <v>2026-07-30T21:45:32.500Z</v>
       </c>
     </row>
     <row r="385">
@@ -6938,10 +6938,10 @@
         <v>Passed</v>
       </c>
       <c r="D385">
-        <v>0.22</v>
+        <v>1.17</v>
       </c>
       <c r="E385" t="str">
-        <v>2026-07-30T14:05:41.551Z</v>
+        <v>2026-07-30T21:45:33.500Z</v>
       </c>
     </row>
     <row r="386">
@@ -6955,10 +6955,10 @@
         <v>Passed</v>
       </c>
       <c r="D386">
-        <v>0.01</v>
+        <v>0.43</v>
       </c>
       <c r="E386" t="str">
-        <v>2026-07-30T14:05:42.551Z</v>
+        <v>2026-07-30T21:45:34.500Z</v>
       </c>
     </row>
     <row r="387">
@@ -6972,10 +6972,10 @@
         <v>Passed</v>
       </c>
       <c r="D387">
-        <v>1.61</v>
+        <v>1.18</v>
       </c>
       <c r="E387" t="str">
-        <v>2026-07-30T14:05:43.551Z</v>
+        <v>2026-07-30T21:45:35.500Z</v>
       </c>
     </row>
     <row r="388">
@@ -6989,10 +6989,10 @@
         <v>Passed</v>
       </c>
       <c r="D388">
-        <v>0.53</v>
+        <v>0.14</v>
       </c>
       <c r="E388" t="str">
-        <v>2026-07-30T14:05:44.551Z</v>
+        <v>2026-07-30T21:45:36.500Z</v>
       </c>
     </row>
     <row r="389">
@@ -7006,10 +7006,10 @@
         <v>Passed</v>
       </c>
       <c r="D389">
-        <v>1.1</v>
+        <v>1.84</v>
       </c>
       <c r="E389" t="str">
-        <v>2026-07-30T14:05:45.551Z</v>
+        <v>2026-07-30T21:45:37.500Z</v>
       </c>
     </row>
     <row r="390">
@@ -7023,10 +7023,10 @@
         <v>Passed</v>
       </c>
       <c r="D390">
-        <v>1.55</v>
+        <v>0.32</v>
       </c>
       <c r="E390" t="str">
-        <v>2026-07-30T14:05:46.551Z</v>
+        <v>2026-07-30T21:45:38.500Z</v>
       </c>
     </row>
     <row r="391">
@@ -7040,10 +7040,10 @@
         <v>Passed</v>
       </c>
       <c r="D391">
-        <v>1.34</v>
+        <v>0.58</v>
       </c>
       <c r="E391" t="str">
-        <v>2026-07-30T14:05:47.551Z</v>
+        <v>2026-07-30T21:45:39.500Z</v>
       </c>
     </row>
     <row r="392">
@@ -7057,10 +7057,10 @@
         <v>Passed</v>
       </c>
       <c r="D392">
-        <v>1.69</v>
+        <v>0.27</v>
       </c>
       <c r="E392" t="str">
-        <v>2026-07-30T14:05:48.551Z</v>
+        <v>2026-07-30T21:45:40.500Z</v>
       </c>
     </row>
     <row r="393">
@@ -7074,10 +7074,10 @@
         <v>Passed</v>
       </c>
       <c r="D393">
-        <v>0.44</v>
+        <v>0.77</v>
       </c>
       <c r="E393" t="str">
-        <v>2026-07-30T14:05:49.551Z</v>
+        <v>2026-07-30T21:45:41.500Z</v>
       </c>
     </row>
     <row r="394">
@@ -7091,10 +7091,10 @@
         <v>Passed</v>
       </c>
       <c r="D394">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="E394" t="str">
-        <v>2026-07-30T14:05:50.551Z</v>
+        <v>2026-07-30T21:45:42.500Z</v>
       </c>
     </row>
     <row r="395">
@@ -7108,10 +7108,10 @@
         <v>Passed</v>
       </c>
       <c r="D395">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="E395" t="str">
-        <v>2026-07-30T14:05:51.551Z</v>
+        <v>2026-07-30T21:45:43.500Z</v>
       </c>
     </row>
     <row r="396">
@@ -7125,10 +7125,10 @@
         <v>Passed</v>
       </c>
       <c r="D396">
-        <v>1.54</v>
+        <v>1.1</v>
       </c>
       <c r="E396" t="str">
-        <v>2026-07-30T14:05:52.551Z</v>
+        <v>2026-07-30T21:45:44.500Z</v>
       </c>
     </row>
     <row r="397">
@@ -7142,10 +7142,10 @@
         <v>Passed</v>
       </c>
       <c r="D397">
-        <v>0.46</v>
+        <v>1.52</v>
       </c>
       <c r="E397" t="str">
-        <v>2026-07-30T14:05:53.551Z</v>
+        <v>2026-07-30T21:45:45.500Z</v>
       </c>
     </row>
     <row r="398">
@@ -7159,10 +7159,10 @@
         <v>Passed</v>
       </c>
       <c r="D398">
-        <v>1.41</v>
+        <v>1.93</v>
       </c>
       <c r="E398" t="str">
-        <v>2026-07-30T14:05:54.551Z</v>
+        <v>2026-07-30T21:45:46.500Z</v>
       </c>
     </row>
     <row r="399">
@@ -7176,10 +7176,10 @@
         <v>Passed</v>
       </c>
       <c r="D399">
-        <v>0.14</v>
+        <v>1.32</v>
       </c>
       <c r="E399" t="str">
-        <v>2026-07-30T14:05:55.551Z</v>
+        <v>2026-07-30T21:45:47.500Z</v>
       </c>
     </row>
     <row r="400">
@@ -7193,10 +7193,10 @@
         <v>Passed</v>
       </c>
       <c r="D400">
-        <v>1.04</v>
+        <v>0.43</v>
       </c>
       <c r="E400" t="str">
-        <v>2026-07-30T14:05:56.551Z</v>
+        <v>2026-07-30T21:45:48.500Z</v>
       </c>
     </row>
     <row r="401">
@@ -7210,10 +7210,10 @@
         <v>Passed</v>
       </c>
       <c r="D401">
-        <v>1.62</v>
+        <v>0.77</v>
       </c>
       <c r="E401" t="str">
-        <v>2026-07-30T14:05:57.551Z</v>
+        <v>2026-07-30T21:45:49.500Z</v>
       </c>
     </row>
     <row r="402">
@@ -7227,10 +7227,10 @@
         <v>Passed</v>
       </c>
       <c r="D402">
-        <v>1.33</v>
+        <v>0.64</v>
       </c>
       <c r="E402" t="str">
-        <v>2026-07-30T14:05:58.551Z</v>
+        <v>2026-07-30T21:45:50.500Z</v>
       </c>
     </row>
     <row r="403">
@@ -7244,10 +7244,10 @@
         <v>Passed</v>
       </c>
       <c r="D403">
-        <v>0.07</v>
+        <v>1.59</v>
       </c>
       <c r="E403" t="str">
-        <v>2026-07-30T14:05:59.551Z</v>
+        <v>2026-07-30T21:45:51.500Z</v>
       </c>
     </row>
     <row r="404">
@@ -7261,10 +7261,10 @@
         <v>Passed</v>
       </c>
       <c r="D404">
-        <v>1.59</v>
+        <v>0.4</v>
       </c>
       <c r="E404" t="str">
-        <v>2026-07-30T14:06:00.551Z</v>
+        <v>2026-07-30T21:45:52.500Z</v>
       </c>
     </row>
     <row r="405">
@@ -7278,10 +7278,10 @@
         <v>Passed</v>
       </c>
       <c r="D405">
-        <v>0.95</v>
+        <v>1.47</v>
       </c>
       <c r="E405" t="str">
-        <v>2026-07-30T14:06:01.551Z</v>
+        <v>2026-07-30T21:45:53.500Z</v>
       </c>
     </row>
     <row r="406">
@@ -7295,10 +7295,10 @@
         <v>Passed</v>
       </c>
       <c r="D406">
-        <v>1.62</v>
+        <v>0.76</v>
       </c>
       <c r="E406" t="str">
-        <v>2026-07-30T14:06:02.551Z</v>
+        <v>2026-07-30T21:45:54.500Z</v>
       </c>
     </row>
     <row r="407">
@@ -7312,10 +7312,10 @@
         <v>Passed</v>
       </c>
       <c r="D407">
-        <v>1.95</v>
+        <v>0.27</v>
       </c>
       <c r="E407" t="str">
-        <v>2026-07-30T14:06:03.551Z</v>
+        <v>2026-07-30T21:45:55.500Z</v>
       </c>
     </row>
     <row r="408">
@@ -7329,10 +7329,10 @@
         <v>Passed</v>
       </c>
       <c r="D408">
-        <v>0.6</v>
+        <v>1.04</v>
       </c>
       <c r="E408" t="str">
-        <v>2026-07-30T14:06:04.551Z</v>
+        <v>2026-07-30T21:45:56.500Z</v>
       </c>
     </row>
     <row r="409">
@@ -7346,10 +7346,10 @@
         <v>Passed</v>
       </c>
       <c r="D409">
-        <v>1.98</v>
+        <v>0.36</v>
       </c>
       <c r="E409" t="str">
-        <v>2026-07-30T14:06:05.551Z</v>
+        <v>2026-07-30T21:45:57.500Z</v>
       </c>
     </row>
     <row r="410">
@@ -7363,10 +7363,10 @@
         <v>Passed</v>
       </c>
       <c r="D410">
-        <v>0.08</v>
+        <v>1.09</v>
       </c>
       <c r="E410" t="str">
-        <v>2026-07-30T14:06:06.551Z</v>
+        <v>2026-07-30T21:45:58.500Z</v>
       </c>
     </row>
     <row r="411">
@@ -7380,10 +7380,10 @@
         <v>Passed</v>
       </c>
       <c r="D411">
-        <v>1.29</v>
+        <v>0.26</v>
       </c>
       <c r="E411" t="str">
-        <v>2026-07-30T14:06:07.551Z</v>
+        <v>2026-07-30T21:45:59.500Z</v>
       </c>
     </row>
     <row r="412">
@@ -7397,10 +7397,10 @@
         <v>Passed</v>
       </c>
       <c r="D412">
-        <v>1.21</v>
+        <v>0.14</v>
       </c>
       <c r="E412" t="str">
-        <v>2026-07-30T14:06:08.551Z</v>
+        <v>2026-07-30T21:46:00.500Z</v>
       </c>
     </row>
     <row r="413">
@@ -7414,10 +7414,10 @@
         <v>Passed</v>
       </c>
       <c r="D413">
-        <v>1.46</v>
+        <v>0.53</v>
       </c>
       <c r="E413" t="str">
-        <v>2026-07-30T14:06:09.551Z</v>
+        <v>2026-07-30T21:46:01.500Z</v>
       </c>
     </row>
     <row r="414">
@@ -7431,10 +7431,10 @@
         <v>Passed</v>
       </c>
       <c r="D414">
-        <v>0.3</v>
+        <v>1.38</v>
       </c>
       <c r="E414" t="str">
-        <v>2026-07-30T14:06:10.551Z</v>
+        <v>2026-07-30T21:46:02.500Z</v>
       </c>
     </row>
     <row r="415">
@@ -7448,10 +7448,10 @@
         <v>Passed</v>
       </c>
       <c r="D415">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="E415" t="str">
-        <v>2026-07-30T14:06:11.551Z</v>
+        <v>2026-07-30T21:46:03.500Z</v>
       </c>
     </row>
     <row r="416">
@@ -7465,10 +7465,10 @@
         <v>Passed</v>
       </c>
       <c r="D416">
-        <v>0.93</v>
+        <v>1.67</v>
       </c>
       <c r="E416" t="str">
-        <v>2026-07-30T14:06:12.551Z</v>
+        <v>2026-07-30T21:46:04.500Z</v>
       </c>
     </row>
     <row r="417">
@@ -7482,10 +7482,10 @@
         <v>Passed</v>
       </c>
       <c r="D417">
-        <v>1.28</v>
+        <v>0.18</v>
       </c>
       <c r="E417" t="str">
-        <v>2026-07-30T14:06:13.551Z</v>
+        <v>2026-07-30T21:46:05.500Z</v>
       </c>
     </row>
     <row r="418">
@@ -7499,10 +7499,10 @@
         <v>Passed</v>
       </c>
       <c r="D418">
-        <v>0.58</v>
+        <v>0.87</v>
       </c>
       <c r="E418" t="str">
-        <v>2026-07-30T14:06:14.551Z</v>
+        <v>2026-07-30T21:46:06.500Z</v>
       </c>
     </row>
     <row r="419">
@@ -7516,10 +7516,10 @@
         <v>Passed</v>
       </c>
       <c r="D419">
-        <v>0.51</v>
+        <v>0.45</v>
       </c>
       <c r="E419" t="str">
-        <v>2026-07-30T14:06:15.551Z</v>
+        <v>2026-07-30T21:46:07.500Z</v>
       </c>
     </row>
     <row r="420">
@@ -7533,10 +7533,10 @@
         <v>Passed</v>
       </c>
       <c r="D420">
-        <v>0.28</v>
+        <v>1.33</v>
       </c>
       <c r="E420" t="str">
-        <v>2026-07-30T14:06:16.551Z</v>
+        <v>2026-07-30T21:46:08.500Z</v>
       </c>
     </row>
     <row r="421">
@@ -7550,10 +7550,10 @@
         <v>Passed</v>
       </c>
       <c r="D421">
-        <v>1.82</v>
+        <v>0.45</v>
       </c>
       <c r="E421" t="str">
-        <v>2026-07-30T14:06:17.551Z</v>
+        <v>2026-07-30T21:46:09.500Z</v>
       </c>
     </row>
     <row r="422">
@@ -7567,10 +7567,10 @@
         <v>Passed</v>
       </c>
       <c r="D422">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="E422" t="str">
-        <v>2026-07-30T14:06:18.551Z</v>
+        <v>2026-07-30T21:46:10.500Z</v>
       </c>
     </row>
     <row r="423">
@@ -7584,10 +7584,10 @@
         <v>Passed</v>
       </c>
       <c r="D423">
-        <v>1.27</v>
+        <v>0.9</v>
       </c>
       <c r="E423" t="str">
-        <v>2026-07-30T14:06:19.551Z</v>
+        <v>2026-07-30T21:46:11.500Z</v>
       </c>
     </row>
     <row r="424">
@@ -7601,10 +7601,10 @@
         <v>Passed</v>
       </c>
       <c r="D424">
-        <v>0.37</v>
+        <v>1.05</v>
       </c>
       <c r="E424" t="str">
-        <v>2026-07-30T14:06:20.551Z</v>
+        <v>2026-07-30T21:46:12.500Z</v>
       </c>
     </row>
     <row r="425">
@@ -7618,10 +7618,10 @@
         <v>Passed</v>
       </c>
       <c r="D425">
-        <v>1.91</v>
+        <v>1.11</v>
       </c>
       <c r="E425" t="str">
-        <v>2026-07-30T14:06:21.551Z</v>
+        <v>2026-07-30T21:46:13.500Z</v>
       </c>
     </row>
     <row r="426">
@@ -7635,10 +7635,10 @@
         <v>Passed</v>
       </c>
       <c r="D426">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="E426" t="str">
-        <v>2026-07-30T14:06:22.551Z</v>
+        <v>2026-07-30T21:46:14.500Z</v>
       </c>
     </row>
     <row r="427">
@@ -7652,10 +7652,10 @@
         <v>Passed</v>
       </c>
       <c r="D427">
-        <v>0.14</v>
+        <v>0.38</v>
       </c>
       <c r="E427" t="str">
-        <v>2026-07-30T14:06:23.551Z</v>
+        <v>2026-07-30T21:46:15.500Z</v>
       </c>
     </row>
     <row r="428">
@@ -7669,10 +7669,10 @@
         <v>Passed</v>
       </c>
       <c r="D428">
-        <v>0.48</v>
+        <v>1.43</v>
       </c>
       <c r="E428" t="str">
-        <v>2026-07-30T14:06:24.551Z</v>
+        <v>2026-07-30T21:46:16.500Z</v>
       </c>
     </row>
     <row r="429">
@@ -7686,10 +7686,10 @@
         <v>Passed</v>
       </c>
       <c r="D429">
-        <v>1.15</v>
+        <v>1.74</v>
       </c>
       <c r="E429" t="str">
-        <v>2026-07-30T14:06:25.551Z</v>
+        <v>2026-07-30T21:46:17.500Z</v>
       </c>
     </row>
     <row r="430">
@@ -7703,10 +7703,10 @@
         <v>Passed</v>
       </c>
       <c r="D430">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="E430" t="str">
-        <v>2026-07-30T14:06:26.551Z</v>
+        <v>2026-07-30T21:46:18.500Z</v>
       </c>
     </row>
     <row r="431">
@@ -7720,10 +7720,10 @@
         <v>Passed</v>
       </c>
       <c r="D431">
-        <v>1.66</v>
+        <v>0.92</v>
       </c>
       <c r="E431" t="str">
-        <v>2026-07-30T14:06:27.551Z</v>
+        <v>2026-07-30T21:46:19.500Z</v>
       </c>
     </row>
     <row r="432">
@@ -7737,10 +7737,10 @@
         <v>Passed</v>
       </c>
       <c r="D432">
-        <v>0.18</v>
+        <v>1.06</v>
       </c>
       <c r="E432" t="str">
-        <v>2026-07-30T14:06:28.551Z</v>
+        <v>2026-07-30T21:46:20.500Z</v>
       </c>
     </row>
     <row r="433">
@@ -7754,10 +7754,10 @@
         <v>Passed</v>
       </c>
       <c r="D433">
-        <v>1.89</v>
+        <v>1.13</v>
       </c>
       <c r="E433" t="str">
-        <v>2026-07-30T14:06:29.551Z</v>
+        <v>2026-07-30T21:46:21.500Z</v>
       </c>
     </row>
     <row r="434">
@@ -7771,10 +7771,10 @@
         <v>Passed</v>
       </c>
       <c r="D434">
-        <v>0.6</v>
+        <v>1.93</v>
       </c>
       <c r="E434" t="str">
-        <v>2026-07-30T14:06:30.551Z</v>
+        <v>2026-07-30T21:46:22.500Z</v>
       </c>
     </row>
     <row r="435">
@@ -7788,10 +7788,10 @@
         <v>Passed</v>
       </c>
       <c r="D435">
-        <v>1.31</v>
+        <v>0.13</v>
       </c>
       <c r="E435" t="str">
-        <v>2026-07-30T14:06:31.551Z</v>
+        <v>2026-07-30T21:46:23.500Z</v>
       </c>
     </row>
     <row r="436">
@@ -7805,10 +7805,10 @@
         <v>Passed</v>
       </c>
       <c r="D436">
-        <v>0.05</v>
+        <v>1.25</v>
       </c>
       <c r="E436" t="str">
-        <v>2026-07-30T14:06:32.551Z</v>
+        <v>2026-07-30T21:46:24.500Z</v>
       </c>
     </row>
     <row r="437">
@@ -7822,10 +7822,10 @@
         <v>Passed</v>
       </c>
       <c r="D437">
-        <v>1.53</v>
+        <v>1.02</v>
       </c>
       <c r="E437" t="str">
-        <v>2026-07-30T14:06:33.551Z</v>
+        <v>2026-07-30T21:46:25.500Z</v>
       </c>
     </row>
     <row r="438">
@@ -7839,10 +7839,10 @@
         <v>Passed</v>
       </c>
       <c r="D438">
-        <v>0.87</v>
+        <v>0.19</v>
       </c>
       <c r="E438" t="str">
-        <v>2026-07-30T14:06:34.551Z</v>
+        <v>2026-07-30T21:46:26.500Z</v>
       </c>
     </row>
     <row r="439">
@@ -7856,10 +7856,10 @@
         <v>Passed</v>
       </c>
       <c r="D439">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="E439" t="str">
-        <v>2026-07-30T14:06:35.551Z</v>
+        <v>2026-07-30T21:46:27.500Z</v>
       </c>
     </row>
     <row r="440">
@@ -7873,10 +7873,10 @@
         <v>Passed</v>
       </c>
       <c r="D440">
-        <v>0.96</v>
+        <v>1.59</v>
       </c>
       <c r="E440" t="str">
-        <v>2026-07-30T14:06:36.551Z</v>
+        <v>2026-07-30T21:46:28.500Z</v>
       </c>
     </row>
     <row r="441">
@@ -7890,10 +7890,10 @@
         <v>Passed</v>
       </c>
       <c r="D441">
-        <v>0.48</v>
+        <v>1.1</v>
       </c>
       <c r="E441" t="str">
-        <v>2026-07-30T14:06:37.551Z</v>
+        <v>2026-07-30T21:46:29.500Z</v>
       </c>
     </row>
     <row r="442">
@@ -7907,10 +7907,10 @@
         <v>Passed</v>
       </c>
       <c r="D442">
-        <v>0.05</v>
+        <v>1.24</v>
       </c>
       <c r="E442" t="str">
-        <v>2026-07-30T14:06:38.551Z</v>
+        <v>2026-07-30T21:46:30.500Z</v>
       </c>
     </row>
     <row r="443">
@@ -7924,10 +7924,10 @@
         <v>Passed</v>
       </c>
       <c r="D443">
-        <v>0.34</v>
+        <v>0.16</v>
       </c>
       <c r="E443" t="str">
-        <v>2026-07-30T14:06:39.551Z</v>
+        <v>2026-07-30T21:46:31.500Z</v>
       </c>
     </row>
     <row r="444">
@@ -7941,10 +7941,10 @@
         <v>Passed</v>
       </c>
       <c r="D444">
-        <v>0.54</v>
+        <v>0.41</v>
       </c>
       <c r="E444" t="str">
-        <v>2026-07-30T14:06:40.551Z</v>
+        <v>2026-07-30T21:46:32.500Z</v>
       </c>
     </row>
     <row r="445">
@@ -7958,10 +7958,10 @@
         <v>Passed</v>
       </c>
       <c r="D445">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="E445" t="str">
-        <v>2026-07-30T14:06:41.551Z</v>
+        <v>2026-07-30T21:46:33.500Z</v>
       </c>
     </row>
     <row r="446">
@@ -7975,10 +7975,10 @@
         <v>Passed</v>
       </c>
       <c r="D446">
-        <v>0.37</v>
+        <v>1.88</v>
       </c>
       <c r="E446" t="str">
-        <v>2026-07-30T14:06:42.551Z</v>
+        <v>2026-07-30T21:46:34.500Z</v>
       </c>
     </row>
     <row r="447">
@@ -7992,10 +7992,10 @@
         <v>Passed</v>
       </c>
       <c r="D447">
-        <v>0.4</v>
+        <v>1.65</v>
       </c>
       <c r="E447" t="str">
-        <v>2026-07-30T14:06:43.551Z</v>
+        <v>2026-07-30T21:46:35.500Z</v>
       </c>
     </row>
     <row r="448">
@@ -8009,10 +8009,10 @@
         <v>Passed</v>
       </c>
       <c r="D448">
-        <v>1.25</v>
+        <v>0.64</v>
       </c>
       <c r="E448" t="str">
-        <v>2026-07-30T14:06:44.551Z</v>
+        <v>2026-07-30T21:46:36.500Z</v>
       </c>
     </row>
     <row r="449">
@@ -8026,10 +8026,10 @@
         <v>Passed</v>
       </c>
       <c r="D449">
-        <v>0.13</v>
+        <v>1.85</v>
       </c>
       <c r="E449" t="str">
-        <v>2026-07-30T14:06:45.551Z</v>
+        <v>2026-07-30T21:46:37.500Z</v>
       </c>
     </row>
     <row r="450">
@@ -8043,10 +8043,10 @@
         <v>Passed</v>
       </c>
       <c r="D450">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="E450" t="str">
-        <v>2026-07-30T14:06:46.551Z</v>
+        <v>2026-07-30T21:46:38.500Z</v>
       </c>
     </row>
     <row r="451">
@@ -8060,10 +8060,10 @@
         <v>Passed</v>
       </c>
       <c r="D451">
-        <v>0.89</v>
+        <v>1.08</v>
       </c>
       <c r="E451" t="str">
-        <v>2026-07-30T14:06:47.551Z</v>
+        <v>2026-07-30T21:46:39.500Z</v>
       </c>
     </row>
     <row r="452">
@@ -8077,10 +8077,10 @@
         <v>Passed</v>
       </c>
       <c r="D452">
-        <v>0.17</v>
+        <v>0.77</v>
       </c>
       <c r="E452" t="str">
-        <v>2026-07-30T14:06:48.551Z</v>
+        <v>2026-07-30T21:46:40.500Z</v>
       </c>
     </row>
     <row r="453">
@@ -8094,10 +8094,10 @@
         <v>Passed</v>
       </c>
       <c r="D453">
-        <v>1.4</v>
+        <v>0.32</v>
       </c>
       <c r="E453" t="str">
-        <v>2026-07-30T14:06:49.551Z</v>
+        <v>2026-07-30T21:46:41.500Z</v>
       </c>
     </row>
     <row r="454">
@@ -8111,10 +8111,10 @@
         <v>Passed</v>
       </c>
       <c r="D454">
-        <v>0.59</v>
+        <v>0.92</v>
       </c>
       <c r="E454" t="str">
-        <v>2026-07-30T14:06:50.551Z</v>
+        <v>2026-07-30T21:46:42.500Z</v>
       </c>
     </row>
     <row r="455">
@@ -8128,10 +8128,10 @@
         <v>Passed</v>
       </c>
       <c r="D455">
-        <v>0.27</v>
+        <v>0.02</v>
       </c>
       <c r="E455" t="str">
-        <v>2026-07-30T14:06:51.551Z</v>
+        <v>2026-07-30T21:46:43.500Z</v>
       </c>
     </row>
     <row r="456">
@@ -8145,10 +8145,10 @@
         <v>Passed</v>
       </c>
       <c r="D456">
-        <v>0.21</v>
+        <v>0.88</v>
       </c>
       <c r="E456" t="str">
-        <v>2026-07-30T14:06:52.551Z</v>
+        <v>2026-07-30T21:46:44.500Z</v>
       </c>
     </row>
     <row r="457">
@@ -8162,10 +8162,10 @@
         <v>Passed</v>
       </c>
       <c r="D457">
-        <v>1.02</v>
+        <v>0.92</v>
       </c>
       <c r="E457" t="str">
-        <v>2026-07-30T14:06:53.551Z</v>
+        <v>2026-07-30T21:46:45.500Z</v>
       </c>
     </row>
     <row r="458">
@@ -8179,10 +8179,10 @@
         <v>Passed</v>
       </c>
       <c r="D458">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="E458" t="str">
-        <v>2026-07-30T14:06:54.551Z</v>
+        <v>2026-07-30T21:46:46.500Z</v>
       </c>
     </row>
     <row r="459">
@@ -8196,10 +8196,10 @@
         <v>Passed</v>
       </c>
       <c r="D459">
-        <v>0.21</v>
+        <v>1.51</v>
       </c>
       <c r="E459" t="str">
-        <v>2026-07-30T14:06:55.551Z</v>
+        <v>2026-07-30T21:46:47.500Z</v>
       </c>
     </row>
     <row r="460">
@@ -8213,10 +8213,10 @@
         <v>Passed</v>
       </c>
       <c r="D460">
-        <v>1.31</v>
+        <v>1.86</v>
       </c>
       <c r="E460" t="str">
-        <v>2026-07-30T14:06:56.551Z</v>
+        <v>2026-07-30T21:46:48.500Z</v>
       </c>
     </row>
     <row r="461">
@@ -8230,10 +8230,10 @@
         <v>Passed</v>
       </c>
       <c r="D461">
-        <v>1.64</v>
+        <v>1.06</v>
       </c>
       <c r="E461" t="str">
-        <v>2026-07-30T14:06:57.551Z</v>
+        <v>2026-07-30T21:46:49.500Z</v>
       </c>
     </row>
     <row r="462">
@@ -8247,10 +8247,10 @@
         <v>Passed</v>
       </c>
       <c r="D462">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E462" t="str">
-        <v>2026-07-30T14:06:58.551Z</v>
+        <v>2026-07-30T21:46:50.500Z</v>
       </c>
     </row>
     <row r="463">
@@ -8264,10 +8264,10 @@
         <v>Passed</v>
       </c>
       <c r="D463">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="E463" t="str">
-        <v>2026-07-30T14:06:59.551Z</v>
+        <v>2026-07-30T21:46:51.500Z</v>
       </c>
     </row>
     <row r="464">
@@ -8281,10 +8281,10 @@
         <v>Passed</v>
       </c>
       <c r="D464">
-        <v>0.42</v>
+        <v>1.21</v>
       </c>
       <c r="E464" t="str">
-        <v>2026-07-30T14:07:00.551Z</v>
+        <v>2026-07-30T21:46:52.500Z</v>
       </c>
     </row>
     <row r="465">
@@ -8298,10 +8298,10 @@
         <v>Passed</v>
       </c>
       <c r="D465">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="E465" t="str">
-        <v>2026-07-30T14:07:01.551Z</v>
+        <v>2026-07-30T21:46:53.500Z</v>
       </c>
     </row>
     <row r="466">
@@ -8315,10 +8315,10 @@
         <v>Passed</v>
       </c>
       <c r="D466">
-        <v>0.73</v>
+        <v>0.4</v>
       </c>
       <c r="E466" t="str">
-        <v>2026-07-30T14:07:02.551Z</v>
+        <v>2026-07-30T21:46:54.500Z</v>
       </c>
     </row>
     <row r="467">
@@ -8332,10 +8332,10 @@
         <v>Passed</v>
       </c>
       <c r="D467">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="E467" t="str">
-        <v>2026-07-30T14:07:03.551Z</v>
+        <v>2026-07-30T21:46:55.500Z</v>
       </c>
     </row>
     <row r="468">
@@ -8349,10 +8349,10 @@
         <v>Passed</v>
       </c>
       <c r="D468">
-        <v>1.56</v>
+        <v>0.42</v>
       </c>
       <c r="E468" t="str">
-        <v>2026-07-30T14:07:04.551Z</v>
+        <v>2026-07-30T21:46:56.500Z</v>
       </c>
     </row>
     <row r="469">
@@ -8366,10 +8366,10 @@
         <v>Passed</v>
       </c>
       <c r="D469">
-        <v>0.67</v>
+        <v>0.94</v>
       </c>
       <c r="E469" t="str">
-        <v>2026-07-30T14:07:05.551Z</v>
+        <v>2026-07-30T21:46:57.500Z</v>
       </c>
     </row>
     <row r="470">
@@ -8383,10 +8383,10 @@
         <v>Passed</v>
       </c>
       <c r="D470">
-        <v>0.19</v>
+        <v>1.26</v>
       </c>
       <c r="E470" t="str">
-        <v>2026-07-30T14:07:06.551Z</v>
+        <v>2026-07-30T21:46:58.500Z</v>
       </c>
     </row>
     <row r="471">
@@ -8400,10 +8400,10 @@
         <v>Passed</v>
       </c>
       <c r="D471">
-        <v>1.05</v>
+        <v>1.47</v>
       </c>
       <c r="E471" t="str">
-        <v>2026-07-30T14:07:07.551Z</v>
+        <v>2026-07-30T21:46:59.500Z</v>
       </c>
     </row>
     <row r="472">
@@ -8417,10 +8417,10 @@
         <v>Passed</v>
       </c>
       <c r="D472">
-        <v>1.85</v>
+        <v>0.22</v>
       </c>
       <c r="E472" t="str">
-        <v>2026-07-30T14:07:08.551Z</v>
+        <v>2026-07-30T21:47:00.500Z</v>
       </c>
     </row>
     <row r="473">
@@ -8434,10 +8434,10 @@
         <v>Passed</v>
       </c>
       <c r="D473">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="E473" t="str">
-        <v>2026-07-30T14:07:09.551Z</v>
+        <v>2026-07-30T21:47:01.500Z</v>
       </c>
     </row>
     <row r="474">
@@ -8451,10 +8451,10 @@
         <v>Passed</v>
       </c>
       <c r="D474">
-        <v>1.82</v>
+        <v>0.1</v>
       </c>
       <c r="E474" t="str">
-        <v>2026-07-30T14:07:10.551Z</v>
+        <v>2026-07-30T21:47:02.500Z</v>
       </c>
     </row>
     <row r="475">
@@ -8468,10 +8468,10 @@
         <v>Passed</v>
       </c>
       <c r="D475">
-        <v>0.95</v>
+        <v>0.74</v>
       </c>
       <c r="E475" t="str">
-        <v>2026-07-30T14:07:11.551Z</v>
+        <v>2026-07-30T21:47:03.500Z</v>
       </c>
     </row>
     <row r="476">
@@ -8485,10 +8485,10 @@
         <v>Passed</v>
       </c>
       <c r="D476">
-        <v>1.31</v>
+        <v>0.47</v>
       </c>
       <c r="E476" t="str">
-        <v>2026-07-30T14:07:12.551Z</v>
+        <v>2026-07-30T21:47:04.500Z</v>
       </c>
     </row>
     <row r="477">
@@ -8502,10 +8502,10 @@
         <v>Passed</v>
       </c>
       <c r="D477">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="E477" t="str">
-        <v>2026-07-30T14:07:13.551Z</v>
+        <v>2026-07-30T21:47:05.500Z</v>
       </c>
     </row>
     <row r="478">
@@ -8519,10 +8519,10 @@
         <v>Passed</v>
       </c>
       <c r="D478">
-        <v>1.21</v>
+        <v>1.92</v>
       </c>
       <c r="E478" t="str">
-        <v>2026-07-30T14:07:14.551Z</v>
+        <v>2026-07-30T21:47:06.500Z</v>
       </c>
     </row>
     <row r="479">
@@ -8536,10 +8536,10 @@
         <v>Passed</v>
       </c>
       <c r="D479">
-        <v>0.41</v>
+        <v>1.91</v>
       </c>
       <c r="E479" t="str">
-        <v>2026-07-30T14:07:15.551Z</v>
+        <v>2026-07-30T21:47:07.500Z</v>
       </c>
     </row>
     <row r="480">
@@ -8553,15 +8553,338 @@
         <v>Passed</v>
       </c>
       <c r="D480">
-        <v>0.99</v>
+        <v>1.73</v>
       </c>
       <c r="E480" t="str">
-        <v>2026-07-30T14:07:16.551Z</v>
+        <v>2026-07-30T21:47:08.500Z</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="str">
+        <v>Security-TC-0480</v>
+      </c>
+      <c r="B481" t="str">
+        <v>Verify Security functionality module 480</v>
+      </c>
+      <c r="C481" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D481">
+        <v>0.05</v>
+      </c>
+      <c r="E481" t="str">
+        <v>2026-07-30T21:47:09.500Z</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="str">
+        <v>Security-TC-0481</v>
+      </c>
+      <c r="B482" t="str">
+        <v>Verify Security functionality module 481</v>
+      </c>
+      <c r="C482" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D482">
+        <v>1.56</v>
+      </c>
+      <c r="E482" t="str">
+        <v>2026-07-30T21:47:10.500Z</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="str">
+        <v>Security-TC-0482</v>
+      </c>
+      <c r="B483" t="str">
+        <v>Verify Security functionality module 482</v>
+      </c>
+      <c r="C483" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D483">
+        <v>1.58</v>
+      </c>
+      <c r="E483" t="str">
+        <v>2026-07-30T21:47:11.500Z</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="str">
+        <v>Security-TC-0483</v>
+      </c>
+      <c r="B484" t="str">
+        <v>Verify Security functionality module 483</v>
+      </c>
+      <c r="C484" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D484">
+        <v>0.96</v>
+      </c>
+      <c r="E484" t="str">
+        <v>2026-07-30T21:47:12.500Z</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="str">
+        <v>Security-TC-0484</v>
+      </c>
+      <c r="B485" t="str">
+        <v>Verify Security functionality module 484</v>
+      </c>
+      <c r="C485" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D485">
+        <v>0.45</v>
+      </c>
+      <c r="E485" t="str">
+        <v>2026-07-30T21:47:13.500Z</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="str">
+        <v>Security-TC-0485</v>
+      </c>
+      <c r="B486" t="str">
+        <v>Verify Security functionality module 485</v>
+      </c>
+      <c r="C486" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D486">
+        <v>0.31</v>
+      </c>
+      <c r="E486" t="str">
+        <v>2026-07-30T21:47:14.500Z</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="str">
+        <v>Security-TC-0486</v>
+      </c>
+      <c r="B487" t="str">
+        <v>Verify Security functionality module 486</v>
+      </c>
+      <c r="C487" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D487">
+        <v>0.22</v>
+      </c>
+      <c r="E487" t="str">
+        <v>2026-07-30T21:47:15.500Z</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="str">
+        <v>Security-TC-0487</v>
+      </c>
+      <c r="B488" t="str">
+        <v>Verify Security functionality module 487</v>
+      </c>
+      <c r="C488" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D488">
+        <v>1.78</v>
+      </c>
+      <c r="E488" t="str">
+        <v>2026-07-30T21:47:16.500Z</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="str">
+        <v>Security-TC-0488</v>
+      </c>
+      <c r="B489" t="str">
+        <v>Verify Security functionality module 488</v>
+      </c>
+      <c r="C489" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D489">
+        <v>0.08</v>
+      </c>
+      <c r="E489" t="str">
+        <v>2026-07-30T21:47:17.500Z</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="str">
+        <v>Security-TC-0489</v>
+      </c>
+      <c r="B490" t="str">
+        <v>Verify Security functionality module 489</v>
+      </c>
+      <c r="C490" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D490">
+        <v>0.78</v>
+      </c>
+      <c r="E490" t="str">
+        <v>2026-07-30T21:47:18.500Z</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="str">
+        <v>Security-TC-0490</v>
+      </c>
+      <c r="B491" t="str">
+        <v>Verify Security functionality module 490</v>
+      </c>
+      <c r="C491" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D491">
+        <v>1.93</v>
+      </c>
+      <c r="E491" t="str">
+        <v>2026-07-30T21:47:19.500Z</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="str">
+        <v>Security-TC-0491</v>
+      </c>
+      <c r="B492" t="str">
+        <v>Verify Security functionality module 491</v>
+      </c>
+      <c r="C492" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D492">
+        <v>1.91</v>
+      </c>
+      <c r="E492" t="str">
+        <v>2026-07-30T21:47:20.500Z</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="str">
+        <v>Security-TC-0492</v>
+      </c>
+      <c r="B493" t="str">
+        <v>Verify Security functionality module 492</v>
+      </c>
+      <c r="C493" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D493">
+        <v>1.32</v>
+      </c>
+      <c r="E493" t="str">
+        <v>2026-07-30T21:47:21.500Z</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="str">
+        <v>Security-TC-0493</v>
+      </c>
+      <c r="B494" t="str">
+        <v>Verify Security functionality module 493</v>
+      </c>
+      <c r="C494" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D494">
+        <v>0.66</v>
+      </c>
+      <c r="E494" t="str">
+        <v>2026-07-30T21:47:22.500Z</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="str">
+        <v>Security-TC-0494</v>
+      </c>
+      <c r="B495" t="str">
+        <v>Verify Security functionality module 494</v>
+      </c>
+      <c r="C495" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D495">
+        <v>1.46</v>
+      </c>
+      <c r="E495" t="str">
+        <v>2026-07-30T21:47:23.500Z</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="str">
+        <v>Security-TC-0495</v>
+      </c>
+      <c r="B496" t="str">
+        <v>Verify Security functionality module 495</v>
+      </c>
+      <c r="C496" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D496">
+        <v>0.04</v>
+      </c>
+      <c r="E496" t="str">
+        <v>2026-07-30T21:47:24.500Z</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="str">
+        <v>Security-TC-0496</v>
+      </c>
+      <c r="B497" t="str">
+        <v>Verify Security functionality module 496</v>
+      </c>
+      <c r="C497" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D497">
+        <v>0.2</v>
+      </c>
+      <c r="E497" t="str">
+        <v>2026-07-30T21:47:25.500Z</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="str">
+        <v>Security-TC-0497</v>
+      </c>
+      <c r="B498" t="str">
+        <v>Verify Security functionality module 497</v>
+      </c>
+      <c r="C498" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D498">
+        <v>1.97</v>
+      </c>
+      <c r="E498" t="str">
+        <v>2026-07-30T21:47:26.500Z</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="str">
+        <v>Security-TC-0498</v>
+      </c>
+      <c r="B499" t="str">
+        <v>Verify Security functionality module 498</v>
+      </c>
+      <c r="C499" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D499">
+        <v>1.13</v>
+      </c>
+      <c r="E499" t="str">
+        <v>2026-07-30T21:47:27.500Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E480"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E499"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reports/latest/backend/Backend_Security_Assessment.xlsx
+++ b/reports/latest/backend/Backend_Security_Assessment.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Test Results" sheetId="1" r:id="rId1"/>
+    <sheet name="Security_Test_Report" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E499"/>
+  <dimension ref="A1:E461"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,10 +427,10 @@
         <v>Passed</v>
       </c>
       <c r="D2">
-        <v>1.91</v>
+        <v>1.35</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-07-30T21:39:10.500Z</v>
+        <v>2026-07-30T21:44:46.069Z</v>
       </c>
     </row>
     <row r="3">
@@ -444,10 +444,10 @@
         <v>Passed</v>
       </c>
       <c r="D3">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-07-30T21:39:11.500Z</v>
+        <v>2026-07-30T21:44:47.069Z</v>
       </c>
     </row>
     <row r="4">
@@ -461,10 +461,10 @@
         <v>Passed</v>
       </c>
       <c r="D4">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-07-30T21:39:12.500Z</v>
+        <v>2026-07-30T21:44:48.069Z</v>
       </c>
     </row>
     <row r="5">
@@ -478,10 +478,10 @@
         <v>Passed</v>
       </c>
       <c r="D5">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-07-30T21:39:13.500Z</v>
+        <v>2026-07-30T21:44:49.069Z</v>
       </c>
     </row>
     <row r="6">
@@ -495,10 +495,10 @@
         <v>Passed</v>
       </c>
       <c r="D6">
-        <v>1.28</v>
+        <v>1.73</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-07-30T21:39:14.500Z</v>
+        <v>2026-07-30T21:44:50.069Z</v>
       </c>
     </row>
     <row r="7">
@@ -512,10 +512,10 @@
         <v>Passed</v>
       </c>
       <c r="D7">
-        <v>0.07</v>
+        <v>1.81</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-07-30T21:39:15.500Z</v>
+        <v>2026-07-30T21:44:51.069Z</v>
       </c>
     </row>
     <row r="8">
@@ -529,10 +529,10 @@
         <v>Passed</v>
       </c>
       <c r="D8">
-        <v>0.75</v>
+        <v>1.22</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-07-30T21:39:16.500Z</v>
+        <v>2026-07-30T21:44:52.069Z</v>
       </c>
     </row>
     <row r="9">
@@ -546,10 +546,10 @@
         <v>Passed</v>
       </c>
       <c r="D9">
-        <v>0.49</v>
+        <v>0.94</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-07-30T21:39:17.500Z</v>
+        <v>2026-07-30T21:44:53.069Z</v>
       </c>
     </row>
     <row r="10">
@@ -563,10 +563,10 @@
         <v>Passed</v>
       </c>
       <c r="D10">
-        <v>1.54</v>
+        <v>1.88</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-07-30T21:39:18.500Z</v>
+        <v>2026-07-30T21:44:54.069Z</v>
       </c>
     </row>
     <row r="11">
@@ -580,10 +580,10 @@
         <v>Passed</v>
       </c>
       <c r="D11">
-        <v>0.81</v>
+        <v>0.15</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-07-30T21:39:19.500Z</v>
+        <v>2026-07-30T21:44:55.069Z</v>
       </c>
     </row>
     <row r="12">
@@ -597,10 +597,10 @@
         <v>Passed</v>
       </c>
       <c r="D12">
-        <v>0.87</v>
+        <v>0.57</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-07-30T21:39:20.500Z</v>
+        <v>2026-07-30T21:44:56.069Z</v>
       </c>
     </row>
     <row r="13">
@@ -614,10 +614,10 @@
         <v>Passed</v>
       </c>
       <c r="D13">
-        <v>1.72</v>
+        <v>0.34</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-07-30T21:39:21.500Z</v>
+        <v>2026-07-30T21:44:57.069Z</v>
       </c>
     </row>
     <row r="14">
@@ -631,10 +631,10 @@
         <v>Passed</v>
       </c>
       <c r="D14">
-        <v>0.66</v>
+        <v>1.72</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-07-30T21:39:22.500Z</v>
+        <v>2026-07-30T21:44:58.069Z</v>
       </c>
     </row>
     <row r="15">
@@ -648,10 +648,10 @@
         <v>Passed</v>
       </c>
       <c r="D15">
-        <v>0.14</v>
+        <v>1.85</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-07-30T21:39:23.500Z</v>
+        <v>2026-07-30T21:44:59.069Z</v>
       </c>
     </row>
     <row r="16">
@@ -665,10 +665,10 @@
         <v>Passed</v>
       </c>
       <c r="D16">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-07-30T21:39:24.500Z</v>
+        <v>2026-07-30T21:45:00.069Z</v>
       </c>
     </row>
     <row r="17">
@@ -682,10 +682,10 @@
         <v>Passed</v>
       </c>
       <c r="D17">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-07-30T21:39:25.500Z</v>
+        <v>2026-07-30T21:45:01.069Z</v>
       </c>
     </row>
     <row r="18">
@@ -699,10 +699,10 @@
         <v>Passed</v>
       </c>
       <c r="D18">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-07-30T21:39:26.500Z</v>
+        <v>2026-07-30T21:45:02.069Z</v>
       </c>
     </row>
     <row r="19">
@@ -716,10 +716,10 @@
         <v>Passed</v>
       </c>
       <c r="D19">
-        <v>0.56</v>
+        <v>1.86</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-07-30T21:39:27.500Z</v>
+        <v>2026-07-30T21:45:03.069Z</v>
       </c>
     </row>
     <row r="20">
@@ -733,10 +733,10 @@
         <v>Passed</v>
       </c>
       <c r="D20">
-        <v>0.54</v>
+        <v>0.03</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-07-30T21:39:28.500Z</v>
+        <v>2026-07-30T21:45:04.069Z</v>
       </c>
     </row>
     <row r="21">
@@ -750,10 +750,10 @@
         <v>Passed</v>
       </c>
       <c r="D21">
-        <v>0.75</v>
+        <v>0.43</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-07-30T21:39:29.500Z</v>
+        <v>2026-07-30T21:45:05.069Z</v>
       </c>
     </row>
     <row r="22">
@@ -767,10 +767,10 @@
         <v>Passed</v>
       </c>
       <c r="D22">
-        <v>1.84</v>
+        <v>1.14</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-07-30T21:39:30.500Z</v>
+        <v>2026-07-30T21:45:06.069Z</v>
       </c>
     </row>
     <row r="23">
@@ -784,10 +784,10 @@
         <v>Passed</v>
       </c>
       <c r="D23">
-        <v>0.72</v>
+        <v>0.04</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-07-30T21:39:31.500Z</v>
+        <v>2026-07-30T21:45:07.069Z</v>
       </c>
     </row>
     <row r="24">
@@ -801,10 +801,10 @@
         <v>Passed</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-07-30T21:39:32.500Z</v>
+        <v>2026-07-30T21:45:08.069Z</v>
       </c>
     </row>
     <row r="25">
@@ -818,10 +818,10 @@
         <v>Passed</v>
       </c>
       <c r="D25">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-07-30T21:39:33.500Z</v>
+        <v>2026-07-30T21:45:09.069Z</v>
       </c>
     </row>
     <row r="26">
@@ -835,10 +835,10 @@
         <v>Passed</v>
       </c>
       <c r="D26">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-07-30T21:39:34.500Z</v>
+        <v>2026-07-30T21:45:10.069Z</v>
       </c>
     </row>
     <row r="27">
@@ -852,10 +852,10 @@
         <v>Passed</v>
       </c>
       <c r="D27">
-        <v>0.22</v>
+        <v>1.39</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-07-30T21:39:35.500Z</v>
+        <v>2026-07-30T21:45:11.069Z</v>
       </c>
     </row>
     <row r="28">
@@ -869,10 +869,10 @@
         <v>Passed</v>
       </c>
       <c r="D28">
-        <v>1.22</v>
+        <v>1.54</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-07-30T21:39:36.500Z</v>
+        <v>2026-07-30T21:45:12.069Z</v>
       </c>
     </row>
     <row r="29">
@@ -886,10 +886,10 @@
         <v>Passed</v>
       </c>
       <c r="D29">
-        <v>1.02</v>
+        <v>0.58</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-07-30T21:39:37.500Z</v>
+        <v>2026-07-30T21:45:13.069Z</v>
       </c>
     </row>
     <row r="30">
@@ -903,10 +903,10 @@
         <v>Passed</v>
       </c>
       <c r="D30">
-        <v>0.13</v>
+        <v>1.98</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-07-30T21:39:38.500Z</v>
+        <v>2026-07-30T21:45:14.069Z</v>
       </c>
     </row>
     <row r="31">
@@ -920,10 +920,10 @@
         <v>Passed</v>
       </c>
       <c r="D31">
-        <v>0.77</v>
+        <v>1.86</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-07-30T21:39:39.500Z</v>
+        <v>2026-07-30T21:45:15.069Z</v>
       </c>
     </row>
     <row r="32">
@@ -934,13 +934,13 @@
         <v>Verify Security functionality module 31</v>
       </c>
       <c r="C32" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D32">
-        <v>0.09</v>
+        <v>1.13</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-07-30T21:39:40.500Z</v>
+        <v>2026-07-30T21:45:16.069Z</v>
       </c>
     </row>
     <row r="33">
@@ -954,10 +954,10 @@
         <v>Passed</v>
       </c>
       <c r="D33">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-07-30T21:39:41.500Z</v>
+        <v>2026-07-30T21:45:17.069Z</v>
       </c>
     </row>
     <row r="34">
@@ -971,10 +971,10 @@
         <v>Passed</v>
       </c>
       <c r="D34">
-        <v>0.09</v>
+        <v>0.56</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-07-30T21:39:42.500Z</v>
+        <v>2026-07-30T21:45:18.069Z</v>
       </c>
     </row>
     <row r="35">
@@ -988,10 +988,10 @@
         <v>Passed</v>
       </c>
       <c r="D35">
-        <v>0.29</v>
+        <v>1.65</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-07-30T21:39:43.500Z</v>
+        <v>2026-07-30T21:45:19.069Z</v>
       </c>
     </row>
     <row r="36">
@@ -1005,10 +1005,10 @@
         <v>Passed</v>
       </c>
       <c r="D36">
-        <v>1.41</v>
+        <v>0.61</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-07-30T21:39:44.500Z</v>
+        <v>2026-07-30T21:45:20.069Z</v>
       </c>
     </row>
     <row r="37">
@@ -1022,10 +1022,10 @@
         <v>Passed</v>
       </c>
       <c r="D37">
-        <v>1.68</v>
+        <v>0.7</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-07-30T21:39:45.500Z</v>
+        <v>2026-07-30T21:45:21.069Z</v>
       </c>
     </row>
     <row r="38">
@@ -1039,10 +1039,10 @@
         <v>Passed</v>
       </c>
       <c r="D38">
-        <v>0.52</v>
+        <v>1.8</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-07-30T21:39:46.500Z</v>
+        <v>2026-07-30T21:45:22.069Z</v>
       </c>
     </row>
     <row r="39">
@@ -1056,10 +1056,10 @@
         <v>Passed</v>
       </c>
       <c r="D39">
-        <v>1.97</v>
+        <v>0.58</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-07-30T21:39:47.500Z</v>
+        <v>2026-07-30T21:45:23.069Z</v>
       </c>
     </row>
     <row r="40">
@@ -1073,10 +1073,10 @@
         <v>Passed</v>
       </c>
       <c r="D40">
-        <v>1.67</v>
+        <v>0.49</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-07-30T21:39:48.500Z</v>
+        <v>2026-07-30T21:45:24.069Z</v>
       </c>
     </row>
     <row r="41">
@@ -1090,10 +1090,10 @@
         <v>Passed</v>
       </c>
       <c r="D41">
-        <v>0.51</v>
+        <v>1.86</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-07-30T21:39:49.500Z</v>
+        <v>2026-07-30T21:45:25.069Z</v>
       </c>
     </row>
     <row r="42">
@@ -1107,10 +1107,10 @@
         <v>Passed</v>
       </c>
       <c r="D42">
-        <v>0.1</v>
+        <v>0.63</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-07-30T21:39:50.500Z</v>
+        <v>2026-07-30T21:45:26.069Z</v>
       </c>
     </row>
     <row r="43">
@@ -1124,10 +1124,10 @@
         <v>Passed</v>
       </c>
       <c r="D43">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-07-30T21:39:51.500Z</v>
+        <v>2026-07-30T21:45:27.069Z</v>
       </c>
     </row>
     <row r="44">
@@ -1141,10 +1141,10 @@
         <v>Passed</v>
       </c>
       <c r="D44">
-        <v>1.37</v>
+        <v>1.85</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-07-30T21:39:52.500Z</v>
+        <v>2026-07-30T21:45:28.069Z</v>
       </c>
     </row>
     <row r="45">
@@ -1158,10 +1158,10 @@
         <v>Passed</v>
       </c>
       <c r="D45">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-07-30T21:39:53.500Z</v>
+        <v>2026-07-30T21:45:29.069Z</v>
       </c>
     </row>
     <row r="46">
@@ -1175,10 +1175,10 @@
         <v>Passed</v>
       </c>
       <c r="D46">
-        <v>0.41</v>
+        <v>0.71</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-07-30T21:39:54.500Z</v>
+        <v>2026-07-30T21:45:30.069Z</v>
       </c>
     </row>
     <row r="47">
@@ -1192,10 +1192,10 @@
         <v>Passed</v>
       </c>
       <c r="D47">
-        <v>0.27</v>
+        <v>1.99</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-07-30T21:39:55.500Z</v>
+        <v>2026-07-30T21:45:31.069Z</v>
       </c>
     </row>
     <row r="48">
@@ -1209,10 +1209,10 @@
         <v>Passed</v>
       </c>
       <c r="D48">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-07-30T21:39:56.500Z</v>
+        <v>2026-07-30T21:45:32.069Z</v>
       </c>
     </row>
     <row r="49">
@@ -1226,10 +1226,10 @@
         <v>Passed</v>
       </c>
       <c r="D49">
-        <v>1.53</v>
+        <v>0.89</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-07-30T21:39:57.500Z</v>
+        <v>2026-07-30T21:45:33.069Z</v>
       </c>
     </row>
     <row r="50">
@@ -1243,10 +1243,10 @@
         <v>Passed</v>
       </c>
       <c r="D50">
-        <v>1.14</v>
+        <v>1.42</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-07-30T21:39:58.500Z</v>
+        <v>2026-07-30T21:45:34.069Z</v>
       </c>
     </row>
     <row r="51">
@@ -1260,10 +1260,10 @@
         <v>Passed</v>
       </c>
       <c r="D51">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="E51" t="str">
-        <v>2026-07-30T21:39:59.500Z</v>
+        <v>2026-07-30T21:45:35.069Z</v>
       </c>
     </row>
     <row r="52">
@@ -1277,10 +1277,10 @@
         <v>Passed</v>
       </c>
       <c r="D52">
-        <v>0.93</v>
+        <v>0.58</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-07-30T21:40:00.500Z</v>
+        <v>2026-07-30T21:45:36.069Z</v>
       </c>
     </row>
     <row r="53">
@@ -1294,10 +1294,10 @@
         <v>Passed</v>
       </c>
       <c r="D53">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-07-30T21:40:01.500Z</v>
+        <v>2026-07-30T21:45:37.069Z</v>
       </c>
     </row>
     <row r="54">
@@ -1311,10 +1311,10 @@
         <v>Passed</v>
       </c>
       <c r="D54">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-07-30T21:40:02.500Z</v>
+        <v>2026-07-30T21:45:38.069Z</v>
       </c>
     </row>
     <row r="55">
@@ -1328,10 +1328,10 @@
         <v>Passed</v>
       </c>
       <c r="D55">
-        <v>1.53</v>
+        <v>1.99</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-07-30T21:40:03.500Z</v>
+        <v>2026-07-30T21:45:39.069Z</v>
       </c>
     </row>
     <row r="56">
@@ -1345,10 +1345,10 @@
         <v>Passed</v>
       </c>
       <c r="D56">
-        <v>0.76</v>
+        <v>1.22</v>
       </c>
       <c r="E56" t="str">
-        <v>2026-07-30T21:40:04.500Z</v>
+        <v>2026-07-30T21:45:40.069Z</v>
       </c>
     </row>
     <row r="57">
@@ -1362,10 +1362,10 @@
         <v>Passed</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="E57" t="str">
-        <v>2026-07-30T21:40:05.500Z</v>
+        <v>2026-07-30T21:45:41.069Z</v>
       </c>
     </row>
     <row r="58">
@@ -1379,10 +1379,10 @@
         <v>Passed</v>
       </c>
       <c r="D58">
-        <v>1.12</v>
+        <v>0.67</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-07-30T21:40:06.500Z</v>
+        <v>2026-07-30T21:45:42.069Z</v>
       </c>
     </row>
     <row r="59">
@@ -1396,10 +1396,10 @@
         <v>Passed</v>
       </c>
       <c r="D59">
-        <v>0.37</v>
+        <v>1.35</v>
       </c>
       <c r="E59" t="str">
-        <v>2026-07-30T21:40:07.500Z</v>
+        <v>2026-07-30T21:45:43.069Z</v>
       </c>
     </row>
     <row r="60">
@@ -1413,10 +1413,10 @@
         <v>Passed</v>
       </c>
       <c r="D60">
-        <v>0.37</v>
+        <v>1.98</v>
       </c>
       <c r="E60" t="str">
-        <v>2026-07-30T21:40:08.500Z</v>
+        <v>2026-07-30T21:45:44.069Z</v>
       </c>
     </row>
     <row r="61">
@@ -1430,10 +1430,10 @@
         <v>Passed</v>
       </c>
       <c r="D61">
-        <v>0.53</v>
+        <v>0.97</v>
       </c>
       <c r="E61" t="str">
-        <v>2026-07-30T21:40:09.500Z</v>
+        <v>2026-07-30T21:45:45.069Z</v>
       </c>
     </row>
     <row r="62">
@@ -1447,10 +1447,10 @@
         <v>Passed</v>
       </c>
       <c r="D62">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-07-30T21:40:10.500Z</v>
+        <v>2026-07-30T21:45:46.069Z</v>
       </c>
     </row>
     <row r="63">
@@ -1464,10 +1464,10 @@
         <v>Passed</v>
       </c>
       <c r="D63">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-07-30T21:40:11.500Z</v>
+        <v>2026-07-30T21:45:47.069Z</v>
       </c>
     </row>
     <row r="64">
@@ -1481,10 +1481,10 @@
         <v>Passed</v>
       </c>
       <c r="D64">
-        <v>1.58</v>
+        <v>1.02</v>
       </c>
       <c r="E64" t="str">
-        <v>2026-07-30T21:40:12.500Z</v>
+        <v>2026-07-30T21:45:48.069Z</v>
       </c>
     </row>
     <row r="65">
@@ -1498,10 +1498,10 @@
         <v>Passed</v>
       </c>
       <c r="D65">
-        <v>1.69</v>
+        <v>1.88</v>
       </c>
       <c r="E65" t="str">
-        <v>2026-07-30T21:40:13.500Z</v>
+        <v>2026-07-30T21:45:49.069Z</v>
       </c>
     </row>
     <row r="66">
@@ -1515,10 +1515,10 @@
         <v>Passed</v>
       </c>
       <c r="D66">
-        <v>0.23</v>
+        <v>1.66</v>
       </c>
       <c r="E66" t="str">
-        <v>2026-07-30T21:40:14.500Z</v>
+        <v>2026-07-30T21:45:50.069Z</v>
       </c>
     </row>
     <row r="67">
@@ -1532,10 +1532,10 @@
         <v>Passed</v>
       </c>
       <c r="D67">
-        <v>1.53</v>
+        <v>1.06</v>
       </c>
       <c r="E67" t="str">
-        <v>2026-07-30T21:40:15.500Z</v>
+        <v>2026-07-30T21:45:51.069Z</v>
       </c>
     </row>
     <row r="68">
@@ -1549,10 +1549,10 @@
         <v>Passed</v>
       </c>
       <c r="D68">
-        <v>0.92</v>
+        <v>1.33</v>
       </c>
       <c r="E68" t="str">
-        <v>2026-07-30T21:40:16.500Z</v>
+        <v>2026-07-30T21:45:52.069Z</v>
       </c>
     </row>
     <row r="69">
@@ -1566,10 +1566,10 @@
         <v>Passed</v>
       </c>
       <c r="D69">
-        <v>0.25</v>
+        <v>1.75</v>
       </c>
       <c r="E69" t="str">
-        <v>2026-07-30T21:40:17.500Z</v>
+        <v>2026-07-30T21:45:53.069Z</v>
       </c>
     </row>
     <row r="70">
@@ -1583,10 +1583,10 @@
         <v>Passed</v>
       </c>
       <c r="D70">
-        <v>0.51</v>
+        <v>1.35</v>
       </c>
       <c r="E70" t="str">
-        <v>2026-07-30T21:40:18.500Z</v>
+        <v>2026-07-30T21:45:54.069Z</v>
       </c>
     </row>
     <row r="71">
@@ -1600,10 +1600,10 @@
         <v>Passed</v>
       </c>
       <c r="D71">
-        <v>1.98</v>
+        <v>0.52</v>
       </c>
       <c r="E71" t="str">
-        <v>2026-07-30T21:40:19.500Z</v>
+        <v>2026-07-30T21:45:55.069Z</v>
       </c>
     </row>
     <row r="72">
@@ -1617,10 +1617,10 @@
         <v>Passed</v>
       </c>
       <c r="D72">
-        <v>0.97</v>
+        <v>0.16</v>
       </c>
       <c r="E72" t="str">
-        <v>2026-07-30T21:40:20.500Z</v>
+        <v>2026-07-30T21:45:56.069Z</v>
       </c>
     </row>
     <row r="73">
@@ -1634,10 +1634,10 @@
         <v>Passed</v>
       </c>
       <c r="D73">
-        <v>1.81</v>
+        <v>1.32</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-07-30T21:40:21.500Z</v>
+        <v>2026-07-30T21:45:57.069Z</v>
       </c>
     </row>
     <row r="74">
@@ -1651,10 +1651,10 @@
         <v>Passed</v>
       </c>
       <c r="D74">
-        <v>0.11</v>
+        <v>0.33</v>
       </c>
       <c r="E74" t="str">
-        <v>2026-07-30T21:40:22.500Z</v>
+        <v>2026-07-30T21:45:58.069Z</v>
       </c>
     </row>
     <row r="75">
@@ -1668,10 +1668,10 @@
         <v>Passed</v>
       </c>
       <c r="D75">
-        <v>0.2</v>
+        <v>1.77</v>
       </c>
       <c r="E75" t="str">
-        <v>2026-07-30T21:40:23.500Z</v>
+        <v>2026-07-30T21:45:59.069Z</v>
       </c>
     </row>
     <row r="76">
@@ -1685,10 +1685,10 @@
         <v>Passed</v>
       </c>
       <c r="D76">
-        <v>1.25</v>
+        <v>0.33</v>
       </c>
       <c r="E76" t="str">
-        <v>2026-07-30T21:40:24.500Z</v>
+        <v>2026-07-30T21:46:00.069Z</v>
       </c>
     </row>
     <row r="77">
@@ -1702,10 +1702,10 @@
         <v>Passed</v>
       </c>
       <c r="D77">
-        <v>0.41</v>
+        <v>1.99</v>
       </c>
       <c r="E77" t="str">
-        <v>2026-07-30T21:40:25.500Z</v>
+        <v>2026-07-30T21:46:01.069Z</v>
       </c>
     </row>
     <row r="78">
@@ -1719,10 +1719,10 @@
         <v>Passed</v>
       </c>
       <c r="D78">
-        <v>1.37</v>
+        <v>0.1</v>
       </c>
       <c r="E78" t="str">
-        <v>2026-07-30T21:40:26.500Z</v>
+        <v>2026-07-30T21:46:02.069Z</v>
       </c>
     </row>
     <row r="79">
@@ -1736,10 +1736,10 @@
         <v>Passed</v>
       </c>
       <c r="D79">
-        <v>1.55</v>
+        <v>0.3</v>
       </c>
       <c r="E79" t="str">
-        <v>2026-07-30T21:40:27.500Z</v>
+        <v>2026-07-30T21:46:03.069Z</v>
       </c>
     </row>
     <row r="80">
@@ -1753,10 +1753,10 @@
         <v>Passed</v>
       </c>
       <c r="D80">
-        <v>0.12</v>
+        <v>0.01</v>
       </c>
       <c r="E80" t="str">
-        <v>2026-07-30T21:40:28.500Z</v>
+        <v>2026-07-30T21:46:04.069Z</v>
       </c>
     </row>
     <row r="81">
@@ -1770,10 +1770,10 @@
         <v>Passed</v>
       </c>
       <c r="D81">
-        <v>0.85</v>
+        <v>0.13</v>
       </c>
       <c r="E81" t="str">
-        <v>2026-07-30T21:40:29.500Z</v>
+        <v>2026-07-30T21:46:05.069Z</v>
       </c>
     </row>
     <row r="82">
@@ -1787,10 +1787,10 @@
         <v>Passed</v>
       </c>
       <c r="D82">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="E82" t="str">
-        <v>2026-07-30T21:40:30.500Z</v>
+        <v>2026-07-30T21:46:06.069Z</v>
       </c>
     </row>
     <row r="83">
@@ -1804,10 +1804,10 @@
         <v>Passed</v>
       </c>
       <c r="D83">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="E83" t="str">
-        <v>2026-07-30T21:40:31.500Z</v>
+        <v>2026-07-30T21:46:07.069Z</v>
       </c>
     </row>
     <row r="84">
@@ -1821,10 +1821,10 @@
         <v>Passed</v>
       </c>
       <c r="D84">
-        <v>0.17</v>
+        <v>1.03</v>
       </c>
       <c r="E84" t="str">
-        <v>2026-07-30T21:40:32.500Z</v>
+        <v>2026-07-30T21:46:08.069Z</v>
       </c>
     </row>
     <row r="85">
@@ -1838,10 +1838,10 @@
         <v>Passed</v>
       </c>
       <c r="D85">
-        <v>0.91</v>
+        <v>0.08</v>
       </c>
       <c r="E85" t="str">
-        <v>2026-07-30T21:40:33.500Z</v>
+        <v>2026-07-30T21:46:09.069Z</v>
       </c>
     </row>
     <row r="86">
@@ -1855,10 +1855,10 @@
         <v>Passed</v>
       </c>
       <c r="D86">
-        <v>1.12</v>
+        <v>1.58</v>
       </c>
       <c r="E86" t="str">
-        <v>2026-07-30T21:40:34.500Z</v>
+        <v>2026-07-30T21:46:10.069Z</v>
       </c>
     </row>
     <row r="87">
@@ -1872,10 +1872,10 @@
         <v>Passed</v>
       </c>
       <c r="D87">
-        <v>1.69</v>
+        <v>0.8</v>
       </c>
       <c r="E87" t="str">
-        <v>2026-07-30T21:40:35.500Z</v>
+        <v>2026-07-30T21:46:11.069Z</v>
       </c>
     </row>
     <row r="88">
@@ -1889,10 +1889,10 @@
         <v>Passed</v>
       </c>
       <c r="D88">
-        <v>1.81</v>
+        <v>0.91</v>
       </c>
       <c r="E88" t="str">
-        <v>2026-07-30T21:40:36.500Z</v>
+        <v>2026-07-30T21:46:12.069Z</v>
       </c>
     </row>
     <row r="89">
@@ -1906,10 +1906,10 @@
         <v>Passed</v>
       </c>
       <c r="D89">
-        <v>1.44</v>
+        <v>0.47</v>
       </c>
       <c r="E89" t="str">
-        <v>2026-07-30T21:40:37.500Z</v>
+        <v>2026-07-30T21:46:13.069Z</v>
       </c>
     </row>
     <row r="90">
@@ -1923,10 +1923,10 @@
         <v>Passed</v>
       </c>
       <c r="D90">
-        <v>1.57</v>
+        <v>0.37</v>
       </c>
       <c r="E90" t="str">
-        <v>2026-07-30T21:40:38.500Z</v>
+        <v>2026-07-30T21:46:14.069Z</v>
       </c>
     </row>
     <row r="91">
@@ -1940,10 +1940,10 @@
         <v>Passed</v>
       </c>
       <c r="D91">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E91" t="str">
-        <v>2026-07-30T21:40:39.500Z</v>
+        <v>2026-07-30T21:46:15.069Z</v>
       </c>
     </row>
     <row r="92">
@@ -1954,13 +1954,13 @@
         <v>Verify Security functionality module 91</v>
       </c>
       <c r="C92" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D92">
-        <v>1.45</v>
+        <v>0.86</v>
       </c>
       <c r="E92" t="str">
-        <v>2026-07-30T21:40:40.500Z</v>
+        <v>2026-07-30T21:46:16.069Z</v>
       </c>
     </row>
     <row r="93">
@@ -1971,13 +1971,13 @@
         <v>Verify Security functionality module 92</v>
       </c>
       <c r="C93" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D93">
-        <v>1.53</v>
+        <v>0.07</v>
       </c>
       <c r="E93" t="str">
-        <v>2026-07-30T21:40:41.500Z</v>
+        <v>2026-07-30T21:46:17.069Z</v>
       </c>
     </row>
     <row r="94">
@@ -1991,10 +1991,10 @@
         <v>Passed</v>
       </c>
       <c r="D94">
-        <v>0.5</v>
+        <v>1.02</v>
       </c>
       <c r="E94" t="str">
-        <v>2026-07-30T21:40:42.500Z</v>
+        <v>2026-07-30T21:46:18.069Z</v>
       </c>
     </row>
     <row r="95">
@@ -2008,10 +2008,10 @@
         <v>Passed</v>
       </c>
       <c r="D95">
-        <v>0.92</v>
+        <v>0.71</v>
       </c>
       <c r="E95" t="str">
-        <v>2026-07-30T21:40:43.500Z</v>
+        <v>2026-07-30T21:46:19.069Z</v>
       </c>
     </row>
     <row r="96">
@@ -2025,10 +2025,10 @@
         <v>Passed</v>
       </c>
       <c r="D96">
-        <v>1.1</v>
+        <v>1.85</v>
       </c>
       <c r="E96" t="str">
-        <v>2026-07-30T21:40:44.500Z</v>
+        <v>2026-07-30T21:46:20.069Z</v>
       </c>
     </row>
     <row r="97">
@@ -2042,10 +2042,10 @@
         <v>Passed</v>
       </c>
       <c r="D97">
-        <v>0.72</v>
+        <v>1.07</v>
       </c>
       <c r="E97" t="str">
-        <v>2026-07-30T21:40:45.500Z</v>
+        <v>2026-07-30T21:46:21.069Z</v>
       </c>
     </row>
     <row r="98">
@@ -2059,10 +2059,10 @@
         <v>Passed</v>
       </c>
       <c r="D98">
-        <v>0.85</v>
+        <v>1.82</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-07-30T21:40:46.500Z</v>
+        <v>2026-07-30T21:46:22.069Z</v>
       </c>
     </row>
     <row r="99">
@@ -2076,10 +2076,10 @@
         <v>Passed</v>
       </c>
       <c r="D99">
-        <v>1.97</v>
+        <v>1.79</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-07-30T21:40:47.500Z</v>
+        <v>2026-07-30T21:46:23.069Z</v>
       </c>
     </row>
     <row r="100">
@@ -2093,10 +2093,10 @@
         <v>Passed</v>
       </c>
       <c r="D100">
-        <v>0.17</v>
+        <v>0.32</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-07-30T21:40:48.500Z</v>
+        <v>2026-07-30T21:46:24.069Z</v>
       </c>
     </row>
     <row r="101">
@@ -2110,10 +2110,10 @@
         <v>Passed</v>
       </c>
       <c r="D101">
-        <v>0.02</v>
+        <v>0.98</v>
       </c>
       <c r="E101" t="str">
-        <v>2026-07-30T21:40:49.500Z</v>
+        <v>2026-07-30T21:46:25.069Z</v>
       </c>
     </row>
     <row r="102">
@@ -2127,10 +2127,10 @@
         <v>Passed</v>
       </c>
       <c r="D102">
-        <v>1.02</v>
+        <v>0.32</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-07-30T21:40:50.500Z</v>
+        <v>2026-07-30T21:46:26.069Z</v>
       </c>
     </row>
     <row r="103">
@@ -2144,10 +2144,10 @@
         <v>Passed</v>
       </c>
       <c r="D103">
-        <v>0.49</v>
+        <v>1.6</v>
       </c>
       <c r="E103" t="str">
-        <v>2026-07-30T21:40:51.500Z</v>
+        <v>2026-07-30T21:46:27.069Z</v>
       </c>
     </row>
     <row r="104">
@@ -2161,10 +2161,10 @@
         <v>Passed</v>
       </c>
       <c r="D104">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="E104" t="str">
-        <v>2026-07-30T21:40:52.500Z</v>
+        <v>2026-07-30T21:46:28.069Z</v>
       </c>
     </row>
     <row r="105">
@@ -2178,10 +2178,10 @@
         <v>Passed</v>
       </c>
       <c r="D105">
-        <v>1.03</v>
+        <v>0.24</v>
       </c>
       <c r="E105" t="str">
-        <v>2026-07-30T21:40:53.500Z</v>
+        <v>2026-07-30T21:46:29.069Z</v>
       </c>
     </row>
     <row r="106">
@@ -2195,10 +2195,10 @@
         <v>Passed</v>
       </c>
       <c r="D106">
-        <v>1.61</v>
+        <v>1</v>
       </c>
       <c r="E106" t="str">
-        <v>2026-07-30T21:40:54.500Z</v>
+        <v>2026-07-30T21:46:30.069Z</v>
       </c>
     </row>
     <row r="107">
@@ -2212,10 +2212,10 @@
         <v>Passed</v>
       </c>
       <c r="D107">
-        <v>0.87</v>
+        <v>1.94</v>
       </c>
       <c r="E107" t="str">
-        <v>2026-07-30T21:40:55.500Z</v>
+        <v>2026-07-30T21:46:31.069Z</v>
       </c>
     </row>
     <row r="108">
@@ -2229,10 +2229,10 @@
         <v>Passed</v>
       </c>
       <c r="D108">
-        <v>1.97</v>
+        <v>1.18</v>
       </c>
       <c r="E108" t="str">
-        <v>2026-07-30T21:40:56.500Z</v>
+        <v>2026-07-30T21:46:32.069Z</v>
       </c>
     </row>
     <row r="109">
@@ -2246,10 +2246,10 @@
         <v>Passed</v>
       </c>
       <c r="D109">
-        <v>0.55</v>
+        <v>0.27</v>
       </c>
       <c r="E109" t="str">
-        <v>2026-07-30T21:40:57.500Z</v>
+        <v>2026-07-30T21:46:33.069Z</v>
       </c>
     </row>
     <row r="110">
@@ -2263,10 +2263,10 @@
         <v>Passed</v>
       </c>
       <c r="D110">
-        <v>0.96</v>
+        <v>0.72</v>
       </c>
       <c r="E110" t="str">
-        <v>2026-07-30T21:40:58.500Z</v>
+        <v>2026-07-30T21:46:34.069Z</v>
       </c>
     </row>
     <row r="111">
@@ -2280,10 +2280,10 @@
         <v>Passed</v>
       </c>
       <c r="D111">
-        <v>1.63</v>
+        <v>0.27</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-07-30T21:40:59.500Z</v>
+        <v>2026-07-30T21:46:35.069Z</v>
       </c>
     </row>
     <row r="112">
@@ -2297,10 +2297,10 @@
         <v>Passed</v>
       </c>
       <c r="D112">
-        <v>0.97</v>
+        <v>0.29</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-07-30T21:41:00.500Z</v>
+        <v>2026-07-30T21:46:36.069Z</v>
       </c>
     </row>
     <row r="113">
@@ -2314,10 +2314,10 @@
         <v>Passed</v>
       </c>
       <c r="D113">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-07-30T21:41:01.500Z</v>
+        <v>2026-07-30T21:46:37.069Z</v>
       </c>
     </row>
     <row r="114">
@@ -2331,10 +2331,10 @@
         <v>Passed</v>
       </c>
       <c r="D114">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-07-30T21:41:02.500Z</v>
+        <v>2026-07-30T21:46:38.069Z</v>
       </c>
     </row>
     <row r="115">
@@ -2348,10 +2348,10 @@
         <v>Passed</v>
       </c>
       <c r="D115">
-        <v>0.71</v>
+        <v>1.55</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-07-30T21:41:03.500Z</v>
+        <v>2026-07-30T21:46:39.069Z</v>
       </c>
     </row>
     <row r="116">
@@ -2365,10 +2365,10 @@
         <v>Passed</v>
       </c>
       <c r="D116">
-        <v>1.49</v>
+        <v>0.7</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-07-30T21:41:04.500Z</v>
+        <v>2026-07-30T21:46:40.069Z</v>
       </c>
     </row>
     <row r="117">
@@ -2382,10 +2382,10 @@
         <v>Passed</v>
       </c>
       <c r="D117">
-        <v>1.14</v>
+        <v>0.23</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-07-30T21:41:05.500Z</v>
+        <v>2026-07-30T21:46:41.069Z</v>
       </c>
     </row>
     <row r="118">
@@ -2399,10 +2399,10 @@
         <v>Passed</v>
       </c>
       <c r="D118">
-        <v>1.13</v>
+        <v>0.1</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-07-30T21:41:06.500Z</v>
+        <v>2026-07-30T21:46:42.069Z</v>
       </c>
     </row>
     <row r="119">
@@ -2416,10 +2416,10 @@
         <v>Passed</v>
       </c>
       <c r="D119">
-        <v>1.88</v>
+        <v>1.06</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-07-30T21:41:07.500Z</v>
+        <v>2026-07-30T21:46:43.069Z</v>
       </c>
     </row>
     <row r="120">
@@ -2433,10 +2433,10 @@
         <v>Passed</v>
       </c>
       <c r="D120">
-        <v>0.24</v>
+        <v>1.21</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-07-30T21:41:08.500Z</v>
+        <v>2026-07-30T21:46:44.069Z</v>
       </c>
     </row>
     <row r="121">
@@ -2450,10 +2450,10 @@
         <v>Passed</v>
       </c>
       <c r="D121">
-        <v>0.16</v>
+        <v>1.95</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-07-30T21:41:09.500Z</v>
+        <v>2026-07-30T21:46:45.069Z</v>
       </c>
     </row>
     <row r="122">
@@ -2467,10 +2467,10 @@
         <v>Passed</v>
       </c>
       <c r="D122">
-        <v>0.21</v>
+        <v>1.34</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-07-30T21:41:10.500Z</v>
+        <v>2026-07-30T21:46:46.069Z</v>
       </c>
     </row>
     <row r="123">
@@ -2484,10 +2484,10 @@
         <v>Passed</v>
       </c>
       <c r="D123">
-        <v>0.52</v>
+        <v>0.63</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-07-30T21:41:11.500Z</v>
+        <v>2026-07-30T21:46:47.069Z</v>
       </c>
     </row>
     <row r="124">
@@ -2501,10 +2501,10 @@
         <v>Passed</v>
       </c>
       <c r="D124">
-        <v>0.65</v>
+        <v>0.03</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-07-30T21:41:12.500Z</v>
+        <v>2026-07-30T21:46:48.069Z</v>
       </c>
     </row>
     <row r="125">
@@ -2518,10 +2518,10 @@
         <v>Passed</v>
       </c>
       <c r="D125">
-        <v>1.71</v>
+        <v>0.58</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-07-30T21:41:13.500Z</v>
+        <v>2026-07-30T21:46:49.069Z</v>
       </c>
     </row>
     <row r="126">
@@ -2535,10 +2535,10 @@
         <v>Passed</v>
       </c>
       <c r="D126">
-        <v>0.51</v>
+        <v>0.75</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-07-30T21:41:14.500Z</v>
+        <v>2026-07-30T21:46:50.069Z</v>
       </c>
     </row>
     <row r="127">
@@ -2552,10 +2552,10 @@
         <v>Passed</v>
       </c>
       <c r="D127">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-07-30T21:41:15.500Z</v>
+        <v>2026-07-30T21:46:51.069Z</v>
       </c>
     </row>
     <row r="128">
@@ -2569,10 +2569,10 @@
         <v>Passed</v>
       </c>
       <c r="D128">
-        <v>0.05</v>
+        <v>1.63</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-07-30T21:41:16.500Z</v>
+        <v>2026-07-30T21:46:52.069Z</v>
       </c>
     </row>
     <row r="129">
@@ -2586,10 +2586,10 @@
         <v>Passed</v>
       </c>
       <c r="D129">
-        <v>1.32</v>
+        <v>0.77</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-07-30T21:41:17.500Z</v>
+        <v>2026-07-30T21:46:53.069Z</v>
       </c>
     </row>
     <row r="130">
@@ -2603,10 +2603,10 @@
         <v>Passed</v>
       </c>
       <c r="D130">
-        <v>0.04</v>
+        <v>0.14</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-07-30T21:41:18.500Z</v>
+        <v>2026-07-30T21:46:54.069Z</v>
       </c>
     </row>
     <row r="131">
@@ -2620,10 +2620,10 @@
         <v>Passed</v>
       </c>
       <c r="D131">
-        <v>0.4</v>
+        <v>0.09</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-07-30T21:41:19.500Z</v>
+        <v>2026-07-30T21:46:55.069Z</v>
       </c>
     </row>
     <row r="132">
@@ -2637,10 +2637,10 @@
         <v>Passed</v>
       </c>
       <c r="D132">
-        <v>0.76</v>
+        <v>1.87</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-07-30T21:41:20.500Z</v>
+        <v>2026-07-30T21:46:56.069Z</v>
       </c>
     </row>
     <row r="133">
@@ -2654,10 +2654,10 @@
         <v>Passed</v>
       </c>
       <c r="D133">
-        <v>1.55</v>
+        <v>0.19</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-07-30T21:41:21.500Z</v>
+        <v>2026-07-30T21:46:57.069Z</v>
       </c>
     </row>
     <row r="134">
@@ -2671,10 +2671,10 @@
         <v>Passed</v>
       </c>
       <c r="D134">
-        <v>0.48</v>
+        <v>1.1</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-07-30T21:41:22.500Z</v>
+        <v>2026-07-30T21:46:58.069Z</v>
       </c>
     </row>
     <row r="135">
@@ -2688,10 +2688,10 @@
         <v>Passed</v>
       </c>
       <c r="D135">
-        <v>0.22</v>
+        <v>1.23</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-07-30T21:41:23.500Z</v>
+        <v>2026-07-30T21:46:59.069Z</v>
       </c>
     </row>
     <row r="136">
@@ -2705,10 +2705,10 @@
         <v>Passed</v>
       </c>
       <c r="D136">
-        <v>1.83</v>
+        <v>0.41</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-07-30T21:41:24.500Z</v>
+        <v>2026-07-30T21:47:00.069Z</v>
       </c>
     </row>
     <row r="137">
@@ -2722,10 +2722,10 @@
         <v>Passed</v>
       </c>
       <c r="D137">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-07-30T21:41:25.500Z</v>
+        <v>2026-07-30T21:47:01.069Z</v>
       </c>
     </row>
     <row r="138">
@@ -2739,10 +2739,10 @@
         <v>Passed</v>
       </c>
       <c r="D138">
-        <v>0.32</v>
+        <v>1.15</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-07-30T21:41:26.500Z</v>
+        <v>2026-07-30T21:47:02.069Z</v>
       </c>
     </row>
     <row r="139">
@@ -2756,10 +2756,10 @@
         <v>Passed</v>
       </c>
       <c r="D139">
-        <v>0.89</v>
+        <v>1.02</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-07-30T21:41:27.500Z</v>
+        <v>2026-07-30T21:47:03.069Z</v>
       </c>
     </row>
     <row r="140">
@@ -2773,10 +2773,10 @@
         <v>Passed</v>
       </c>
       <c r="D140">
-        <v>0.85</v>
+        <v>1.93</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-07-30T21:41:28.500Z</v>
+        <v>2026-07-30T21:47:04.069Z</v>
       </c>
     </row>
     <row r="141">
@@ -2790,10 +2790,10 @@
         <v>Passed</v>
       </c>
       <c r="D141">
-        <v>1.24</v>
+        <v>0.49</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-07-30T21:41:29.500Z</v>
+        <v>2026-07-30T21:47:05.069Z</v>
       </c>
     </row>
     <row r="142">
@@ -2807,10 +2807,10 @@
         <v>Passed</v>
       </c>
       <c r="D142">
-        <v>1.31</v>
+        <v>0.14</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-07-30T21:41:30.500Z</v>
+        <v>2026-07-30T21:47:06.069Z</v>
       </c>
     </row>
     <row r="143">
@@ -2824,10 +2824,10 @@
         <v>Passed</v>
       </c>
       <c r="D143">
-        <v>0.17</v>
+        <v>1.36</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-07-30T21:41:31.500Z</v>
+        <v>2026-07-30T21:47:07.069Z</v>
       </c>
     </row>
     <row r="144">
@@ -2841,10 +2841,10 @@
         <v>Passed</v>
       </c>
       <c r="D144">
-        <v>1.26</v>
+        <v>0.64</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-07-30T21:41:32.500Z</v>
+        <v>2026-07-30T21:47:08.069Z</v>
       </c>
     </row>
     <row r="145">
@@ -2858,10 +2858,10 @@
         <v>Passed</v>
       </c>
       <c r="D145">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-07-30T21:41:33.500Z</v>
+        <v>2026-07-30T21:47:09.069Z</v>
       </c>
     </row>
     <row r="146">
@@ -2875,10 +2875,10 @@
         <v>Passed</v>
       </c>
       <c r="D146">
-        <v>1.02</v>
+        <v>0.76</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-07-30T21:41:34.500Z</v>
+        <v>2026-07-30T21:47:10.069Z</v>
       </c>
     </row>
     <row r="147">
@@ -2892,10 +2892,10 @@
         <v>Passed</v>
       </c>
       <c r="D147">
-        <v>0.29</v>
+        <v>1.76</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-07-30T21:41:35.500Z</v>
+        <v>2026-07-30T21:47:11.069Z</v>
       </c>
     </row>
     <row r="148">
@@ -2909,10 +2909,10 @@
         <v>Passed</v>
       </c>
       <c r="D148">
-        <v>0.28</v>
+        <v>1.23</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-07-30T21:41:36.500Z</v>
+        <v>2026-07-30T21:47:12.069Z</v>
       </c>
     </row>
     <row r="149">
@@ -2926,10 +2926,10 @@
         <v>Passed</v>
       </c>
       <c r="D149">
-        <v>0.37</v>
+        <v>1.78</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-07-30T21:41:37.500Z</v>
+        <v>2026-07-30T21:47:13.069Z</v>
       </c>
     </row>
     <row r="150">
@@ -2943,10 +2943,10 @@
         <v>Passed</v>
       </c>
       <c r="D150">
-        <v>0.4</v>
+        <v>0.62</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-07-30T21:41:38.500Z</v>
+        <v>2026-07-30T21:47:14.069Z</v>
       </c>
     </row>
     <row r="151">
@@ -2960,10 +2960,10 @@
         <v>Passed</v>
       </c>
       <c r="D151">
-        <v>0.17</v>
+        <v>0.53</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-07-30T21:41:39.500Z</v>
+        <v>2026-07-30T21:47:15.069Z</v>
       </c>
     </row>
     <row r="152">
@@ -2977,10 +2977,10 @@
         <v>Passed</v>
       </c>
       <c r="D152">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-07-30T21:41:40.500Z</v>
+        <v>2026-07-30T21:47:16.069Z</v>
       </c>
     </row>
     <row r="153">
@@ -2994,10 +2994,10 @@
         <v>Passed</v>
       </c>
       <c r="D153">
-        <v>0.65</v>
+        <v>1.1</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-07-30T21:41:41.500Z</v>
+        <v>2026-07-30T21:47:17.069Z</v>
       </c>
     </row>
     <row r="154">
@@ -3011,10 +3011,10 @@
         <v>Passed</v>
       </c>
       <c r="D154">
-        <v>0.1</v>
+        <v>0.72</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-07-30T21:41:42.500Z</v>
+        <v>2026-07-30T21:47:18.069Z</v>
       </c>
     </row>
     <row r="155">
@@ -3028,10 +3028,10 @@
         <v>Passed</v>
       </c>
       <c r="D155">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="E155" t="str">
-        <v>2026-07-30T21:41:43.500Z</v>
+        <v>2026-07-30T21:47:19.069Z</v>
       </c>
     </row>
     <row r="156">
@@ -3045,10 +3045,10 @@
         <v>Passed</v>
       </c>
       <c r="D156">
-        <v>0.81</v>
+        <v>1.49</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-07-30T21:41:44.500Z</v>
+        <v>2026-07-30T21:47:20.069Z</v>
       </c>
     </row>
     <row r="157">
@@ -3062,10 +3062,10 @@
         <v>Passed</v>
       </c>
       <c r="D157">
-        <v>0.35</v>
+        <v>1.16</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-07-30T21:41:45.500Z</v>
+        <v>2026-07-30T21:47:21.069Z</v>
       </c>
     </row>
     <row r="158">
@@ -3079,10 +3079,10 @@
         <v>Passed</v>
       </c>
       <c r="D158">
-        <v>1.41</v>
+        <v>0.92</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-07-30T21:41:46.500Z</v>
+        <v>2026-07-30T21:47:22.069Z</v>
       </c>
     </row>
     <row r="159">
@@ -3096,10 +3096,10 @@
         <v>Passed</v>
       </c>
       <c r="D159">
-        <v>0.24</v>
+        <v>1.97</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-07-30T21:41:47.500Z</v>
+        <v>2026-07-30T21:47:23.069Z</v>
       </c>
     </row>
     <row r="160">
@@ -3113,10 +3113,10 @@
         <v>Passed</v>
       </c>
       <c r="D160">
-        <v>0.49</v>
+        <v>0.32</v>
       </c>
       <c r="E160" t="str">
-        <v>2026-07-30T21:41:48.500Z</v>
+        <v>2026-07-30T21:47:24.069Z</v>
       </c>
     </row>
     <row r="161">
@@ -3130,10 +3130,10 @@
         <v>Passed</v>
       </c>
       <c r="D161">
-        <v>1.82</v>
+        <v>0.1</v>
       </c>
       <c r="E161" t="str">
-        <v>2026-07-30T21:41:49.500Z</v>
+        <v>2026-07-30T21:47:25.069Z</v>
       </c>
     </row>
     <row r="162">
@@ -3147,10 +3147,10 @@
         <v>Passed</v>
       </c>
       <c r="D162">
-        <v>1.17</v>
+        <v>0.8</v>
       </c>
       <c r="E162" t="str">
-        <v>2026-07-30T21:41:50.500Z</v>
+        <v>2026-07-30T21:47:26.069Z</v>
       </c>
     </row>
     <row r="163">
@@ -3164,10 +3164,10 @@
         <v>Passed</v>
       </c>
       <c r="D163">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="E163" t="str">
-        <v>2026-07-30T21:41:51.500Z</v>
+        <v>2026-07-30T21:47:27.069Z</v>
       </c>
     </row>
     <row r="164">
@@ -3181,10 +3181,10 @@
         <v>Passed</v>
       </c>
       <c r="D164">
-        <v>0.49</v>
+        <v>0.23</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-07-30T21:41:52.500Z</v>
+        <v>2026-07-30T21:47:28.069Z</v>
       </c>
     </row>
     <row r="165">
@@ -3198,10 +3198,10 @@
         <v>Passed</v>
       </c>
       <c r="D165">
-        <v>0.71</v>
+        <v>1.61</v>
       </c>
       <c r="E165" t="str">
-        <v>2026-07-30T21:41:53.500Z</v>
+        <v>2026-07-30T21:47:29.069Z</v>
       </c>
     </row>
     <row r="166">
@@ -3215,10 +3215,10 @@
         <v>Passed</v>
       </c>
       <c r="D166">
-        <v>1.66</v>
+        <v>0.31</v>
       </c>
       <c r="E166" t="str">
-        <v>2026-07-30T21:41:54.500Z</v>
+        <v>2026-07-30T21:47:30.069Z</v>
       </c>
     </row>
     <row r="167">
@@ -3232,10 +3232,10 @@
         <v>Passed</v>
       </c>
       <c r="D167">
-        <v>0.4</v>
+        <v>1.04</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-07-30T21:41:55.500Z</v>
+        <v>2026-07-30T21:47:31.069Z</v>
       </c>
     </row>
     <row r="168">
@@ -3246,13 +3246,13 @@
         <v>Verify Security functionality module 167</v>
       </c>
       <c r="C168" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D168">
-        <v>0.88</v>
+        <v>1.09</v>
       </c>
       <c r="E168" t="str">
-        <v>2026-07-30T21:41:56.500Z</v>
+        <v>2026-07-30T21:47:32.069Z</v>
       </c>
     </row>
     <row r="169">
@@ -3266,10 +3266,10 @@
         <v>Passed</v>
       </c>
       <c r="D169">
-        <v>1.53</v>
+        <v>0.2</v>
       </c>
       <c r="E169" t="str">
-        <v>2026-07-30T21:41:57.500Z</v>
+        <v>2026-07-30T21:47:33.069Z</v>
       </c>
     </row>
     <row r="170">
@@ -3283,10 +3283,10 @@
         <v>Passed</v>
       </c>
       <c r="D170">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="E170" t="str">
-        <v>2026-07-30T21:41:58.500Z</v>
+        <v>2026-07-30T21:47:34.069Z</v>
       </c>
     </row>
     <row r="171">
@@ -3300,10 +3300,10 @@
         <v>Passed</v>
       </c>
       <c r="D171">
-        <v>1.71</v>
+        <v>0.54</v>
       </c>
       <c r="E171" t="str">
-        <v>2026-07-30T21:41:59.500Z</v>
+        <v>2026-07-30T21:47:35.069Z</v>
       </c>
     </row>
     <row r="172">
@@ -3317,10 +3317,10 @@
         <v>Passed</v>
       </c>
       <c r="D172">
-        <v>1.88</v>
+        <v>0.47</v>
       </c>
       <c r="E172" t="str">
-        <v>2026-07-30T21:42:00.500Z</v>
+        <v>2026-07-30T21:47:36.069Z</v>
       </c>
     </row>
     <row r="173">
@@ -3334,10 +3334,10 @@
         <v>Passed</v>
       </c>
       <c r="D173">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="E173" t="str">
-        <v>2026-07-30T21:42:01.500Z</v>
+        <v>2026-07-30T21:47:37.069Z</v>
       </c>
     </row>
     <row r="174">
@@ -3351,10 +3351,10 @@
         <v>Passed</v>
       </c>
       <c r="D174">
-        <v>1.61</v>
+        <v>0.89</v>
       </c>
       <c r="E174" t="str">
-        <v>2026-07-30T21:42:02.500Z</v>
+        <v>2026-07-30T21:47:38.069Z</v>
       </c>
     </row>
     <row r="175">
@@ -3368,10 +3368,10 @@
         <v>Passed</v>
       </c>
       <c r="D175">
-        <v>1.47</v>
+        <v>0.34</v>
       </c>
       <c r="E175" t="str">
-        <v>2026-07-30T21:42:03.500Z</v>
+        <v>2026-07-30T21:47:39.069Z</v>
       </c>
     </row>
     <row r="176">
@@ -3385,10 +3385,10 @@
         <v>Passed</v>
       </c>
       <c r="D176">
-        <v>0.62</v>
+        <v>1.15</v>
       </c>
       <c r="E176" t="str">
-        <v>2026-07-30T21:42:04.500Z</v>
+        <v>2026-07-30T21:47:40.069Z</v>
       </c>
     </row>
     <row r="177">
@@ -3402,10 +3402,10 @@
         <v>Passed</v>
       </c>
       <c r="D177">
-        <v>0.72</v>
+        <v>0.83</v>
       </c>
       <c r="E177" t="str">
-        <v>2026-07-30T21:42:05.500Z</v>
+        <v>2026-07-30T21:47:41.069Z</v>
       </c>
     </row>
     <row r="178">
@@ -3419,10 +3419,10 @@
         <v>Passed</v>
       </c>
       <c r="D178">
-        <v>0.23</v>
+        <v>1.37</v>
       </c>
       <c r="E178" t="str">
-        <v>2026-07-30T21:42:06.500Z</v>
+        <v>2026-07-30T21:47:42.069Z</v>
       </c>
     </row>
     <row r="179">
@@ -3436,10 +3436,10 @@
         <v>Passed</v>
       </c>
       <c r="D179">
-        <v>0.06</v>
+        <v>1.24</v>
       </c>
       <c r="E179" t="str">
-        <v>2026-07-30T21:42:07.500Z</v>
+        <v>2026-07-30T21:47:43.069Z</v>
       </c>
     </row>
     <row r="180">
@@ -3453,10 +3453,10 @@
         <v>Passed</v>
       </c>
       <c r="D180">
-        <v>1.14</v>
+        <v>0.1</v>
       </c>
       <c r="E180" t="str">
-        <v>2026-07-30T21:42:08.500Z</v>
+        <v>2026-07-30T21:47:44.069Z</v>
       </c>
     </row>
     <row r="181">
@@ -3470,10 +3470,10 @@
         <v>Passed</v>
       </c>
       <c r="D181">
-        <v>1.59</v>
+        <v>0.73</v>
       </c>
       <c r="E181" t="str">
-        <v>2026-07-30T21:42:09.500Z</v>
+        <v>2026-07-30T21:47:45.069Z</v>
       </c>
     </row>
     <row r="182">
@@ -3487,10 +3487,10 @@
         <v>Passed</v>
       </c>
       <c r="D182">
-        <v>0.15</v>
+        <v>1.18</v>
       </c>
       <c r="E182" t="str">
-        <v>2026-07-30T21:42:10.500Z</v>
+        <v>2026-07-30T21:47:46.069Z</v>
       </c>
     </row>
     <row r="183">
@@ -3504,10 +3504,10 @@
         <v>Passed</v>
       </c>
       <c r="D183">
-        <v>0.05</v>
+        <v>0.63</v>
       </c>
       <c r="E183" t="str">
-        <v>2026-07-30T21:42:11.500Z</v>
+        <v>2026-07-30T21:47:47.069Z</v>
       </c>
     </row>
     <row r="184">
@@ -3521,10 +3521,10 @@
         <v>Passed</v>
       </c>
       <c r="D184">
-        <v>1.26</v>
+        <v>0.02</v>
       </c>
       <c r="E184" t="str">
-        <v>2026-07-30T21:42:12.500Z</v>
+        <v>2026-07-30T21:47:48.069Z</v>
       </c>
     </row>
     <row r="185">
@@ -3538,10 +3538,10 @@
         <v>Passed</v>
       </c>
       <c r="D185">
-        <v>0.48</v>
+        <v>1.3</v>
       </c>
       <c r="E185" t="str">
-        <v>2026-07-30T21:42:13.500Z</v>
+        <v>2026-07-30T21:47:49.069Z</v>
       </c>
     </row>
     <row r="186">
@@ -3555,10 +3555,10 @@
         <v>Passed</v>
       </c>
       <c r="D186">
-        <v>1.77</v>
+        <v>1.22</v>
       </c>
       <c r="E186" t="str">
-        <v>2026-07-30T21:42:14.500Z</v>
+        <v>2026-07-30T21:47:50.069Z</v>
       </c>
     </row>
     <row r="187">
@@ -3572,10 +3572,10 @@
         <v>Passed</v>
       </c>
       <c r="D187">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="E187" t="str">
-        <v>2026-07-30T21:42:15.500Z</v>
+        <v>2026-07-30T21:47:51.069Z</v>
       </c>
     </row>
     <row r="188">
@@ -3589,10 +3589,10 @@
         <v>Passed</v>
       </c>
       <c r="D188">
-        <v>1.64</v>
+        <v>0.64</v>
       </c>
       <c r="E188" t="str">
-        <v>2026-07-30T21:42:16.500Z</v>
+        <v>2026-07-30T21:47:52.069Z</v>
       </c>
     </row>
     <row r="189">
@@ -3606,10 +3606,10 @@
         <v>Passed</v>
       </c>
       <c r="D189">
-        <v>1.25</v>
+        <v>0.1</v>
       </c>
       <c r="E189" t="str">
-        <v>2026-07-30T21:42:17.500Z</v>
+        <v>2026-07-30T21:47:53.069Z</v>
       </c>
     </row>
     <row r="190">
@@ -3623,10 +3623,10 @@
         <v>Passed</v>
       </c>
       <c r="D190">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="E190" t="str">
-        <v>2026-07-30T21:42:18.500Z</v>
+        <v>2026-07-30T21:47:54.069Z</v>
       </c>
     </row>
     <row r="191">
@@ -3640,10 +3640,10 @@
         <v>Passed</v>
       </c>
       <c r="D191">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="E191" t="str">
-        <v>2026-07-30T21:42:19.500Z</v>
+        <v>2026-07-30T21:47:55.069Z</v>
       </c>
     </row>
     <row r="192">
@@ -3657,10 +3657,10 @@
         <v>Passed</v>
       </c>
       <c r="D192">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="E192" t="str">
-        <v>2026-07-30T21:42:20.500Z</v>
+        <v>2026-07-30T21:47:56.069Z</v>
       </c>
     </row>
     <row r="193">
@@ -3674,10 +3674,10 @@
         <v>Passed</v>
       </c>
       <c r="D193">
-        <v>0.41</v>
+        <v>1.95</v>
       </c>
       <c r="E193" t="str">
-        <v>2026-07-30T21:42:21.500Z</v>
+        <v>2026-07-30T21:47:57.069Z</v>
       </c>
     </row>
     <row r="194">
@@ -3691,10 +3691,10 @@
         <v>Passed</v>
       </c>
       <c r="D194">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="E194" t="str">
-        <v>2026-07-30T21:42:22.500Z</v>
+        <v>2026-07-30T21:47:58.069Z</v>
       </c>
     </row>
     <row r="195">
@@ -3708,10 +3708,10 @@
         <v>Passed</v>
       </c>
       <c r="D195">
-        <v>1.03</v>
+        <v>0.81</v>
       </c>
       <c r="E195" t="str">
-        <v>2026-07-30T21:42:23.500Z</v>
+        <v>2026-07-30T21:47:59.069Z</v>
       </c>
     </row>
     <row r="196">
@@ -3725,10 +3725,10 @@
         <v>Passed</v>
       </c>
       <c r="D196">
-        <v>1.53</v>
+        <v>0.91</v>
       </c>
       <c r="E196" t="str">
-        <v>2026-07-30T21:42:24.500Z</v>
+        <v>2026-07-30T21:48:00.069Z</v>
       </c>
     </row>
     <row r="197">
@@ -3742,10 +3742,10 @@
         <v>Passed</v>
       </c>
       <c r="D197">
-        <v>0.84</v>
+        <v>1.37</v>
       </c>
       <c r="E197" t="str">
-        <v>2026-07-30T21:42:25.500Z</v>
+        <v>2026-07-30T21:48:01.069Z</v>
       </c>
     </row>
     <row r="198">
@@ -3759,10 +3759,10 @@
         <v>Passed</v>
       </c>
       <c r="D198">
-        <v>1.18</v>
+        <v>1.59</v>
       </c>
       <c r="E198" t="str">
-        <v>2026-07-30T21:42:26.500Z</v>
+        <v>2026-07-30T21:48:02.069Z</v>
       </c>
     </row>
     <row r="199">
@@ -3773,13 +3773,13 @@
         <v>Verify Security functionality module 198</v>
       </c>
       <c r="C199" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D199">
-        <v>0.62</v>
+        <v>1.76</v>
       </c>
       <c r="E199" t="str">
-        <v>2026-07-30T21:42:27.500Z</v>
+        <v>2026-07-30T21:48:03.069Z</v>
       </c>
     </row>
     <row r="200">
@@ -3793,10 +3793,10 @@
         <v>Passed</v>
       </c>
       <c r="D200">
-        <v>0.43</v>
+        <v>1.03</v>
       </c>
       <c r="E200" t="str">
-        <v>2026-07-30T21:42:28.500Z</v>
+        <v>2026-07-30T21:48:04.069Z</v>
       </c>
     </row>
     <row r="201">
@@ -3810,10 +3810,10 @@
         <v>Passed</v>
       </c>
       <c r="D201">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="E201" t="str">
-        <v>2026-07-30T21:42:29.500Z</v>
+        <v>2026-07-30T21:48:05.069Z</v>
       </c>
     </row>
     <row r="202">
@@ -3827,10 +3827,10 @@
         <v>Passed</v>
       </c>
       <c r="D202">
-        <v>0.23</v>
+        <v>0.45</v>
       </c>
       <c r="E202" t="str">
-        <v>2026-07-30T21:42:30.500Z</v>
+        <v>2026-07-30T21:48:06.069Z</v>
       </c>
     </row>
     <row r="203">
@@ -3844,10 +3844,10 @@
         <v>Passed</v>
       </c>
       <c r="D203">
-        <v>0.63</v>
+        <v>0.34</v>
       </c>
       <c r="E203" t="str">
-        <v>2026-07-30T21:42:31.500Z</v>
+        <v>2026-07-30T21:48:07.069Z</v>
       </c>
     </row>
     <row r="204">
@@ -3861,10 +3861,10 @@
         <v>Passed</v>
       </c>
       <c r="D204">
-        <v>1.82</v>
+        <v>0.06</v>
       </c>
       <c r="E204" t="str">
-        <v>2026-07-30T21:42:32.500Z</v>
+        <v>2026-07-30T21:48:08.069Z</v>
       </c>
     </row>
     <row r="205">
@@ -3878,10 +3878,10 @@
         <v>Passed</v>
       </c>
       <c r="D205">
-        <v>2</v>
+        <v>0.71</v>
       </c>
       <c r="E205" t="str">
-        <v>2026-07-30T21:42:33.500Z</v>
+        <v>2026-07-30T21:48:09.069Z</v>
       </c>
     </row>
     <row r="206">
@@ -3895,10 +3895,10 @@
         <v>Passed</v>
       </c>
       <c r="D206">
-        <v>0.71</v>
+        <v>0.9</v>
       </c>
       <c r="E206" t="str">
-        <v>2026-07-30T21:42:34.500Z</v>
+        <v>2026-07-30T21:48:10.069Z</v>
       </c>
     </row>
     <row r="207">
@@ -3912,10 +3912,10 @@
         <v>Passed</v>
       </c>
       <c r="D207">
-        <v>0.15</v>
+        <v>0.29</v>
       </c>
       <c r="E207" t="str">
-        <v>2026-07-30T21:42:35.500Z</v>
+        <v>2026-07-30T21:48:11.069Z</v>
       </c>
     </row>
     <row r="208">
@@ -3929,10 +3929,10 @@
         <v>Passed</v>
       </c>
       <c r="D208">
-        <v>0.91</v>
+        <v>0.12</v>
       </c>
       <c r="E208" t="str">
-        <v>2026-07-30T21:42:36.500Z</v>
+        <v>2026-07-30T21:48:12.069Z</v>
       </c>
     </row>
     <row r="209">
@@ -3946,10 +3946,10 @@
         <v>Passed</v>
       </c>
       <c r="D209">
-        <v>1.97</v>
+        <v>0.3</v>
       </c>
       <c r="E209" t="str">
-        <v>2026-07-30T21:42:37.500Z</v>
+        <v>2026-07-30T21:48:13.069Z</v>
       </c>
     </row>
     <row r="210">
@@ -3963,10 +3963,10 @@
         <v>Passed</v>
       </c>
       <c r="D210">
-        <v>1.79</v>
+        <v>1.31</v>
       </c>
       <c r="E210" t="str">
-        <v>2026-07-30T21:42:38.500Z</v>
+        <v>2026-07-30T21:48:14.069Z</v>
       </c>
     </row>
     <row r="211">
@@ -3980,10 +3980,10 @@
         <v>Passed</v>
       </c>
       <c r="D211">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="E211" t="str">
-        <v>2026-07-30T21:42:39.500Z</v>
+        <v>2026-07-30T21:48:15.069Z</v>
       </c>
     </row>
     <row r="212">
@@ -3997,10 +3997,10 @@
         <v>Passed</v>
       </c>
       <c r="D212">
-        <v>0.99</v>
+        <v>0.64</v>
       </c>
       <c r="E212" t="str">
-        <v>2026-07-30T21:42:40.500Z</v>
+        <v>2026-07-30T21:48:16.069Z</v>
       </c>
     </row>
     <row r="213">
@@ -4014,10 +4014,10 @@
         <v>Passed</v>
       </c>
       <c r="D213">
-        <v>1.02</v>
+        <v>1.66</v>
       </c>
       <c r="E213" t="str">
-        <v>2026-07-30T21:42:41.500Z</v>
+        <v>2026-07-30T21:48:17.069Z</v>
       </c>
     </row>
     <row r="214">
@@ -4031,10 +4031,10 @@
         <v>Passed</v>
       </c>
       <c r="D214">
-        <v>0.04</v>
+        <v>1.94</v>
       </c>
       <c r="E214" t="str">
-        <v>2026-07-30T21:42:42.500Z</v>
+        <v>2026-07-30T21:48:18.069Z</v>
       </c>
     </row>
     <row r="215">
@@ -4048,10 +4048,10 @@
         <v>Passed</v>
       </c>
       <c r="D215">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="E215" t="str">
-        <v>2026-07-30T21:42:43.500Z</v>
+        <v>2026-07-30T21:48:19.069Z</v>
       </c>
     </row>
     <row r="216">
@@ -4065,10 +4065,10 @@
         <v>Passed</v>
       </c>
       <c r="D216">
-        <v>1.47</v>
+        <v>0.58</v>
       </c>
       <c r="E216" t="str">
-        <v>2026-07-30T21:42:44.500Z</v>
+        <v>2026-07-30T21:48:20.069Z</v>
       </c>
     </row>
     <row r="217">
@@ -4082,10 +4082,10 @@
         <v>Passed</v>
       </c>
       <c r="D217">
-        <v>1.19</v>
+        <v>1.55</v>
       </c>
       <c r="E217" t="str">
-        <v>2026-07-30T21:42:45.500Z</v>
+        <v>2026-07-30T21:48:21.069Z</v>
       </c>
     </row>
     <row r="218">
@@ -4099,10 +4099,10 @@
         <v>Passed</v>
       </c>
       <c r="D218">
-        <v>1.35</v>
+        <v>1.98</v>
       </c>
       <c r="E218" t="str">
-        <v>2026-07-30T21:42:46.500Z</v>
+        <v>2026-07-30T21:48:22.069Z</v>
       </c>
     </row>
     <row r="219">
@@ -4116,10 +4116,10 @@
         <v>Passed</v>
       </c>
       <c r="D219">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="E219" t="str">
-        <v>2026-07-30T21:42:47.500Z</v>
+        <v>2026-07-30T21:48:23.069Z</v>
       </c>
     </row>
     <row r="220">
@@ -4133,10 +4133,10 @@
         <v>Passed</v>
       </c>
       <c r="D220">
-        <v>0.21</v>
+        <v>0.74</v>
       </c>
       <c r="E220" t="str">
-        <v>2026-07-30T21:42:48.500Z</v>
+        <v>2026-07-30T21:48:24.069Z</v>
       </c>
     </row>
     <row r="221">
@@ -4150,10 +4150,10 @@
         <v>Passed</v>
       </c>
       <c r="D221">
-        <v>0.4</v>
+        <v>1.11</v>
       </c>
       <c r="E221" t="str">
-        <v>2026-07-30T21:42:49.500Z</v>
+        <v>2026-07-30T21:48:25.069Z</v>
       </c>
     </row>
     <row r="222">
@@ -4167,10 +4167,10 @@
         <v>Passed</v>
       </c>
       <c r="D222">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="E222" t="str">
-        <v>2026-07-30T21:42:50.500Z</v>
+        <v>2026-07-30T21:48:26.069Z</v>
       </c>
     </row>
     <row r="223">
@@ -4184,10 +4184,10 @@
         <v>Passed</v>
       </c>
       <c r="D223">
-        <v>0.72</v>
+        <v>1.45</v>
       </c>
       <c r="E223" t="str">
-        <v>2026-07-30T21:42:51.500Z</v>
+        <v>2026-07-30T21:48:27.069Z</v>
       </c>
     </row>
     <row r="224">
@@ -4201,10 +4201,10 @@
         <v>Passed</v>
       </c>
       <c r="D224">
-        <v>0.19</v>
+        <v>1.47</v>
       </c>
       <c r="E224" t="str">
-        <v>2026-07-30T21:42:52.500Z</v>
+        <v>2026-07-30T21:48:28.069Z</v>
       </c>
     </row>
     <row r="225">
@@ -4218,10 +4218,10 @@
         <v>Passed</v>
       </c>
       <c r="D225">
-        <v>0.86</v>
+        <v>1.88</v>
       </c>
       <c r="E225" t="str">
-        <v>2026-07-30T21:42:53.500Z</v>
+        <v>2026-07-30T21:48:29.069Z</v>
       </c>
     </row>
     <row r="226">
@@ -4235,10 +4235,10 @@
         <v>Passed</v>
       </c>
       <c r="D226">
-        <v>1.39</v>
+        <v>0.85</v>
       </c>
       <c r="E226" t="str">
-        <v>2026-07-30T21:42:54.500Z</v>
+        <v>2026-07-30T21:48:30.069Z</v>
       </c>
     </row>
     <row r="227">
@@ -4252,10 +4252,10 @@
         <v>Passed</v>
       </c>
       <c r="D227">
-        <v>0.9</v>
+        <v>1.95</v>
       </c>
       <c r="E227" t="str">
-        <v>2026-07-30T21:42:55.500Z</v>
+        <v>2026-07-30T21:48:31.069Z</v>
       </c>
     </row>
     <row r="228">
@@ -4269,10 +4269,10 @@
         <v>Passed</v>
       </c>
       <c r="D228">
-        <v>0.08</v>
+        <v>1.67</v>
       </c>
       <c r="E228" t="str">
-        <v>2026-07-30T21:42:56.500Z</v>
+        <v>2026-07-30T21:48:32.069Z</v>
       </c>
     </row>
     <row r="229">
@@ -4286,10 +4286,10 @@
         <v>Passed</v>
       </c>
       <c r="D229">
-        <v>0.96</v>
+        <v>0.32</v>
       </c>
       <c r="E229" t="str">
-        <v>2026-07-30T21:42:57.500Z</v>
+        <v>2026-07-30T21:48:33.069Z</v>
       </c>
     </row>
     <row r="230">
@@ -4303,10 +4303,10 @@
         <v>Passed</v>
       </c>
       <c r="D230">
-        <v>1.86</v>
+        <v>1.31</v>
       </c>
       <c r="E230" t="str">
-        <v>2026-07-30T21:42:58.500Z</v>
+        <v>2026-07-30T21:48:34.069Z</v>
       </c>
     </row>
     <row r="231">
@@ -4320,10 +4320,10 @@
         <v>Passed</v>
       </c>
       <c r="D231">
-        <v>0.88</v>
+        <v>1.36</v>
       </c>
       <c r="E231" t="str">
-        <v>2026-07-30T21:42:59.500Z</v>
+        <v>2026-07-30T21:48:35.069Z</v>
       </c>
     </row>
     <row r="232">
@@ -4337,10 +4337,10 @@
         <v>Passed</v>
       </c>
       <c r="D232">
-        <v>1.45</v>
+        <v>0.26</v>
       </c>
       <c r="E232" t="str">
-        <v>2026-07-30T21:43:00.500Z</v>
+        <v>2026-07-30T21:48:36.069Z</v>
       </c>
     </row>
     <row r="233">
@@ -4351,13 +4351,13 @@
         <v>Verify Security functionality module 232</v>
       </c>
       <c r="C233" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D233">
-        <v>0.86</v>
+        <v>1.39</v>
       </c>
       <c r="E233" t="str">
-        <v>2026-07-30T21:43:01.500Z</v>
+        <v>2026-07-30T21:48:37.069Z</v>
       </c>
     </row>
     <row r="234">
@@ -4371,10 +4371,10 @@
         <v>Passed</v>
       </c>
       <c r="D234">
-        <v>0.72</v>
+        <v>1.3</v>
       </c>
       <c r="E234" t="str">
-        <v>2026-07-30T21:43:02.500Z</v>
+        <v>2026-07-30T21:48:38.069Z</v>
       </c>
     </row>
     <row r="235">
@@ -4385,13 +4385,13 @@
         <v>Verify Security functionality module 234</v>
       </c>
       <c r="C235" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D235">
-        <v>1.07</v>
+        <v>1.96</v>
       </c>
       <c r="E235" t="str">
-        <v>2026-07-30T21:43:03.500Z</v>
+        <v>2026-07-30T21:48:39.069Z</v>
       </c>
     </row>
     <row r="236">
@@ -4405,10 +4405,10 @@
         <v>Passed</v>
       </c>
       <c r="D236">
-        <v>0.38</v>
+        <v>0.25</v>
       </c>
       <c r="E236" t="str">
-        <v>2026-07-30T21:43:04.500Z</v>
+        <v>2026-07-30T21:48:40.069Z</v>
       </c>
     </row>
     <row r="237">
@@ -4422,10 +4422,10 @@
         <v>Passed</v>
       </c>
       <c r="D237">
-        <v>1.56</v>
+        <v>1.17</v>
       </c>
       <c r="E237" t="str">
-        <v>2026-07-30T21:43:05.500Z</v>
+        <v>2026-07-30T21:48:41.069Z</v>
       </c>
     </row>
     <row r="238">
@@ -4439,10 +4439,10 @@
         <v>Passed</v>
       </c>
       <c r="D238">
-        <v>0.87</v>
+        <v>0.64</v>
       </c>
       <c r="E238" t="str">
-        <v>2026-07-30T21:43:06.500Z</v>
+        <v>2026-07-30T21:48:42.069Z</v>
       </c>
     </row>
     <row r="239">
@@ -4456,10 +4456,10 @@
         <v>Passed</v>
       </c>
       <c r="D239">
-        <v>1.02</v>
+        <v>0.54</v>
       </c>
       <c r="E239" t="str">
-        <v>2026-07-30T21:43:07.500Z</v>
+        <v>2026-07-30T21:48:43.069Z</v>
       </c>
     </row>
     <row r="240">
@@ -4473,10 +4473,10 @@
         <v>Passed</v>
       </c>
       <c r="D240">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="E240" t="str">
-        <v>2026-07-30T21:43:08.500Z</v>
+        <v>2026-07-30T21:48:44.069Z</v>
       </c>
     </row>
     <row r="241">
@@ -4490,10 +4490,10 @@
         <v>Passed</v>
       </c>
       <c r="D241">
-        <v>0.26</v>
+        <v>0.77</v>
       </c>
       <c r="E241" t="str">
-        <v>2026-07-30T21:43:09.500Z</v>
+        <v>2026-07-30T21:48:45.069Z</v>
       </c>
     </row>
     <row r="242">
@@ -4507,10 +4507,10 @@
         <v>Passed</v>
       </c>
       <c r="D242">
-        <v>0.09</v>
+        <v>0.5</v>
       </c>
       <c r="E242" t="str">
-        <v>2026-07-30T21:43:10.500Z</v>
+        <v>2026-07-30T21:48:46.069Z</v>
       </c>
     </row>
     <row r="243">
@@ -4524,10 +4524,10 @@
         <v>Passed</v>
       </c>
       <c r="D243">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="E243" t="str">
-        <v>2026-07-30T21:43:11.500Z</v>
+        <v>2026-07-30T21:48:47.069Z</v>
       </c>
     </row>
     <row r="244">
@@ -4541,10 +4541,10 @@
         <v>Passed</v>
       </c>
       <c r="D244">
-        <v>1.48</v>
+        <v>0.13</v>
       </c>
       <c r="E244" t="str">
-        <v>2026-07-30T21:43:12.500Z</v>
+        <v>2026-07-30T21:48:48.069Z</v>
       </c>
     </row>
     <row r="245">
@@ -4558,10 +4558,10 @@
         <v>Passed</v>
       </c>
       <c r="D245">
-        <v>1.58</v>
+        <v>0.12</v>
       </c>
       <c r="E245" t="str">
-        <v>2026-07-30T21:43:13.500Z</v>
+        <v>2026-07-30T21:48:49.069Z</v>
       </c>
     </row>
     <row r="246">
@@ -4575,10 +4575,10 @@
         <v>Passed</v>
       </c>
       <c r="D246">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="E246" t="str">
-        <v>2026-07-30T21:43:14.500Z</v>
+        <v>2026-07-30T21:48:50.069Z</v>
       </c>
     </row>
     <row r="247">
@@ -4592,10 +4592,10 @@
         <v>Passed</v>
       </c>
       <c r="D247">
-        <v>0.22</v>
+        <v>0.11</v>
       </c>
       <c r="E247" t="str">
-        <v>2026-07-30T21:43:15.500Z</v>
+        <v>2026-07-30T21:48:51.069Z</v>
       </c>
     </row>
     <row r="248">
@@ -4609,10 +4609,10 @@
         <v>Passed</v>
       </c>
       <c r="D248">
-        <v>0.64</v>
+        <v>1.88</v>
       </c>
       <c r="E248" t="str">
-        <v>2026-07-30T21:43:16.500Z</v>
+        <v>2026-07-30T21:48:52.069Z</v>
       </c>
     </row>
     <row r="249">
@@ -4626,10 +4626,10 @@
         <v>Passed</v>
       </c>
       <c r="D249">
-        <v>1.5</v>
+        <v>0.48</v>
       </c>
       <c r="E249" t="str">
-        <v>2026-07-30T21:43:17.500Z</v>
+        <v>2026-07-30T21:48:53.069Z</v>
       </c>
     </row>
     <row r="250">
@@ -4643,10 +4643,10 @@
         <v>Passed</v>
       </c>
       <c r="D250">
-        <v>0.98</v>
+        <v>0.37</v>
       </c>
       <c r="E250" t="str">
-        <v>2026-07-30T21:43:18.500Z</v>
+        <v>2026-07-30T21:48:54.069Z</v>
       </c>
     </row>
     <row r="251">
@@ -4660,10 +4660,10 @@
         <v>Passed</v>
       </c>
       <c r="D251">
-        <v>1.49</v>
+        <v>0.94</v>
       </c>
       <c r="E251" t="str">
-        <v>2026-07-30T21:43:19.500Z</v>
+        <v>2026-07-30T21:48:55.069Z</v>
       </c>
     </row>
     <row r="252">
@@ -4677,10 +4677,10 @@
         <v>Passed</v>
       </c>
       <c r="D252">
-        <v>0.58</v>
+        <v>1.7</v>
       </c>
       <c r="E252" t="str">
-        <v>2026-07-30T21:43:20.500Z</v>
+        <v>2026-07-30T21:48:56.069Z</v>
       </c>
     </row>
     <row r="253">
@@ -4694,10 +4694,10 @@
         <v>Passed</v>
       </c>
       <c r="D253">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="E253" t="str">
-        <v>2026-07-30T21:43:21.500Z</v>
+        <v>2026-07-30T21:48:57.069Z</v>
       </c>
     </row>
     <row r="254">
@@ -4711,10 +4711,10 @@
         <v>Passed</v>
       </c>
       <c r="D254">
-        <v>1.12</v>
+        <v>0.86</v>
       </c>
       <c r="E254" t="str">
-        <v>2026-07-30T21:43:22.500Z</v>
+        <v>2026-07-30T21:48:58.069Z</v>
       </c>
     </row>
     <row r="255">
@@ -4728,10 +4728,10 @@
         <v>Passed</v>
       </c>
       <c r="D255">
-        <v>0.86</v>
+        <v>0.65</v>
       </c>
       <c r="E255" t="str">
-        <v>2026-07-30T21:43:23.500Z</v>
+        <v>2026-07-30T21:48:59.069Z</v>
       </c>
     </row>
     <row r="256">
@@ -4745,10 +4745,10 @@
         <v>Passed</v>
       </c>
       <c r="D256">
-        <v>0.28</v>
+        <v>1.91</v>
       </c>
       <c r="E256" t="str">
-        <v>2026-07-30T21:43:24.500Z</v>
+        <v>2026-07-30T21:49:00.069Z</v>
       </c>
     </row>
     <row r="257">
@@ -4762,10 +4762,10 @@
         <v>Passed</v>
       </c>
       <c r="D257">
-        <v>0.13</v>
+        <v>1.75</v>
       </c>
       <c r="E257" t="str">
-        <v>2026-07-30T21:43:25.500Z</v>
+        <v>2026-07-30T21:49:01.069Z</v>
       </c>
     </row>
     <row r="258">
@@ -4779,10 +4779,10 @@
         <v>Passed</v>
       </c>
       <c r="D258">
-        <v>0.82</v>
+        <v>1.76</v>
       </c>
       <c r="E258" t="str">
-        <v>2026-07-30T21:43:26.500Z</v>
+        <v>2026-07-30T21:49:02.069Z</v>
       </c>
     </row>
     <row r="259">
@@ -4796,10 +4796,10 @@
         <v>Passed</v>
       </c>
       <c r="D259">
-        <v>1.99</v>
+        <v>1.43</v>
       </c>
       <c r="E259" t="str">
-        <v>2026-07-30T21:43:27.500Z</v>
+        <v>2026-07-30T21:49:03.069Z</v>
       </c>
     </row>
     <row r="260">
@@ -4813,10 +4813,10 @@
         <v>Passed</v>
       </c>
       <c r="D260">
-        <v>0.75</v>
+        <v>1.19</v>
       </c>
       <c r="E260" t="str">
-        <v>2026-07-30T21:43:28.500Z</v>
+        <v>2026-07-30T21:49:04.069Z</v>
       </c>
     </row>
     <row r="261">
@@ -4830,10 +4830,10 @@
         <v>Passed</v>
       </c>
       <c r="D261">
-        <v>1.89</v>
+        <v>0.22</v>
       </c>
       <c r="E261" t="str">
-        <v>2026-07-30T21:43:29.500Z</v>
+        <v>2026-07-30T21:49:05.069Z</v>
       </c>
     </row>
     <row r="262">
@@ -4847,10 +4847,10 @@
         <v>Passed</v>
       </c>
       <c r="D262">
-        <v>0.7</v>
+        <v>1.08</v>
       </c>
       <c r="E262" t="str">
-        <v>2026-07-30T21:43:30.500Z</v>
+        <v>2026-07-30T21:49:06.069Z</v>
       </c>
     </row>
     <row r="263">
@@ -4864,10 +4864,10 @@
         <v>Passed</v>
       </c>
       <c r="D263">
-        <v>0.36</v>
+        <v>1.93</v>
       </c>
       <c r="E263" t="str">
-        <v>2026-07-30T21:43:31.500Z</v>
+        <v>2026-07-30T21:49:07.069Z</v>
       </c>
     </row>
     <row r="264">
@@ -4881,10 +4881,10 @@
         <v>Passed</v>
       </c>
       <c r="D264">
-        <v>0.9</v>
+        <v>0.21</v>
       </c>
       <c r="E264" t="str">
-        <v>2026-07-30T21:43:32.500Z</v>
+        <v>2026-07-30T21:49:08.069Z</v>
       </c>
     </row>
     <row r="265">
@@ -4898,10 +4898,10 @@
         <v>Passed</v>
       </c>
       <c r="D265">
-        <v>1.98</v>
+        <v>1.13</v>
       </c>
       <c r="E265" t="str">
-        <v>2026-07-30T21:43:33.500Z</v>
+        <v>2026-07-30T21:49:09.069Z</v>
       </c>
     </row>
     <row r="266">
@@ -4915,10 +4915,10 @@
         <v>Passed</v>
       </c>
       <c r="D266">
-        <v>1.96</v>
+        <v>1.55</v>
       </c>
       <c r="E266" t="str">
-        <v>2026-07-30T21:43:34.500Z</v>
+        <v>2026-07-30T21:49:10.069Z</v>
       </c>
     </row>
     <row r="267">
@@ -4932,10 +4932,10 @@
         <v>Passed</v>
       </c>
       <c r="D267">
-        <v>0.3</v>
+        <v>1.75</v>
       </c>
       <c r="E267" t="str">
-        <v>2026-07-30T21:43:35.500Z</v>
+        <v>2026-07-30T21:49:11.069Z</v>
       </c>
     </row>
     <row r="268">
@@ -4949,10 +4949,10 @@
         <v>Passed</v>
       </c>
       <c r="D268">
-        <v>1.07</v>
+        <v>0.05</v>
       </c>
       <c r="E268" t="str">
-        <v>2026-07-30T21:43:36.500Z</v>
+        <v>2026-07-30T21:49:12.069Z</v>
       </c>
     </row>
     <row r="269">
@@ -4966,10 +4966,10 @@
         <v>Passed</v>
       </c>
       <c r="D269">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="E269" t="str">
-        <v>2026-07-30T21:43:37.500Z</v>
+        <v>2026-07-30T21:49:13.069Z</v>
       </c>
     </row>
     <row r="270">
@@ -4983,10 +4983,10 @@
         <v>Passed</v>
       </c>
       <c r="D270">
-        <v>0.2</v>
+        <v>1.34</v>
       </c>
       <c r="E270" t="str">
-        <v>2026-07-30T21:43:38.500Z</v>
+        <v>2026-07-30T21:49:14.069Z</v>
       </c>
     </row>
     <row r="271">
@@ -5000,10 +5000,10 @@
         <v>Passed</v>
       </c>
       <c r="D271">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="E271" t="str">
-        <v>2026-07-30T21:43:39.500Z</v>
+        <v>2026-07-30T21:49:15.069Z</v>
       </c>
     </row>
     <row r="272">
@@ -5017,10 +5017,10 @@
         <v>Passed</v>
       </c>
       <c r="D272">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="E272" t="str">
-        <v>2026-07-30T21:43:40.500Z</v>
+        <v>2026-07-30T21:49:16.069Z</v>
       </c>
     </row>
     <row r="273">
@@ -5034,10 +5034,10 @@
         <v>Passed</v>
       </c>
       <c r="D273">
-        <v>0.57</v>
+        <v>1.99</v>
       </c>
       <c r="E273" t="str">
-        <v>2026-07-30T21:43:41.500Z</v>
+        <v>2026-07-30T21:49:17.069Z</v>
       </c>
     </row>
     <row r="274">
@@ -5051,10 +5051,10 @@
         <v>Passed</v>
       </c>
       <c r="D274">
-        <v>1.61</v>
+        <v>0.86</v>
       </c>
       <c r="E274" t="str">
-        <v>2026-07-30T21:43:42.500Z</v>
+        <v>2026-07-30T21:49:18.069Z</v>
       </c>
     </row>
     <row r="275">
@@ -5068,10 +5068,10 @@
         <v>Passed</v>
       </c>
       <c r="D275">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E275" t="str">
-        <v>2026-07-30T21:43:43.500Z</v>
+        <v>2026-07-30T21:49:19.069Z</v>
       </c>
     </row>
     <row r="276">
@@ -5085,10 +5085,10 @@
         <v>Passed</v>
       </c>
       <c r="D276">
-        <v>0.46</v>
+        <v>0.69</v>
       </c>
       <c r="E276" t="str">
-        <v>2026-07-30T21:43:44.500Z</v>
+        <v>2026-07-30T21:49:20.069Z</v>
       </c>
     </row>
     <row r="277">
@@ -5102,10 +5102,10 @@
         <v>Passed</v>
       </c>
       <c r="D277">
-        <v>0.17</v>
+        <v>1.7</v>
       </c>
       <c r="E277" t="str">
-        <v>2026-07-30T21:43:45.500Z</v>
+        <v>2026-07-30T21:49:21.069Z</v>
       </c>
     </row>
     <row r="278">
@@ -5119,10 +5119,10 @@
         <v>Passed</v>
       </c>
       <c r="D278">
-        <v>0.31</v>
+        <v>0.19</v>
       </c>
       <c r="E278" t="str">
-        <v>2026-07-30T21:43:46.500Z</v>
+        <v>2026-07-30T21:49:22.069Z</v>
       </c>
     </row>
     <row r="279">
@@ -5136,10 +5136,10 @@
         <v>Passed</v>
       </c>
       <c r="D279">
-        <v>1.52</v>
+        <v>0.7</v>
       </c>
       <c r="E279" t="str">
-        <v>2026-07-30T21:43:47.500Z</v>
+        <v>2026-07-30T21:49:23.069Z</v>
       </c>
     </row>
     <row r="280">
@@ -5153,10 +5153,10 @@
         <v>Passed</v>
       </c>
       <c r="D280">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="E280" t="str">
-        <v>2026-07-30T21:43:48.500Z</v>
+        <v>2026-07-30T21:49:24.069Z</v>
       </c>
     </row>
     <row r="281">
@@ -5170,10 +5170,10 @@
         <v>Passed</v>
       </c>
       <c r="D281">
-        <v>0.23</v>
+        <v>0.68</v>
       </c>
       <c r="E281" t="str">
-        <v>2026-07-30T21:43:49.500Z</v>
+        <v>2026-07-30T21:49:25.069Z</v>
       </c>
     </row>
     <row r="282">
@@ -5187,10 +5187,10 @@
         <v>Passed</v>
       </c>
       <c r="D282">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="E282" t="str">
-        <v>2026-07-30T21:43:50.500Z</v>
+        <v>2026-07-30T21:49:26.069Z</v>
       </c>
     </row>
     <row r="283">
@@ -5204,10 +5204,10 @@
         <v>Passed</v>
       </c>
       <c r="D283">
-        <v>0.64</v>
+        <v>1.19</v>
       </c>
       <c r="E283" t="str">
-        <v>2026-07-30T21:43:51.500Z</v>
+        <v>2026-07-30T21:49:27.069Z</v>
       </c>
     </row>
     <row r="284">
@@ -5221,10 +5221,10 @@
         <v>Passed</v>
       </c>
       <c r="D284">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="E284" t="str">
-        <v>2026-07-30T21:43:52.500Z</v>
+        <v>2026-07-30T21:49:28.069Z</v>
       </c>
     </row>
     <row r="285">
@@ -5238,10 +5238,10 @@
         <v>Passed</v>
       </c>
       <c r="D285">
-        <v>0.34</v>
+        <v>0.53</v>
       </c>
       <c r="E285" t="str">
-        <v>2026-07-30T21:43:53.500Z</v>
+        <v>2026-07-30T21:49:29.069Z</v>
       </c>
     </row>
     <row r="286">
@@ -5255,10 +5255,10 @@
         <v>Passed</v>
       </c>
       <c r="D286">
-        <v>0.15</v>
+        <v>0.77</v>
       </c>
       <c r="E286" t="str">
-        <v>2026-07-30T21:43:54.500Z</v>
+        <v>2026-07-30T21:49:30.069Z</v>
       </c>
     </row>
     <row r="287">
@@ -5272,10 +5272,10 @@
         <v>Passed</v>
       </c>
       <c r="D287">
-        <v>0.62</v>
+        <v>1.21</v>
       </c>
       <c r="E287" t="str">
-        <v>2026-07-30T21:43:55.500Z</v>
+        <v>2026-07-30T21:49:31.069Z</v>
       </c>
     </row>
     <row r="288">
@@ -5289,10 +5289,10 @@
         <v>Passed</v>
       </c>
       <c r="D288">
-        <v>1.4</v>
+        <v>0.55</v>
       </c>
       <c r="E288" t="str">
-        <v>2026-07-30T21:43:56.500Z</v>
+        <v>2026-07-30T21:49:32.069Z</v>
       </c>
     </row>
     <row r="289">
@@ -5306,10 +5306,10 @@
         <v>Passed</v>
       </c>
       <c r="D289">
-        <v>0.42</v>
+        <v>0.09</v>
       </c>
       <c r="E289" t="str">
-        <v>2026-07-30T21:43:57.500Z</v>
+        <v>2026-07-30T21:49:33.069Z</v>
       </c>
     </row>
     <row r="290">
@@ -5323,10 +5323,10 @@
         <v>Passed</v>
       </c>
       <c r="D290">
-        <v>0.67</v>
+        <v>0.69</v>
       </c>
       <c r="E290" t="str">
-        <v>2026-07-30T21:43:58.500Z</v>
+        <v>2026-07-30T21:49:34.069Z</v>
       </c>
     </row>
     <row r="291">
@@ -5340,10 +5340,10 @@
         <v>Passed</v>
       </c>
       <c r="D291">
-        <v>0.94</v>
+        <v>0.81</v>
       </c>
       <c r="E291" t="str">
-        <v>2026-07-30T21:43:59.500Z</v>
+        <v>2026-07-30T21:49:35.069Z</v>
       </c>
     </row>
     <row r="292">
@@ -5357,10 +5357,10 @@
         <v>Passed</v>
       </c>
       <c r="D292">
-        <v>0.29</v>
+        <v>1.46</v>
       </c>
       <c r="E292" t="str">
-        <v>2026-07-30T21:44:00.500Z</v>
+        <v>2026-07-30T21:49:36.069Z</v>
       </c>
     </row>
     <row r="293">
@@ -5374,10 +5374,10 @@
         <v>Passed</v>
       </c>
       <c r="D293">
-        <v>0.7</v>
+        <v>0.62</v>
       </c>
       <c r="E293" t="str">
-        <v>2026-07-30T21:44:01.500Z</v>
+        <v>2026-07-30T21:49:37.069Z</v>
       </c>
     </row>
     <row r="294">
@@ -5391,10 +5391,10 @@
         <v>Passed</v>
       </c>
       <c r="D294">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="E294" t="str">
-        <v>2026-07-30T21:44:02.500Z</v>
+        <v>2026-07-30T21:49:38.069Z</v>
       </c>
     </row>
     <row r="295">
@@ -5408,10 +5408,10 @@
         <v>Passed</v>
       </c>
       <c r="D295">
-        <v>0.36</v>
+        <v>1.85</v>
       </c>
       <c r="E295" t="str">
-        <v>2026-07-30T21:44:03.500Z</v>
+        <v>2026-07-30T21:49:39.069Z</v>
       </c>
     </row>
     <row r="296">
@@ -5425,10 +5425,10 @@
         <v>Passed</v>
       </c>
       <c r="D296">
-        <v>1.44</v>
+        <v>0.14</v>
       </c>
       <c r="E296" t="str">
-        <v>2026-07-30T21:44:04.500Z</v>
+        <v>2026-07-30T21:49:40.069Z</v>
       </c>
     </row>
     <row r="297">
@@ -5442,10 +5442,10 @@
         <v>Passed</v>
       </c>
       <c r="D297">
-        <v>1.66</v>
+        <v>1.99</v>
       </c>
       <c r="E297" t="str">
-        <v>2026-07-30T21:44:05.500Z</v>
+        <v>2026-07-30T21:49:41.069Z</v>
       </c>
     </row>
     <row r="298">
@@ -5459,10 +5459,10 @@
         <v>Passed</v>
       </c>
       <c r="D298">
-        <v>0.01</v>
+        <v>0.38</v>
       </c>
       <c r="E298" t="str">
-        <v>2026-07-30T21:44:06.500Z</v>
+        <v>2026-07-30T21:49:42.069Z</v>
       </c>
     </row>
     <row r="299">
@@ -5476,10 +5476,10 @@
         <v>Passed</v>
       </c>
       <c r="D299">
-        <v>1.83</v>
+        <v>0.3</v>
       </c>
       <c r="E299" t="str">
-        <v>2026-07-30T21:44:07.500Z</v>
+        <v>2026-07-30T21:49:43.069Z</v>
       </c>
     </row>
     <row r="300">
@@ -5490,13 +5490,13 @@
         <v>Verify Security functionality module 299</v>
       </c>
       <c r="C300" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D300">
-        <v>0.37</v>
+        <v>1.59</v>
       </c>
       <c r="E300" t="str">
-        <v>2026-07-30T21:44:08.500Z</v>
+        <v>2026-07-30T21:49:44.069Z</v>
       </c>
     </row>
     <row r="301">
@@ -5510,10 +5510,10 @@
         <v>Passed</v>
       </c>
       <c r="D301">
-        <v>0.98</v>
+        <v>0.33</v>
       </c>
       <c r="E301" t="str">
-        <v>2026-07-30T21:44:09.500Z</v>
+        <v>2026-07-30T21:49:45.069Z</v>
       </c>
     </row>
     <row r="302">
@@ -5527,10 +5527,10 @@
         <v>Passed</v>
       </c>
       <c r="D302">
-        <v>0.85</v>
+        <v>0.52</v>
       </c>
       <c r="E302" t="str">
-        <v>2026-07-30T21:44:10.500Z</v>
+        <v>2026-07-30T21:49:46.069Z</v>
       </c>
     </row>
     <row r="303">
@@ -5544,10 +5544,10 @@
         <v>Passed</v>
       </c>
       <c r="D303">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="E303" t="str">
-        <v>2026-07-30T21:44:11.500Z</v>
+        <v>2026-07-30T21:49:47.069Z</v>
       </c>
     </row>
     <row r="304">
@@ -5561,10 +5561,10 @@
         <v>Passed</v>
       </c>
       <c r="D304">
-        <v>0.86</v>
+        <v>1.93</v>
       </c>
       <c r="E304" t="str">
-        <v>2026-07-30T21:44:12.500Z</v>
+        <v>2026-07-30T21:49:48.069Z</v>
       </c>
     </row>
     <row r="305">
@@ -5578,10 +5578,10 @@
         <v>Passed</v>
       </c>
       <c r="D305">
-        <v>1.12</v>
+        <v>0.89</v>
       </c>
       <c r="E305" t="str">
-        <v>2026-07-30T21:44:13.500Z</v>
+        <v>2026-07-30T21:49:49.069Z</v>
       </c>
     </row>
     <row r="306">
@@ -5595,10 +5595,10 @@
         <v>Passed</v>
       </c>
       <c r="D306">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="E306" t="str">
-        <v>2026-07-30T21:44:14.500Z</v>
+        <v>2026-07-30T21:49:50.069Z</v>
       </c>
     </row>
     <row r="307">
@@ -5612,10 +5612,10 @@
         <v>Passed</v>
       </c>
       <c r="D307">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="E307" t="str">
-        <v>2026-07-30T21:44:15.500Z</v>
+        <v>2026-07-30T21:49:51.069Z</v>
       </c>
     </row>
     <row r="308">
@@ -5629,10 +5629,10 @@
         <v>Passed</v>
       </c>
       <c r="D308">
-        <v>0.3</v>
+        <v>0.78</v>
       </c>
       <c r="E308" t="str">
-        <v>2026-07-30T21:44:16.500Z</v>
+        <v>2026-07-30T21:49:52.069Z</v>
       </c>
     </row>
     <row r="309">
@@ -5646,10 +5646,10 @@
         <v>Passed</v>
       </c>
       <c r="D309">
-        <v>0.4</v>
+        <v>1.25</v>
       </c>
       <c r="E309" t="str">
-        <v>2026-07-30T21:44:17.500Z</v>
+        <v>2026-07-30T21:49:53.069Z</v>
       </c>
     </row>
     <row r="310">
@@ -5663,10 +5663,10 @@
         <v>Passed</v>
       </c>
       <c r="D310">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="E310" t="str">
-        <v>2026-07-30T21:44:18.500Z</v>
+        <v>2026-07-30T21:49:54.069Z</v>
       </c>
     </row>
     <row r="311">
@@ -5680,10 +5680,10 @@
         <v>Passed</v>
       </c>
       <c r="D311">
-        <v>1.57</v>
+        <v>0.2</v>
       </c>
       <c r="E311" t="str">
-        <v>2026-07-30T21:44:19.500Z</v>
+        <v>2026-07-30T21:49:55.069Z</v>
       </c>
     </row>
     <row r="312">
@@ -5697,10 +5697,10 @@
         <v>Passed</v>
       </c>
       <c r="D312">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="E312" t="str">
-        <v>2026-07-30T21:44:20.500Z</v>
+        <v>2026-07-30T21:49:56.069Z</v>
       </c>
     </row>
     <row r="313">
@@ -5714,10 +5714,10 @@
         <v>Passed</v>
       </c>
       <c r="D313">
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="E313" t="str">
-        <v>2026-07-30T21:44:21.500Z</v>
+        <v>2026-07-30T21:49:57.069Z</v>
       </c>
     </row>
     <row r="314">
@@ -5731,10 +5731,10 @@
         <v>Passed</v>
       </c>
       <c r="D314">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="E314" t="str">
-        <v>2026-07-30T21:44:22.500Z</v>
+        <v>2026-07-30T21:49:58.069Z</v>
       </c>
     </row>
     <row r="315">
@@ -5748,10 +5748,10 @@
         <v>Passed</v>
       </c>
       <c r="D315">
-        <v>0.45</v>
+        <v>1.85</v>
       </c>
       <c r="E315" t="str">
-        <v>2026-07-30T21:44:23.500Z</v>
+        <v>2026-07-30T21:49:59.069Z</v>
       </c>
     </row>
     <row r="316">
@@ -5765,10 +5765,10 @@
         <v>Passed</v>
       </c>
       <c r="D316">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="E316" t="str">
-        <v>2026-07-30T21:44:24.500Z</v>
+        <v>2026-07-30T21:50:00.069Z</v>
       </c>
     </row>
     <row r="317">
@@ -5782,10 +5782,10 @@
         <v>Passed</v>
       </c>
       <c r="D317">
-        <v>0.98</v>
+        <v>1.56</v>
       </c>
       <c r="E317" t="str">
-        <v>2026-07-30T21:44:25.500Z</v>
+        <v>2026-07-30T21:50:01.069Z</v>
       </c>
     </row>
     <row r="318">
@@ -5799,10 +5799,10 @@
         <v>Passed</v>
       </c>
       <c r="D318">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="E318" t="str">
-        <v>2026-07-30T21:44:26.500Z</v>
+        <v>2026-07-30T21:50:02.069Z</v>
       </c>
     </row>
     <row r="319">
@@ -5816,10 +5816,10 @@
         <v>Passed</v>
       </c>
       <c r="D319">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="E319" t="str">
-        <v>2026-07-30T21:44:27.500Z</v>
+        <v>2026-07-30T21:50:03.069Z</v>
       </c>
     </row>
     <row r="320">
@@ -5833,10 +5833,10 @@
         <v>Passed</v>
       </c>
       <c r="D320">
-        <v>0.77</v>
+        <v>0.55</v>
       </c>
       <c r="E320" t="str">
-        <v>2026-07-30T21:44:28.500Z</v>
+        <v>2026-07-30T21:50:04.069Z</v>
       </c>
     </row>
     <row r="321">
@@ -5850,10 +5850,10 @@
         <v>Passed</v>
       </c>
       <c r="D321">
-        <v>1.84</v>
+        <v>0.22</v>
       </c>
       <c r="E321" t="str">
-        <v>2026-07-30T21:44:29.500Z</v>
+        <v>2026-07-30T21:50:05.069Z</v>
       </c>
     </row>
     <row r="322">
@@ -5867,10 +5867,10 @@
         <v>Passed</v>
       </c>
       <c r="D322">
-        <v>1.02</v>
+        <v>0.75</v>
       </c>
       <c r="E322" t="str">
-        <v>2026-07-30T21:44:30.500Z</v>
+        <v>2026-07-30T21:50:06.069Z</v>
       </c>
     </row>
     <row r="323">
@@ -5884,10 +5884,10 @@
         <v>Passed</v>
       </c>
       <c r="D323">
-        <v>1.07</v>
+        <v>0.71</v>
       </c>
       <c r="E323" t="str">
-        <v>2026-07-30T21:44:31.500Z</v>
+        <v>2026-07-30T21:50:07.069Z</v>
       </c>
     </row>
     <row r="324">
@@ -5901,10 +5901,10 @@
         <v>Passed</v>
       </c>
       <c r="D324">
-        <v>1.8</v>
+        <v>0.98</v>
       </c>
       <c r="E324" t="str">
-        <v>2026-07-30T21:44:32.500Z</v>
+        <v>2026-07-30T21:50:08.069Z</v>
       </c>
     </row>
     <row r="325">
@@ -5918,10 +5918,10 @@
         <v>Passed</v>
       </c>
       <c r="D325">
-        <v>1.72</v>
+        <v>0.34</v>
       </c>
       <c r="E325" t="str">
-        <v>2026-07-30T21:44:33.500Z</v>
+        <v>2026-07-30T21:50:09.069Z</v>
       </c>
     </row>
     <row r="326">
@@ -5935,10 +5935,10 @@
         <v>Passed</v>
       </c>
       <c r="D326">
-        <v>1.91</v>
+        <v>0.6</v>
       </c>
       <c r="E326" t="str">
-        <v>2026-07-30T21:44:34.500Z</v>
+        <v>2026-07-30T21:50:10.069Z</v>
       </c>
     </row>
     <row r="327">
@@ -5952,10 +5952,10 @@
         <v>Passed</v>
       </c>
       <c r="D327">
-        <v>0.32</v>
+        <v>0.95</v>
       </c>
       <c r="E327" t="str">
-        <v>2026-07-30T21:44:35.500Z</v>
+        <v>2026-07-30T21:50:11.069Z</v>
       </c>
     </row>
     <row r="328">
@@ -5969,10 +5969,10 @@
         <v>Passed</v>
       </c>
       <c r="D328">
-        <v>1.57</v>
+        <v>0.72</v>
       </c>
       <c r="E328" t="str">
-        <v>2026-07-30T21:44:36.500Z</v>
+        <v>2026-07-30T21:50:12.069Z</v>
       </c>
     </row>
     <row r="329">
@@ -5986,10 +5986,10 @@
         <v>Passed</v>
       </c>
       <c r="D329">
-        <v>1.97</v>
+        <v>1.17</v>
       </c>
       <c r="E329" t="str">
-        <v>2026-07-30T21:44:37.500Z</v>
+        <v>2026-07-30T21:50:13.069Z</v>
       </c>
     </row>
     <row r="330">
@@ -6003,10 +6003,10 @@
         <v>Passed</v>
       </c>
       <c r="D330">
-        <v>1.88</v>
+        <v>0.8</v>
       </c>
       <c r="E330" t="str">
-        <v>2026-07-30T21:44:38.500Z</v>
+        <v>2026-07-30T21:50:14.069Z</v>
       </c>
     </row>
     <row r="331">
@@ -6020,10 +6020,10 @@
         <v>Passed</v>
       </c>
       <c r="D331">
-        <v>0.04</v>
+        <v>1.49</v>
       </c>
       <c r="E331" t="str">
-        <v>2026-07-30T21:44:39.500Z</v>
+        <v>2026-07-30T21:50:15.069Z</v>
       </c>
     </row>
     <row r="332">
@@ -6037,10 +6037,10 @@
         <v>Passed</v>
       </c>
       <c r="D332">
-        <v>1.08</v>
+        <v>0.4</v>
       </c>
       <c r="E332" t="str">
-        <v>2026-07-30T21:44:40.500Z</v>
+        <v>2026-07-30T21:50:16.069Z</v>
       </c>
     </row>
     <row r="333">
@@ -6054,10 +6054,10 @@
         <v>Passed</v>
       </c>
       <c r="D333">
-        <v>1.78</v>
+        <v>0.76</v>
       </c>
       <c r="E333" t="str">
-        <v>2026-07-30T21:44:41.500Z</v>
+        <v>2026-07-30T21:50:17.069Z</v>
       </c>
     </row>
     <row r="334">
@@ -6071,10 +6071,10 @@
         <v>Passed</v>
       </c>
       <c r="D334">
-        <v>0.22</v>
+        <v>1.99</v>
       </c>
       <c r="E334" t="str">
-        <v>2026-07-30T21:44:42.500Z</v>
+        <v>2026-07-30T21:50:18.069Z</v>
       </c>
     </row>
     <row r="335">
@@ -6088,10 +6088,10 @@
         <v>Passed</v>
       </c>
       <c r="D335">
-        <v>0.48</v>
+        <v>0.09</v>
       </c>
       <c r="E335" t="str">
-        <v>2026-07-30T21:44:43.500Z</v>
+        <v>2026-07-30T21:50:19.069Z</v>
       </c>
     </row>
     <row r="336">
@@ -6105,10 +6105,10 @@
         <v>Passed</v>
       </c>
       <c r="D336">
-        <v>0.28</v>
+        <v>1.28</v>
       </c>
       <c r="E336" t="str">
-        <v>2026-07-30T21:44:44.500Z</v>
+        <v>2026-07-30T21:50:20.069Z</v>
       </c>
     </row>
     <row r="337">
@@ -6122,10 +6122,10 @@
         <v>Passed</v>
       </c>
       <c r="D337">
-        <v>1.21</v>
+        <v>0.11</v>
       </c>
       <c r="E337" t="str">
-        <v>2026-07-30T21:44:45.500Z</v>
+        <v>2026-07-30T21:50:21.069Z</v>
       </c>
     </row>
     <row r="338">
@@ -6139,10 +6139,10 @@
         <v>Passed</v>
       </c>
       <c r="D338">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="E338" t="str">
-        <v>2026-07-30T21:44:46.500Z</v>
+        <v>2026-07-30T21:50:22.069Z</v>
       </c>
     </row>
     <row r="339">
@@ -6156,10 +6156,10 @@
         <v>Passed</v>
       </c>
       <c r="D339">
-        <v>0.03</v>
+        <v>1.41</v>
       </c>
       <c r="E339" t="str">
-        <v>2026-07-30T21:44:47.500Z</v>
+        <v>2026-07-30T21:50:23.069Z</v>
       </c>
     </row>
     <row r="340">
@@ -6173,10 +6173,10 @@
         <v>Passed</v>
       </c>
       <c r="D340">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="E340" t="str">
-        <v>2026-07-30T21:44:48.500Z</v>
+        <v>2026-07-30T21:50:24.069Z</v>
       </c>
     </row>
     <row r="341">
@@ -6190,10 +6190,10 @@
         <v>Passed</v>
       </c>
       <c r="D341">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="E341" t="str">
-        <v>2026-07-30T21:44:49.500Z</v>
+        <v>2026-07-30T21:50:25.069Z</v>
       </c>
     </row>
     <row r="342">
@@ -6207,10 +6207,10 @@
         <v>Passed</v>
       </c>
       <c r="D342">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="E342" t="str">
-        <v>2026-07-30T21:44:50.500Z</v>
+        <v>2026-07-30T21:50:26.069Z</v>
       </c>
     </row>
     <row r="343">
@@ -6224,10 +6224,10 @@
         <v>Passed</v>
       </c>
       <c r="D343">
-        <v>0.74</v>
+        <v>1.22</v>
       </c>
       <c r="E343" t="str">
-        <v>2026-07-30T21:44:51.500Z</v>
+        <v>2026-07-30T21:50:27.069Z</v>
       </c>
     </row>
     <row r="344">
@@ -6241,10 +6241,10 @@
         <v>Passed</v>
       </c>
       <c r="D344">
-        <v>1.69</v>
+        <v>0.8</v>
       </c>
       <c r="E344" t="str">
-        <v>2026-07-30T21:44:52.500Z</v>
+        <v>2026-07-30T21:50:28.069Z</v>
       </c>
     </row>
     <row r="345">
@@ -6255,13 +6255,13 @@
         <v>Verify Security functionality module 344</v>
       </c>
       <c r="C345" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D345">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="E345" t="str">
-        <v>2026-07-30T21:44:53.500Z</v>
+        <v>2026-07-30T21:50:29.069Z</v>
       </c>
     </row>
     <row r="346">
@@ -6275,10 +6275,10 @@
         <v>Passed</v>
       </c>
       <c r="D346">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="E346" t="str">
-        <v>2026-07-30T21:44:54.500Z</v>
+        <v>2026-07-30T21:50:30.069Z</v>
       </c>
     </row>
     <row r="347">
@@ -6292,10 +6292,10 @@
         <v>Passed</v>
       </c>
       <c r="D347">
-        <v>1.68</v>
+        <v>1.07</v>
       </c>
       <c r="E347" t="str">
-        <v>2026-07-30T21:44:55.500Z</v>
+        <v>2026-07-30T21:50:31.069Z</v>
       </c>
     </row>
     <row r="348">
@@ -6309,10 +6309,10 @@
         <v>Passed</v>
       </c>
       <c r="D348">
-        <v>0.14</v>
+        <v>0.65</v>
       </c>
       <c r="E348" t="str">
-        <v>2026-07-30T21:44:56.500Z</v>
+        <v>2026-07-30T21:50:32.069Z</v>
       </c>
     </row>
     <row r="349">
@@ -6326,10 +6326,10 @@
         <v>Passed</v>
       </c>
       <c r="D349">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
       <c r="E349" t="str">
-        <v>2026-07-30T21:44:57.500Z</v>
+        <v>2026-07-30T21:50:33.069Z</v>
       </c>
     </row>
     <row r="350">
@@ -6343,10 +6343,10 @@
         <v>Passed</v>
       </c>
       <c r="D350">
-        <v>0.97</v>
+        <v>1.45</v>
       </c>
       <c r="E350" t="str">
-        <v>2026-07-30T21:44:58.500Z</v>
+        <v>2026-07-30T21:50:34.069Z</v>
       </c>
     </row>
     <row r="351">
@@ -6360,10 +6360,10 @@
         <v>Passed</v>
       </c>
       <c r="D351">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="E351" t="str">
-        <v>2026-07-30T21:44:59.500Z</v>
+        <v>2026-07-30T21:50:35.069Z</v>
       </c>
     </row>
     <row r="352">
@@ -6377,10 +6377,10 @@
         <v>Passed</v>
       </c>
       <c r="D352">
-        <v>1.47</v>
+        <v>0.18</v>
       </c>
       <c r="E352" t="str">
-        <v>2026-07-30T21:45:00.500Z</v>
+        <v>2026-07-30T21:50:36.069Z</v>
       </c>
     </row>
     <row r="353">
@@ -6394,10 +6394,10 @@
         <v>Passed</v>
       </c>
       <c r="D353">
-        <v>0.36</v>
+        <v>1.94</v>
       </c>
       <c r="E353" t="str">
-        <v>2026-07-30T21:45:01.500Z</v>
+        <v>2026-07-30T21:50:37.069Z</v>
       </c>
     </row>
     <row r="354">
@@ -6411,10 +6411,10 @@
         <v>Passed</v>
       </c>
       <c r="D354">
-        <v>0.05</v>
+        <v>1.86</v>
       </c>
       <c r="E354" t="str">
-        <v>2026-07-30T21:45:02.500Z</v>
+        <v>2026-07-30T21:50:38.069Z</v>
       </c>
     </row>
     <row r="355">
@@ -6428,10 +6428,10 @@
         <v>Passed</v>
       </c>
       <c r="D355">
-        <v>1.57</v>
+        <v>0.08</v>
       </c>
       <c r="E355" t="str">
-        <v>2026-07-30T21:45:03.500Z</v>
+        <v>2026-07-30T21:50:39.069Z</v>
       </c>
     </row>
     <row r="356">
@@ -6445,10 +6445,10 @@
         <v>Passed</v>
       </c>
       <c r="D356">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="E356" t="str">
-        <v>2026-07-30T21:45:04.500Z</v>
+        <v>2026-07-30T21:50:40.069Z</v>
       </c>
     </row>
     <row r="357">
@@ -6462,10 +6462,10 @@
         <v>Passed</v>
       </c>
       <c r="D357">
-        <v>0.87</v>
+        <v>1.6</v>
       </c>
       <c r="E357" t="str">
-        <v>2026-07-30T21:45:05.500Z</v>
+        <v>2026-07-30T21:50:41.069Z</v>
       </c>
     </row>
     <row r="358">
@@ -6479,10 +6479,10 @@
         <v>Passed</v>
       </c>
       <c r="D358">
-        <v>0.66</v>
+        <v>0.53</v>
       </c>
       <c r="E358" t="str">
-        <v>2026-07-30T21:45:06.500Z</v>
+        <v>2026-07-30T21:50:42.069Z</v>
       </c>
     </row>
     <row r="359">
@@ -6496,10 +6496,10 @@
         <v>Passed</v>
       </c>
       <c r="D359">
-        <v>1.11</v>
+        <v>0.46</v>
       </c>
       <c r="E359" t="str">
-        <v>2026-07-30T21:45:07.500Z</v>
+        <v>2026-07-30T21:50:43.069Z</v>
       </c>
     </row>
     <row r="360">
@@ -6513,10 +6513,10 @@
         <v>Passed</v>
       </c>
       <c r="D360">
-        <v>1.72</v>
+        <v>0.6</v>
       </c>
       <c r="E360" t="str">
-        <v>2026-07-30T21:45:08.500Z</v>
+        <v>2026-07-30T21:50:44.069Z</v>
       </c>
     </row>
     <row r="361">
@@ -6530,10 +6530,10 @@
         <v>Passed</v>
       </c>
       <c r="D361">
-        <v>0.59</v>
+        <v>0.92</v>
       </c>
       <c r="E361" t="str">
-        <v>2026-07-30T21:45:09.500Z</v>
+        <v>2026-07-30T21:50:45.069Z</v>
       </c>
     </row>
     <row r="362">
@@ -6547,10 +6547,10 @@
         <v>Passed</v>
       </c>
       <c r="D362">
-        <v>1.85</v>
+        <v>0.77</v>
       </c>
       <c r="E362" t="str">
-        <v>2026-07-30T21:45:10.500Z</v>
+        <v>2026-07-30T21:50:46.069Z</v>
       </c>
     </row>
     <row r="363">
@@ -6564,10 +6564,10 @@
         <v>Passed</v>
       </c>
       <c r="D363">
-        <v>0.57</v>
+        <v>1.47</v>
       </c>
       <c r="E363" t="str">
-        <v>2026-07-30T21:45:11.500Z</v>
+        <v>2026-07-30T21:50:47.069Z</v>
       </c>
     </row>
     <row r="364">
@@ -6581,10 +6581,10 @@
         <v>Passed</v>
       </c>
       <c r="D364">
-        <v>1.13</v>
+        <v>1.94</v>
       </c>
       <c r="E364" t="str">
-        <v>2026-07-30T21:45:12.500Z</v>
+        <v>2026-07-30T21:50:48.069Z</v>
       </c>
     </row>
     <row r="365">
@@ -6595,13 +6595,13 @@
         <v>Verify Security functionality module 364</v>
       </c>
       <c r="C365" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D365">
-        <v>0.85</v>
+        <v>1.9</v>
       </c>
       <c r="E365" t="str">
-        <v>2026-07-30T21:45:13.500Z</v>
+        <v>2026-07-30T21:50:49.069Z</v>
       </c>
     </row>
     <row r="366">
@@ -6615,10 +6615,10 @@
         <v>Passed</v>
       </c>
       <c r="D366">
-        <v>1.47</v>
+        <v>0.44</v>
       </c>
       <c r="E366" t="str">
-        <v>2026-07-30T21:45:14.500Z</v>
+        <v>2026-07-30T21:50:50.069Z</v>
       </c>
     </row>
     <row r="367">
@@ -6632,10 +6632,10 @@
         <v>Passed</v>
       </c>
       <c r="D367">
-        <v>0.37</v>
+        <v>1.5</v>
       </c>
       <c r="E367" t="str">
-        <v>2026-07-30T21:45:15.500Z</v>
+        <v>2026-07-30T21:50:51.069Z</v>
       </c>
     </row>
     <row r="368">
@@ -6649,10 +6649,10 @@
         <v>Passed</v>
       </c>
       <c r="D368">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="E368" t="str">
-        <v>2026-07-30T21:45:16.500Z</v>
+        <v>2026-07-30T21:50:52.069Z</v>
       </c>
     </row>
     <row r="369">
@@ -6663,13 +6663,13 @@
         <v>Verify Security functionality module 368</v>
       </c>
       <c r="C369" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D369">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="E369" t="str">
-        <v>2026-07-30T21:45:17.500Z</v>
+        <v>2026-07-30T21:50:53.069Z</v>
       </c>
     </row>
     <row r="370">
@@ -6683,10 +6683,10 @@
         <v>Passed</v>
       </c>
       <c r="D370">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="E370" t="str">
-        <v>2026-07-30T21:45:18.500Z</v>
+        <v>2026-07-30T21:50:54.069Z</v>
       </c>
     </row>
     <row r="371">
@@ -6700,10 +6700,10 @@
         <v>Passed</v>
       </c>
       <c r="D371">
-        <v>0.07</v>
+        <v>0.23</v>
       </c>
       <c r="E371" t="str">
-        <v>2026-07-30T21:45:19.500Z</v>
+        <v>2026-07-30T21:50:55.069Z</v>
       </c>
     </row>
     <row r="372">
@@ -6717,10 +6717,10 @@
         <v>Passed</v>
       </c>
       <c r="D372">
-        <v>1.13</v>
+        <v>1.85</v>
       </c>
       <c r="E372" t="str">
-        <v>2026-07-30T21:45:20.500Z</v>
+        <v>2026-07-30T21:50:56.069Z</v>
       </c>
     </row>
     <row r="373">
@@ -6734,10 +6734,10 @@
         <v>Passed</v>
       </c>
       <c r="D373">
-        <v>0.32</v>
+        <v>1.25</v>
       </c>
       <c r="E373" t="str">
-        <v>2026-07-30T21:45:21.500Z</v>
+        <v>2026-07-30T21:50:57.069Z</v>
       </c>
     </row>
     <row r="374">
@@ -6751,10 +6751,10 @@
         <v>Passed</v>
       </c>
       <c r="D374">
-        <v>0.21</v>
+        <v>1.44</v>
       </c>
       <c r="E374" t="str">
-        <v>2026-07-30T21:45:22.500Z</v>
+        <v>2026-07-30T21:50:58.069Z</v>
       </c>
     </row>
     <row r="375">
@@ -6768,10 +6768,10 @@
         <v>Passed</v>
       </c>
       <c r="D375">
-        <v>0.16</v>
+        <v>0.37</v>
       </c>
       <c r="E375" t="str">
-        <v>2026-07-30T21:45:23.500Z</v>
+        <v>2026-07-30T21:50:59.069Z</v>
       </c>
     </row>
     <row r="376">
@@ -6785,10 +6785,10 @@
         <v>Passed</v>
       </c>
       <c r="D376">
-        <v>1.02</v>
+        <v>0.31</v>
       </c>
       <c r="E376" t="str">
-        <v>2026-07-30T21:45:24.500Z</v>
+        <v>2026-07-30T21:51:00.069Z</v>
       </c>
     </row>
     <row r="377">
@@ -6802,10 +6802,10 @@
         <v>Passed</v>
       </c>
       <c r="D377">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="E377" t="str">
-        <v>2026-07-30T21:45:25.500Z</v>
+        <v>2026-07-30T21:51:01.069Z</v>
       </c>
     </row>
     <row r="378">
@@ -6819,10 +6819,10 @@
         <v>Passed</v>
       </c>
       <c r="D378">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="E378" t="str">
-        <v>2026-07-30T21:45:26.500Z</v>
+        <v>2026-07-30T21:51:02.069Z</v>
       </c>
     </row>
     <row r="379">
@@ -6836,10 +6836,10 @@
         <v>Passed</v>
       </c>
       <c r="D379">
-        <v>0.93</v>
+        <v>0.72</v>
       </c>
       <c r="E379" t="str">
-        <v>2026-07-30T21:45:27.500Z</v>
+        <v>2026-07-30T21:51:03.069Z</v>
       </c>
     </row>
     <row r="380">
@@ -6853,10 +6853,10 @@
         <v>Passed</v>
       </c>
       <c r="D380">
-        <v>1.31</v>
+        <v>0.69</v>
       </c>
       <c r="E380" t="str">
-        <v>2026-07-30T21:45:28.500Z</v>
+        <v>2026-07-30T21:51:04.069Z</v>
       </c>
     </row>
     <row r="381">
@@ -6870,10 +6870,10 @@
         <v>Passed</v>
       </c>
       <c r="D381">
-        <v>0.63</v>
+        <v>0.33</v>
       </c>
       <c r="E381" t="str">
-        <v>2026-07-30T21:45:29.500Z</v>
+        <v>2026-07-30T21:51:05.069Z</v>
       </c>
     </row>
     <row r="382">
@@ -6887,10 +6887,10 @@
         <v>Passed</v>
       </c>
       <c r="D382">
-        <v>0.92</v>
+        <v>1.53</v>
       </c>
       <c r="E382" t="str">
-        <v>2026-07-30T21:45:30.500Z</v>
+        <v>2026-07-30T21:51:06.069Z</v>
       </c>
     </row>
     <row r="383">
@@ -6904,10 +6904,10 @@
         <v>Passed</v>
       </c>
       <c r="D383">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="E383" t="str">
-        <v>2026-07-30T21:45:31.500Z</v>
+        <v>2026-07-30T21:51:07.069Z</v>
       </c>
     </row>
     <row r="384">
@@ -6918,13 +6918,13 @@
         <v>Verify Security functionality module 383</v>
       </c>
       <c r="C384" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D384">
-        <v>0.19</v>
+        <v>1.15</v>
       </c>
       <c r="E384" t="str">
-        <v>2026-07-30T21:45:32.500Z</v>
+        <v>2026-07-30T21:51:08.069Z</v>
       </c>
     </row>
     <row r="385">
@@ -6938,10 +6938,10 @@
         <v>Passed</v>
       </c>
       <c r="D385">
-        <v>1.17</v>
+        <v>1.74</v>
       </c>
       <c r="E385" t="str">
-        <v>2026-07-30T21:45:33.500Z</v>
+        <v>2026-07-30T21:51:09.069Z</v>
       </c>
     </row>
     <row r="386">
@@ -6955,10 +6955,10 @@
         <v>Passed</v>
       </c>
       <c r="D386">
-        <v>0.43</v>
+        <v>0.48</v>
       </c>
       <c r="E386" t="str">
-        <v>2026-07-30T21:45:34.500Z</v>
+        <v>2026-07-30T21:51:10.069Z</v>
       </c>
     </row>
     <row r="387">
@@ -6972,10 +6972,10 @@
         <v>Passed</v>
       </c>
       <c r="D387">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="E387" t="str">
-        <v>2026-07-30T21:45:35.500Z</v>
+        <v>2026-07-30T21:51:11.069Z</v>
       </c>
     </row>
     <row r="388">
@@ -6989,10 +6989,10 @@
         <v>Passed</v>
       </c>
       <c r="D388">
-        <v>0.14</v>
+        <v>1.54</v>
       </c>
       <c r="E388" t="str">
-        <v>2026-07-30T21:45:36.500Z</v>
+        <v>2026-07-30T21:51:12.069Z</v>
       </c>
     </row>
     <row r="389">
@@ -7006,10 +7006,10 @@
         <v>Passed</v>
       </c>
       <c r="D389">
-        <v>1.84</v>
+        <v>0.22</v>
       </c>
       <c r="E389" t="str">
-        <v>2026-07-30T21:45:37.500Z</v>
+        <v>2026-07-30T21:51:13.069Z</v>
       </c>
     </row>
     <row r="390">
@@ -7023,10 +7023,10 @@
         <v>Passed</v>
       </c>
       <c r="D390">
-        <v>0.32</v>
+        <v>0.17</v>
       </c>
       <c r="E390" t="str">
-        <v>2026-07-30T21:45:38.500Z</v>
+        <v>2026-07-30T21:51:14.069Z</v>
       </c>
     </row>
     <row r="391">
@@ -7040,10 +7040,10 @@
         <v>Passed</v>
       </c>
       <c r="D391">
-        <v>0.58</v>
+        <v>0.09</v>
       </c>
       <c r="E391" t="str">
-        <v>2026-07-30T21:45:39.500Z</v>
+        <v>2026-07-30T21:51:15.069Z</v>
       </c>
     </row>
     <row r="392">
@@ -7057,10 +7057,10 @@
         <v>Passed</v>
       </c>
       <c r="D392">
-        <v>0.27</v>
+        <v>0.09</v>
       </c>
       <c r="E392" t="str">
-        <v>2026-07-30T21:45:40.500Z</v>
+        <v>2026-07-30T21:51:16.069Z</v>
       </c>
     </row>
     <row r="393">
@@ -7074,10 +7074,10 @@
         <v>Passed</v>
       </c>
       <c r="D393">
-        <v>0.77</v>
+        <v>0.92</v>
       </c>
       <c r="E393" t="str">
-        <v>2026-07-30T21:45:41.500Z</v>
+        <v>2026-07-30T21:51:17.069Z</v>
       </c>
     </row>
     <row r="394">
@@ -7091,10 +7091,10 @@
         <v>Passed</v>
       </c>
       <c r="D394">
-        <v>1.02</v>
+        <v>0.84</v>
       </c>
       <c r="E394" t="str">
-        <v>2026-07-30T21:45:42.500Z</v>
+        <v>2026-07-30T21:51:18.069Z</v>
       </c>
     </row>
     <row r="395">
@@ -7108,10 +7108,10 @@
         <v>Passed</v>
       </c>
       <c r="D395">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="E395" t="str">
-        <v>2026-07-30T21:45:43.500Z</v>
+        <v>2026-07-30T21:51:19.069Z</v>
       </c>
     </row>
     <row r="396">
@@ -7125,10 +7125,10 @@
         <v>Passed</v>
       </c>
       <c r="D396">
-        <v>1.1</v>
+        <v>1.78</v>
       </c>
       <c r="E396" t="str">
-        <v>2026-07-30T21:45:44.500Z</v>
+        <v>2026-07-30T21:51:20.069Z</v>
       </c>
     </row>
     <row r="397">
@@ -7142,10 +7142,10 @@
         <v>Passed</v>
       </c>
       <c r="D397">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="E397" t="str">
-        <v>2026-07-30T21:45:45.500Z</v>
+        <v>2026-07-30T21:51:21.069Z</v>
       </c>
     </row>
     <row r="398">
@@ -7159,10 +7159,10 @@
         <v>Passed</v>
       </c>
       <c r="D398">
-        <v>1.93</v>
+        <v>1</v>
       </c>
       <c r="E398" t="str">
-        <v>2026-07-30T21:45:46.500Z</v>
+        <v>2026-07-30T21:51:22.069Z</v>
       </c>
     </row>
     <row r="399">
@@ -7176,10 +7176,10 @@
         <v>Passed</v>
       </c>
       <c r="D399">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="E399" t="str">
-        <v>2026-07-30T21:45:47.500Z</v>
+        <v>2026-07-30T21:51:23.069Z</v>
       </c>
     </row>
     <row r="400">
@@ -7193,10 +7193,10 @@
         <v>Passed</v>
       </c>
       <c r="D400">
-        <v>0.43</v>
+        <v>1.62</v>
       </c>
       <c r="E400" t="str">
-        <v>2026-07-30T21:45:48.500Z</v>
+        <v>2026-07-30T21:51:24.069Z</v>
       </c>
     </row>
     <row r="401">
@@ -7210,10 +7210,10 @@
         <v>Passed</v>
       </c>
       <c r="D401">
-        <v>0.77</v>
+        <v>1.11</v>
       </c>
       <c r="E401" t="str">
-        <v>2026-07-30T21:45:49.500Z</v>
+        <v>2026-07-30T21:51:25.069Z</v>
       </c>
     </row>
     <row r="402">
@@ -7227,10 +7227,10 @@
         <v>Passed</v>
       </c>
       <c r="D402">
-        <v>0.64</v>
+        <v>1.82</v>
       </c>
       <c r="E402" t="str">
-        <v>2026-07-30T21:45:50.500Z</v>
+        <v>2026-07-30T21:51:26.069Z</v>
       </c>
     </row>
     <row r="403">
@@ -7244,10 +7244,10 @@
         <v>Passed</v>
       </c>
       <c r="D403">
-        <v>1.59</v>
+        <v>1.97</v>
       </c>
       <c r="E403" t="str">
-        <v>2026-07-30T21:45:51.500Z</v>
+        <v>2026-07-30T21:51:27.069Z</v>
       </c>
     </row>
     <row r="404">
@@ -7261,10 +7261,10 @@
         <v>Passed</v>
       </c>
       <c r="D404">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="E404" t="str">
-        <v>2026-07-30T21:45:52.500Z</v>
+        <v>2026-07-30T21:51:28.069Z</v>
       </c>
     </row>
     <row r="405">
@@ -7278,10 +7278,10 @@
         <v>Passed</v>
       </c>
       <c r="D405">
-        <v>1.47</v>
+        <v>0.81</v>
       </c>
       <c r="E405" t="str">
-        <v>2026-07-30T21:45:53.500Z</v>
+        <v>2026-07-30T21:51:29.069Z</v>
       </c>
     </row>
     <row r="406">
@@ -7295,10 +7295,10 @@
         <v>Passed</v>
       </c>
       <c r="D406">
-        <v>0.76</v>
+        <v>1.67</v>
       </c>
       <c r="E406" t="str">
-        <v>2026-07-30T21:45:54.500Z</v>
+        <v>2026-07-30T21:51:30.069Z</v>
       </c>
     </row>
     <row r="407">
@@ -7312,10 +7312,10 @@
         <v>Passed</v>
       </c>
       <c r="D407">
-        <v>0.27</v>
+        <v>1.96</v>
       </c>
       <c r="E407" t="str">
-        <v>2026-07-30T21:45:55.500Z</v>
+        <v>2026-07-30T21:51:31.069Z</v>
       </c>
     </row>
     <row r="408">
@@ -7329,10 +7329,10 @@
         <v>Passed</v>
       </c>
       <c r="D408">
-        <v>1.04</v>
+        <v>1.75</v>
       </c>
       <c r="E408" t="str">
-        <v>2026-07-30T21:45:56.500Z</v>
+        <v>2026-07-30T21:51:32.069Z</v>
       </c>
     </row>
     <row r="409">
@@ -7346,10 +7346,10 @@
         <v>Passed</v>
       </c>
       <c r="D409">
-        <v>0.36</v>
+        <v>0.48</v>
       </c>
       <c r="E409" t="str">
-        <v>2026-07-30T21:45:57.500Z</v>
+        <v>2026-07-30T21:51:33.069Z</v>
       </c>
     </row>
     <row r="410">
@@ -7363,10 +7363,10 @@
         <v>Passed</v>
       </c>
       <c r="D410">
-        <v>1.09</v>
+        <v>0.04</v>
       </c>
       <c r="E410" t="str">
-        <v>2026-07-30T21:45:58.500Z</v>
+        <v>2026-07-30T21:51:34.069Z</v>
       </c>
     </row>
     <row r="411">
@@ -7380,10 +7380,10 @@
         <v>Passed</v>
       </c>
       <c r="D411">
-        <v>0.26</v>
+        <v>0.67</v>
       </c>
       <c r="E411" t="str">
-        <v>2026-07-30T21:45:59.500Z</v>
+        <v>2026-07-30T21:51:35.069Z</v>
       </c>
     </row>
     <row r="412">
@@ -7397,10 +7397,10 @@
         <v>Passed</v>
       </c>
       <c r="D412">
-        <v>0.14</v>
+        <v>1.14</v>
       </c>
       <c r="E412" t="str">
-        <v>2026-07-30T21:46:00.500Z</v>
+        <v>2026-07-30T21:51:36.069Z</v>
       </c>
     </row>
     <row r="413">
@@ -7414,10 +7414,10 @@
         <v>Passed</v>
       </c>
       <c r="D413">
-        <v>0.53</v>
+        <v>1.71</v>
       </c>
       <c r="E413" t="str">
-        <v>2026-07-30T21:46:01.500Z</v>
+        <v>2026-07-30T21:51:37.069Z</v>
       </c>
     </row>
     <row r="414">
@@ -7431,10 +7431,10 @@
         <v>Passed</v>
       </c>
       <c r="D414">
-        <v>1.38</v>
+        <v>0.19</v>
       </c>
       <c r="E414" t="str">
-        <v>2026-07-30T21:46:02.500Z</v>
+        <v>2026-07-30T21:51:38.069Z</v>
       </c>
     </row>
     <row r="415">
@@ -7448,10 +7448,10 @@
         <v>Passed</v>
       </c>
       <c r="D415">
-        <v>1.59</v>
+        <v>0.44</v>
       </c>
       <c r="E415" t="str">
-        <v>2026-07-30T21:46:03.500Z</v>
+        <v>2026-07-30T21:51:39.069Z</v>
       </c>
     </row>
     <row r="416">
@@ -7465,10 +7465,10 @@
         <v>Passed</v>
       </c>
       <c r="D416">
-        <v>1.67</v>
+        <v>0.22</v>
       </c>
       <c r="E416" t="str">
-        <v>2026-07-30T21:46:04.500Z</v>
+        <v>2026-07-30T21:51:40.069Z</v>
       </c>
     </row>
     <row r="417">
@@ -7482,10 +7482,10 @@
         <v>Passed</v>
       </c>
       <c r="D417">
-        <v>0.18</v>
+        <v>1.87</v>
       </c>
       <c r="E417" t="str">
-        <v>2026-07-30T21:46:05.500Z</v>
+        <v>2026-07-30T21:51:41.069Z</v>
       </c>
     </row>
     <row r="418">
@@ -7499,10 +7499,10 @@
         <v>Passed</v>
       </c>
       <c r="D418">
-        <v>0.87</v>
+        <v>0.15</v>
       </c>
       <c r="E418" t="str">
-        <v>2026-07-30T21:46:06.500Z</v>
+        <v>2026-07-30T21:51:42.069Z</v>
       </c>
     </row>
     <row r="419">
@@ -7516,10 +7516,10 @@
         <v>Passed</v>
       </c>
       <c r="D419">
-        <v>0.45</v>
+        <v>0.75</v>
       </c>
       <c r="E419" t="str">
-        <v>2026-07-30T21:46:07.500Z</v>
+        <v>2026-07-30T21:51:43.069Z</v>
       </c>
     </row>
     <row r="420">
@@ -7533,10 +7533,10 @@
         <v>Passed</v>
       </c>
       <c r="D420">
-        <v>1.33</v>
+        <v>0.26</v>
       </c>
       <c r="E420" t="str">
-        <v>2026-07-30T21:46:08.500Z</v>
+        <v>2026-07-30T21:51:44.069Z</v>
       </c>
     </row>
     <row r="421">
@@ -7550,10 +7550,10 @@
         <v>Passed</v>
       </c>
       <c r="D421">
-        <v>0.45</v>
+        <v>1.89</v>
       </c>
       <c r="E421" t="str">
-        <v>2026-07-30T21:46:09.500Z</v>
+        <v>2026-07-30T21:51:45.069Z</v>
       </c>
     </row>
     <row r="422">
@@ -7567,10 +7567,10 @@
         <v>Passed</v>
       </c>
       <c r="D422">
-        <v>1.47</v>
+        <v>0.12</v>
       </c>
       <c r="E422" t="str">
-        <v>2026-07-30T21:46:10.500Z</v>
+        <v>2026-07-30T21:51:46.069Z</v>
       </c>
     </row>
     <row r="423">
@@ -7584,10 +7584,10 @@
         <v>Passed</v>
       </c>
       <c r="D423">
-        <v>0.9</v>
+        <v>1.97</v>
       </c>
       <c r="E423" t="str">
-        <v>2026-07-30T21:46:11.500Z</v>
+        <v>2026-07-30T21:51:47.069Z</v>
       </c>
     </row>
     <row r="424">
@@ -7601,10 +7601,10 @@
         <v>Passed</v>
       </c>
       <c r="D424">
-        <v>1.05</v>
+        <v>0.29</v>
       </c>
       <c r="E424" t="str">
-        <v>2026-07-30T21:46:12.500Z</v>
+        <v>2026-07-30T21:51:48.069Z</v>
       </c>
     </row>
     <row r="425">
@@ -7618,10 +7618,10 @@
         <v>Passed</v>
       </c>
       <c r="D425">
-        <v>1.11</v>
+        <v>1.52</v>
       </c>
       <c r="E425" t="str">
-        <v>2026-07-30T21:46:13.500Z</v>
+        <v>2026-07-30T21:51:49.069Z</v>
       </c>
     </row>
     <row r="426">
@@ -7635,10 +7635,10 @@
         <v>Passed</v>
       </c>
       <c r="D426">
-        <v>1.31</v>
+        <v>0.75</v>
       </c>
       <c r="E426" t="str">
-        <v>2026-07-30T21:46:14.500Z</v>
+        <v>2026-07-30T21:51:50.069Z</v>
       </c>
     </row>
     <row r="427">
@@ -7652,10 +7652,10 @@
         <v>Passed</v>
       </c>
       <c r="D427">
-        <v>0.38</v>
+        <v>1.78</v>
       </c>
       <c r="E427" t="str">
-        <v>2026-07-30T21:46:15.500Z</v>
+        <v>2026-07-30T21:51:51.069Z</v>
       </c>
     </row>
     <row r="428">
@@ -7669,10 +7669,10 @@
         <v>Passed</v>
       </c>
       <c r="D428">
-        <v>1.43</v>
+        <v>0.1</v>
       </c>
       <c r="E428" t="str">
-        <v>2026-07-30T21:46:16.500Z</v>
+        <v>2026-07-30T21:51:52.069Z</v>
       </c>
     </row>
     <row r="429">
@@ -7686,10 +7686,10 @@
         <v>Passed</v>
       </c>
       <c r="D429">
-        <v>1.74</v>
+        <v>0.91</v>
       </c>
       <c r="E429" t="str">
-        <v>2026-07-30T21:46:17.500Z</v>
+        <v>2026-07-30T21:51:53.069Z</v>
       </c>
     </row>
     <row r="430">
@@ -7703,10 +7703,10 @@
         <v>Passed</v>
       </c>
       <c r="D430">
-        <v>0.09</v>
+        <v>1.33</v>
       </c>
       <c r="E430" t="str">
-        <v>2026-07-30T21:46:18.500Z</v>
+        <v>2026-07-30T21:51:54.069Z</v>
       </c>
     </row>
     <row r="431">
@@ -7720,10 +7720,10 @@
         <v>Passed</v>
       </c>
       <c r="D431">
-        <v>0.92</v>
+        <v>0.49</v>
       </c>
       <c r="E431" t="str">
-        <v>2026-07-30T21:46:19.500Z</v>
+        <v>2026-07-30T21:51:55.069Z</v>
       </c>
     </row>
     <row r="432">
@@ -7737,10 +7737,10 @@
         <v>Passed</v>
       </c>
       <c r="D432">
-        <v>1.06</v>
+        <v>1.58</v>
       </c>
       <c r="E432" t="str">
-        <v>2026-07-30T21:46:20.500Z</v>
+        <v>2026-07-30T21:51:56.069Z</v>
       </c>
     </row>
     <row r="433">
@@ -7754,10 +7754,10 @@
         <v>Passed</v>
       </c>
       <c r="D433">
-        <v>1.13</v>
+        <v>0.14</v>
       </c>
       <c r="E433" t="str">
-        <v>2026-07-30T21:46:21.500Z</v>
+        <v>2026-07-30T21:51:57.069Z</v>
       </c>
     </row>
     <row r="434">
@@ -7771,10 +7771,10 @@
         <v>Passed</v>
       </c>
       <c r="D434">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="E434" t="str">
-        <v>2026-07-30T21:46:22.500Z</v>
+        <v>2026-07-30T21:51:58.069Z</v>
       </c>
     </row>
     <row r="435">
@@ -7788,10 +7788,10 @@
         <v>Passed</v>
       </c>
       <c r="D435">
-        <v>0.13</v>
+        <v>0.84</v>
       </c>
       <c r="E435" t="str">
-        <v>2026-07-30T21:46:23.500Z</v>
+        <v>2026-07-30T21:51:59.069Z</v>
       </c>
     </row>
     <row r="436">
@@ -7805,10 +7805,10 @@
         <v>Passed</v>
       </c>
       <c r="D436">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="E436" t="str">
-        <v>2026-07-30T21:46:24.500Z</v>
+        <v>2026-07-30T21:52:00.069Z</v>
       </c>
     </row>
     <row r="437">
@@ -7822,10 +7822,10 @@
         <v>Passed</v>
       </c>
       <c r="D437">
-        <v>1.02</v>
+        <v>0.87</v>
       </c>
       <c r="E437" t="str">
-        <v>2026-07-30T21:46:25.500Z</v>
+        <v>2026-07-30T21:52:01.069Z</v>
       </c>
     </row>
     <row r="438">
@@ -7839,10 +7839,10 @@
         <v>Passed</v>
       </c>
       <c r="D438">
-        <v>0.19</v>
+        <v>0.37</v>
       </c>
       <c r="E438" t="str">
-        <v>2026-07-30T21:46:26.500Z</v>
+        <v>2026-07-30T21:52:02.069Z</v>
       </c>
     </row>
     <row r="439">
@@ -7856,10 +7856,10 @@
         <v>Passed</v>
       </c>
       <c r="D439">
-        <v>1.72</v>
+        <v>1.37</v>
       </c>
       <c r="E439" t="str">
-        <v>2026-07-30T21:46:27.500Z</v>
+        <v>2026-07-30T21:52:03.069Z</v>
       </c>
     </row>
     <row r="440">
@@ -7873,10 +7873,10 @@
         <v>Passed</v>
       </c>
       <c r="D440">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="E440" t="str">
-        <v>2026-07-30T21:46:28.500Z</v>
+        <v>2026-07-30T21:52:04.069Z</v>
       </c>
     </row>
     <row r="441">
@@ -7890,10 +7890,10 @@
         <v>Passed</v>
       </c>
       <c r="D441">
-        <v>1.1</v>
+        <v>1.64</v>
       </c>
       <c r="E441" t="str">
-        <v>2026-07-30T21:46:29.500Z</v>
+        <v>2026-07-30T21:52:05.069Z</v>
       </c>
     </row>
     <row r="442">
@@ -7907,10 +7907,10 @@
         <v>Passed</v>
       </c>
       <c r="D442">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="E442" t="str">
-        <v>2026-07-30T21:46:30.500Z</v>
+        <v>2026-07-30T21:52:06.069Z</v>
       </c>
     </row>
     <row r="443">
@@ -7924,10 +7924,10 @@
         <v>Passed</v>
       </c>
       <c r="D443">
-        <v>0.16</v>
+        <v>1.49</v>
       </c>
       <c r="E443" t="str">
-        <v>2026-07-30T21:46:31.500Z</v>
+        <v>2026-07-30T21:52:07.069Z</v>
       </c>
     </row>
     <row r="444">
@@ -7941,10 +7941,10 @@
         <v>Passed</v>
       </c>
       <c r="D444">
-        <v>0.41</v>
+        <v>1.44</v>
       </c>
       <c r="E444" t="str">
-        <v>2026-07-30T21:46:32.500Z</v>
+        <v>2026-07-30T21:52:08.069Z</v>
       </c>
     </row>
     <row r="445">
@@ -7958,10 +7958,10 @@
         <v>Passed</v>
       </c>
       <c r="D445">
-        <v>1.75</v>
+        <v>0.45</v>
       </c>
       <c r="E445" t="str">
-        <v>2026-07-30T21:46:33.500Z</v>
+        <v>2026-07-30T21:52:09.069Z</v>
       </c>
     </row>
     <row r="446">
@@ -7975,10 +7975,10 @@
         <v>Passed</v>
       </c>
       <c r="D446">
-        <v>1.88</v>
+        <v>0.51</v>
       </c>
       <c r="E446" t="str">
-        <v>2026-07-30T21:46:34.500Z</v>
+        <v>2026-07-30T21:52:10.069Z</v>
       </c>
     </row>
     <row r="447">
@@ -7992,10 +7992,10 @@
         <v>Passed</v>
       </c>
       <c r="D447">
-        <v>1.65</v>
+        <v>1.09</v>
       </c>
       <c r="E447" t="str">
-        <v>2026-07-30T21:46:35.500Z</v>
+        <v>2026-07-30T21:52:11.069Z</v>
       </c>
     </row>
     <row r="448">
@@ -8009,10 +8009,10 @@
         <v>Passed</v>
       </c>
       <c r="D448">
-        <v>0.64</v>
+        <v>0.17</v>
       </c>
       <c r="E448" t="str">
-        <v>2026-07-30T21:46:36.500Z</v>
+        <v>2026-07-30T21:52:12.069Z</v>
       </c>
     </row>
     <row r="449">
@@ -8026,10 +8026,10 @@
         <v>Passed</v>
       </c>
       <c r="D449">
-        <v>1.85</v>
+        <v>1.19</v>
       </c>
       <c r="E449" t="str">
-        <v>2026-07-30T21:46:37.500Z</v>
+        <v>2026-07-30T21:52:13.069Z</v>
       </c>
     </row>
     <row r="450">
@@ -8043,10 +8043,10 @@
         <v>Passed</v>
       </c>
       <c r="D450">
-        <v>0.8</v>
+        <v>1.26</v>
       </c>
       <c r="E450" t="str">
-        <v>2026-07-30T21:46:38.500Z</v>
+        <v>2026-07-30T21:52:14.069Z</v>
       </c>
     </row>
     <row r="451">
@@ -8060,10 +8060,10 @@
         <v>Passed</v>
       </c>
       <c r="D451">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="E451" t="str">
-        <v>2026-07-30T21:46:39.500Z</v>
+        <v>2026-07-30T21:52:15.069Z</v>
       </c>
     </row>
     <row r="452">
@@ -8077,10 +8077,10 @@
         <v>Passed</v>
       </c>
       <c r="D452">
-        <v>0.77</v>
+        <v>1.06</v>
       </c>
       <c r="E452" t="str">
-        <v>2026-07-30T21:46:40.500Z</v>
+        <v>2026-07-30T21:52:16.069Z</v>
       </c>
     </row>
     <row r="453">
@@ -8094,10 +8094,10 @@
         <v>Passed</v>
       </c>
       <c r="D453">
-        <v>0.32</v>
+        <v>1.14</v>
       </c>
       <c r="E453" t="str">
-        <v>2026-07-30T21:46:41.500Z</v>
+        <v>2026-07-30T21:52:17.069Z</v>
       </c>
     </row>
     <row r="454">
@@ -8111,10 +8111,10 @@
         <v>Passed</v>
       </c>
       <c r="D454">
-        <v>0.92</v>
+        <v>1.18</v>
       </c>
       <c r="E454" t="str">
-        <v>2026-07-30T21:46:42.500Z</v>
+        <v>2026-07-30T21:52:18.069Z</v>
       </c>
     </row>
     <row r="455">
@@ -8128,10 +8128,10 @@
         <v>Passed</v>
       </c>
       <c r="D455">
-        <v>0.02</v>
+        <v>1.36</v>
       </c>
       <c r="E455" t="str">
-        <v>2026-07-30T21:46:43.500Z</v>
+        <v>2026-07-30T21:52:19.069Z</v>
       </c>
     </row>
     <row r="456">
@@ -8145,10 +8145,10 @@
         <v>Passed</v>
       </c>
       <c r="D456">
-        <v>0.88</v>
+        <v>0.07</v>
       </c>
       <c r="E456" t="str">
-        <v>2026-07-30T21:46:44.500Z</v>
+        <v>2026-07-30T21:52:20.069Z</v>
       </c>
     </row>
     <row r="457">
@@ -8162,10 +8162,10 @@
         <v>Passed</v>
       </c>
       <c r="D457">
-        <v>0.92</v>
+        <v>0.16</v>
       </c>
       <c r="E457" t="str">
-        <v>2026-07-30T21:46:45.500Z</v>
+        <v>2026-07-30T21:52:21.069Z</v>
       </c>
     </row>
     <row r="458">
@@ -8179,10 +8179,10 @@
         <v>Passed</v>
       </c>
       <c r="D458">
-        <v>1.3</v>
+        <v>0.22</v>
       </c>
       <c r="E458" t="str">
-        <v>2026-07-30T21:46:46.500Z</v>
+        <v>2026-07-30T21:52:22.069Z</v>
       </c>
     </row>
     <row r="459">
@@ -8196,10 +8196,10 @@
         <v>Passed</v>
       </c>
       <c r="D459">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="E459" t="str">
-        <v>2026-07-30T21:46:47.500Z</v>
+        <v>2026-07-30T21:52:23.069Z</v>
       </c>
     </row>
     <row r="460">
@@ -8213,10 +8213,10 @@
         <v>Passed</v>
       </c>
       <c r="D460">
-        <v>1.86</v>
+        <v>0.04</v>
       </c>
       <c r="E460" t="str">
-        <v>2026-07-30T21:46:48.500Z</v>
+        <v>2026-07-30T21:52:24.069Z</v>
       </c>
     </row>
     <row r="461">
@@ -8230,661 +8230,15 @@
         <v>Passed</v>
       </c>
       <c r="D461">
-        <v>1.06</v>
+        <v>0.54</v>
       </c>
       <c r="E461" t="str">
-        <v>2026-07-30T21:46:49.500Z</v>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="str">
-        <v>Security-TC-0461</v>
-      </c>
-      <c r="B462" t="str">
-        <v>Verify Security functionality module 461</v>
-      </c>
-      <c r="C462" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D462">
-        <v>0.03</v>
-      </c>
-      <c r="E462" t="str">
-        <v>2026-07-30T21:46:50.500Z</v>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="str">
-        <v>Security-TC-0462</v>
-      </c>
-      <c r="B463" t="str">
-        <v>Verify Security functionality module 462</v>
-      </c>
-      <c r="C463" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D463">
-        <v>1.67</v>
-      </c>
-      <c r="E463" t="str">
-        <v>2026-07-30T21:46:51.500Z</v>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="str">
-        <v>Security-TC-0463</v>
-      </c>
-      <c r="B464" t="str">
-        <v>Verify Security functionality module 463</v>
-      </c>
-      <c r="C464" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D464">
-        <v>1.21</v>
-      </c>
-      <c r="E464" t="str">
-        <v>2026-07-30T21:46:52.500Z</v>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" t="str">
-        <v>Security-TC-0464</v>
-      </c>
-      <c r="B465" t="str">
-        <v>Verify Security functionality module 464</v>
-      </c>
-      <c r="C465" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D465">
-        <v>1.36</v>
-      </c>
-      <c r="E465" t="str">
-        <v>2026-07-30T21:46:53.500Z</v>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" t="str">
-        <v>Security-TC-0465</v>
-      </c>
-      <c r="B466" t="str">
-        <v>Verify Security functionality module 465</v>
-      </c>
-      <c r="C466" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D466">
-        <v>0.4</v>
-      </c>
-      <c r="E466" t="str">
-        <v>2026-07-30T21:46:54.500Z</v>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" t="str">
-        <v>Security-TC-0466</v>
-      </c>
-      <c r="B467" t="str">
-        <v>Verify Security functionality module 466</v>
-      </c>
-      <c r="C467" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D467">
-        <v>1.51</v>
-      </c>
-      <c r="E467" t="str">
-        <v>2026-07-30T21:46:55.500Z</v>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" t="str">
-        <v>Security-TC-0467</v>
-      </c>
-      <c r="B468" t="str">
-        <v>Verify Security functionality module 467</v>
-      </c>
-      <c r="C468" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D468">
-        <v>0.42</v>
-      </c>
-      <c r="E468" t="str">
-        <v>2026-07-30T21:46:56.500Z</v>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469" t="str">
-        <v>Security-TC-0468</v>
-      </c>
-      <c r="B469" t="str">
-        <v>Verify Security functionality module 468</v>
-      </c>
-      <c r="C469" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D469">
-        <v>0.94</v>
-      </c>
-      <c r="E469" t="str">
-        <v>2026-07-30T21:46:57.500Z</v>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" t="str">
-        <v>Security-TC-0469</v>
-      </c>
-      <c r="B470" t="str">
-        <v>Verify Security functionality module 469</v>
-      </c>
-      <c r="C470" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D470">
-        <v>1.26</v>
-      </c>
-      <c r="E470" t="str">
-        <v>2026-07-30T21:46:58.500Z</v>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" t="str">
-        <v>Security-TC-0470</v>
-      </c>
-      <c r="B471" t="str">
-        <v>Verify Security functionality module 470</v>
-      </c>
-      <c r="C471" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D471">
-        <v>1.47</v>
-      </c>
-      <c r="E471" t="str">
-        <v>2026-07-30T21:46:59.500Z</v>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" t="str">
-        <v>Security-TC-0471</v>
-      </c>
-      <c r="B472" t="str">
-        <v>Verify Security functionality module 471</v>
-      </c>
-      <c r="C472" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D472">
-        <v>0.22</v>
-      </c>
-      <c r="E472" t="str">
-        <v>2026-07-30T21:47:00.500Z</v>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" t="str">
-        <v>Security-TC-0472</v>
-      </c>
-      <c r="B473" t="str">
-        <v>Verify Security functionality module 472</v>
-      </c>
-      <c r="C473" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D473">
-        <v>1.07</v>
-      </c>
-      <c r="E473" t="str">
-        <v>2026-07-30T21:47:01.500Z</v>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" t="str">
-        <v>Security-TC-0473</v>
-      </c>
-      <c r="B474" t="str">
-        <v>Verify Security functionality module 473</v>
-      </c>
-      <c r="C474" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D474">
-        <v>0.1</v>
-      </c>
-      <c r="E474" t="str">
-        <v>2026-07-30T21:47:02.500Z</v>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" t="str">
-        <v>Security-TC-0474</v>
-      </c>
-      <c r="B475" t="str">
-        <v>Verify Security functionality module 474</v>
-      </c>
-      <c r="C475" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D475">
-        <v>0.74</v>
-      </c>
-      <c r="E475" t="str">
-        <v>2026-07-30T21:47:03.500Z</v>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="str">
-        <v>Security-TC-0475</v>
-      </c>
-      <c r="B476" t="str">
-        <v>Verify Security functionality module 475</v>
-      </c>
-      <c r="C476" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D476">
-        <v>0.47</v>
-      </c>
-      <c r="E476" t="str">
-        <v>2026-07-30T21:47:04.500Z</v>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="str">
-        <v>Security-TC-0476</v>
-      </c>
-      <c r="B477" t="str">
-        <v>Verify Security functionality module 476</v>
-      </c>
-      <c r="C477" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D477">
-        <v>1.78</v>
-      </c>
-      <c r="E477" t="str">
-        <v>2026-07-30T21:47:05.500Z</v>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="str">
-        <v>Security-TC-0477</v>
-      </c>
-      <c r="B478" t="str">
-        <v>Verify Security functionality module 477</v>
-      </c>
-      <c r="C478" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D478">
-        <v>1.92</v>
-      </c>
-      <c r="E478" t="str">
-        <v>2026-07-30T21:47:06.500Z</v>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="str">
-        <v>Security-TC-0478</v>
-      </c>
-      <c r="B479" t="str">
-        <v>Verify Security functionality module 478</v>
-      </c>
-      <c r="C479" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D479">
-        <v>1.91</v>
-      </c>
-      <c r="E479" t="str">
-        <v>2026-07-30T21:47:07.500Z</v>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="str">
-        <v>Security-TC-0479</v>
-      </c>
-      <c r="B480" t="str">
-        <v>Verify Security functionality module 479</v>
-      </c>
-      <c r="C480" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D480">
-        <v>1.73</v>
-      </c>
-      <c r="E480" t="str">
-        <v>2026-07-30T21:47:08.500Z</v>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" t="str">
-        <v>Security-TC-0480</v>
-      </c>
-      <c r="B481" t="str">
-        <v>Verify Security functionality module 480</v>
-      </c>
-      <c r="C481" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D481">
-        <v>0.05</v>
-      </c>
-      <c r="E481" t="str">
-        <v>2026-07-30T21:47:09.500Z</v>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" t="str">
-        <v>Security-TC-0481</v>
-      </c>
-      <c r="B482" t="str">
-        <v>Verify Security functionality module 481</v>
-      </c>
-      <c r="C482" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D482">
-        <v>1.56</v>
-      </c>
-      <c r="E482" t="str">
-        <v>2026-07-30T21:47:10.500Z</v>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" t="str">
-        <v>Security-TC-0482</v>
-      </c>
-      <c r="B483" t="str">
-        <v>Verify Security functionality module 482</v>
-      </c>
-      <c r="C483" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D483">
-        <v>1.58</v>
-      </c>
-      <c r="E483" t="str">
-        <v>2026-07-30T21:47:11.500Z</v>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" t="str">
-        <v>Security-TC-0483</v>
-      </c>
-      <c r="B484" t="str">
-        <v>Verify Security functionality module 483</v>
-      </c>
-      <c r="C484" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D484">
-        <v>0.96</v>
-      </c>
-      <c r="E484" t="str">
-        <v>2026-07-30T21:47:12.500Z</v>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" t="str">
-        <v>Security-TC-0484</v>
-      </c>
-      <c r="B485" t="str">
-        <v>Verify Security functionality module 484</v>
-      </c>
-      <c r="C485" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D485">
-        <v>0.45</v>
-      </c>
-      <c r="E485" t="str">
-        <v>2026-07-30T21:47:13.500Z</v>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" t="str">
-        <v>Security-TC-0485</v>
-      </c>
-      <c r="B486" t="str">
-        <v>Verify Security functionality module 485</v>
-      </c>
-      <c r="C486" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D486">
-        <v>0.31</v>
-      </c>
-      <c r="E486" t="str">
-        <v>2026-07-30T21:47:14.500Z</v>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" t="str">
-        <v>Security-TC-0486</v>
-      </c>
-      <c r="B487" t="str">
-        <v>Verify Security functionality module 486</v>
-      </c>
-      <c r="C487" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D487">
-        <v>0.22</v>
-      </c>
-      <c r="E487" t="str">
-        <v>2026-07-30T21:47:15.500Z</v>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" t="str">
-        <v>Security-TC-0487</v>
-      </c>
-      <c r="B488" t="str">
-        <v>Verify Security functionality module 487</v>
-      </c>
-      <c r="C488" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D488">
-        <v>1.78</v>
-      </c>
-      <c r="E488" t="str">
-        <v>2026-07-30T21:47:16.500Z</v>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489" t="str">
-        <v>Security-TC-0488</v>
-      </c>
-      <c r="B489" t="str">
-        <v>Verify Security functionality module 488</v>
-      </c>
-      <c r="C489" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D489">
-        <v>0.08</v>
-      </c>
-      <c r="E489" t="str">
-        <v>2026-07-30T21:47:17.500Z</v>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" t="str">
-        <v>Security-TC-0489</v>
-      </c>
-      <c r="B490" t="str">
-        <v>Verify Security functionality module 489</v>
-      </c>
-      <c r="C490" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D490">
-        <v>0.78</v>
-      </c>
-      <c r="E490" t="str">
-        <v>2026-07-30T21:47:18.500Z</v>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" t="str">
-        <v>Security-TC-0490</v>
-      </c>
-      <c r="B491" t="str">
-        <v>Verify Security functionality module 490</v>
-      </c>
-      <c r="C491" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D491">
-        <v>1.93</v>
-      </c>
-      <c r="E491" t="str">
-        <v>2026-07-30T21:47:19.500Z</v>
-      </c>
-    </row>
-    <row r="492">
-      <c r="A492" t="str">
-        <v>Security-TC-0491</v>
-      </c>
-      <c r="B492" t="str">
-        <v>Verify Security functionality module 491</v>
-      </c>
-      <c r="C492" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D492">
-        <v>1.91</v>
-      </c>
-      <c r="E492" t="str">
-        <v>2026-07-30T21:47:20.500Z</v>
-      </c>
-    </row>
-    <row r="493">
-      <c r="A493" t="str">
-        <v>Security-TC-0492</v>
-      </c>
-      <c r="B493" t="str">
-        <v>Verify Security functionality module 492</v>
-      </c>
-      <c r="C493" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D493">
-        <v>1.32</v>
-      </c>
-      <c r="E493" t="str">
-        <v>2026-07-30T21:47:21.500Z</v>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494" t="str">
-        <v>Security-TC-0493</v>
-      </c>
-      <c r="B494" t="str">
-        <v>Verify Security functionality module 493</v>
-      </c>
-      <c r="C494" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D494">
-        <v>0.66</v>
-      </c>
-      <c r="E494" t="str">
-        <v>2026-07-30T21:47:22.500Z</v>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495" t="str">
-        <v>Security-TC-0494</v>
-      </c>
-      <c r="B495" t="str">
-        <v>Verify Security functionality module 494</v>
-      </c>
-      <c r="C495" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D495">
-        <v>1.46</v>
-      </c>
-      <c r="E495" t="str">
-        <v>2026-07-30T21:47:23.500Z</v>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496" t="str">
-        <v>Security-TC-0495</v>
-      </c>
-      <c r="B496" t="str">
-        <v>Verify Security functionality module 495</v>
-      </c>
-      <c r="C496" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D496">
-        <v>0.04</v>
-      </c>
-      <c r="E496" t="str">
-        <v>2026-07-30T21:47:24.500Z</v>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" t="str">
-        <v>Security-TC-0496</v>
-      </c>
-      <c r="B497" t="str">
-        <v>Verify Security functionality module 496</v>
-      </c>
-      <c r="C497" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D497">
-        <v>0.2</v>
-      </c>
-      <c r="E497" t="str">
-        <v>2026-07-30T21:47:25.500Z</v>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" t="str">
-        <v>Security-TC-0497</v>
-      </c>
-      <c r="B498" t="str">
-        <v>Verify Security functionality module 497</v>
-      </c>
-      <c r="C498" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D498">
-        <v>1.97</v>
-      </c>
-      <c r="E498" t="str">
-        <v>2026-07-30T21:47:26.500Z</v>
-      </c>
-    </row>
-    <row r="499">
-      <c r="A499" t="str">
-        <v>Security-TC-0498</v>
-      </c>
-      <c r="B499" t="str">
-        <v>Verify Security functionality module 498</v>
-      </c>
-      <c r="C499" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D499">
-        <v>1.13</v>
-      </c>
-      <c r="E499" t="str">
-        <v>2026-07-30T21:47:27.500Z</v>
+        <v>2026-07-30T21:52:25.069Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E499"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E461"/>
   </ignoredErrors>
 </worksheet>
 </file>